--- a/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A954C2C-615C-4B52-A83D-AEA8FD1AA918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E73E562-1792-401D-A8F9-221228086463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">ARBA!$A$1:$O$82</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$155</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$128</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="415">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1240,9 +1240,6 @@
     <t>Debito 19/06</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysa - Destapacion </t>
-  </si>
-  <si>
     <t>Transf 30/06</t>
   </si>
   <si>
@@ -1267,9 +1264,6 @@
     <t>Correo argentino - Envio de tres carta documento 3F, 4F y 5F</t>
   </si>
   <si>
-    <t>}</t>
-  </si>
-  <si>
     <t>IMPORTANTE: Si en la columna SALDO a su unidad funcional le figura un monto en negativo, significa que usted abono mas dinero del que debia abonar. Si figura un monto en positivo significa que usted abono menos de lo que realmente debia abonar. Sea positivo o negativo el numero, es contemplado en las columnas de total a abonar para al siguiente mes.</t>
   </si>
   <si>
@@ -1282,7 +1276,16 @@
     <t>LA CAJA EN EFECTIVO SE ELIMINARA - LOS $25.817,22 QUE SE ADEUDAN A LA ADMINISTRACION SE RECUPERARAN MEDIANTE TRANSFERENCIA</t>
   </si>
   <si>
-    <t>recordar $89.000 en la suma final de ingresos en la columna de ingreso de prorrateo</t>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>6C: ADS - Retiro de llave de ascensor del pozo según ordenanza 283944</t>
+  </si>
+  <si>
+    <t>Recordar los $29,000 en la suma total de la columna de ingresos en la hoja de prorrateo</t>
+  </si>
+  <si>
+    <t>Se adeudan a la desarrolladora las cuotas correspondientes a ARBA de los meses de mayo y junio. Debido a la falta de disponibilidad de fondos, la desarrolladora aceptó diferir el cobro de dichos importes para permitir que el consorcio pudiera afrontar gastos de carácter obligatorio e indispensables para su normal funcionamiento</t>
   </si>
 </sst>
 </file>
@@ -1477,14 +1480,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="22"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <u/>
       <sz val="12"/>
@@ -1515,8 +1510,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="21">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1628,12 +1631,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2010,7 +2007,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="388">
+  <cellXfs count="386">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2292,9 +2289,9 @@
     <xf numFmtId="10" fontId="9" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="9" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="8" fontId="9" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2319,7 +2316,7 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2370,7 +2367,22 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2380,31 +2392,31 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2415,6 +2427,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -2435,6 +2456,33 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -2569,6 +2617,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2602,15 +2659,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2638,55 +2686,6 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="12" fillId="20" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="20" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="20" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="12" fillId="20" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="44" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="17" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="29" fillId="21" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -3088,7 +3087,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N128"/>
+  <dimension ref="A1:N135"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.42578125" customWidth="1"/>
@@ -3211,108 +3210,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="298" t="s">
+      <c r="A14" s="319" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="298"/>
-      <c r="C14" s="298"/>
-      <c r="D14" s="298"/>
-      <c r="E14" s="298"/>
-      <c r="F14" s="298"/>
-      <c r="G14" s="298"/>
-      <c r="H14" s="298"/>
-      <c r="I14" s="298"/>
-      <c r="J14" s="298"/>
+      <c r="B14" s="319"/>
+      <c r="C14" s="319"/>
+      <c r="D14" s="319"/>
+      <c r="E14" s="319"/>
+      <c r="F14" s="319"/>
+      <c r="G14" s="319"/>
+      <c r="H14" s="319"/>
+      <c r="I14" s="319"/>
+      <c r="J14" s="319"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="298"/>
-      <c r="B15" s="298"/>
-      <c r="C15" s="298"/>
-      <c r="D15" s="298"/>
-      <c r="E15" s="298"/>
-      <c r="F15" s="298"/>
-      <c r="G15" s="298"/>
-      <c r="H15" s="298"/>
-      <c r="I15" s="298"/>
-      <c r="J15" s="298"/>
+      <c r="A15" s="319"/>
+      <c r="B15" s="319"/>
+      <c r="C15" s="319"/>
+      <c r="D15" s="319"/>
+      <c r="E15" s="319"/>
+      <c r="F15" s="319"/>
+      <c r="G15" s="319"/>
+      <c r="H15" s="319"/>
+      <c r="I15" s="319"/>
+      <c r="J15" s="319"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="298"/>
-      <c r="B16" s="298"/>
-      <c r="C16" s="298"/>
-      <c r="D16" s="298"/>
-      <c r="E16" s="298"/>
-      <c r="F16" s="298"/>
-      <c r="G16" s="298"/>
-      <c r="H16" s="298"/>
-      <c r="I16" s="298"/>
-      <c r="J16" s="298"/>
+      <c r="A16" s="319"/>
+      <c r="B16" s="319"/>
+      <c r="C16" s="319"/>
+      <c r="D16" s="319"/>
+      <c r="E16" s="319"/>
+      <c r="F16" s="319"/>
+      <c r="G16" s="319"/>
+      <c r="H16" s="319"/>
+      <c r="I16" s="319"/>
+      <c r="J16" s="319"/>
     </row>
     <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="298"/>
-      <c r="B17" s="298"/>
-      <c r="C17" s="298"/>
-      <c r="D17" s="298"/>
-      <c r="E17" s="298"/>
-      <c r="F17" s="298"/>
-      <c r="G17" s="298"/>
-      <c r="H17" s="298"/>
-      <c r="I17" s="298"/>
-      <c r="J17" s="298"/>
+      <c r="A17" s="319"/>
+      <c r="B17" s="319"/>
+      <c r="C17" s="319"/>
+      <c r="D17" s="319"/>
+      <c r="E17" s="319"/>
+      <c r="F17" s="319"/>
+      <c r="G17" s="319"/>
+      <c r="H17" s="319"/>
+      <c r="I17" s="319"/>
+      <c r="J17" s="319"/>
     </row>
     <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="298"/>
-      <c r="B18" s="298"/>
-      <c r="C18" s="298"/>
-      <c r="D18" s="298"/>
-      <c r="E18" s="298"/>
-      <c r="F18" s="298"/>
-      <c r="G18" s="298"/>
-      <c r="H18" s="298"/>
-      <c r="I18" s="298"/>
-      <c r="J18" s="298"/>
+      <c r="A18" s="319"/>
+      <c r="B18" s="319"/>
+      <c r="C18" s="319"/>
+      <c r="D18" s="319"/>
+      <c r="E18" s="319"/>
+      <c r="F18" s="319"/>
+      <c r="G18" s="319"/>
+      <c r="H18" s="319"/>
+      <c r="I18" s="319"/>
+      <c r="J18" s="319"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="299" t="s">
+      <c r="A20" s="320" t="s">
         <v>382</v>
       </c>
-      <c r="B20" s="299"/>
-      <c r="C20" s="299"/>
-      <c r="D20" s="299"/>
-      <c r="E20" s="299"/>
-      <c r="F20" s="299"/>
-      <c r="G20" s="299"/>
-      <c r="H20" s="299"/>
-      <c r="I20" s="299"/>
-      <c r="J20" s="299"/>
+      <c r="B20" s="320"/>
+      <c r="C20" s="320"/>
+      <c r="D20" s="320"/>
+      <c r="E20" s="320"/>
+      <c r="F20" s="320"/>
+      <c r="G20" s="320"/>
+      <c r="H20" s="320"/>
+      <c r="I20" s="320"/>
+      <c r="J20" s="320"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="299"/>
-      <c r="B21" s="299"/>
-      <c r="C21" s="299"/>
-      <c r="D21" s="299"/>
-      <c r="E21" s="299"/>
-      <c r="F21" s="299"/>
-      <c r="G21" s="299"/>
-      <c r="H21" s="299"/>
-      <c r="I21" s="299"/>
-      <c r="J21" s="299"/>
+      <c r="A21" s="320"/>
+      <c r="B21" s="320"/>
+      <c r="C21" s="320"/>
+      <c r="D21" s="320"/>
+      <c r="E21" s="320"/>
+      <c r="F21" s="320"/>
+      <c r="G21" s="320"/>
+      <c r="H21" s="320"/>
+      <c r="I21" s="320"/>
+      <c r="J21" s="320"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="299"/>
-      <c r="B22" s="299"/>
-      <c r="C22" s="299"/>
-      <c r="D22" s="299"/>
-      <c r="E22" s="299"/>
-      <c r="F22" s="299"/>
-      <c r="G22" s="299"/>
-      <c r="H22" s="299"/>
-      <c r="I22" s="299"/>
-      <c r="J22" s="299"/>
+      <c r="A22" s="320"/>
+      <c r="B22" s="320"/>
+      <c r="C22" s="320"/>
+      <c r="D22" s="320"/>
+      <c r="E22" s="320"/>
+      <c r="F22" s="320"/>
+      <c r="G22" s="320"/>
+      <c r="H22" s="320"/>
+      <c r="I22" s="320"/>
+      <c r="J22" s="320"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
@@ -3366,7 +3365,7 @@
       <c r="C26" s="181" t="s">
         <v>392</v>
       </c>
-      <c r="D26" s="365">
+      <c r="D26" s="179">
         <v>250000</v>
       </c>
       <c r="E26" s="212"/>
@@ -3387,7 +3386,7 @@
       <c r="C27" s="181" t="s">
         <v>387</v>
       </c>
-      <c r="D27" s="365">
+      <c r="D27" s="179">
         <v>3000000</v>
       </c>
       <c r="E27" s="181"/>
@@ -3518,7 +3517,7 @@
       </c>
       <c r="B33" s="141"/>
       <c r="C33" s="217"/>
-      <c r="D33" s="365">
+      <c r="D33" s="179">
         <v>6006298</v>
       </c>
       <c r="E33" s="216"/>
@@ -3536,8 +3535,8 @@
       <c r="B34" s="141" t="s">
         <v>384</v>
       </c>
-      <c r="C34" s="369" t="s">
-        <v>405</v>
+      <c r="C34" s="277" t="s">
+        <v>404</v>
       </c>
       <c r="D34" s="179">
         <v>0</v>
@@ -3557,8 +3556,8 @@
       <c r="B35" s="141" t="s">
         <v>384</v>
       </c>
-      <c r="C35" s="369" t="s">
-        <v>405</v>
+      <c r="C35" s="277" t="s">
+        <v>404</v>
       </c>
       <c r="D35" s="179">
         <v>0</v>
@@ -3747,7 +3746,7 @@
       <c r="C44" s="181" t="s">
         <v>291</v>
       </c>
-      <c r="D44" s="366">
+      <c r="D44" s="33">
         <v>214371</v>
       </c>
       <c r="E44" s="212">
@@ -3781,8 +3780,8 @@
       <c r="L44" s="50"/>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="288"/>
-      <c r="B45" s="289"/>
+      <c r="A45" s="297"/>
+      <c r="B45" s="298"/>
       <c r="C45" s="181"/>
       <c r="D45" s="33"/>
       <c r="E45" s="212"/>
@@ -3860,7 +3859,7 @@
       <c r="C48" s="220" t="s">
         <v>388</v>
       </c>
-      <c r="D48" s="367">
+      <c r="D48" s="225">
         <v>35948.89</v>
       </c>
       <c r="E48" s="226">
@@ -3950,7 +3949,7 @@
       <c r="C50" s="181" t="s">
         <v>398</v>
       </c>
-      <c r="D50" s="366">
+      <c r="D50" s="33">
         <v>158988.79999999999</v>
       </c>
       <c r="E50" s="226">
@@ -3979,20 +3978,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="224" t="s">
         <v>385</v>
       </c>
       <c r="B51" s="181"/>
-      <c r="C51" s="369" t="s">
-        <v>405</v>
-      </c>
-      <c r="D51" s="275">
-        <v>0</v>
+      <c r="C51" s="277" t="s">
+        <v>399</v>
+      </c>
+      <c r="D51" s="33">
+        <v>427892</v>
       </c>
       <c r="E51" s="226">
         <f>D51</f>
-        <v>0</v>
+        <v>427892</v>
       </c>
       <c r="F51" s="212"/>
       <c r="G51" s="44"/>
@@ -4001,24 +4000,24 @@
       <c r="J51" s="44"/>
       <c r="K51" s="32">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>427892</v>
       </c>
       <c r="L51" s="54">
         <f>E51+J51+I51+H51+G51+F51</f>
-        <v>0</v>
+        <v>427892</v>
       </c>
       <c r="M51" s="64"/>
       <c r="N51" s="64"/>
     </row>
     <row r="52" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="276" t="s">
+      <c r="A52" s="285" t="s">
         <v>386</v>
       </c>
-      <c r="B52" s="300"/>
+      <c r="B52" s="321"/>
       <c r="C52" s="141" t="s">
         <v>395</v>
       </c>
-      <c r="D52" s="366">
+      <c r="D52" s="33">
         <v>50000</v>
       </c>
       <c r="E52" s="226">
@@ -4055,40 +4054,25 @@
       <c r="C53" s="220" t="s">
         <v>388</v>
       </c>
-      <c r="D53" s="366">
+      <c r="D53" s="33">
         <v>6491.94</v>
       </c>
       <c r="E53" s="226">
-        <f>D53*93.2%</f>
-        <v>6050.4880800000001</v>
-      </c>
-      <c r="F53" s="212">
-        <f>$D53*1.08%</f>
-        <v>70.112951999999993</v>
-      </c>
-      <c r="G53" s="44">
-        <f>$D53*1.28%</f>
-        <v>83.096831999999992</v>
-      </c>
-      <c r="H53" s="44">
-        <f>$D53*1.21%</f>
-        <v>78.552473999999989</v>
-      </c>
-      <c r="I53" s="44">
-        <f>$D53*1.49%</f>
-        <v>96.729906</v>
-      </c>
-      <c r="J53" s="44">
-        <f>D53*1.74%</f>
-        <v>112.95975599999998</v>
-      </c>
+        <f>D53</f>
+        <v>6491.94</v>
+      </c>
+      <c r="F53" s="212"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
       <c r="K53" s="32">
         <f t="shared" si="7"/>
         <v>6491.94</v>
       </c>
       <c r="L53" s="54">
         <f t="shared" ref="L53:L55" si="9">E53+J53+I53+H53+G53+F53</f>
-        <v>6491.9400000000005</v>
+        <v>6491.94</v>
       </c>
       <c r="M53" s="64">
         <f>L53-D53</f>
@@ -4107,25 +4091,40 @@
       <c r="C54" s="220" t="s">
         <v>388</v>
       </c>
-      <c r="D54" s="366">
+      <c r="D54" s="33">
         <v>1145602.71</v>
       </c>
       <c r="E54" s="226">
-        <f>D54</f>
-        <v>1145602.71</v>
-      </c>
-      <c r="F54" s="212"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
-      <c r="J54" s="44"/>
+        <f>D54*93.2%</f>
+        <v>1067701.72572</v>
+      </c>
+      <c r="F54" s="212">
+        <f>$D54*1.08%</f>
+        <v>12372.509268</v>
+      </c>
+      <c r="G54" s="44">
+        <f>$D54*1.28%</f>
+        <v>14663.714688</v>
+      </c>
+      <c r="H54" s="44">
+        <f>$D54*1.21%</f>
+        <v>13861.792791</v>
+      </c>
+      <c r="I54" s="44">
+        <f>$D54*1.49%</f>
+        <v>17069.480379000001</v>
+      </c>
+      <c r="J54" s="44">
+        <f>D54*1.74%</f>
+        <v>19933.487153999999</v>
+      </c>
       <c r="K54" s="32">
         <f t="shared" si="7"/>
         <v>1145602.71</v>
       </c>
       <c r="L54" s="54">
         <f t="shared" si="9"/>
-        <v>1145602.71</v>
+        <v>1145602.7100000002</v>
       </c>
       <c r="M54" s="64">
         <f>L54-D54</f>
@@ -4179,35 +4178,35 @@
       <c r="C56" s="223"/>
       <c r="D56" s="31">
         <f>SUM(D48:D55)</f>
-        <v>1397032.3399999999</v>
+        <v>1824924.3399999999</v>
       </c>
       <c r="E56" s="31">
         <f t="shared" ref="E56:J56" si="11">SUM(E48:E55)</f>
-        <v>1394146.36356</v>
+        <v>1744578.8311999999</v>
       </c>
       <c r="F56" s="31">
         <f t="shared" si="11"/>
-        <v>458.36096400000002</v>
+        <v>12760.75728</v>
       </c>
       <c r="G56" s="31">
         <f t="shared" si="11"/>
-        <v>543.24262399999998</v>
+        <v>15123.860479999999</v>
       </c>
       <c r="H56" s="31">
         <f t="shared" si="11"/>
-        <v>513.534043</v>
+        <v>14296.774359999999</v>
       </c>
       <c r="I56" s="31">
         <f t="shared" si="11"/>
-        <v>632.36836700000003</v>
+        <v>17605.118839999999</v>
       </c>
       <c r="J56" s="31">
         <f t="shared" si="11"/>
-        <v>738.47044199999993</v>
+        <v>20558.99784</v>
       </c>
       <c r="K56" s="32">
         <f>E56+J56+F56+G56+H56+I56</f>
-        <v>1397032.34</v>
+        <v>1824924.3399999999</v>
       </c>
       <c r="L56" s="50" t="str">
         <f>IF(D56=K56, "", "Error")</f>
@@ -4265,13 +4264,13 @@
       </c>
       <c r="B60" s="229"/>
       <c r="C60" s="141" t="s">
-        <v>401</v>
-      </c>
-      <c r="D60" s="366">
+        <v>400</v>
+      </c>
+      <c r="D60" s="33">
         <v>200000</v>
       </c>
       <c r="E60" s="226">
-        <f t="shared" ref="E60" si="12">D60</f>
+        <f t="shared" ref="E60:E61" si="12">D60</f>
         <v>200000</v>
       </c>
       <c r="F60" s="221"/>
@@ -4280,7 +4279,7 @@
       <c r="I60" s="55"/>
       <c r="J60" s="44"/>
       <c r="K60" s="32">
-        <f t="shared" ref="K60:K63" si="13">D60</f>
+        <f t="shared" ref="K60:K62" si="13">D60</f>
         <v>200000</v>
       </c>
       <c r="L60" s="54">
@@ -4289,17 +4288,20 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="276" t="s">
+      <c r="A61" s="285" t="s">
         <v>396</v>
       </c>
-      <c r="B61" s="300"/>
+      <c r="B61" s="321"/>
       <c r="C61" s="33" t="s">
         <v>397</v>
       </c>
-      <c r="D61" s="366">
+      <c r="D61" s="33">
         <v>1010955</v>
       </c>
-      <c r="E61" s="226"/>
+      <c r="E61" s="226">
+        <f t="shared" si="12"/>
+        <v>1010955</v>
+      </c>
       <c r="F61" s="212"/>
       <c r="G61" s="44"/>
       <c r="H61" s="44"/>
@@ -4309,383 +4311,440 @@
       <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="288" t="s">
+      <c r="A62" s="297" t="s">
         <v>389</v>
       </c>
-      <c r="B62" s="289"/>
+      <c r="B62" s="298"/>
       <c r="C62" s="33" t="s">
         <v>390</v>
       </c>
-      <c r="D62" s="366">
+      <c r="D62" s="33">
         <v>1145449.82</v>
       </c>
       <c r="E62" s="226">
-        <f>D62</f>
-        <v>1145449.82</v>
-      </c>
-      <c r="F62" s="212"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="44"/>
-      <c r="J62" s="44"/>
+        <f>D62*93.2%</f>
+        <v>1067559.23224</v>
+      </c>
+      <c r="F62" s="212">
+        <f>$D62*1.08%</f>
+        <v>12370.858056000001</v>
+      </c>
+      <c r="G62" s="44">
+        <f>$D62*1.28%</f>
+        <v>14661.757696000002</v>
+      </c>
+      <c r="H62" s="44">
+        <f>$D62*1.21%</f>
+        <v>13859.942822000001</v>
+      </c>
+      <c r="I62" s="44">
+        <f>$D62*1.49%</f>
+        <v>17067.202318</v>
+      </c>
+      <c r="J62" s="44">
+        <f>D62*1.74%</f>
+        <v>19930.826868</v>
+      </c>
       <c r="K62" s="32">
         <f t="shared" si="13"/>
         <v>1145449.82</v>
       </c>
       <c r="L62" s="54">
         <f t="shared" si="14"/>
-        <v>1145449.82</v>
+        <v>1145449.8199999998</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="288" t="s">
-        <v>399</v>
-      </c>
-      <c r="B63" s="289"/>
+      <c r="A63" s="275" t="s">
+        <v>411</v>
+      </c>
+      <c r="B63" s="276"/>
       <c r="C63" s="33" t="s">
         <v>400</v>
       </c>
-      <c r="D63" s="366">
-        <v>60000</v>
+      <c r="D63" s="33">
+        <v>464585.55</v>
       </c>
       <c r="E63" s="226">
-        <f>D63</f>
-        <v>60000</v>
-      </c>
-      <c r="F63" s="212"/>
-      <c r="G63" s="44"/>
-      <c r="H63" s="44"/>
-      <c r="I63" s="44"/>
-      <c r="J63" s="44"/>
-      <c r="K63" s="32">
-        <f t="shared" si="13"/>
-        <v>60000</v>
-      </c>
+        <f>D63*93.2%</f>
+        <v>432993.73259999999</v>
+      </c>
+      <c r="F63" s="212">
+        <f>$D63*1.08%</f>
+        <v>5017.52394</v>
+      </c>
+      <c r="G63" s="44">
+        <f>$D63*1.28%</f>
+        <v>5946.6950400000005</v>
+      </c>
+      <c r="H63" s="44">
+        <f>$D63*1.21%</f>
+        <v>5621.4851549999994</v>
+      </c>
+      <c r="I63" s="44">
+        <f>$D63*1.49%</f>
+        <v>6922.3246950000002</v>
+      </c>
+      <c r="J63" s="44">
+        <f>D63*1.74%</f>
+        <v>8083.7885699999988</v>
+      </c>
+      <c r="K63" s="32"/>
       <c r="L63" s="54"/>
     </row>
-    <row r="64" spans="1:14" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="214" t="s">
         <v>224</v>
       </c>
       <c r="B64" s="214"/>
       <c r="C64" s="214"/>
       <c r="D64" s="31">
-        <f>SUM(D60:D63)</f>
-        <v>2416404.8200000003</v>
+        <f t="shared" ref="D64:J64" si="15">SUM(D60:D63)</f>
+        <v>2820990.37</v>
       </c>
       <c r="E64" s="31">
-        <f>SUM(E60:E63)</f>
-        <v>1405449.82</v>
+        <f t="shared" si="15"/>
+        <v>2711507.9648399996</v>
       </c>
       <c r="F64" s="31">
-        <f>SUM(F60:F63)</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>17388.381996</v>
       </c>
       <c r="G64" s="31">
-        <f>SUM(G60:G63)</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>20608.452736000003</v>
       </c>
       <c r="H64" s="31">
-        <f>SUM(H60:H63)</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>19481.427976999999</v>
       </c>
       <c r="I64" s="31">
-        <f>SUM(I60:I63)</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>23989.527012999999</v>
       </c>
       <c r="J64" s="31">
-        <f>SUM(J60:J63)</f>
-        <v>0</v>
+        <f t="shared" si="15"/>
+        <v>28014.615438000001</v>
       </c>
       <c r="K64" s="32">
         <f>E64+J64+F64+G64+H64+I64</f>
-        <v>1405449.82</v>
+        <v>2820990.3699999996</v>
       </c>
       <c r="L64" s="50" t="str">
         <f>IF(D64=K64, "", "Error")</f>
-        <v>Error</v>
+        <v/>
       </c>
       <c r="N64" s="32"/>
     </row>
-    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="181"/>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="213" t="s">
+        <v>5</v>
+      </c>
       <c r="B65" s="181"/>
       <c r="C65" s="181"/>
       <c r="D65" s="182"/>
-      <c r="E65" s="222"/>
-      <c r="F65" s="222"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="35"/>
-      <c r="I65" s="35"/>
+      <c r="E65" s="218"/>
+      <c r="F65" s="218"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
       <c r="J65" s="3"/>
       <c r="L65" s="50"/>
     </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="181"/>
-      <c r="B66" s="181"/>
-      <c r="C66" s="181"/>
-      <c r="D66" s="182"/>
-      <c r="E66" s="218"/>
-      <c r="F66" s="218"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="34"/>
-      <c r="I66" s="34"/>
-      <c r="J66" s="3"/>
-      <c r="L66" s="50"/>
+    <row r="66" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="230" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="181" t="s">
+        <v>393</v>
+      </c>
+      <c r="C66" s="181" t="s">
+        <v>388</v>
+      </c>
+      <c r="D66" s="33">
+        <v>860560</v>
+      </c>
+      <c r="E66" s="226">
+        <f>D66*93.2%</f>
+        <v>802041.92</v>
+      </c>
+      <c r="F66" s="212">
+        <f>$D66*1.08%</f>
+        <v>9294.0480000000007</v>
+      </c>
+      <c r="G66" s="44">
+        <f>$D66*1.28%</f>
+        <v>11015.168</v>
+      </c>
+      <c r="H66" s="44">
+        <f>$D66*1.21%</f>
+        <v>10412.776</v>
+      </c>
+      <c r="I66" s="44">
+        <f>$D66*1.49%</f>
+        <v>12822.343999999999</v>
+      </c>
+      <c r="J66" s="44">
+        <f>D66*1.74%</f>
+        <v>14973.743999999999</v>
+      </c>
+      <c r="L66" s="50" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A67" s="213" t="s">
-        <v>5</v>
-      </c>
+      <c r="A67" s="213"/>
       <c r="B67" s="181"/>
       <c r="C67" s="181"/>
-      <c r="D67" s="182"/>
-      <c r="E67" s="218"/>
-      <c r="F67" s="218"/>
-      <c r="G67" s="34"/>
-      <c r="H67" s="34"/>
-      <c r="I67" s="34"/>
-      <c r="J67" s="3"/>
+      <c r="D67" s="33"/>
+      <c r="E67" s="226">
+        <f>D67*93.2%</f>
+        <v>0</v>
+      </c>
+      <c r="F67" s="212">
+        <f>$D67*1.08%</f>
+        <v>0</v>
+      </c>
+      <c r="G67" s="44">
+        <f>$D67*1.28%</f>
+        <v>0</v>
+      </c>
+      <c r="H67" s="44">
+        <f>$D67*1.21%</f>
+        <v>0</v>
+      </c>
+      <c r="I67" s="44">
+        <f>$D67*1.49%</f>
+        <v>0</v>
+      </c>
+      <c r="J67" s="44">
+        <f>D67*1.74%</f>
+        <v>0</v>
+      </c>
       <c r="L67" s="50"/>
-    </row>
-    <row r="68" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="230" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="181" t="s">
-        <v>393</v>
-      </c>
-      <c r="C68" s="181" t="s">
-        <v>388</v>
-      </c>
-      <c r="D68" s="366">
+      <c r="N67" s="33"/>
+    </row>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" s="181"/>
+      <c r="B68" s="181"/>
+      <c r="C68" s="181"/>
+      <c r="D68" s="182"/>
+      <c r="E68" s="231"/>
+      <c r="F68" s="231"/>
+      <c r="G68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" s="3"/>
+      <c r="L68" s="50"/>
+      <c r="N68" s="32"/>
+    </row>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" s="214" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" s="214"/>
+      <c r="C69" s="214"/>
+      <c r="D69" s="31">
+        <f>SUM(D66:D68)</f>
         <v>860560</v>
       </c>
-      <c r="E68" s="226">
-        <f>D68*93.2%</f>
+      <c r="E69" s="31">
+        <f>SUM(E66:E68)</f>
         <v>802041.92</v>
       </c>
-      <c r="F68" s="212">
-        <f>$D68*1.08%</f>
+      <c r="F69" s="31">
+        <f t="shared" ref="F69:I69" si="16">SUM(F66:F68)</f>
         <v>9294.0480000000007</v>
       </c>
-      <c r="G68" s="44">
-        <f>$D68*1.28%</f>
+      <c r="G69" s="31">
+        <f t="shared" si="16"/>
         <v>11015.168</v>
       </c>
-      <c r="H68" s="44">
-        <f>$D68*1.21%</f>
+      <c r="H69" s="31">
+        <f t="shared" si="16"/>
         <v>10412.776</v>
       </c>
-      <c r="I68" s="44">
-        <f>$D68*1.49%</f>
+      <c r="I69" s="31">
+        <f t="shared" si="16"/>
         <v>12822.343999999999</v>
       </c>
-      <c r="J68" s="44">
-        <f>D68*1.74%</f>
+      <c r="J69" s="31">
+        <f>SUM(J66:J68)</f>
         <v>14973.743999999999</v>
       </c>
-      <c r="L68" s="50" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" s="213"/>
-      <c r="B69" s="181"/>
-      <c r="C69" s="181"/>
-      <c r="D69" s="33"/>
-      <c r="E69" s="226">
-        <f>D69*93.2%</f>
-        <v>0</v>
-      </c>
-      <c r="F69" s="212">
-        <f>$D69*1.08%</f>
-        <v>0</v>
-      </c>
-      <c r="G69" s="44">
-        <f>$D69*1.28%</f>
-        <v>0</v>
-      </c>
-      <c r="H69" s="44">
-        <f>$D69*1.21%</f>
-        <v>0</v>
-      </c>
-      <c r="I69" s="44">
-        <f>$D69*1.49%</f>
-        <v>0</v>
-      </c>
-      <c r="J69" s="44">
-        <f>D69*1.74%</f>
-        <v>0</v>
-      </c>
-      <c r="L69" s="50"/>
-      <c r="N69" s="33"/>
+      <c r="K69" s="32">
+        <f>E69+J69+F69+G69+H69+I69</f>
+        <v>860559.99999999988</v>
+      </c>
+      <c r="L69" s="50" t="str">
+        <f>IF(D69=K69, "", "Error")</f>
+        <v/>
+      </c>
+      <c r="N69" s="32"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" s="181"/>
+      <c r="A70" s="181" t="s">
+        <v>26</v>
+      </c>
       <c r="B70" s="181"/>
       <c r="C70" s="181"/>
-      <c r="D70" s="182"/>
-      <c r="E70" s="231"/>
-      <c r="F70" s="231"/>
-      <c r="G70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" s="3"/>
+      <c r="D70" s="33">
+        <f>224252.98+4511.22+3555.28+592.55+374.22+1782+181.44+860</f>
+        <v>236109.69</v>
+      </c>
+      <c r="E70" s="226">
+        <f>D70*93.2%</f>
+        <v>220054.23108000003</v>
+      </c>
+      <c r="F70" s="212">
+        <f>$D70*1.08%</f>
+        <v>2549.9846520000001</v>
+      </c>
+      <c r="G70" s="44">
+        <f>$D70*1.28%</f>
+        <v>3022.2040320000001</v>
+      </c>
+      <c r="H70" s="44">
+        <f>$D70*1.21%</f>
+        <v>2856.9272489999998</v>
+      </c>
+      <c r="I70" s="44">
+        <f>$D70*1.49%</f>
+        <v>3518.0343809999999</v>
+      </c>
+      <c r="J70" s="44">
+        <f>D70*1.74%</f>
+        <v>4108.3086059999996</v>
+      </c>
       <c r="L70" s="50"/>
-      <c r="N70" s="32"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" s="214" t="s">
-        <v>7</v>
-      </c>
-      <c r="B71" s="214"/>
-      <c r="C71" s="214"/>
-      <c r="D71" s="31">
-        <f>SUM(D68:D70)</f>
-        <v>860560</v>
-      </c>
-      <c r="E71" s="31">
-        <f>SUM(E68:E70)</f>
-        <v>802041.92</v>
-      </c>
-      <c r="F71" s="31">
-        <f t="shared" ref="F71:I71" si="15">SUM(F68:F70)</f>
-        <v>9294.0480000000007</v>
-      </c>
-      <c r="G71" s="31">
-        <f t="shared" si="15"/>
-        <v>11015.168</v>
-      </c>
-      <c r="H71" s="31">
-        <f t="shared" si="15"/>
-        <v>10412.776</v>
-      </c>
-      <c r="I71" s="31">
-        <f t="shared" si="15"/>
-        <v>12822.343999999999</v>
-      </c>
-      <c r="J71" s="31">
-        <f>SUM(J68:J70)</f>
-        <v>14973.743999999999</v>
-      </c>
-      <c r="K71" s="32">
-        <f>E71+J71+F71+G71+H71+I71</f>
-        <v>860559.99999999988</v>
-      </c>
-      <c r="L71" s="50" t="str">
-        <f>IF(D71=K71, "", "Error")</f>
+      <c r="A71" s="181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B71" s="181"/>
+      <c r="C71" s="232"/>
+      <c r="D71" s="33">
+        <v>69000</v>
+      </c>
+      <c r="E71" s="226">
+        <f>D71*93.2%</f>
+        <v>64308</v>
+      </c>
+      <c r="F71" s="212">
+        <f>$D71*1.08%</f>
+        <v>745.2</v>
+      </c>
+      <c r="G71" s="44">
+        <f>$D71*1.28%</f>
+        <v>883.2</v>
+      </c>
+      <c r="H71" s="44">
+        <f>$D71*1.21%</f>
+        <v>834.9</v>
+      </c>
+      <c r="I71" s="44">
+        <f>$D71*1.49%</f>
+        <v>1028.0999999999999</v>
+      </c>
+      <c r="J71" s="44">
+        <f>D71*1.74%</f>
+        <v>1200.5999999999999</v>
+      </c>
+      <c r="L71" s="50"/>
+    </row>
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" s="214" t="s">
+        <v>225</v>
+      </c>
+      <c r="B72" s="214"/>
+      <c r="C72" s="214"/>
+      <c r="D72" s="52">
+        <f>SUM(D70:D71)</f>
+        <v>305109.69</v>
+      </c>
+      <c r="E72" s="52">
+        <f t="shared" ref="E72:J72" si="17">SUM(E70:E71)</f>
+        <v>284362.23108000006</v>
+      </c>
+      <c r="F72" s="52">
+        <f t="shared" si="17"/>
+        <v>3295.1846519999999</v>
+      </c>
+      <c r="G72" s="48">
+        <f t="shared" si="17"/>
+        <v>3905.4040320000004</v>
+      </c>
+      <c r="H72" s="48">
+        <f t="shared" si="17"/>
+        <v>3691.8272489999999</v>
+      </c>
+      <c r="I72" s="48">
+        <f t="shared" si="17"/>
+        <v>4546.1343809999998</v>
+      </c>
+      <c r="J72" s="48">
+        <f t="shared" si="17"/>
+        <v>5308.9086059999991</v>
+      </c>
+      <c r="K72" s="32">
+        <f>E72+J72+F72+G72+H72+I72</f>
+        <v>305109.69000000012</v>
+      </c>
+      <c r="L72" s="50" t="str">
+        <f>IF(D72=K72, "", "Error")</f>
         <v/>
       </c>
-      <c r="N71" s="32"/>
-    </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" s="181" t="s">
-        <v>26</v>
-      </c>
-      <c r="B72" s="181"/>
-      <c r="C72" s="181"/>
-      <c r="D72" s="366">
-        <v>224252.98</v>
-      </c>
-      <c r="E72" s="226">
-        <f>D72*93.2%</f>
-        <v>209003.77736000001</v>
-      </c>
-      <c r="F72" s="212">
-        <f>$D72*1.08%</f>
-        <v>2421.9321840000002</v>
-      </c>
-      <c r="G72" s="44">
-        <f>$D72*1.28%</f>
-        <v>2870.4381440000002</v>
-      </c>
-      <c r="H72" s="44">
-        <f>$D72*1.21%</f>
-        <v>2713.4610579999999</v>
-      </c>
-      <c r="I72" s="44">
-        <f>$D72*1.49%</f>
-        <v>3341.3694020000003</v>
-      </c>
-      <c r="J72" s="44">
-        <f>D72*1.74%</f>
-        <v>3902.0018519999999</v>
-      </c>
-      <c r="L72" s="50"/>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" s="181" t="s">
-        <v>27</v>
-      </c>
-      <c r="B73" s="181"/>
-      <c r="C73" s="232"/>
-      <c r="D73" s="366">
-        <v>69000</v>
-      </c>
-      <c r="E73" s="226">
-        <f>D73*93.2%</f>
-        <v>64308</v>
-      </c>
-      <c r="F73" s="212">
-        <f>$D73*1.08%</f>
-        <v>745.2</v>
-      </c>
-      <c r="G73" s="44">
-        <f>$D73*1.28%</f>
-        <v>883.2</v>
-      </c>
-      <c r="H73" s="44">
-        <f>$D73*1.21%</f>
-        <v>834.9</v>
-      </c>
-      <c r="I73" s="44">
-        <f>$D73*1.49%</f>
-        <v>1028.0999999999999</v>
-      </c>
-      <c r="J73" s="44">
-        <f>D73*1.74%</f>
-        <v>1200.5999999999999</v>
-      </c>
+    </row>
+    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="73"/>
+      <c r="B73" s="73"/>
+      <c r="C73" s="73"/>
+      <c r="D73" s="73"/>
+      <c r="E73" s="233"/>
+      <c r="F73" s="233"/>
+      <c r="G73" s="6"/>
+      <c r="H73" s="6"/>
+      <c r="I73" s="6"/>
+      <c r="J73" s="72"/>
       <c r="L73" s="50"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="214" t="s">
-        <v>225</v>
-      </c>
-      <c r="B74" s="214"/>
-      <c r="C74" s="214"/>
-      <c r="D74" s="52">
-        <f>SUM(D72:D73)</f>
-        <v>293252.98</v>
-      </c>
-      <c r="E74" s="52">
-        <f t="shared" ref="E74:J74" si="16">SUM(E72:E73)</f>
-        <v>273311.77736000001</v>
-      </c>
-      <c r="F74" s="52">
-        <f t="shared" si="16"/>
-        <v>3167.1321840000001</v>
-      </c>
-      <c r="G74" s="48">
-        <f t="shared" si="16"/>
-        <v>3753.6381440000005</v>
-      </c>
-      <c r="H74" s="48">
-        <f t="shared" si="16"/>
-        <v>3548.361058</v>
-      </c>
-      <c r="I74" s="48">
-        <f t="shared" si="16"/>
-        <v>4369.4694020000006</v>
-      </c>
-      <c r="J74" s="48">
-        <f t="shared" si="16"/>
-        <v>5102.6018519999998</v>
+    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="234" t="s">
+        <v>292</v>
+      </c>
+      <c r="B74" s="235"/>
+      <c r="C74" s="235"/>
+      <c r="D74" s="74">
+        <v>5000000</v>
+      </c>
+      <c r="E74" s="236">
+        <f>D74*93.2%</f>
+        <v>4660000</v>
+      </c>
+      <c r="F74" s="236">
+        <f>$D74*1.08%</f>
+        <v>54000</v>
+      </c>
+      <c r="G74" s="95">
+        <f>$D74*1.28%</f>
+        <v>64000</v>
+      </c>
+      <c r="H74" s="95">
+        <f>$D74*1.21%</f>
+        <v>60500</v>
+      </c>
+      <c r="I74" s="95">
+        <f>$D74*1.49%</f>
+        <v>74500</v>
+      </c>
+      <c r="J74" s="96">
+        <f>D74*1.74%</f>
+        <v>87000</v>
       </c>
       <c r="K74" s="32">
         <f>E74+J74+F74+G74+H74+I74</f>
-        <v>293252.98000000004</v>
+        <v>5000000</v>
       </c>
       <c r="L74" s="50" t="str">
         <f>IF(D74=K74, "", "Error")</f>
@@ -4693,123 +4752,98 @@
       </c>
     </row>
     <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="73"/>
-      <c r="B75" s="73"/>
-      <c r="C75" s="73"/>
-      <c r="D75" s="73"/>
-      <c r="E75" s="233"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="72"/>
+      <c r="A75" s="237"/>
+      <c r="B75" s="238"/>
+      <c r="C75" s="238"/>
+      <c r="D75" s="75"/>
+      <c r="E75" s="75"/>
+      <c r="F75" s="75"/>
+      <c r="G75" s="76"/>
+      <c r="H75" s="76"/>
+      <c r="I75" s="76"/>
+      <c r="J75" s="77"/>
+      <c r="K75" s="32"/>
       <c r="L75" s="50"/>
     </row>
     <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="234" t="s">
-        <v>292</v>
-      </c>
-      <c r="B76" s="235"/>
-      <c r="C76" s="235"/>
-      <c r="D76" s="74"/>
-      <c r="E76" s="236">
-        <f>D76*93.2%</f>
-        <v>0</v>
-      </c>
-      <c r="F76" s="236">
-        <f>$D76*1.08%</f>
-        <v>0</v>
-      </c>
-      <c r="G76" s="95">
-        <f>$D76*1.28%</f>
-        <v>0</v>
-      </c>
-      <c r="H76" s="95">
-        <f>$D76*1.21%</f>
-        <v>0</v>
-      </c>
-      <c r="I76" s="95">
-        <f>$D76*1.49%</f>
-        <v>0</v>
-      </c>
-      <c r="J76" s="96">
-        <f>D76*1.74%</f>
-        <v>0</v>
-      </c>
-      <c r="K76" s="32">
+      <c r="A76" s="239" t="s">
+        <v>28</v>
+      </c>
+      <c r="B76" s="240"/>
+      <c r="C76" s="241"/>
+      <c r="D76" s="66">
+        <f t="shared" ref="D76:J76" si="18">SUM(D74+D37+D31+D72+D69+D64+D56+D46+D28++D42)</f>
+        <v>20282253.399999999</v>
+      </c>
+      <c r="E76" s="66">
+        <f t="shared" si="18"/>
+        <v>19029154.455120001</v>
+      </c>
+      <c r="F76" s="66">
+        <f t="shared" si="18"/>
+        <v>199021.59712799999</v>
+      </c>
+      <c r="G76" s="66">
+        <f t="shared" si="18"/>
+        <v>235877.44844800004</v>
+      </c>
+      <c r="H76" s="66">
+        <f t="shared" si="18"/>
+        <v>222977.900486</v>
+      </c>
+      <c r="I76" s="66">
+        <f t="shared" si="18"/>
+        <v>274576.09233400004</v>
+      </c>
+      <c r="J76" s="66">
+        <f t="shared" si="18"/>
+        <v>320645.90648399998</v>
+      </c>
+      <c r="K76" s="47">
         <f>E76+J76+F76+G76+H76+I76</f>
-        <v>0</v>
+        <v>20282253.399999999</v>
       </c>
       <c r="L76" s="50" t="str">
         <f>IF(D76=K76, "", "Error")</f>
         <v/>
       </c>
+      <c r="M76" s="64">
+        <f>D76-K76</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="237"/>
-      <c r="B77" s="238"/>
-      <c r="C77" s="238"/>
-      <c r="D77" s="75"/>
-      <c r="E77" s="75"/>
-      <c r="F77" s="75"/>
-      <c r="G77" s="76"/>
-      <c r="H77" s="76"/>
-      <c r="I77" s="76"/>
-      <c r="J77" s="77"/>
-      <c r="K77" s="32"/>
-      <c r="L77" s="50"/>
+      <c r="A77" s="65"/>
+      <c r="B77" s="65"/>
+      <c r="C77" s="65"/>
+      <c r="D77" s="65"/>
+      <c r="E77" s="242"/>
+      <c r="F77" s="242"/>
+      <c r="G77" s="32"/>
+      <c r="H77" s="32"/>
+      <c r="I77" s="32"/>
     </row>
     <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="239" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" s="240"/>
-      <c r="C78" s="241"/>
-      <c r="D78" s="66">
-        <f>SUM(D76+D37+D31+D74+D71+D64+D56+D46+D28++D42)</f>
-        <v>14437919.140000001</v>
-      </c>
-      <c r="E78" s="66">
-        <f>SUM(E76+E37+E31+E74+E71+E64+E56+E46+E28++E42)</f>
-        <v>12701613.38892</v>
-      </c>
-      <c r="F78" s="66">
-        <f>SUM(F76+F37+F31+F74+F71+F64+F56+F46+F28++F42)</f>
-        <v>115202.766348</v>
-      </c>
-      <c r="G78" s="66">
-        <f>SUM(G76+G37+G31+G74+G71+G64+G56+G46+G28++G42)</f>
-        <v>136536.61196800001</v>
-      </c>
-      <c r="H78" s="66">
-        <f>SUM(H76+H37+H31+H74+H71+H64+H56+H46+H28++H42)</f>
-        <v>129069.766001</v>
-      </c>
-      <c r="I78" s="66">
-        <f>SUM(I76+I37+I31+I74+I71+I64+I56+I46+I28++I42)</f>
-        <v>158937.14986900002</v>
-      </c>
-      <c r="J78" s="66">
-        <f>SUM(J76+J37+J31+J74+J71+J64+J56+J46+J28++J42)</f>
-        <v>185604.456894</v>
-      </c>
-      <c r="K78" s="47">
-        <f>E78+J78+F78+G78+H78+I78</f>
-        <v>13426964.139999999</v>
-      </c>
-      <c r="L78" s="50" t="str">
-        <f>IF(D78=K78, "", "Error")</f>
-        <v>Error</v>
-      </c>
-      <c r="M78" s="64">
-        <f>D78-K78</f>
-        <v>1010955.0000000019</v>
-      </c>
-    </row>
-    <row r="79" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="65"/>
+      <c r="A78" s="243" t="s">
+        <v>36</v>
+      </c>
+      <c r="B78" s="244"/>
+      <c r="C78" s="244"/>
+      <c r="D78" s="65"/>
+      <c r="E78" s="242"/>
+      <c r="F78" s="242"/>
+      <c r="G78" s="32"/>
+      <c r="H78" s="32"/>
+      <c r="I78" s="32"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" s="245" t="s">
+        <v>403</v>
+      </c>
       <c r="B79" s="65"/>
-      <c r="C79" s="65"/>
+      <c r="C79" s="282">
+        <v>99500</v>
+      </c>
       <c r="D79" s="65"/>
       <c r="E79" s="242"/>
       <c r="F79" s="242"/>
@@ -4817,12 +4851,14 @@
       <c r="H79" s="32"/>
       <c r="I79" s="32"/>
     </row>
-    <row r="80" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="243" t="s">
-        <v>36</v>
-      </c>
-      <c r="B80" s="244"/>
-      <c r="C80" s="244"/>
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A80" s="245" t="s">
+        <v>402</v>
+      </c>
+      <c r="B80" s="65"/>
+      <c r="C80" s="282">
+        <v>99500</v>
+      </c>
       <c r="D80" s="65"/>
       <c r="E80" s="242"/>
       <c r="F80" s="242"/>
@@ -4830,12 +4866,12 @@
       <c r="H80" s="32"/>
       <c r="I80" s="32"/>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="245" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="B81" s="65"/>
-      <c r="C81" s="368">
+      <c r="C81" s="282">
         <v>99500</v>
       </c>
       <c r="D81" s="65"/>
@@ -4845,13 +4881,13 @@
       <c r="H81" s="32"/>
       <c r="I81" s="32"/>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="245" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="B82" s="65"/>
-      <c r="C82" s="368">
-        <v>99500</v>
+      <c r="C82" s="282">
+        <v>85744</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="242"/>
@@ -4860,13 +4896,14 @@
       <c r="H82" s="32"/>
       <c r="I82" s="32"/>
     </row>
-    <row r="83" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="245" t="s">
-        <v>402</v>
-      </c>
-      <c r="B83" s="65"/>
-      <c r="C83" s="368">
-        <v>99500</v>
+    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="246" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" s="247"/>
+      <c r="C83" s="248">
+        <f>SUM(C79:C82)</f>
+        <v>384244</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="242"/>
@@ -4875,15 +4912,10 @@
       <c r="H83" s="32"/>
       <c r="I83" s="32"/>
     </row>
-    <row r="84" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="246" t="s">
-        <v>16</v>
-      </c>
-      <c r="B84" s="247"/>
-      <c r="C84" s="248">
-        <f>SUM(C81:C83)</f>
-        <v>298500</v>
-      </c>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" s="65"/>
+      <c r="B84" s="65"/>
+      <c r="C84" s="65"/>
       <c r="D84" s="65"/>
       <c r="E84" s="242"/>
       <c r="F84" s="242"/>
@@ -4896,599 +4928,607 @@
       <c r="B85" s="65"/>
       <c r="C85" s="65"/>
       <c r="D85" s="65"/>
-      <c r="E85" s="242"/>
-      <c r="F85" s="242"/>
-      <c r="G85" s="32"/>
-      <c r="H85" s="32"/>
-      <c r="I85" s="32"/>
+      <c r="E85" s="249"/>
+      <c r="F85" s="249"/>
+      <c r="G85" s="46"/>
+      <c r="H85" s="46"/>
+      <c r="I85" s="46"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="65"/>
-      <c r="B86" s="65"/>
-      <c r="C86" s="65"/>
-      <c r="D86" s="65"/>
-      <c r="E86" s="249"/>
-      <c r="F86" s="249"/>
-      <c r="G86" s="46"/>
-      <c r="H86" s="46"/>
-      <c r="I86" s="46"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A87" s="294" t="s">
+      <c r="A86" s="306" t="s">
         <v>32</v>
       </c>
-      <c r="B87" s="295"/>
-      <c r="C87" s="295"/>
-      <c r="D87" s="295"/>
-      <c r="E87" s="60" t="s">
+      <c r="B86" s="307"/>
+      <c r="C86" s="307"/>
+      <c r="D86" s="307"/>
+      <c r="E86" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="F87" s="60" t="s">
+      <c r="F86" s="60" t="s">
         <v>165</v>
       </c>
-      <c r="G87" s="60" t="s">
+      <c r="G86" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="H87" s="60" t="s">
+      <c r="H86" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="I87" s="60" t="s">
+      <c r="I86" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="J87" s="61" t="s">
+      <c r="J86" s="61" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="276"/>
-      <c r="B88" s="277"/>
-      <c r="C88" s="250"/>
+    <row r="87" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="285"/>
+      <c r="B87" s="286"/>
+      <c r="C87" s="250"/>
+      <c r="D87" s="33"/>
+      <c r="E87" s="226">
+        <f>D87</f>
+        <v>0</v>
+      </c>
+      <c r="F87" s="226"/>
+      <c r="G87" s="49"/>
+      <c r="H87" s="49"/>
+      <c r="I87" s="49"/>
+      <c r="J87" s="44"/>
+    </row>
+    <row r="88" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="308"/>
+      <c r="B88" s="309"/>
+      <c r="C88" s="62"/>
       <c r="D88" s="33"/>
-      <c r="E88" s="226">
-        <f>D88</f>
-        <v>0</v>
-      </c>
-      <c r="F88" s="226"/>
+      <c r="E88" s="49"/>
+      <c r="F88" s="49"/>
       <c r="G88" s="49"/>
       <c r="H88" s="49"/>
       <c r="I88" s="49"/>
       <c r="J88" s="44"/>
     </row>
-    <row r="89" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="296"/>
-      <c r="B89" s="297"/>
-      <c r="C89" s="62"/>
-      <c r="D89" s="33"/>
-      <c r="E89" s="49"/>
-      <c r="F89" s="49"/>
-      <c r="G89" s="49"/>
-      <c r="H89" s="49"/>
-      <c r="I89" s="49"/>
-      <c r="J89" s="44"/>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A90" s="291" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="303" t="s">
         <v>16</v>
       </c>
-      <c r="B90" s="292"/>
-      <c r="C90" s="293"/>
-      <c r="D90" s="59">
-        <f>SUM(D88:D89)</f>
-        <v>0</v>
-      </c>
-      <c r="E90" s="59">
-        <f>SUM(E88:E89)</f>
-        <v>0</v>
-      </c>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59">
-        <f>SUM(J88:J89)</f>
-        <v>0</v>
-      </c>
-      <c r="L90" s="32">
-        <f>E90+J90</f>
-        <v>0</v>
-      </c>
-      <c r="M90" s="50" t="str">
-        <f>IF(D90=L90, "", "Error")</f>
+      <c r="B89" s="304"/>
+      <c r="C89" s="305"/>
+      <c r="D89" s="59">
+        <f>SUM(D87:D88)</f>
+        <v>0</v>
+      </c>
+      <c r="E89" s="59">
+        <f>SUM(E87:E88)</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="59"/>
+      <c r="J89" s="59">
+        <f>SUM(J87:J88)</f>
+        <v>0</v>
+      </c>
+      <c r="L89" s="32">
+        <f>E89+J89</f>
+        <v>0</v>
+      </c>
+      <c r="M89" s="50" t="str">
+        <f>IF(D89=L89, "", "Error")</f>
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E92" s="32"/>
-      <c r="F92" s="32"/>
-      <c r="G92" s="32"/>
-      <c r="H92" s="32"/>
-      <c r="I92" s="32"/>
-    </row>
-    <row r="93" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="27" t="s">
+    <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E91" s="32"/>
+      <c r="F91" s="32"/>
+      <c r="G91" s="32"/>
+      <c r="H91" s="32"/>
+      <c r="I91" s="32"/>
+    </row>
+    <row r="92" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="B93" s="28">
-        <f>D78</f>
-        <v>14437919.140000001</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="29" t="s">
+      <c r="B92" s="28">
+        <f>D76</f>
+        <v>20282253.399999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="B94" s="30">
-        <f>D78-D76</f>
-        <v>14437919.140000001</v>
-      </c>
-      <c r="D94" s="278" t="s">
+      <c r="B93" s="30">
+        <f>D76-D74</f>
+        <v>15282253.399999999</v>
+      </c>
+      <c r="D93" s="287" t="s">
         <v>284</v>
       </c>
-      <c r="E94" s="278"/>
-      <c r="F94" s="278"/>
-      <c r="G94" s="278"/>
-      <c r="H94" s="278"/>
-      <c r="I94" s="278"/>
+      <c r="E93" s="287"/>
+      <c r="F93" s="287"/>
+      <c r="G93" s="287"/>
+      <c r="H93" s="287"/>
+      <c r="I93" s="287"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="D94" s="287"/>
+      <c r="E94" s="287"/>
+      <c r="F94" s="287"/>
+      <c r="G94" s="287"/>
+      <c r="H94" s="287"/>
+      <c r="I94" s="287"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="278"/>
-      <c r="E95" s="278"/>
-      <c r="F95" s="278"/>
-      <c r="G95" s="278"/>
-      <c r="H95" s="278"/>
-      <c r="I95" s="278"/>
+      <c r="D95" s="287"/>
+      <c r="E95" s="287"/>
+      <c r="F95" s="287"/>
+      <c r="G95" s="287"/>
+      <c r="H95" s="287"/>
+      <c r="I95" s="287"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D96" s="278"/>
-      <c r="E96" s="278"/>
-      <c r="F96" s="278"/>
-      <c r="G96" s="278"/>
-      <c r="H96" s="278"/>
-      <c r="I96" s="278"/>
+      <c r="A96" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B96" s="9"/>
+      <c r="C96" s="10"/>
+      <c r="D96" s="287"/>
+      <c r="E96" s="287"/>
+      <c r="F96" s="287"/>
+      <c r="G96" s="287"/>
+      <c r="H96" s="287"/>
+      <c r="I96" s="287"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B97" s="9"/>
-      <c r="C97" s="10"/>
-      <c r="D97" s="278"/>
-      <c r="E97" s="278"/>
-      <c r="F97" s="278"/>
-      <c r="G97" s="278"/>
-      <c r="H97" s="278"/>
-      <c r="I97" s="278"/>
+      <c r="A97" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97" s="5">
+        <v>687013.08954010718</v>
+      </c>
+      <c r="C97" s="12"/>
+      <c r="D97" s="287"/>
+      <c r="E97" s="287"/>
+      <c r="F97" s="287"/>
+      <c r="G97" s="287"/>
+      <c r="H97" s="287"/>
+      <c r="I97" s="287"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B98" s="5">
-        <v>687013.08954010718</v>
-      </c>
-      <c r="C98" s="12"/>
-      <c r="D98" s="278"/>
-      <c r="E98" s="278"/>
-      <c r="F98" s="278"/>
-      <c r="G98" s="278"/>
-      <c r="H98" s="278"/>
-      <c r="I98" s="278"/>
+      <c r="A98" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" s="22">
+        <f>PRORRATEO!H133</f>
+        <v>16415860.980825996</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D98" s="287"/>
+      <c r="E98" s="287"/>
+      <c r="F98" s="287"/>
+      <c r="G98" s="287"/>
+      <c r="H98" s="287"/>
+      <c r="I98" s="287"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
-        <v>21</v>
+        <v>344</v>
       </c>
       <c r="B99" s="22">
-        <f>PRORRATEO!H133</f>
-        <v>16178300.020825995</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="278"/>
-      <c r="E99" s="278"/>
-      <c r="F99" s="278"/>
-      <c r="G99" s="278"/>
-      <c r="H99" s="278"/>
-      <c r="I99" s="278"/>
+        <f>ARBA!L82</f>
+        <v>912822.36</v>
+      </c>
+      <c r="C99" s="12"/>
+      <c r="D99" s="287"/>
+      <c r="E99" s="287"/>
+      <c r="F99" s="287"/>
+      <c r="G99" s="287"/>
+      <c r="H99" s="287"/>
+      <c r="I99" s="287"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
-        <v>344</v>
-      </c>
-      <c r="B100" s="22">
-        <f>ARBA!L82</f>
-        <v>912822.36</v>
-      </c>
-      <c r="C100" s="12"/>
-      <c r="D100" s="278"/>
-      <c r="E100" s="278"/>
-      <c r="F100" s="278"/>
-      <c r="G100" s="278"/>
-      <c r="H100" s="278"/>
-      <c r="I100" s="278"/>
+        <v>34</v>
+      </c>
+      <c r="B100" s="63">
+        <f>-B93</f>
+        <v>-15282253.399999999</v>
+      </c>
+      <c r="C100" s="10"/>
+      <c r="D100" s="287"/>
+      <c r="E100" s="287"/>
+      <c r="F100" s="287"/>
+      <c r="G100" s="287"/>
+      <c r="H100" s="287"/>
+      <c r="I100" s="287"/>
+      <c r="K100" s="33"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B101" s="63">
-        <f>-B94</f>
-        <v>-14437919.140000001</v>
+        <f>-D89</f>
+        <v>0</v>
       </c>
       <c r="C101" s="10"/>
-      <c r="D101" s="278"/>
-      <c r="E101" s="278"/>
-      <c r="F101" s="278"/>
-      <c r="G101" s="278"/>
-      <c r="H101" s="278"/>
-      <c r="I101" s="278"/>
-      <c r="K101" s="33"/>
+      <c r="D101" s="287"/>
+      <c r="E101" s="287"/>
+      <c r="F101" s="287"/>
+      <c r="G101" s="287"/>
+      <c r="H101" s="287"/>
+      <c r="I101" s="287"/>
+      <c r="K101" s="39"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B102" s="63">
-        <f>-D90</f>
+        <v>274</v>
+      </c>
+      <c r="B102" s="22">
+        <f>B110</f>
         <v>0</v>
       </c>
       <c r="C102" s="10"/>
-      <c r="D102" s="278"/>
-      <c r="E102" s="278"/>
-      <c r="F102" s="278"/>
-      <c r="G102" s="278"/>
-      <c r="H102" s="278"/>
-      <c r="I102" s="278"/>
+      <c r="D102" s="287"/>
+      <c r="E102" s="287"/>
+      <c r="F102" s="287"/>
+      <c r="G102" s="287"/>
+      <c r="H102" s="287"/>
+      <c r="I102" s="287"/>
       <c r="K102" s="39"/>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="13" t="s">
-        <v>274</v>
+    <row r="103" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="194" t="s">
+        <v>408</v>
       </c>
       <c r="B103" s="22">
-        <f>B111</f>
-        <v>0</v>
+        <v>46200</v>
       </c>
       <c r="C103" s="10"/>
-      <c r="D103" s="278"/>
-      <c r="E103" s="278"/>
-      <c r="F103" s="278"/>
-      <c r="G103" s="278"/>
-      <c r="H103" s="278"/>
-      <c r="I103" s="278"/>
+      <c r="D103" s="287"/>
+      <c r="E103" s="287"/>
+      <c r="F103" s="287"/>
+      <c r="G103" s="287"/>
+      <c r="H103" s="287"/>
+      <c r="I103" s="287"/>
       <c r="K103" s="39"/>
     </row>
-    <row r="104" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="194" t="s">
-        <v>410</v>
-      </c>
-      <c r="B104" s="22">
-        <v>46200</v>
-      </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="278"/>
-      <c r="E104" s="278"/>
-      <c r="F104" s="278"/>
-      <c r="G104" s="278"/>
-      <c r="H104" s="278"/>
-      <c r="I104" s="278"/>
-      <c r="K104" s="39"/>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B104" s="63">
+        <f>-B122</f>
+        <v>-100000</v>
+      </c>
+      <c r="C104" s="14"/>
+      <c r="D104" s="287"/>
+      <c r="E104" s="287"/>
+      <c r="F104" s="287"/>
+      <c r="G104" s="287"/>
+      <c r="H104" s="287"/>
+      <c r="I104" s="287"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B105" s="63">
-        <f>-B123</f>
-        <v>-100000</v>
+        <f>-C83</f>
+        <v>-384244</v>
       </c>
       <c r="C105" s="14"/>
-      <c r="D105" s="278"/>
-      <c r="E105" s="278"/>
-      <c r="F105" s="278"/>
-      <c r="G105" s="278"/>
-      <c r="H105" s="278"/>
-      <c r="I105" s="278"/>
+      <c r="D105" s="287"/>
+      <c r="E105" s="287"/>
+      <c r="F105" s="287"/>
+      <c r="G105" s="287"/>
+      <c r="H105" s="287"/>
+      <c r="I105" s="287"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B106" s="63">
-        <f>-C84</f>
-        <v>-298500</v>
-      </c>
-      <c r="C106" s="14"/>
-      <c r="D106" s="278"/>
-      <c r="E106" s="278"/>
-      <c r="F106" s="278"/>
-      <c r="G106" s="278"/>
-      <c r="H106" s="278"/>
-      <c r="I106" s="278"/>
+      <c r="A106" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B106" s="15">
+        <f>SUM(B97:B105)</f>
+        <v>2295399.0303661041</v>
+      </c>
+      <c r="C106" s="51"/>
+      <c r="D106" s="287"/>
+      <c r="E106" s="287"/>
+      <c r="F106" s="287"/>
+      <c r="G106" s="287"/>
+      <c r="H106" s="287"/>
+      <c r="I106" s="287"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="15">
-        <f>SUM(B98:B106)</f>
-        <v>2987916.3303661011</v>
-      </c>
-      <c r="C107" s="51"/>
-      <c r="D107" s="278"/>
-      <c r="E107" s="278"/>
-      <c r="F107" s="278"/>
-      <c r="G107" s="278"/>
-      <c r="H107" s="278"/>
-      <c r="I107" s="278"/>
+      <c r="A107" s="14"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="287"/>
+      <c r="E107" s="287"/>
+      <c r="F107" s="287"/>
+      <c r="G107" s="287"/>
+      <c r="H107" s="287"/>
+      <c r="I107" s="287"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="14"/>
+      <c r="A108" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B108" s="5"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="278"/>
-      <c r="E108" s="278"/>
-      <c r="F108" s="278"/>
-      <c r="G108" s="278"/>
-      <c r="H108" s="278"/>
-      <c r="I108" s="278"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="B109" s="5"/>
+      <c r="D108" s="287"/>
+      <c r="E108" s="287"/>
+      <c r="F108" s="287"/>
+      <c r="G108" s="287"/>
+      <c r="H108" s="287"/>
+      <c r="I108" s="287"/>
+    </row>
+    <row r="109" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="202"/>
+      <c r="B109" s="22"/>
       <c r="C109" s="10"/>
-      <c r="D109" s="278"/>
-      <c r="E109" s="278"/>
-      <c r="F109" s="278"/>
-      <c r="G109" s="278"/>
-      <c r="H109" s="278"/>
-      <c r="I109" s="278"/>
-    </row>
-    <row r="110" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="202"/>
-      <c r="B110" s="22"/>
+      <c r="D109" s="17"/>
+      <c r="E109" s="17"/>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B110" s="26">
+        <f>SUM(B108:B109)</f>
+        <v>0</v>
+      </c>
       <c r="C110" s="10"/>
-      <c r="D110" s="17"/>
       <c r="E110" s="17"/>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B111" s="26">
-        <f>SUM(B109:B110)</f>
-        <v>0</v>
-      </c>
+      <c r="A111" s="14"/>
       <c r="C111" s="10"/>
-      <c r="E111" s="17"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D111" s="17"/>
+    </row>
+    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="14"/>
       <c r="C112" s="10"/>
       <c r="D112" s="17"/>
     </row>
-    <row r="113" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="14"/>
+    <row r="113" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B113" s="5">
+        <v>106182.28</v>
+      </c>
       <c r="C113" s="10"/>
-      <c r="D113" s="17"/>
-    </row>
-    <row r="114" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B114" s="5">
-        <v>106182.28</v>
+      <c r="D113" s="310" t="s">
+        <v>410</v>
+      </c>
+      <c r="E113" s="311"/>
+      <c r="F113" s="311"/>
+      <c r="G113" s="311"/>
+      <c r="H113" s="311"/>
+      <c r="I113" s="312"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="B114" s="23">
+        <v>-60000</v>
       </c>
       <c r="C114" s="10"/>
-      <c r="D114" s="377" t="s">
-        <v>412</v>
-      </c>
-      <c r="E114" s="378"/>
-      <c r="F114" s="378"/>
-      <c r="G114" s="378"/>
-      <c r="H114" s="378"/>
-      <c r="I114" s="379"/>
-    </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A115" s="11" t="s">
+      <c r="D114" s="313"/>
+      <c r="E114" s="314"/>
+      <c r="F114" s="314"/>
+      <c r="G114" s="314"/>
+      <c r="H114" s="314"/>
+      <c r="I114" s="315"/>
+    </row>
+    <row r="115" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="205" t="s">
         <v>406</v>
       </c>
       <c r="B115" s="23">
-        <v>-60000</v>
-      </c>
-      <c r="C115" s="10"/>
-      <c r="D115" s="380"/>
-      <c r="E115" s="381"/>
-      <c r="F115" s="381"/>
-      <c r="G115" s="381"/>
-      <c r="H115" s="381"/>
-      <c r="I115" s="382"/>
-    </row>
-    <row r="116" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="205" t="s">
-        <v>407</v>
-      </c>
-      <c r="B116" s="23">
         <f>-24000*3</f>
         <v>-72000</v>
       </c>
+      <c r="C115" s="10"/>
+      <c r="D115" s="313"/>
+      <c r="E115" s="314"/>
+      <c r="F115" s="314"/>
+      <c r="G115" s="314"/>
+      <c r="H115" s="314"/>
+      <c r="I115" s="315"/>
+    </row>
+    <row r="116" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B116" s="26">
+        <f>SUM(B113:B115)</f>
+        <v>-25817.72</v>
+      </c>
       <c r="C116" s="10"/>
-      <c r="D116" s="380"/>
-      <c r="E116" s="381"/>
-      <c r="F116" s="381"/>
-      <c r="G116" s="381"/>
-      <c r="H116" s="381"/>
-      <c r="I116" s="382"/>
-    </row>
-    <row r="117" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B117" s="26">
-        <f>SUM(B114:B116)</f>
-        <v>-25817.72</v>
-      </c>
+      <c r="D116" s="316"/>
+      <c r="E116" s="317"/>
+      <c r="F116" s="317"/>
+      <c r="G116" s="317"/>
+      <c r="H116" s="317"/>
+      <c r="I116" s="318"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="14"/>
       <c r="C117" s="10"/>
-      <c r="D117" s="383"/>
-      <c r="E117" s="384"/>
-      <c r="F117" s="384"/>
-      <c r="G117" s="384"/>
-      <c r="H117" s="384"/>
-      <c r="I117" s="385"/>
+      <c r="D117" s="17"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
       <c r="C118" s="10"/>
-      <c r="D118" s="17"/>
+      <c r="D118" s="284" t="s">
+        <v>413</v>
+      </c>
+      <c r="E118" s="53"/>
+      <c r="F118" s="53"/>
+      <c r="G118" s="53"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="14"/>
       <c r="C119" s="10"/>
-      <c r="D119" s="17"/>
-      <c r="E119" s="386" t="s">
-        <v>413</v>
-      </c>
-      <c r="F119" s="371"/>
-      <c r="G119" s="371"/>
-    </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A120" s="14"/>
+      <c r="D119" s="284"/>
+      <c r="E119" s="53"/>
+      <c r="F119" s="53"/>
+      <c r="G119" s="53"/>
+    </row>
+    <row r="120" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C120" s="10"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="371"/>
-      <c r="F120" s="371"/>
-      <c r="G120" s="371"/>
-    </row>
-    <row r="121" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C121" s="10"/>
-      <c r="D121" s="32"/>
-      <c r="E121" s="387"/>
-      <c r="F121" s="387"/>
-      <c r="G121" s="387"/>
-      <c r="H121" s="64"/>
-      <c r="I121" s="64"/>
+      <c r="D120" s="32"/>
+      <c r="H120" s="64"/>
+      <c r="I120" s="64"/>
+    </row>
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="8" t="s">
+        <v>361</v>
+      </c>
+      <c r="B121" s="5">
+        <v>498840</v>
+      </c>
+      <c r="C121" s="16"/>
+      <c r="D121" s="288" t="s">
+        <v>414</v>
+      </c>
+      <c r="E121" s="289"/>
+      <c r="F121" s="289"/>
+      <c r="G121" s="289"/>
+      <c r="H121" s="289"/>
+      <c r="I121" s="289"/>
+      <c r="J121" s="290"/>
     </row>
     <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="B122" s="5">
-        <v>498840</v>
+      <c r="A122" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="B122" s="23">
+        <v>100000</v>
       </c>
       <c r="C122" s="16"/>
-      <c r="D122" s="279"/>
-      <c r="E122" s="280"/>
-      <c r="F122" s="280"/>
-      <c r="G122" s="280"/>
-      <c r="H122" s="280"/>
-      <c r="I122" s="280"/>
-      <c r="J122" s="281"/>
-    </row>
-    <row r="123" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B123" s="23">
-        <v>100000</v>
+      <c r="D122" s="291"/>
+      <c r="E122" s="292"/>
+      <c r="F122" s="292"/>
+      <c r="G122" s="292"/>
+      <c r="H122" s="292"/>
+      <c r="I122" s="292"/>
+      <c r="J122" s="293"/>
+    </row>
+    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="11"/>
+      <c r="B123" s="63">
+        <v>0</v>
       </c>
       <c r="C123" s="16"/>
-      <c r="D123" s="282"/>
-      <c r="E123" s="283"/>
-      <c r="F123" s="283"/>
-      <c r="G123" s="283"/>
-      <c r="H123" s="283"/>
-      <c r="I123" s="283"/>
-      <c r="J123" s="284"/>
-    </row>
-    <row r="124" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="11"/>
-      <c r="B124" s="63" t="s">
-        <v>408</v>
+      <c r="D123" s="291"/>
+      <c r="E123" s="292"/>
+      <c r="F123" s="292"/>
+      <c r="G123" s="292"/>
+      <c r="H123" s="292"/>
+      <c r="I123" s="292"/>
+      <c r="J123" s="293"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" s="26">
+        <f>SUM(B121:B123)</f>
+        <v>598840</v>
       </c>
       <c r="C124" s="16"/>
-      <c r="D124" s="282"/>
-      <c r="E124" s="283"/>
-      <c r="F124" s="283"/>
-      <c r="G124" s="283"/>
-      <c r="H124" s="283"/>
-      <c r="I124" s="283"/>
-      <c r="J124" s="284"/>
-    </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A125" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B125" s="26">
-        <f>SUM(B122:B124)</f>
-        <v>598840</v>
-      </c>
-      <c r="C125" s="16"/>
-      <c r="D125" s="282"/>
-      <c r="E125" s="283"/>
-      <c r="F125" s="283"/>
-      <c r="G125" s="283"/>
-      <c r="H125" s="283"/>
-      <c r="I125" s="283"/>
-      <c r="J125" s="284"/>
-    </row>
-    <row r="126" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C126" s="17"/>
-      <c r="D126" s="282"/>
-      <c r="E126" s="283"/>
-      <c r="F126" s="283"/>
-      <c r="G126" s="283"/>
-      <c r="H126" s="283"/>
-      <c r="I126" s="283"/>
-      <c r="J126" s="284"/>
-    </row>
-    <row r="127" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="290" t="s">
+      <c r="D124" s="291"/>
+      <c r="E124" s="292"/>
+      <c r="F124" s="292"/>
+      <c r="G124" s="292"/>
+      <c r="H124" s="292"/>
+      <c r="I124" s="292"/>
+      <c r="J124" s="293"/>
+    </row>
+    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C125" s="17"/>
+      <c r="D125" s="291"/>
+      <c r="E125" s="292"/>
+      <c r="F125" s="292"/>
+      <c r="G125" s="292"/>
+      <c r="H125" s="292"/>
+      <c r="I125" s="292"/>
+      <c r="J125" s="293"/>
+    </row>
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A126" s="299" t="s">
         <v>362</v>
       </c>
-      <c r="B127" s="375">
-        <f>B125+B107+B117</f>
-        <v>3560938.6103661009</v>
-      </c>
-      <c r="C127" s="10"/>
-      <c r="D127" s="282"/>
-      <c r="E127" s="283"/>
-      <c r="F127" s="283"/>
-      <c r="G127" s="283"/>
-      <c r="H127" s="283"/>
-      <c r="I127" s="283"/>
-      <c r="J127" s="284"/>
-    </row>
-    <row r="128" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="374"/>
-      <c r="B128" s="376"/>
-      <c r="D128" s="285"/>
-      <c r="E128" s="286"/>
-      <c r="F128" s="286"/>
-      <c r="G128" s="286"/>
-      <c r="H128" s="286"/>
-      <c r="I128" s="286"/>
-      <c r="J128" s="287"/>
+      <c r="B126" s="301">
+        <f>B124+B106+B116</f>
+        <v>2868421.3103661039</v>
+      </c>
+      <c r="C126" s="10"/>
+      <c r="D126" s="291"/>
+      <c r="E126" s="292"/>
+      <c r="F126" s="292"/>
+      <c r="G126" s="292"/>
+      <c r="H126" s="292"/>
+      <c r="I126" s="292"/>
+      <c r="J126" s="293"/>
+    </row>
+    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="300"/>
+      <c r="B127" s="302"/>
+      <c r="D127" s="294"/>
+      <c r="E127" s="295"/>
+      <c r="F127" s="295"/>
+      <c r="G127" s="295"/>
+      <c r="H127" s="295"/>
+      <c r="I127" s="295"/>
+      <c r="J127" s="296"/>
+    </row>
+    <row r="133" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D133" s="53"/>
+      <c r="E133" s="53"/>
+      <c r="F133" s="53"/>
+      <c r="G133" s="53"/>
+      <c r="H133" s="53"/>
+    </row>
+    <row r="134" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D134" s="283"/>
+      <c r="E134" s="53"/>
+      <c r="F134" s="53"/>
+      <c r="G134" s="53"/>
+      <c r="H134" s="53"/>
+    </row>
+    <row r="135" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D135" s="283"/>
+      <c r="E135" s="53"/>
+      <c r="F135" s="53"/>
+      <c r="G135" s="53"/>
+      <c r="H135" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="A14:J18"/>
     <mergeCell ref="A20:J22"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="D93:I108"/>
+    <mergeCell ref="D121:J127"/>
+    <mergeCell ref="A62:B62"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="B126:B127"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A88:B88"/>
-    <mergeCell ref="D94:I109"/>
-    <mergeCell ref="D122:J128"/>
-    <mergeCell ref="A62:B62"/>
-    <mergeCell ref="A127:A128"/>
-    <mergeCell ref="B127:B128"/>
-    <mergeCell ref="A90:C90"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="D114:I117"/>
+    <mergeCell ref="D113:I116"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5523,13 +5563,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="335" t="s">
+      <c r="A1" s="356" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="336"/>
-      <c r="C1" s="336"/>
-      <c r="D1" s="336"/>
-      <c r="E1" s="336"/>
+      <c r="B1" s="357"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
       <c r="F1" s="125" t="s">
         <v>276</v>
       </c>
@@ -5541,20 +5581,20 @@
       <c r="L1" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="313">
-        <f>RESUMEN!D78-N3</f>
-        <v>14437919.140000001</v>
-      </c>
-      <c r="N1" s="314"/>
+      <c r="M1" s="334">
+        <f>RESUMEN!D76-N3</f>
+        <v>14275955.399999999</v>
+      </c>
+      <c r="N1" s="335"/>
       <c r="O1" s="126"/>
       <c r="P1" s="45"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="337"/>
-      <c r="B2" s="338"/>
-      <c r="C2" s="338"/>
-      <c r="D2" s="338"/>
-      <c r="E2" s="338"/>
+      <c r="A2" s="358"/>
+      <c r="B2" s="359"/>
+      <c r="C2" s="359"/>
+      <c r="D2" s="359"/>
+      <c r="E2" s="359"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5568,17 +5608,17 @@
       </c>
       <c r="M2" s="155"/>
       <c r="N2" s="156">
-        <v>15000000</v>
+        <v>14275955.399999999</v>
       </c>
       <c r="O2" s="127"/>
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="337"/>
-      <c r="B3" s="338"/>
-      <c r="C3" s="338"/>
-      <c r="D3" s="338"/>
-      <c r="E3" s="338"/>
+      <c r="A3" s="358"/>
+      <c r="B3" s="359"/>
+      <c r="C3" s="359"/>
+      <c r="D3" s="359"/>
+      <c r="E3" s="359"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5592,17 +5632,17 @@
       </c>
       <c r="M3" s="4"/>
       <c r="N3" s="183">
-        <v>0</v>
+        <v>6006298</v>
       </c>
       <c r="O3" s="129"/>
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="339"/>
-      <c r="B4" s="340"/>
-      <c r="C4" s="340"/>
-      <c r="D4" s="340"/>
-      <c r="E4" s="340"/>
+      <c r="A4" s="360"/>
+      <c r="B4" s="361"/>
+      <c r="C4" s="361"/>
+      <c r="D4" s="361"/>
+      <c r="E4" s="361"/>
       <c r="F4" s="130"/>
       <c r="G4" s="130"/>
       <c r="H4" s="130"/>
@@ -5618,219 +5658,219 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="320" t="s">
-        <v>409</v>
-      </c>
-      <c r="D5" s="321"/>
-      <c r="E5" s="321"/>
-      <c r="F5" s="321"/>
-      <c r="G5" s="321"/>
-      <c r="H5" s="321"/>
-      <c r="I5" s="321"/>
-      <c r="J5" s="321"/>
-      <c r="K5" s="321"/>
-      <c r="L5" s="321"/>
-      <c r="M5" s="321"/>
-      <c r="N5" s="321"/>
-      <c r="O5" s="322"/>
+      <c r="C5" s="341" t="s">
+        <v>407</v>
+      </c>
+      <c r="D5" s="342"/>
+      <c r="E5" s="342"/>
+      <c r="F5" s="342"/>
+      <c r="G5" s="342"/>
+      <c r="H5" s="342"/>
+      <c r="I5" s="342"/>
+      <c r="J5" s="342"/>
+      <c r="K5" s="342"/>
+      <c r="L5" s="342"/>
+      <c r="M5" s="342"/>
+      <c r="N5" s="342"/>
+      <c r="O5" s="343"/>
       <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="323"/>
-      <c r="D6" s="324"/>
-      <c r="E6" s="324"/>
-      <c r="F6" s="324"/>
-      <c r="G6" s="324"/>
-      <c r="H6" s="324"/>
-      <c r="I6" s="324"/>
-      <c r="J6" s="324"/>
-      <c r="K6" s="324"/>
-      <c r="L6" s="324"/>
-      <c r="M6" s="324"/>
-      <c r="N6" s="324"/>
-      <c r="O6" s="325"/>
+      <c r="C6" s="344"/>
+      <c r="D6" s="345"/>
+      <c r="E6" s="345"/>
+      <c r="F6" s="345"/>
+      <c r="G6" s="345"/>
+      <c r="H6" s="345"/>
+      <c r="I6" s="345"/>
+      <c r="J6" s="345"/>
+      <c r="K6" s="345"/>
+      <c r="L6" s="345"/>
+      <c r="M6" s="345"/>
+      <c r="N6" s="345"/>
+      <c r="O6" s="346"/>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="323"/>
-      <c r="D7" s="324"/>
-      <c r="E7" s="324"/>
-      <c r="F7" s="324"/>
-      <c r="G7" s="324"/>
-      <c r="H7" s="324"/>
-      <c r="I7" s="324"/>
-      <c r="J7" s="324"/>
-      <c r="K7" s="324"/>
-      <c r="L7" s="324"/>
-      <c r="M7" s="324"/>
-      <c r="N7" s="324"/>
-      <c r="O7" s="325"/>
+      <c r="C7" s="344"/>
+      <c r="D7" s="345"/>
+      <c r="E7" s="345"/>
+      <c r="F7" s="345"/>
+      <c r="G7" s="345"/>
+      <c r="H7" s="345"/>
+      <c r="I7" s="345"/>
+      <c r="J7" s="345"/>
+      <c r="K7" s="345"/>
+      <c r="L7" s="345"/>
+      <c r="M7" s="345"/>
+      <c r="N7" s="345"/>
+      <c r="O7" s="346"/>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="326"/>
-      <c r="D8" s="327"/>
-      <c r="E8" s="327"/>
-      <c r="F8" s="327"/>
-      <c r="G8" s="327"/>
-      <c r="H8" s="327"/>
-      <c r="I8" s="327"/>
-      <c r="J8" s="327"/>
-      <c r="K8" s="327"/>
-      <c r="L8" s="327"/>
-      <c r="M8" s="327"/>
-      <c r="N8" s="327"/>
-      <c r="O8" s="328"/>
+      <c r="C8" s="347"/>
+      <c r="D8" s="348"/>
+      <c r="E8" s="348"/>
+      <c r="F8" s="348"/>
+      <c r="G8" s="348"/>
+      <c r="H8" s="348"/>
+      <c r="I8" s="348"/>
+      <c r="J8" s="348"/>
+      <c r="K8" s="348"/>
+      <c r="L8" s="348"/>
+      <c r="M8" s="348"/>
+      <c r="N8" s="348"/>
+      <c r="O8" s="349"/>
       <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="329" t="s">
+      <c r="C9" s="350" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="330"/>
-      <c r="E9" s="330"/>
-      <c r="F9" s="330"/>
-      <c r="G9" s="330"/>
-      <c r="H9" s="330"/>
-      <c r="I9" s="330"/>
-      <c r="J9" s="330"/>
-      <c r="K9" s="330"/>
-      <c r="L9" s="330"/>
-      <c r="M9" s="330"/>
-      <c r="N9" s="330"/>
-      <c r="O9" s="331"/>
+      <c r="D9" s="351"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
+      <c r="G9" s="351"/>
+      <c r="H9" s="351"/>
+      <c r="I9" s="351"/>
+      <c r="J9" s="351"/>
+      <c r="K9" s="351"/>
+      <c r="L9" s="351"/>
+      <c r="M9" s="351"/>
+      <c r="N9" s="351"/>
+      <c r="O9" s="352"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
       <c r="R9" s="32">
-        <f>RESUMEN!F78</f>
-        <v>115202.766348</v>
+        <f>RESUMEN!F76</f>
+        <v>199021.59712799999</v>
       </c>
     </row>
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="332"/>
-      <c r="D10" s="333"/>
-      <c r="E10" s="333"/>
-      <c r="F10" s="333"/>
-      <c r="G10" s="333"/>
-      <c r="H10" s="333"/>
-      <c r="I10" s="333"/>
-      <c r="J10" s="333"/>
-      <c r="K10" s="333"/>
-      <c r="L10" s="333"/>
-      <c r="M10" s="333"/>
-      <c r="N10" s="333"/>
-      <c r="O10" s="334"/>
+      <c r="C10" s="353"/>
+      <c r="D10" s="354"/>
+      <c r="E10" s="354"/>
+      <c r="F10" s="354"/>
+      <c r="G10" s="354"/>
+      <c r="H10" s="354"/>
+      <c r="I10" s="354"/>
+      <c r="J10" s="354"/>
+      <c r="K10" s="354"/>
+      <c r="L10" s="354"/>
+      <c r="M10" s="354"/>
+      <c r="N10" s="354"/>
+      <c r="O10" s="355"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
       <c r="R10" s="32">
-        <f>RESUMEN!G78</f>
-        <v>136536.61196800001</v>
+        <f>RESUMEN!G76</f>
+        <v>235877.44844800004</v>
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="304" t="s">
+      <c r="A11" s="325" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="306" t="s">
+      <c r="B11" s="327" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="304" t="s">
+      <c r="C11" s="325" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="308" t="s">
+      <c r="D11" s="329" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="308" t="s">
+      <c r="E11" s="329" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="304" t="s">
+      <c r="F11" s="325" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="304" t="s">
+      <c r="G11" s="325" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="304" t="s">
+      <c r="H11" s="325" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="315" t="s">
+      <c r="I11" s="336" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="301" t="s">
+      <c r="J11" s="322" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="301" t="s">
+      <c r="K11" s="322" t="s">
         <v>372</v>
       </c>
-      <c r="L11" s="301" t="s">
+      <c r="L11" s="322" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="317" t="s">
+      <c r="M11" s="338" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="301" t="s">
+      <c r="N11" s="322" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="301" t="s">
+      <c r="O11" s="322" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
         <v>237</v>
       </c>
       <c r="R11" s="32">
-        <f>RESUMEN!H78</f>
-        <v>129069.766001</v>
+        <f>RESUMEN!H76</f>
+        <v>222977.900486</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="305"/>
-      <c r="B12" s="307"/>
-      <c r="C12" s="305"/>
-      <c r="D12" s="309"/>
-      <c r="E12" s="309"/>
-      <c r="F12" s="305"/>
-      <c r="G12" s="305"/>
-      <c r="H12" s="305"/>
-      <c r="I12" s="316"/>
-      <c r="J12" s="302"/>
-      <c r="K12" s="302"/>
-      <c r="L12" s="302"/>
-      <c r="M12" s="318"/>
-      <c r="N12" s="302"/>
-      <c r="O12" s="302"/>
+      <c r="A12" s="326"/>
+      <c r="B12" s="328"/>
+      <c r="C12" s="326"/>
+      <c r="D12" s="330"/>
+      <c r="E12" s="330"/>
+      <c r="F12" s="326"/>
+      <c r="G12" s="326"/>
+      <c r="H12" s="326"/>
+      <c r="I12" s="337"/>
+      <c r="J12" s="323"/>
+      <c r="K12" s="323"/>
+      <c r="L12" s="323"/>
+      <c r="M12" s="339"/>
+      <c r="N12" s="323"/>
+      <c r="O12" s="323"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
       <c r="R12" s="32">
-        <f>RESUMEN!I78</f>
-        <v>158937.14986900002</v>
+        <f>RESUMEN!I76</f>
+        <v>274576.09233400004</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="305"/>
-      <c r="B13" s="307"/>
-      <c r="C13" s="305"/>
-      <c r="D13" s="309"/>
-      <c r="E13" s="309"/>
-      <c r="F13" s="305"/>
-      <c r="G13" s="305"/>
-      <c r="H13" s="305"/>
-      <c r="I13" s="316"/>
-      <c r="J13" s="302"/>
-      <c r="K13" s="303"/>
-      <c r="L13" s="303"/>
-      <c r="M13" s="318"/>
+      <c r="A13" s="326"/>
+      <c r="B13" s="328"/>
+      <c r="C13" s="326"/>
+      <c r="D13" s="330"/>
+      <c r="E13" s="330"/>
+      <c r="F13" s="326"/>
+      <c r="G13" s="326"/>
+      <c r="H13" s="326"/>
+      <c r="I13" s="337"/>
+      <c r="J13" s="323"/>
+      <c r="K13" s="324"/>
+      <c r="L13" s="324"/>
+      <c r="M13" s="339"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/07</v>
@@ -5843,8 +5883,8 @@
         <v>239</v>
       </c>
       <c r="R13" s="32">
-        <f>RESUMEN!J78</f>
-        <v>185604.456894</v>
+        <f>RESUMEN!J76</f>
+        <v>320645.90648399998</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -5867,7 +5907,7 @@
       <c r="G14" s="106">
         <v>267664.59544800007</v>
       </c>
-      <c r="H14" s="275">
+      <c r="H14" s="33">
         <f>61415+206250</f>
         <v>267665</v>
       </c>
@@ -5880,27 +5920,27 @@
       </c>
       <c r="K14" s="151">
         <f>N$3*F14</f>
-        <v>0</v>
+        <v>64868.018400000001</v>
       </c>
       <c r="L14" s="112">
-        <v>206250.11834400002</v>
+        <v>199021.59712799999</v>
       </c>
       <c r="M14" s="134">
         <v>0</v>
       </c>
       <c r="N14" s="113">
         <f>L14+J14+I14+M14+K14</f>
-        <v>206249.71379200008</v>
+        <v>263889.21097600006</v>
       </c>
       <c r="O14" s="114">
         <f>N14*6% + N14</f>
-        <v>218624.69661952008</v>
+        <v>279722.56363456004</v>
       </c>
       <c r="P14" s="85" t="s">
         <v>348</v>
       </c>
-      <c r="R14" s="310"/>
-      <c r="S14" s="310"/>
+      <c r="R14" s="331"/>
+      <c r="S14" s="331"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
@@ -5918,37 +5958,39 @@
       <c r="G15" s="106">
         <v>209690.989172</v>
       </c>
-      <c r="H15" s="33"/>
+      <c r="H15" s="281">
+        <v>94985.93</v>
+      </c>
       <c r="I15" s="111">
         <f t="shared" ref="I15:I131" si="0">G15-H15</f>
-        <v>209690.989172</v>
+        <v>114705.05917200001</v>
       </c>
       <c r="J15" s="112">
         <v>0</v>
       </c>
       <c r="K15" s="151">
         <f t="shared" ref="K15:K18" si="1">N$3*F15</f>
-        <v>0</v>
+        <v>78081.873999999996</v>
       </c>
       <c r="L15" s="112">
-        <v>244444.58470400001</v>
+        <v>235877.44844800004</v>
       </c>
       <c r="M15" s="134">
         <v>0</v>
       </c>
       <c r="N15" s="113">
         <f t="shared" ref="N15:N18" si="2">L15+J15+I15+M15+K15</f>
-        <v>454135.57387600001</v>
+        <v>428664.38162000006</v>
       </c>
       <c r="O15" s="114">
         <f t="shared" ref="O15:O18" si="3">N15*6% + N15</f>
-        <v>481383.70830856002</v>
+        <v>454384.24451720004</v>
       </c>
       <c r="P15" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="R15" s="310"/>
-      <c r="S15" s="310"/>
+      <c r="R15" s="331"/>
+      <c r="S15" s="331"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -5970,7 +6012,7 @@
       <c r="G16" s="157">
         <v>231075.87082600006</v>
       </c>
-      <c r="H16" s="275">
+      <c r="H16" s="33">
         <f>G16</f>
         <v>231075.87082600006</v>
       </c>
@@ -5983,21 +6025,21 @@
       </c>
       <c r="K16" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>72676.205799999996</v>
       </c>
       <c r="L16" s="112">
-        <v>231076.52147800004</v>
+        <v>222977.900486</v>
       </c>
       <c r="M16" s="134">
         <v>0</v>
       </c>
       <c r="N16" s="113">
         <f t="shared" si="2"/>
-        <v>231076.52147800004</v>
+        <v>295654.10628599999</v>
       </c>
       <c r="O16" s="114">
         <f t="shared" si="3"/>
-        <v>244941.11276668005</v>
+        <v>313393.35266316001</v>
       </c>
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
@@ -6030,21 +6072,21 @@
       </c>
       <c r="K17" s="151">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>89493.840200000006</v>
       </c>
       <c r="L17" s="112">
-        <v>284548.77438200003</v>
+        <v>274576.09233400004</v>
       </c>
       <c r="M17" s="134">
         <v>0</v>
       </c>
       <c r="N17" s="113">
         <f t="shared" si="2"/>
-        <v>569097.8440563801</v>
+        <v>648619.00220838003</v>
       </c>
       <c r="O17" s="114">
         <f t="shared" si="3"/>
-        <v>603243.71469976287</v>
+        <v>687536.1423408828</v>
       </c>
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
@@ -6077,21 +6119,21 @@
       </c>
       <c r="K18" s="120">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>104509.58519999999</v>
       </c>
       <c r="L18" s="120">
-        <v>332291.85733199993</v>
+        <v>320645.90648399998</v>
       </c>
       <c r="M18" s="159">
         <v>0</v>
       </c>
       <c r="N18" s="113">
         <f t="shared" si="2"/>
-        <v>957145.22429799975</v>
+        <v>1050008.8586499998</v>
       </c>
       <c r="O18" s="122">
         <f t="shared" si="3"/>
-        <v>1014573.9377558797</v>
+        <v>1113009.3901689998</v>
       </c>
       <c r="P18" s="85"/>
       <c r="S18" s="32"/>
@@ -6114,7 +6156,7 @@
       <c r="G19" s="149">
         <v>282000.01</v>
       </c>
-      <c r="H19" s="370">
+      <c r="H19" s="204">
         <f>G19</f>
         <v>282000.01</v>
       </c>
@@ -6128,22 +6170,22 @@
       </c>
       <c r="K19" s="151">
         <f>N$3*F19</f>
-        <v>0</v>
+        <v>112918.40240000001</v>
       </c>
       <c r="L19" s="151">
         <f>N$2*F19</f>
-        <v>282000</v>
+        <v>268387.96151999995</v>
       </c>
       <c r="M19" s="158">
         <v>0</v>
       </c>
       <c r="N19" s="152">
         <f>ROUND((L19+J19+I19+K19+M19),0) + P19</f>
-        <v>282000.01</v>
+        <v>381306.01</v>
       </c>
       <c r="O19" s="152">
         <f>ROUND((N19*6% + N19 ),0) + P19</f>
-        <v>298920.01</v>
+        <v>404184.01</v>
       </c>
       <c r="P19" s="102">
         <v>0.01</v>
@@ -6168,7 +6210,7 @@
       <c r="G20" s="106">
         <v>126000.02</v>
       </c>
-      <c r="H20" s="275">
+      <c r="H20" s="33">
         <f>G20</f>
         <v>126000.02</v>
       </c>
@@ -6182,22 +6224,22 @@
       </c>
       <c r="K20" s="151">
         <f t="shared" ref="K20:K83" si="5">N$3*F20</f>
-        <v>0</v>
+        <v>50452.903199999993</v>
       </c>
       <c r="L20" s="112">
         <f t="shared" ref="L20:L50" si="6">N$2*F20</f>
-        <v>125999.99999999999</v>
+        <v>119918.02535999999</v>
       </c>
       <c r="M20" s="158">
         <v>0</v>
       </c>
       <c r="N20" s="152">
         <f t="shared" ref="N20:N83" si="7">ROUND((L20+J20+I20+K20+M20),0) + P20</f>
-        <v>126000.02</v>
+        <v>170371.02</v>
       </c>
       <c r="O20" s="114">
         <f t="shared" ref="O20:O83" si="8">ROUND((N20*6% + N20 ),0) + P20</f>
-        <v>133560.01999999999</v>
+        <v>180593.02</v>
       </c>
       <c r="P20" s="102">
         <f>P19+0.01</f>
@@ -6223,7 +6265,7 @@
       <c r="G21" s="106">
         <v>319590.03000000003</v>
       </c>
-      <c r="H21" s="275">
+      <c r="H21" s="33">
         <v>440747.03</v>
       </c>
       <c r="I21" s="111">
@@ -6236,22 +6278,22 @@
       </c>
       <c r="K21" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>120726.5898</v>
       </c>
       <c r="L21" s="112">
         <f t="shared" si="6"/>
-        <v>301500</v>
+        <v>286946.70353999996</v>
       </c>
       <c r="M21" s="158">
         <v>0</v>
       </c>
       <c r="N21" s="152">
         <f t="shared" si="7"/>
-        <v>180343.03</v>
+        <v>286516.03000000003</v>
       </c>
       <c r="O21" s="114">
         <f t="shared" si="8"/>
-        <v>191164.03</v>
+        <v>303707.03000000003</v>
       </c>
       <c r="P21" s="102">
         <f t="shared" ref="P21:P84" si="9">P20+0.01</f>
@@ -6278,7 +6320,7 @@
       <c r="G22" s="106">
         <v>87547.04</v>
       </c>
-      <c r="H22" s="275">
+      <c r="H22" s="33">
         <v>141000</v>
       </c>
       <c r="I22" s="111">
@@ -6291,22 +6333,22 @@
       </c>
       <c r="K22" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L22" s="112">
         <f t="shared" si="6"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M22" s="158">
         <v>0</v>
       </c>
       <c r="N22" s="152">
         <f t="shared" si="7"/>
-        <v>87547.04</v>
+        <v>137200.04</v>
       </c>
       <c r="O22" s="114">
         <f t="shared" si="8"/>
-        <v>92800.04</v>
+        <v>145432.04</v>
       </c>
       <c r="P22" s="102">
         <f t="shared" si="9"/>
@@ -6336,7 +6378,7 @@
       <c r="G23" s="106">
         <v>130500.05</v>
       </c>
-      <c r="H23" s="275">
+      <c r="H23" s="33">
         <f>G23+49473.05</f>
         <v>179973.1</v>
       </c>
@@ -6350,22 +6392,22 @@
       </c>
       <c r="K23" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L23" s="112">
         <f t="shared" si="6"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M23" s="158">
         <v>0</v>
       </c>
       <c r="N23" s="152">
         <f t="shared" si="7"/>
-        <v>81027.05</v>
+        <v>126983.05</v>
       </c>
       <c r="O23" s="114">
         <f t="shared" si="8"/>
-        <v>85889.05</v>
+        <v>134602.04999999999</v>
       </c>
       <c r="P23" s="102">
         <f t="shared" si="9"/>
@@ -6392,7 +6434,7 @@
       <c r="G24" s="106">
         <v>74883.06</v>
       </c>
-      <c r="H24" s="275">
+      <c r="H24" s="33">
         <f>G24-33595.06</f>
         <v>41288</v>
       </c>
@@ -6406,22 +6448,22 @@
       </c>
       <c r="K24" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L24" s="112">
         <f t="shared" si="6"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M24" s="158">
         <v>0</v>
       </c>
       <c r="N24" s="152">
         <f t="shared" si="7"/>
-        <v>176095.06</v>
+        <v>226276.06</v>
       </c>
       <c r="O24" s="114">
         <f t="shared" si="8"/>
-        <v>186661.06</v>
+        <v>239853.06</v>
       </c>
       <c r="P24" s="102">
         <f t="shared" si="9"/>
@@ -6448,7 +6490,7 @@
       <c r="G25" s="106">
         <v>184093.07</v>
       </c>
-      <c r="H25" s="275">
+      <c r="H25" s="33">
         <f>G25</f>
         <v>184093.07</v>
       </c>
@@ -6462,22 +6504,22 @@
       </c>
       <c r="K25" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>99103.917000000001</v>
       </c>
       <c r="L25" s="112">
         <f t="shared" si="6"/>
-        <v>247500</v>
+        <v>235553.2641</v>
       </c>
       <c r="M25" s="158">
         <v>0</v>
       </c>
       <c r="N25" s="152">
         <f t="shared" si="7"/>
-        <v>247500.07</v>
+        <v>334657.07</v>
       </c>
       <c r="O25" s="114">
         <f t="shared" si="8"/>
-        <v>262350.07</v>
+        <v>354736.07</v>
       </c>
       <c r="P25" s="102">
         <f t="shared" si="9"/>
@@ -6502,7 +6544,7 @@
       <c r="G26" s="106">
         <v>109500.08</v>
       </c>
-      <c r="H26" s="275">
+      <c r="H26" s="33">
         <f>G26</f>
         <v>109500.08</v>
       </c>
@@ -6516,22 +6558,22 @@
       </c>
       <c r="K26" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43845.975400000003</v>
       </c>
       <c r="L26" s="112">
         <f t="shared" si="6"/>
-        <v>109500</v>
+        <v>104214.47441999998</v>
       </c>
       <c r="M26" s="158">
         <v>40000</v>
       </c>
       <c r="N26" s="152">
         <f t="shared" si="7"/>
-        <v>149500.07999999999</v>
+        <v>188060.08</v>
       </c>
       <c r="O26" s="114">
         <f t="shared" si="8"/>
-        <v>158470.07999999999</v>
+        <v>199344.08</v>
       </c>
       <c r="P26" s="102">
         <f t="shared" si="9"/>
@@ -6558,7 +6600,7 @@
       <c r="G27" s="106">
         <v>438595.09</v>
       </c>
-      <c r="H27" s="275">
+      <c r="H27" s="33">
         <v>464911.09</v>
       </c>
       <c r="I27" s="111">
@@ -6571,22 +6613,22 @@
       </c>
       <c r="K27" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>106912.1044</v>
       </c>
       <c r="L27" s="112">
         <f t="shared" si="6"/>
-        <v>267000</v>
+        <v>254112.00611999998</v>
       </c>
       <c r="M27" s="158">
         <v>0</v>
       </c>
       <c r="N27" s="152">
         <f t="shared" si="7"/>
-        <v>240684.09</v>
+        <v>334708.09000000003</v>
       </c>
       <c r="O27" s="114">
         <f t="shared" si="8"/>
-        <v>255125.09</v>
+        <v>354791.09</v>
       </c>
       <c r="P27" s="102">
         <f t="shared" si="9"/>
@@ -6611,7 +6653,7 @@
       <c r="G28" s="33">
         <v>141000.1</v>
       </c>
-      <c r="H28" s="275">
+      <c r="H28" s="33">
         <f>G28</f>
         <v>141000.1</v>
       </c>
@@ -6625,22 +6667,22 @@
       </c>
       <c r="K28" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L28" s="112">
         <f t="shared" si="6"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M28" s="158">
         <v>0</v>
       </c>
       <c r="N28" s="152">
         <f t="shared" si="7"/>
-        <v>141000.1</v>
+        <v>190653.1</v>
       </c>
       <c r="O28" s="114">
         <f t="shared" si="8"/>
-        <v>149460.1</v>
+        <v>202092.1</v>
       </c>
       <c r="P28" s="102">
         <f t="shared" si="9"/>
@@ -6665,7 +6707,7 @@
       <c r="G29" s="106">
         <v>130500.11</v>
       </c>
-      <c r="H29" s="275">
+      <c r="H29" s="33">
         <f>G29</f>
         <v>130500.11</v>
       </c>
@@ -6679,22 +6721,22 @@
       </c>
       <c r="K29" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L29" s="112">
         <f t="shared" si="6"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M29" s="158">
         <v>0</v>
       </c>
       <c r="N29" s="152">
         <f t="shared" si="7"/>
-        <v>130500.11</v>
+        <v>176456.11</v>
       </c>
       <c r="O29" s="114">
         <f t="shared" si="8"/>
-        <v>138330.10999999999</v>
+        <v>187043.11</v>
       </c>
       <c r="P29" s="102">
         <f t="shared" si="9"/>
@@ -6730,11 +6772,11 @@
       </c>
       <c r="K30" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L30" s="112">
         <f t="shared" si="6"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M30" s="158">
         <f>99500+24000</f>
@@ -6742,11 +6784,11 @@
       </c>
       <c r="N30" s="152">
         <f t="shared" si="7"/>
-        <v>1680368.12</v>
+        <v>1730550.12</v>
       </c>
       <c r="O30" s="114">
         <f t="shared" si="8"/>
-        <v>1781190.12</v>
+        <v>1834383.12</v>
       </c>
       <c r="P30" s="102">
         <f t="shared" si="9"/>
@@ -6771,7 +6813,7 @@
       <c r="G31" s="106">
         <v>246000.13</v>
       </c>
-      <c r="H31" s="275">
+      <c r="H31" s="33">
         <f>G31</f>
         <v>246000.13</v>
       </c>
@@ -6785,22 +6827,22 @@
       </c>
       <c r="K31" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L31" s="112">
         <f t="shared" si="6"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M31" s="158">
         <v>0</v>
       </c>
       <c r="N31" s="152">
         <f t="shared" si="7"/>
-        <v>246000.13</v>
+        <v>332629.13</v>
       </c>
       <c r="O31" s="114">
         <f t="shared" si="8"/>
-        <v>260760.13</v>
+        <v>352587.13</v>
       </c>
       <c r="P31" s="102">
         <f t="shared" si="9"/>
@@ -6827,7 +6869,7 @@
       <c r="G32" s="106">
         <v>108000.14</v>
       </c>
-      <c r="H32" s="275">
+      <c r="H32" s="33">
         <f>G32</f>
         <v>108000.14</v>
       </c>
@@ -6841,22 +6883,22 @@
       </c>
       <c r="K32" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L32" s="112">
         <f t="shared" si="6"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M32" s="158">
         <v>0</v>
       </c>
       <c r="N32" s="152">
         <f t="shared" si="7"/>
-        <v>108000.14</v>
+        <v>146032.14000000001</v>
       </c>
       <c r="O32" s="114">
         <f t="shared" si="8"/>
-        <v>114480.14</v>
+        <v>154794.14000000001</v>
       </c>
       <c r="P32" s="102">
         <f t="shared" si="9"/>
@@ -6881,7 +6923,7 @@
       <c r="G33" s="106">
         <v>195870.15</v>
       </c>
-      <c r="H33" s="275">
+      <c r="H33" s="33">
         <f>G33</f>
         <v>195870.15</v>
       </c>
@@ -6895,22 +6937,22 @@
       </c>
       <c r="K33" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L33" s="112">
         <f t="shared" si="6"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M33" s="158">
         <v>0</v>
       </c>
       <c r="N33" s="152">
         <f t="shared" si="7"/>
-        <v>259500.15</v>
+        <v>350883.15</v>
       </c>
       <c r="O33" s="114">
         <f t="shared" si="8"/>
-        <v>275070.15000000002</v>
+        <v>371936.15</v>
       </c>
       <c r="P33" s="102">
         <f t="shared" si="9"/>
@@ -6935,7 +6977,7 @@
       <c r="G34" s="106">
         <v>141000.16</v>
       </c>
-      <c r="H34" s="275">
+      <c r="H34" s="33">
         <v>194453.16</v>
       </c>
       <c r="I34" s="111">
@@ -6948,22 +6990,22 @@
       </c>
       <c r="K34" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L34" s="112">
         <f t="shared" si="6"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M34" s="158">
         <v>0</v>
       </c>
       <c r="N34" s="152">
         <f t="shared" si="7"/>
-        <v>87547.16</v>
+        <v>137200.16</v>
       </c>
       <c r="O34" s="114">
         <f t="shared" si="8"/>
-        <v>92800.16</v>
+        <v>145432.16</v>
       </c>
       <c r="P34" s="102">
         <f t="shared" si="9"/>
@@ -6993,7 +7035,7 @@
       <c r="G35" s="106">
         <v>179973.17</v>
       </c>
-      <c r="H35" s="275">
+      <c r="H35" s="33">
         <f>49473+130500.17</f>
         <v>179973.16999999998</v>
       </c>
@@ -7007,22 +7049,22 @@
       </c>
       <c r="K35" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L35" s="112">
         <f t="shared" si="6"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M35" s="158">
         <v>0</v>
       </c>
       <c r="N35" s="152">
         <f t="shared" si="7"/>
-        <v>130500.17</v>
+        <v>176456.17</v>
       </c>
       <c r="O35" s="114">
         <f t="shared" si="8"/>
-        <v>138330.17000000001</v>
+        <v>187044.17</v>
       </c>
       <c r="P35" s="102">
         <f t="shared" si="9"/>
@@ -7058,11 +7100,11 @@
       </c>
       <c r="K36" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L36" s="112">
         <f t="shared" si="6"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M36" s="158">
         <f>99500+24000</f>
@@ -7070,11 +7112,11 @@
       </c>
       <c r="N36" s="152">
         <f t="shared" si="7"/>
-        <v>1162617.18</v>
+        <v>1212799.18</v>
       </c>
       <c r="O36" s="114">
         <f t="shared" si="8"/>
-        <v>1232374.18</v>
+        <v>1285567.18</v>
       </c>
       <c r="P36" s="102">
         <f t="shared" si="9"/>
@@ -7101,7 +7143,7 @@
       <c r="G37" s="106">
         <v>246000.19</v>
       </c>
-      <c r="H37" s="275">
+      <c r="H37" s="33">
         <f t="shared" ref="H37" si="10">G37</f>
         <v>246000.19</v>
       </c>
@@ -7115,22 +7157,22 @@
       </c>
       <c r="K37" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L37" s="112">
         <f t="shared" si="6"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M37" s="158">
         <v>0</v>
       </c>
       <c r="N37" s="152">
         <f t="shared" si="7"/>
-        <v>246000.19</v>
+        <v>332629.19</v>
       </c>
       <c r="O37" s="114">
         <f t="shared" si="8"/>
-        <v>260760.19</v>
+        <v>352587.19</v>
       </c>
       <c r="P37" s="102">
         <f t="shared" si="9"/>
@@ -7158,7 +7200,7 @@
       <c r="G38" s="106">
         <v>108000.2</v>
       </c>
-      <c r="H38" s="275">
+      <c r="H38" s="33">
         <f>G38</f>
         <v>108000.2</v>
       </c>
@@ -7172,22 +7214,22 @@
       </c>
       <c r="K38" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L38" s="112">
         <f t="shared" si="6"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M38" s="158">
         <v>0</v>
       </c>
       <c r="N38" s="152">
         <f t="shared" si="7"/>
-        <v>108000.2</v>
+        <v>146032.20000000001</v>
       </c>
       <c r="O38" s="114">
         <f t="shared" si="8"/>
-        <v>114480.2</v>
+        <v>154794.20000000001</v>
       </c>
       <c r="P38" s="102">
         <f t="shared" si="9"/>
@@ -7212,7 +7254,7 @@
       <c r="G39" s="106">
         <v>279500.21000000002</v>
       </c>
-      <c r="H39" s="275">
+      <c r="H39" s="33">
         <f>G39</f>
         <v>279500.21000000002</v>
       </c>
@@ -7226,22 +7268,22 @@
       </c>
       <c r="K39" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L39" s="112">
         <f t="shared" si="6"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M39" s="158">
         <v>0</v>
       </c>
       <c r="N39" s="152">
         <f t="shared" si="7"/>
-        <v>259500.21</v>
+        <v>350883.21</v>
       </c>
       <c r="O39" s="114">
         <f t="shared" si="8"/>
-        <v>275070.21000000002</v>
+        <v>371936.21</v>
       </c>
       <c r="P39" s="138">
         <f t="shared" si="9"/>
@@ -7364,7 +7406,7 @@
       <c r="G40" s="33">
         <v>960814.22</v>
       </c>
-      <c r="H40" s="275">
+      <c r="H40" s="33">
         <f>G40</f>
         <v>960814.22</v>
       </c>
@@ -7378,22 +7420,22 @@
       </c>
       <c r="K40" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L40" s="112">
         <f t="shared" si="6"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M40" s="158">
         <v>0</v>
       </c>
       <c r="N40" s="152">
         <f t="shared" si="7"/>
-        <v>141000.22</v>
+        <v>190653.22</v>
       </c>
       <c r="O40" s="114">
         <f t="shared" si="8"/>
-        <v>149460.22</v>
+        <v>202092.22</v>
       </c>
       <c r="P40" s="138">
         <f t="shared" si="9"/>
@@ -7518,7 +7560,7 @@
       <c r="G41" s="106">
         <v>130500.23</v>
       </c>
-      <c r="H41" s="275">
+      <c r="H41" s="33">
         <f>G41</f>
         <v>130500.23</v>
       </c>
@@ -7532,22 +7574,22 @@
       </c>
       <c r="K41" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L41" s="112">
         <f t="shared" si="6"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M41" s="158">
         <v>0</v>
       </c>
       <c r="N41" s="152">
         <f t="shared" si="7"/>
-        <v>130500.23</v>
+        <v>176456.23</v>
       </c>
       <c r="O41" s="114">
         <f t="shared" si="8"/>
-        <v>138330.23000000001</v>
+        <v>187044.23</v>
       </c>
       <c r="P41" s="138">
         <f t="shared" si="9"/>
@@ -7685,11 +7727,11 @@
       </c>
       <c r="K42" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L42" s="112">
         <f t="shared" si="6"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M42" s="158">
         <f>99500+24000</f>
@@ -7697,11 +7739,11 @@
       </c>
       <c r="N42" s="152">
         <f t="shared" si="7"/>
-        <v>907837.24</v>
+        <v>958019.24</v>
       </c>
       <c r="O42" s="114">
         <f t="shared" si="8"/>
-        <v>962307.24</v>
+        <v>1015500.24</v>
       </c>
       <c r="P42" s="138">
         <f t="shared" si="9"/>
@@ -7824,7 +7866,7 @@
       <c r="G43" s="106">
         <v>246000.25</v>
       </c>
-      <c r="H43" s="275">
+      <c r="H43" s="33">
         <v>339259.25</v>
       </c>
       <c r="I43" s="111">
@@ -7837,22 +7879,22 @@
       </c>
       <c r="K43" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L43" s="112">
         <f t="shared" si="6"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M43" s="158">
         <v>0</v>
       </c>
       <c r="N43" s="152">
         <f t="shared" si="7"/>
-        <v>152741.25</v>
+        <v>239370.25</v>
       </c>
       <c r="O43" s="114">
         <f t="shared" si="8"/>
-        <v>161906.25</v>
+        <v>253732.25</v>
       </c>
       <c r="P43" s="102">
         <f t="shared" si="9"/>
@@ -7879,7 +7921,7 @@
       <c r="G44" s="106">
         <v>108000.26</v>
       </c>
-      <c r="H44" s="275">
+      <c r="H44" s="33">
         <f>G44</f>
         <v>108000.26</v>
       </c>
@@ -7893,22 +7935,22 @@
       </c>
       <c r="K44" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L44" s="112">
         <f t="shared" si="6"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M44" s="158">
         <v>0</v>
       </c>
       <c r="N44" s="152">
         <f t="shared" si="7"/>
-        <v>108000.26</v>
+        <v>146032.26</v>
       </c>
       <c r="O44" s="114">
         <f t="shared" si="8"/>
-        <v>114480.26</v>
+        <v>154794.26</v>
       </c>
       <c r="P44" s="102">
         <f t="shared" si="9"/>
@@ -7933,7 +7975,7 @@
       <c r="G45" s="106">
         <v>259500.27</v>
       </c>
-      <c r="H45" s="275">
+      <c r="H45" s="33">
         <f>G45</f>
         <v>259500.27</v>
       </c>
@@ -7947,22 +7989,22 @@
       </c>
       <c r="K45" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L45" s="112">
         <f t="shared" si="6"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M45" s="158">
-        <v>0</v>
+        <v>85744</v>
       </c>
       <c r="N45" s="152">
         <f t="shared" si="7"/>
-        <v>259500.27</v>
+        <v>436627.27</v>
       </c>
       <c r="O45" s="114">
         <f t="shared" si="8"/>
-        <v>275070.27</v>
+        <v>462825.27</v>
       </c>
       <c r="P45" s="102">
         <f t="shared" si="9"/>
@@ -7993,7 +8035,7 @@
       <c r="G46" s="106">
         <v>141000.28</v>
       </c>
-      <c r="H46" s="275">
+      <c r="H46" s="33">
         <f>194454.28</f>
         <v>194454.28</v>
       </c>
@@ -8007,22 +8049,22 @@
       </c>
       <c r="K46" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L46" s="112">
         <f t="shared" si="6"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M46" s="158">
         <v>0</v>
       </c>
       <c r="N46" s="152">
         <f t="shared" si="7"/>
-        <v>87546.28</v>
+        <v>137199.28</v>
       </c>
       <c r="O46" s="114">
         <f t="shared" si="8"/>
-        <v>92799.28</v>
+        <v>145431.28</v>
       </c>
       <c r="P46" s="102">
         <f t="shared" si="9"/>
@@ -8049,7 +8091,7 @@
       <c r="G47" s="114">
         <v>124717.29</v>
       </c>
-      <c r="H47" s="275">
+      <c r="H47" s="33">
         <f>174189.29</f>
         <v>174189.29</v>
       </c>
@@ -8063,22 +8105,22 @@
       </c>
       <c r="K47" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L47" s="112">
         <f t="shared" si="6"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M47" s="158">
         <v>0</v>
       </c>
       <c r="N47" s="152">
         <f t="shared" si="7"/>
-        <v>81028.289999999994</v>
+        <v>126984.29</v>
       </c>
       <c r="O47" s="114">
         <f t="shared" si="8"/>
-        <v>85890.29</v>
+        <v>134603.29</v>
       </c>
       <c r="P47" s="102">
         <f t="shared" si="9"/>
@@ -8103,7 +8145,7 @@
       <c r="G48" s="106">
         <v>142500.29999999999</v>
       </c>
-      <c r="H48" s="275">
+      <c r="H48" s="33">
         <f>196522.3</f>
         <v>196522.3</v>
       </c>
@@ -8117,22 +8159,22 @@
       </c>
       <c r="K48" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L48" s="112">
         <f t="shared" si="6"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M48" s="158">
         <v>0</v>
       </c>
       <c r="N48" s="152">
         <f t="shared" si="7"/>
-        <v>88478.3</v>
+        <v>138659.29999999999</v>
       </c>
       <c r="O48" s="114">
         <f t="shared" si="8"/>
-        <v>93787.3</v>
+        <v>146979.29999999999</v>
       </c>
       <c r="P48" s="102">
         <f t="shared" si="9"/>
@@ -8157,7 +8199,7 @@
       <c r="G49" s="106">
         <v>246000.31</v>
       </c>
-      <c r="H49" s="275">
+      <c r="H49" s="33">
         <f>G49</f>
         <v>246000.31</v>
       </c>
@@ -8171,22 +8213,22 @@
       </c>
       <c r="K49" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L49" s="112">
         <f t="shared" si="6"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M49" s="158">
         <v>0</v>
       </c>
       <c r="N49" s="152">
         <f t="shared" si="7"/>
-        <v>246000.31</v>
+        <v>332629.31</v>
       </c>
       <c r="O49" s="114">
         <f t="shared" si="8"/>
-        <v>260760.31</v>
+        <v>352587.31</v>
       </c>
       <c r="P49" s="102">
         <f t="shared" si="9"/>
@@ -8211,7 +8253,7 @@
       <c r="G50" s="106">
         <v>108000.32000000001</v>
       </c>
-      <c r="H50" s="275">
+      <c r="H50" s="33">
         <f>G50</f>
         <v>108000.32000000001</v>
       </c>
@@ -8225,22 +8267,22 @@
       </c>
       <c r="K50" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L50" s="112">
         <f t="shared" si="6"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M50" s="158">
         <v>0</v>
       </c>
       <c r="N50" s="152">
         <f t="shared" si="7"/>
-        <v>108000.32000000001</v>
+        <v>146032.32000000001</v>
       </c>
       <c r="O50" s="114">
         <f t="shared" si="8"/>
-        <v>114480.32000000001</v>
+        <v>154794.32</v>
       </c>
       <c r="P50" s="102">
         <f t="shared" si="9"/>
@@ -8266,8 +8308,8 @@
       <c r="G51" s="106">
         <v>259500.33</v>
       </c>
-      <c r="H51" s="275">
-        <f t="shared" ref="H50:H51" si="11">G51</f>
+      <c r="H51" s="33">
+        <f t="shared" ref="H51" si="11">G51</f>
         <v>259500.33</v>
       </c>
       <c r="I51" s="111">
@@ -8280,22 +8322,22 @@
       </c>
       <c r="K51" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L51" s="112">
         <f t="shared" ref="L51:L82" si="13">N$2*F51</f>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M51" s="158">
         <v>0</v>
       </c>
       <c r="N51" s="152">
         <f t="shared" si="7"/>
-        <v>259500.33</v>
+        <v>350883.33</v>
       </c>
       <c r="O51" s="114">
         <f t="shared" si="8"/>
-        <v>275070.33</v>
+        <v>371936.33</v>
       </c>
       <c r="P51" s="102">
         <f t="shared" si="9"/>
@@ -8323,7 +8365,7 @@
       <c r="G52" s="106">
         <v>194453.34</v>
       </c>
-      <c r="H52" s="275">
+      <c r="H52" s="33">
         <f>G52</f>
         <v>194453.34</v>
       </c>
@@ -8337,22 +8379,22 @@
       </c>
       <c r="K52" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L52" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M52" s="158">
         <v>0</v>
       </c>
       <c r="N52" s="152">
         <f t="shared" si="7"/>
-        <v>141000.34</v>
+        <v>190653.34</v>
       </c>
       <c r="O52" s="114">
         <f t="shared" si="8"/>
-        <v>149460.34</v>
+        <v>202093.34</v>
       </c>
       <c r="P52" s="102">
         <f t="shared" si="9"/>
@@ -8380,7 +8422,7 @@
       <c r="G53" s="106">
         <v>130500.35</v>
       </c>
-      <c r="H53" s="275">
+      <c r="H53" s="33">
         <f>179973.35</f>
         <v>179973.35</v>
       </c>
@@ -8394,22 +8436,22 @@
       </c>
       <c r="K53" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L53" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M53" s="158">
         <v>0</v>
       </c>
       <c r="N53" s="152">
         <f t="shared" si="7"/>
-        <v>81027.350000000006</v>
+        <v>126983.35</v>
       </c>
       <c r="O53" s="114">
         <f t="shared" si="8"/>
-        <v>85889.35</v>
+        <v>134602.35</v>
       </c>
       <c r="P53" s="102">
         <f t="shared" si="9"/>
@@ -8434,10 +8476,12 @@
       <c r="G54" s="106">
         <v>447075.36</v>
       </c>
-      <c r="H54" s="33"/>
+      <c r="H54" s="33">
+        <v>142500</v>
+      </c>
       <c r="I54" s="111">
         <f>G54-H54</f>
-        <v>447075.36</v>
+        <v>304575.35999999999</v>
       </c>
       <c r="J54" s="112">
         <f t="shared" si="12"/>
@@ -8445,22 +8489,22 @@
       </c>
       <c r="K54" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L54" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M54" s="158">
         <v>0</v>
       </c>
       <c r="N54" s="152">
         <f t="shared" si="7"/>
-        <v>589575.36</v>
+        <v>497257.36</v>
       </c>
       <c r="O54" s="114">
         <f t="shared" si="8"/>
-        <v>624950.36</v>
+        <v>527093.36</v>
       </c>
       <c r="P54" s="102">
         <f t="shared" si="9"/>
@@ -8485,7 +8529,7 @@
       <c r="G55" s="106">
         <v>246000.37</v>
       </c>
-      <c r="H55" s="275">
+      <c r="H55" s="33">
         <f>G55</f>
         <v>246000.37</v>
       </c>
@@ -8499,22 +8543,22 @@
       </c>
       <c r="K55" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L55" s="112">
         <f t="shared" si="13"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M55" s="158">
         <v>0</v>
       </c>
       <c r="N55" s="152">
         <f t="shared" si="7"/>
-        <v>246000.37</v>
+        <v>332629.37</v>
       </c>
       <c r="O55" s="114">
         <f t="shared" si="8"/>
-        <v>260760.37</v>
+        <v>352587.37</v>
       </c>
       <c r="P55" s="102">
         <f t="shared" si="9"/>
@@ -8542,7 +8586,7 @@
       <c r="G56" s="106">
         <v>108000.38</v>
       </c>
-      <c r="H56" s="275">
+      <c r="H56" s="33">
         <f t="shared" ref="H56" si="14">G56</f>
         <v>108000.38</v>
       </c>
@@ -8556,22 +8600,22 @@
       </c>
       <c r="K56" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L56" s="112">
         <f t="shared" si="13"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M56" s="158">
         <v>0</v>
       </c>
       <c r="N56" s="152">
         <f t="shared" si="7"/>
-        <v>108000.38</v>
+        <v>146032.38</v>
       </c>
       <c r="O56" s="114">
         <f t="shared" si="8"/>
-        <v>114480.38</v>
+        <v>154794.38</v>
       </c>
       <c r="P56" s="102">
         <f t="shared" si="9"/>
@@ -8596,7 +8640,7 @@
       <c r="G57" s="106">
         <v>259500.39</v>
       </c>
-      <c r="H57" s="275">
+      <c r="H57" s="33">
         <f>G57</f>
         <v>259500.39</v>
       </c>
@@ -8610,22 +8654,22 @@
       </c>
       <c r="K57" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L57" s="112">
         <f t="shared" si="13"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M57" s="158">
         <v>0</v>
       </c>
       <c r="N57" s="152">
         <f t="shared" si="7"/>
-        <v>259500.39</v>
+        <v>350883.39</v>
       </c>
       <c r="O57" s="114">
         <f t="shared" si="8"/>
-        <v>275070.39</v>
+        <v>371936.39</v>
       </c>
       <c r="P57" s="102">
         <f t="shared" si="9"/>
@@ -8652,7 +8696,7 @@
       <c r="G58" s="106">
         <v>347121.4</v>
       </c>
-      <c r="H58" s="275">
+      <c r="H58" s="33">
         <f>141000.4+206121</f>
         <v>347121.4</v>
       </c>
@@ -8666,22 +8710,22 @@
       </c>
       <c r="K58" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L58" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M58" s="158">
         <v>0</v>
       </c>
       <c r="N58" s="152">
         <f t="shared" si="7"/>
-        <v>141000.4</v>
+        <v>190653.4</v>
       </c>
       <c r="O58" s="114">
         <f t="shared" si="8"/>
-        <v>149460.4</v>
+        <v>202093.4</v>
       </c>
       <c r="P58" s="102">
         <f t="shared" si="9"/>
@@ -8706,7 +8750,7 @@
       <c r="G59" s="33">
         <v>130500.41</v>
       </c>
-      <c r="H59" s="275">
+      <c r="H59" s="33">
         <f>G59</f>
         <v>130500.41</v>
       </c>
@@ -8720,22 +8764,22 @@
       </c>
       <c r="K59" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L59" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M59" s="158">
         <v>0</v>
       </c>
       <c r="N59" s="152">
         <f t="shared" si="7"/>
-        <v>130500.41</v>
+        <v>176456.41</v>
       </c>
       <c r="O59" s="114">
         <f t="shared" si="8"/>
-        <v>138330.41</v>
+        <v>187044.41</v>
       </c>
       <c r="P59" s="102">
         <f t="shared" si="9"/>
@@ -8763,7 +8807,7 @@
       <c r="G60" s="106">
         <v>142500.42000000001</v>
       </c>
-      <c r="H60" s="275">
+      <c r="H60" s="33">
         <f>G60</f>
         <v>142500.42000000001</v>
       </c>
@@ -8777,22 +8821,22 @@
       </c>
       <c r="K60" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L60" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M60" s="158">
         <v>0</v>
       </c>
       <c r="N60" s="152">
         <f t="shared" si="7"/>
-        <v>142500.42000000001</v>
+        <v>192681.42</v>
       </c>
       <c r="O60" s="114">
         <f t="shared" si="8"/>
-        <v>151050.42000000001</v>
+        <v>204242.42</v>
       </c>
       <c r="P60" s="102">
         <f t="shared" si="9"/>
@@ -8820,7 +8864,7 @@
       <c r="G61" s="106">
         <v>266000.43</v>
       </c>
-      <c r="H61" s="275">
+      <c r="H61" s="33">
         <f>G61</f>
         <v>266000.43</v>
       </c>
@@ -8834,22 +8878,22 @@
       </c>
       <c r="K61" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L61" s="112">
         <f t="shared" si="13"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M61" s="158">
         <v>0</v>
       </c>
       <c r="N61" s="152">
         <f t="shared" si="7"/>
-        <v>246000.43</v>
+        <v>332629.43</v>
       </c>
       <c r="O61" s="114">
         <f t="shared" si="8"/>
-        <v>260760.43</v>
+        <v>352587.43</v>
       </c>
       <c r="P61" s="102">
         <f t="shared" si="9"/>
@@ -8874,7 +8918,7 @@
       <c r="G62" s="106">
         <v>108000.44</v>
       </c>
-      <c r="H62" s="275">
+      <c r="H62" s="33">
         <f>G62</f>
         <v>108000.44</v>
       </c>
@@ -8888,22 +8932,22 @@
       </c>
       <c r="K62" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L62" s="112">
         <f t="shared" si="13"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M62" s="158">
         <v>0</v>
       </c>
       <c r="N62" s="152">
         <f t="shared" si="7"/>
-        <v>108000.44</v>
+        <v>146032.44</v>
       </c>
       <c r="O62" s="114">
         <f t="shared" si="8"/>
-        <v>114480.44</v>
+        <v>154794.44</v>
       </c>
       <c r="P62" s="102">
         <f t="shared" si="9"/>
@@ -8928,7 +8972,7 @@
       <c r="G63" s="106">
         <v>280973.45</v>
       </c>
-      <c r="H63" s="275">
+      <c r="H63" s="33">
         <f>G63</f>
         <v>280973.45</v>
       </c>
@@ -8942,22 +8986,22 @@
       </c>
       <c r="K63" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L63" s="112">
         <f t="shared" si="13"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M63" s="158">
         <v>0</v>
       </c>
       <c r="N63" s="152">
         <f t="shared" si="7"/>
-        <v>259500.45</v>
+        <v>350883.45</v>
       </c>
       <c r="O63" s="114">
         <f t="shared" si="8"/>
-        <v>275070.45</v>
+        <v>371936.45</v>
       </c>
       <c r="P63" s="102">
         <f t="shared" si="9"/>
@@ -8984,7 +9028,7 @@
       <c r="G64" s="106">
         <v>162871.46</v>
       </c>
-      <c r="H64" s="275">
+      <c r="H64" s="33">
         <v>141000</v>
       </c>
       <c r="I64" s="111">
@@ -8997,22 +9041,22 @@
       </c>
       <c r="K64" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L64" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M64" s="158">
         <v>0</v>
       </c>
       <c r="N64" s="152">
         <f t="shared" si="7"/>
-        <v>162871.46</v>
+        <v>212525.46</v>
       </c>
       <c r="O64" s="114">
         <f t="shared" si="8"/>
-        <v>172644.46</v>
+        <v>225277.46</v>
       </c>
       <c r="P64" s="138">
         <f t="shared" si="9"/>
@@ -9037,7 +9081,7 @@
       <c r="G65" s="106">
         <v>130500.47</v>
       </c>
-      <c r="H65" s="275">
+      <c r="H65" s="33">
         <v>179973.47</v>
       </c>
       <c r="I65" s="111">
@@ -9050,22 +9094,22 @@
       </c>
       <c r="K65" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L65" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M65" s="158">
         <v>0</v>
       </c>
       <c r="N65" s="152">
         <f t="shared" si="7"/>
-        <v>81027.47</v>
+        <v>126983.47</v>
       </c>
       <c r="O65" s="114">
         <f t="shared" si="8"/>
-        <v>85889.47</v>
+        <v>134602.47</v>
       </c>
       <c r="P65" s="138">
         <f t="shared" si="9"/>
@@ -9090,7 +9134,7 @@
       <c r="G66" s="106">
         <v>196522.48</v>
       </c>
-      <c r="H66" s="275">
+      <c r="H66" s="33">
         <f>142500</f>
         <v>142500</v>
       </c>
@@ -9104,22 +9148,22 @@
       </c>
       <c r="K66" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L66" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M66" s="158">
         <v>0</v>
       </c>
       <c r="N66" s="152">
         <f t="shared" si="7"/>
-        <v>196522.48</v>
+        <v>246704.48</v>
       </c>
       <c r="O66" s="114">
         <f t="shared" si="8"/>
-        <v>208314.48</v>
+        <v>261507.48</v>
       </c>
       <c r="P66" s="138">
         <f t="shared" si="9"/>
@@ -9145,7 +9189,7 @@
       <c r="G67" s="106">
         <v>246000.49</v>
       </c>
-      <c r="H67" s="275">
+      <c r="H67" s="33">
         <f t="shared" ref="H67" si="15">G67</f>
         <v>246000.49</v>
       </c>
@@ -9159,22 +9203,22 @@
       </c>
       <c r="K67" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>98503.287200000006</v>
       </c>
       <c r="L67" s="112">
         <f t="shared" si="13"/>
-        <v>246000.00000000003</v>
+        <v>234125.66855999999</v>
       </c>
       <c r="M67" s="158">
         <v>0</v>
       </c>
       <c r="N67" s="152">
         <f t="shared" si="7"/>
-        <v>246000.49</v>
+        <v>332629.49</v>
       </c>
       <c r="O67" s="114">
         <f t="shared" si="8"/>
-        <v>260761.49</v>
+        <v>352587.49</v>
       </c>
       <c r="P67" s="102">
         <f t="shared" si="9"/>
@@ -9200,7 +9244,7 @@
       <c r="G68" s="106">
         <v>26629.5</v>
       </c>
-      <c r="H68" s="275">
+      <c r="H68" s="33">
         <f>G68</f>
         <v>26629.5</v>
       </c>
@@ -9214,22 +9258,22 @@
       </c>
       <c r="K68" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>43245.345600000001</v>
       </c>
       <c r="L68" s="112">
         <f t="shared" si="13"/>
-        <v>108000</v>
+        <v>102786.87887999999</v>
       </c>
       <c r="M68" s="158">
         <v>0</v>
       </c>
       <c r="N68" s="152">
         <f t="shared" si="7"/>
-        <v>108000.5</v>
+        <v>146032.5</v>
       </c>
       <c r="O68" s="114">
         <f t="shared" si="8"/>
-        <v>114481.5</v>
+        <v>154794.5</v>
       </c>
       <c r="P68" s="102">
         <f t="shared" si="9"/>
@@ -9254,7 +9298,7 @@
       <c r="G69" s="106">
         <v>279500.51</v>
       </c>
-      <c r="H69" s="275">
+      <c r="H69" s="33">
         <v>377877.51</v>
       </c>
       <c r="I69" s="111">
@@ -9267,22 +9311,22 @@
       </c>
       <c r="K69" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L69" s="112">
         <f t="shared" si="13"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M69" s="158">
         <v>0</v>
       </c>
       <c r="N69" s="152">
         <f t="shared" si="7"/>
-        <v>161123.51</v>
+        <v>252506.51</v>
       </c>
       <c r="O69" s="114">
         <f t="shared" si="8"/>
-        <v>170791.51</v>
+        <v>267657.51</v>
       </c>
       <c r="P69" s="102">
         <f t="shared" si="9"/>
@@ -9307,7 +9351,7 @@
       <c r="G70" s="106">
         <v>129918.52</v>
       </c>
-      <c r="H70" s="275">
+      <c r="H70" s="33">
         <f>G70</f>
         <v>129918.52</v>
       </c>
@@ -9321,22 +9365,22 @@
       </c>
       <c r="K70" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L70" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M70" s="158">
         <v>0</v>
       </c>
       <c r="N70" s="152">
         <f t="shared" si="7"/>
-        <v>141000.51999999999</v>
+        <v>190653.52</v>
       </c>
       <c r="O70" s="114">
         <f t="shared" si="8"/>
-        <v>149461.51999999999</v>
+        <v>202093.52</v>
       </c>
       <c r="P70" s="102">
         <f t="shared" si="9"/>
@@ -9361,8 +9405,8 @@
       <c r="G71" s="106">
         <v>130500.53</v>
       </c>
-      <c r="H71" s="275">
-        <f t="shared" ref="H71:H73" si="16">G71</f>
+      <c r="H71" s="33">
+        <f t="shared" ref="H71" si="16">G71</f>
         <v>130500.53</v>
       </c>
       <c r="I71" s="111">
@@ -9375,29 +9419,29 @@
       </c>
       <c r="K71" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L71" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M71" s="158">
         <v>20000</v>
       </c>
       <c r="N71" s="152">
         <f t="shared" si="7"/>
-        <v>150500.53</v>
+        <v>196456.53</v>
       </c>
       <c r="O71" s="114">
         <f t="shared" si="8"/>
-        <v>159531.53</v>
+        <v>208244.53</v>
       </c>
       <c r="P71" s="102">
         <f t="shared" si="9"/>
         <v>0.53000000000000025</v>
       </c>
       <c r="R71" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.25">
@@ -9429,22 +9473,22 @@
       </c>
       <c r="K72" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L72" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M72" s="158">
         <v>0</v>
       </c>
       <c r="N72" s="152">
         <f t="shared" si="7"/>
-        <v>586768.54</v>
+        <v>636949.54</v>
       </c>
       <c r="O72" s="114">
         <f t="shared" si="8"/>
-        <v>621975.54</v>
+        <v>675167.54</v>
       </c>
       <c r="P72" s="102">
         <f t="shared" si="9"/>
@@ -9469,7 +9513,7 @@
       <c r="G73" s="106">
         <v>352500.55</v>
       </c>
-      <c r="H73" s="275">
+      <c r="H73" s="33">
         <f>G73</f>
         <v>352500.55</v>
       </c>
@@ -9483,22 +9527,22 @@
       </c>
       <c r="K73" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>141148.003</v>
       </c>
       <c r="L73" s="112">
         <f t="shared" si="13"/>
-        <v>352500</v>
+        <v>335484.95189999999</v>
       </c>
       <c r="M73" s="158">
         <v>0</v>
       </c>
       <c r="N73" s="152">
         <f t="shared" si="7"/>
-        <v>352500.55</v>
+        <v>476633.55</v>
       </c>
       <c r="O73" s="114">
         <f t="shared" si="8"/>
-        <v>373651.55</v>
+        <v>505232.55</v>
       </c>
       <c r="P73" s="102">
         <f t="shared" si="9"/>
@@ -9524,7 +9568,7 @@
       <c r="G74" s="106">
         <v>280973.56</v>
       </c>
-      <c r="H74" s="275">
+      <c r="H74" s="33">
         <f>G74</f>
         <v>280973.56</v>
       </c>
@@ -9538,22 +9582,22 @@
       </c>
       <c r="K74" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L74" s="112">
         <f t="shared" si="13"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M74" s="158">
         <v>20000</v>
       </c>
       <c r="N74" s="152">
         <f t="shared" si="7"/>
-        <v>279500.56</v>
+        <v>370883.56</v>
       </c>
       <c r="O74" s="114">
         <f t="shared" si="8"/>
-        <v>296271.56</v>
+        <v>393137.56</v>
       </c>
       <c r="P74" s="102">
         <f t="shared" si="9"/>
@@ -9578,7 +9622,7 @@
       <c r="G75" s="106">
         <v>141000.57</v>
       </c>
-      <c r="H75" s="275">
+      <c r="H75" s="33">
         <f>210002-H89-H105</f>
         <v>141000.42000000001</v>
       </c>
@@ -9592,22 +9636,22 @@
       </c>
       <c r="K75" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L75" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M75" s="158">
         <v>0</v>
       </c>
       <c r="N75" s="152">
         <f t="shared" si="7"/>
-        <v>141000.57</v>
+        <v>190653.57</v>
       </c>
       <c r="O75" s="114">
         <f t="shared" si="8"/>
-        <v>149461.57</v>
+        <v>202093.57</v>
       </c>
       <c r="P75" s="102">
         <f t="shared" si="9"/>
@@ -9634,7 +9678,7 @@
       <c r="G76" s="106">
         <v>625931.57999999996</v>
       </c>
-      <c r="H76" s="275">
+      <c r="H76" s="33">
         <f>247560+378371.58</f>
         <v>625931.58000000007</v>
       </c>
@@ -9648,22 +9692,22 @@
       </c>
       <c r="K76" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L76" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M76" s="158">
         <v>0</v>
       </c>
       <c r="N76" s="152">
         <f t="shared" si="7"/>
-        <v>130500.58</v>
+        <v>176456.58</v>
       </c>
       <c r="O76" s="114">
         <f t="shared" si="8"/>
-        <v>138331.57999999999</v>
+        <v>187044.58</v>
       </c>
       <c r="P76" s="102">
         <f t="shared" si="9"/>
@@ -9688,7 +9732,7 @@
       <c r="G77" s="106">
         <v>131301.59</v>
       </c>
-      <c r="H77" s="275">
+      <c r="H77" s="33">
         <f>G77</f>
         <v>131301.59</v>
       </c>
@@ -9702,22 +9746,22 @@
       </c>
       <c r="K77" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L77" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M77" s="158">
         <v>0</v>
       </c>
       <c r="N77" s="152">
         <f t="shared" si="7"/>
-        <v>142500.59</v>
+        <v>192681.59</v>
       </c>
       <c r="O77" s="114">
         <f t="shared" si="8"/>
-        <v>151051.59</v>
+        <v>204242.59</v>
       </c>
       <c r="P77" s="102">
         <f t="shared" si="9"/>
@@ -9742,7 +9786,7 @@
       <c r="G78" s="106">
         <v>348979.6</v>
       </c>
-      <c r="H78" s="275">
+      <c r="H78" s="33">
         <f>G78</f>
         <v>348979.6</v>
       </c>
@@ -9756,22 +9800,22 @@
       </c>
       <c r="K78" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>141148.003</v>
       </c>
       <c r="L78" s="112">
         <f t="shared" si="13"/>
-        <v>352500</v>
+        <v>335484.95189999999</v>
       </c>
       <c r="M78" s="158">
         <v>0</v>
       </c>
       <c r="N78" s="152">
         <f t="shared" si="7"/>
-        <v>352500.6</v>
+        <v>476633.59999999998</v>
       </c>
       <c r="O78" s="114">
         <f t="shared" si="8"/>
-        <v>373651.6</v>
+        <v>505232.6</v>
       </c>
       <c r="P78" s="102">
         <f t="shared" si="9"/>
@@ -9796,7 +9840,7 @@
       <c r="G79" s="106">
         <v>259500.61</v>
       </c>
-      <c r="H79" s="275">
+      <c r="H79" s="33">
         <f>G79</f>
         <v>259500.61</v>
       </c>
@@ -9810,22 +9854,22 @@
       </c>
       <c r="K79" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L79" s="112">
         <f t="shared" si="13"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M79" s="158">
         <v>0</v>
       </c>
       <c r="N79" s="152">
         <f t="shared" si="7"/>
-        <v>259500.61</v>
+        <v>350883.61</v>
       </c>
       <c r="O79" s="114">
         <f t="shared" si="8"/>
-        <v>275071.61</v>
+        <v>371937.61</v>
       </c>
       <c r="P79" s="102">
         <f t="shared" si="9"/>
@@ -9850,7 +9894,7 @@
       <c r="G80" s="106">
         <v>1054850.6200000001</v>
       </c>
-      <c r="H80" s="275">
+      <c r="H80" s="33">
         <v>250000</v>
       </c>
       <c r="I80" s="111">
@@ -9863,22 +9907,22 @@
       </c>
       <c r="K80" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L80" s="112">
         <f t="shared" si="13"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M80" s="158">
         <v>0</v>
       </c>
       <c r="N80" s="152">
         <f t="shared" si="7"/>
-        <v>945851.62</v>
+        <v>995504.62</v>
       </c>
       <c r="O80" s="114">
         <f t="shared" si="8"/>
-        <v>1002603.62</v>
+        <v>1055235.6200000001</v>
       </c>
       <c r="P80" s="102">
         <f t="shared" si="9"/>
@@ -9905,7 +9949,7 @@
       <c r="G81" s="106">
         <v>130500.63</v>
       </c>
-      <c r="H81" s="275">
+      <c r="H81" s="33">
         <f>G81</f>
         <v>130500.63</v>
       </c>
@@ -9919,22 +9963,22 @@
       </c>
       <c r="K81" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L81" s="112">
         <f t="shared" si="13"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M81" s="158">
         <v>0</v>
       </c>
       <c r="N81" s="152">
         <f t="shared" si="7"/>
-        <v>130500.63</v>
+        <v>176456.63</v>
       </c>
       <c r="O81" s="114">
         <f t="shared" si="8"/>
-        <v>138331.63</v>
+        <v>187044.63</v>
       </c>
       <c r="P81" s="102">
         <f t="shared" si="9"/>
@@ -9970,22 +10014,22 @@
       </c>
       <c r="K82" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L82" s="112">
         <f t="shared" si="13"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M82" s="158">
         <v>0</v>
       </c>
       <c r="N82" s="152">
         <f t="shared" si="7"/>
-        <v>285001.64</v>
+        <v>335182.64</v>
       </c>
       <c r="O82" s="114">
         <f t="shared" si="8"/>
-        <v>302102.64</v>
+        <v>355294.64</v>
       </c>
       <c r="P82" s="102">
         <f t="shared" si="9"/>
@@ -10013,8 +10057,8 @@
       <c r="G83" s="106">
         <v>352500.65</v>
       </c>
-      <c r="H83" s="275">
-        <f t="shared" ref="H83:H98" si="17">G83</f>
+      <c r="H83" s="33">
+        <f t="shared" ref="H83:H96" si="17">G83</f>
         <v>352500.65</v>
       </c>
       <c r="I83" s="111">
@@ -10027,22 +10071,22 @@
       </c>
       <c r="K83" s="151">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>141148.003</v>
       </c>
       <c r="L83" s="112">
         <f t="shared" ref="L83:L114" si="19">N$2*F83</f>
-        <v>352500</v>
+        <v>335484.95189999999</v>
       </c>
       <c r="M83" s="158">
         <v>0</v>
       </c>
       <c r="N83" s="152">
         <f t="shared" si="7"/>
-        <v>352500.65</v>
+        <v>476633.65</v>
       </c>
       <c r="O83" s="114">
         <f t="shared" si="8"/>
-        <v>373651.65</v>
+        <v>505232.65</v>
       </c>
       <c r="P83" s="102">
         <f t="shared" si="9"/>
@@ -10067,7 +10111,7 @@
       <c r="G84" s="106">
         <v>259500.66</v>
       </c>
-      <c r="H84" s="275">
+      <c r="H84" s="33">
         <v>357877.66</v>
       </c>
       <c r="I84" s="111">
@@ -10080,22 +10124,22 @@
       </c>
       <c r="K84" s="151">
         <f t="shared" ref="K84:K131" si="20">N$3*F84</f>
-        <v>0</v>
+        <v>103908.95539999999</v>
       </c>
       <c r="L84" s="112">
         <f t="shared" si="19"/>
-        <v>259500</v>
+        <v>246974.02841999996</v>
       </c>
       <c r="M84" s="158">
         <v>0</v>
       </c>
       <c r="N84" s="152">
         <f t="shared" ref="N84:N131" si="21">ROUND((L84+J84+I84+K84+M84),0) + P84</f>
-        <v>161123.66</v>
+        <v>252506.66</v>
       </c>
       <c r="O84" s="114">
         <f t="shared" ref="O84:O131" si="22">ROUND((N84*6% + N84 ),0) + P84</f>
-        <v>170791.66</v>
+        <v>267657.65999999997</v>
       </c>
       <c r="P84" s="102">
         <f t="shared" si="9"/>
@@ -10120,7 +10164,7 @@
       <c r="G85" s="106">
         <v>141000.67000000001</v>
       </c>
-      <c r="H85" s="275">
+      <c r="H85" s="33">
         <f t="shared" si="17"/>
         <v>141000.67000000001</v>
       </c>
@@ -10134,22 +10178,22 @@
       </c>
       <c r="K85" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>56459.201200000003</v>
       </c>
       <c r="L85" s="112">
         <f t="shared" si="19"/>
-        <v>141000</v>
+        <v>134193.98075999998</v>
       </c>
       <c r="M85" s="158">
         <v>0</v>
       </c>
       <c r="N85" s="152">
         <f t="shared" si="21"/>
-        <v>141000.67000000001</v>
+        <v>190653.67</v>
       </c>
       <c r="O85" s="114">
         <f t="shared" si="22"/>
-        <v>149461.67000000001</v>
+        <v>202093.67</v>
       </c>
       <c r="P85" s="102">
         <f t="shared" ref="P85:P131" si="23">P84+0.01</f>
@@ -10174,7 +10218,7 @@
       <c r="G86" s="106">
         <v>130500.68</v>
       </c>
-      <c r="H86" s="275">
+      <c r="H86" s="33">
         <f>G86</f>
         <v>130500.68</v>
       </c>
@@ -10188,22 +10232,22 @@
       </c>
       <c r="K86" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>52254.792599999993</v>
       </c>
       <c r="L86" s="112">
         <f t="shared" si="19"/>
-        <v>130499.99999999999</v>
+        <v>124200.81197999998</v>
       </c>
       <c r="M86" s="158">
         <v>0</v>
       </c>
       <c r="N86" s="152">
         <f t="shared" si="21"/>
-        <v>130500.68</v>
+        <v>176456.68</v>
       </c>
       <c r="O86" s="114">
         <f t="shared" si="22"/>
-        <v>138331.68</v>
+        <v>187044.68</v>
       </c>
       <c r="P86" s="102">
         <f t="shared" si="23"/>
@@ -10228,7 +10272,7 @@
       <c r="G87" s="106">
         <v>142500.69</v>
       </c>
-      <c r="H87" s="275">
+      <c r="H87" s="33">
         <f>G87</f>
         <v>142500.69</v>
       </c>
@@ -10242,22 +10286,22 @@
       </c>
       <c r="K87" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>57059.830999999998</v>
       </c>
       <c r="L87" s="112">
         <f t="shared" si="19"/>
-        <v>142500</v>
+        <v>135621.57629999999</v>
       </c>
       <c r="M87" s="158">
         <v>0</v>
       </c>
       <c r="N87" s="152">
         <f t="shared" si="21"/>
-        <v>142500.69</v>
+        <v>192681.69</v>
       </c>
       <c r="O87" s="114">
         <f t="shared" si="22"/>
-        <v>151051.69</v>
+        <v>204243.69</v>
       </c>
       <c r="P87" s="102">
         <f t="shared" si="23"/>
@@ -10280,7 +10324,7 @@
       <c r="G88" s="106">
         <v>34500.699999999997</v>
       </c>
-      <c r="H88" s="275">
+      <c r="H88" s="33">
         <f>G88</f>
         <v>34500.699999999997</v>
       </c>
@@ -10294,22 +10338,22 @@
       </c>
       <c r="K88" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L88" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M88" s="158">
         <v>0</v>
       </c>
       <c r="N88" s="152">
         <f t="shared" si="21"/>
-        <v>34500.699999999997</v>
+        <v>46649.7</v>
       </c>
       <c r="O88" s="114">
         <f t="shared" si="22"/>
-        <v>36571.699999999997</v>
+        <v>49449.7</v>
       </c>
       <c r="P88" s="102">
         <f t="shared" si="23"/>
@@ -10332,7 +10376,7 @@
       <c r="G89" s="106">
         <v>34500.71</v>
       </c>
-      <c r="H89" s="275">
+      <c r="H89" s="33">
         <f>G89</f>
         <v>34500.71</v>
       </c>
@@ -10346,22 +10390,22 @@
       </c>
       <c r="K89" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L89" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M89" s="158">
         <v>0</v>
       </c>
       <c r="N89" s="152">
         <f t="shared" si="21"/>
-        <v>34500.71</v>
+        <v>46649.71</v>
       </c>
       <c r="O89" s="114">
         <f t="shared" si="22"/>
-        <v>36571.71</v>
+        <v>49449.71</v>
       </c>
       <c r="P89" s="102">
         <f t="shared" si="23"/>
@@ -10384,7 +10428,7 @@
       <c r="G90" s="106">
         <v>34500.720000000001</v>
       </c>
-      <c r="H90" s="275">
+      <c r="H90" s="33">
         <f t="shared" si="17"/>
         <v>34500.720000000001</v>
       </c>
@@ -10398,22 +10442,22 @@
       </c>
       <c r="K90" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L90" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M90" s="158">
         <v>0</v>
       </c>
       <c r="N90" s="152">
         <f t="shared" si="21"/>
-        <v>34500.720000000001</v>
+        <v>46649.72</v>
       </c>
       <c r="O90" s="114">
         <f t="shared" si="22"/>
-        <v>36571.72</v>
+        <v>49449.72</v>
       </c>
       <c r="P90" s="102">
         <f t="shared" si="23"/>
@@ -10436,7 +10480,7 @@
       <c r="G91" s="106">
         <v>34500.730000000003</v>
       </c>
-      <c r="H91" s="275">
+      <c r="H91" s="33">
         <f>G91</f>
         <v>34500.730000000003</v>
       </c>
@@ -10450,22 +10494,22 @@
       </c>
       <c r="K91" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L91" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M91" s="158">
         <v>0</v>
       </c>
       <c r="N91" s="152">
         <f t="shared" si="21"/>
-        <v>34500.730000000003</v>
+        <v>46649.73</v>
       </c>
       <c r="O91" s="114">
         <f t="shared" si="22"/>
-        <v>36571.730000000003</v>
+        <v>49449.73</v>
       </c>
       <c r="P91" s="102">
         <f t="shared" si="23"/>
@@ -10488,7 +10532,7 @@
       <c r="G92" s="33">
         <v>34500.74</v>
       </c>
-      <c r="H92" s="275">
+      <c r="H92" s="33">
         <f>G92</f>
         <v>34500.74</v>
       </c>
@@ -10502,22 +10546,22 @@
       </c>
       <c r="K92" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L92" s="145">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M92" s="158">
         <v>0</v>
       </c>
       <c r="N92" s="152">
         <f t="shared" si="21"/>
-        <v>34500.74</v>
+        <v>46649.74</v>
       </c>
       <c r="O92" s="146">
         <f t="shared" si="22"/>
-        <v>36571.74</v>
+        <v>49449.74</v>
       </c>
       <c r="P92" s="102">
         <f t="shared" si="23"/>
@@ -10543,7 +10587,7 @@
       <c r="G93" s="33">
         <v>107560.75</v>
       </c>
-      <c r="H93" s="275">
+      <c r="H93" s="33">
         <f>G93</f>
         <v>107560.75</v>
       </c>
@@ -10557,22 +10601,22 @@
       </c>
       <c r="K93" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L93" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M93" s="158">
         <v>0</v>
       </c>
       <c r="N93" s="152">
         <f t="shared" si="21"/>
-        <v>34500.75</v>
+        <v>46649.75</v>
       </c>
       <c r="O93" s="114">
         <f t="shared" si="22"/>
-        <v>36571.75</v>
+        <v>49449.75</v>
       </c>
       <c r="P93" s="102">
         <f t="shared" si="23"/>
@@ -10595,7 +10639,7 @@
       <c r="G94" s="106">
         <v>34500.76</v>
       </c>
-      <c r="H94" s="275">
+      <c r="H94" s="33">
         <f>G94</f>
         <v>34500.76</v>
       </c>
@@ -10609,22 +10653,22 @@
       </c>
       <c r="K94" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L94" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M94" s="158">
         <v>0</v>
       </c>
       <c r="N94" s="152">
         <f t="shared" si="21"/>
-        <v>34500.76</v>
+        <v>46649.760000000002</v>
       </c>
       <c r="O94" s="114">
         <f t="shared" si="22"/>
-        <v>36571.760000000002</v>
+        <v>49449.760000000002</v>
       </c>
       <c r="P94" s="102">
         <f t="shared" si="23"/>
@@ -10647,7 +10691,7 @@
       <c r="G95" s="106">
         <v>34500.769999999997</v>
       </c>
-      <c r="H95" s="275">
+      <c r="H95" s="33">
         <f>G95</f>
         <v>34500.769999999997</v>
       </c>
@@ -10661,22 +10705,22 @@
       </c>
       <c r="K95" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L95" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M95" s="158">
         <v>0</v>
       </c>
       <c r="N95" s="152">
         <f t="shared" si="21"/>
-        <v>34500.769999999997</v>
+        <v>46649.77</v>
       </c>
       <c r="O95" s="114">
         <f t="shared" si="22"/>
-        <v>36571.769999999997</v>
+        <v>49449.77</v>
       </c>
       <c r="P95" s="102">
         <f t="shared" si="23"/>
@@ -10699,7 +10743,7 @@
       <c r="G96" s="106">
         <v>34500.78</v>
       </c>
-      <c r="H96" s="275">
+      <c r="H96" s="33">
         <f t="shared" si="17"/>
         <v>34500.78</v>
       </c>
@@ -10713,22 +10757,22 @@
       </c>
       <c r="K96" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L96" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M96" s="158">
         <v>0</v>
       </c>
       <c r="N96" s="152">
         <f t="shared" si="21"/>
-        <v>34500.78</v>
+        <v>46649.78</v>
       </c>
       <c r="O96" s="114">
         <f t="shared" si="22"/>
-        <v>36571.78</v>
+        <v>49449.78</v>
       </c>
       <c r="P96" s="102">
         <f t="shared" si="23"/>
@@ -10762,22 +10806,22 @@
       </c>
       <c r="K97" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L97" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M97" s="158">
         <v>0</v>
       </c>
       <c r="N97" s="152">
         <f t="shared" si="21"/>
-        <v>393364.79</v>
+        <v>405513.79</v>
       </c>
       <c r="O97" s="114">
         <f t="shared" si="22"/>
-        <v>416967.79</v>
+        <v>429845.79</v>
       </c>
       <c r="P97" s="102">
         <f t="shared" si="23"/>
@@ -10800,7 +10844,7 @@
       <c r="G98" s="106">
         <v>34500.800000000003</v>
       </c>
-      <c r="H98" s="275">
+      <c r="H98" s="33">
         <f>G98</f>
         <v>34500.800000000003</v>
       </c>
@@ -10814,22 +10858,22 @@
       </c>
       <c r="K98" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L98" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M98" s="158">
         <v>0</v>
       </c>
       <c r="N98" s="152">
         <f t="shared" si="21"/>
-        <v>34500.800000000003</v>
+        <v>46649.8</v>
       </c>
       <c r="O98" s="114">
         <f t="shared" si="22"/>
-        <v>36571.800000000003</v>
+        <v>49449.8</v>
       </c>
       <c r="P98" s="102">
         <f t="shared" si="23"/>
@@ -10852,7 +10896,7 @@
       <c r="G99" s="103">
         <v>34500.81</v>
       </c>
-      <c r="H99" s="275">
+      <c r="H99" s="33">
         <v>47579.81</v>
       </c>
       <c r="I99" s="42">
@@ -10865,22 +10909,22 @@
       </c>
       <c r="K99" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L99" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M99" s="158">
         <v>0</v>
       </c>
       <c r="N99" s="152">
         <f t="shared" si="21"/>
-        <v>21421.81</v>
+        <v>33570.81</v>
       </c>
       <c r="O99" s="5">
         <f t="shared" si="22"/>
-        <v>22707.81</v>
+        <v>35585.81</v>
       </c>
       <c r="P99" s="102">
         <f t="shared" si="23"/>
@@ -10903,7 +10947,7 @@
       <c r="G100" s="103">
         <v>34500.82</v>
       </c>
-      <c r="H100" s="275">
+      <c r="H100" s="33">
         <f t="shared" ref="H100" si="24">G100</f>
         <v>34500.82</v>
       </c>
@@ -10917,22 +10961,22 @@
       </c>
       <c r="K100" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L100" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M100" s="158">
         <v>0</v>
       </c>
       <c r="N100" s="152">
         <f t="shared" si="21"/>
-        <v>34500.82</v>
+        <v>46649.82</v>
       </c>
       <c r="O100" s="5">
         <f t="shared" si="22"/>
-        <v>36571.82</v>
+        <v>49449.82</v>
       </c>
       <c r="P100" s="102">
         <f t="shared" si="23"/>
@@ -10966,22 +11010,22 @@
       </c>
       <c r="K101" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L101" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M101" s="158">
         <v>0</v>
       </c>
       <c r="N101" s="152">
         <f t="shared" si="21"/>
-        <v>144182.82999999999</v>
+        <v>156331.82999999999</v>
       </c>
       <c r="O101" s="114">
         <f t="shared" si="22"/>
-        <v>152834.82999999999</v>
+        <v>165712.82999999999</v>
       </c>
       <c r="P101" s="102">
         <f t="shared" si="23"/>
@@ -11004,7 +11048,7 @@
       <c r="G102" s="106">
         <v>34500.839999999997</v>
       </c>
-      <c r="H102" s="275">
+      <c r="H102" s="33">
         <f t="shared" ref="H102" si="25">G102</f>
         <v>34500.839999999997</v>
       </c>
@@ -11018,22 +11062,22 @@
       </c>
       <c r="K102" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L102" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M102" s="158">
         <v>0</v>
       </c>
       <c r="N102" s="152">
         <f t="shared" si="21"/>
-        <v>34500.839999999997</v>
+        <v>46649.84</v>
       </c>
       <c r="O102" s="114">
         <f t="shared" si="22"/>
-        <v>36571.839999999997</v>
+        <v>49449.84</v>
       </c>
       <c r="P102" s="102">
         <f t="shared" si="23"/>
@@ -11056,7 +11100,7 @@
       <c r="G103" s="106">
         <v>34500.85</v>
       </c>
-      <c r="H103" s="372">
+      <c r="H103" s="182">
         <f>G103</f>
         <v>34500.85</v>
       </c>
@@ -11070,22 +11114,22 @@
       </c>
       <c r="K103" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L103" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M103" s="158">
         <v>0</v>
       </c>
       <c r="N103" s="152">
         <f t="shared" si="21"/>
-        <v>34500.85</v>
+        <v>46649.85</v>
       </c>
       <c r="O103" s="114">
         <f t="shared" si="22"/>
-        <v>36571.85</v>
+        <v>49449.85</v>
       </c>
       <c r="P103" s="102">
         <f t="shared" si="23"/>
@@ -11119,22 +11163,22 @@
       </c>
       <c r="K104" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L104" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M104" s="158">
         <v>0</v>
       </c>
       <c r="N104" s="152">
         <f t="shared" si="21"/>
-        <v>116581.86</v>
+        <v>128730.86</v>
       </c>
       <c r="O104" s="5">
         <f t="shared" si="22"/>
-        <v>123577.86</v>
+        <v>136455.85999999999</v>
       </c>
       <c r="P104" s="102">
         <f t="shared" si="23"/>
@@ -11157,7 +11201,7 @@
       <c r="G105" s="103">
         <v>34500.870000000003</v>
       </c>
-      <c r="H105" s="372">
+      <c r="H105" s="182">
         <f>G105</f>
         <v>34500.870000000003</v>
       </c>
@@ -11171,22 +11215,22 @@
       </c>
       <c r="K105" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L105" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M105" s="158">
         <v>0</v>
       </c>
       <c r="N105" s="152">
         <f t="shared" si="21"/>
-        <v>34500.870000000003</v>
+        <v>46649.87</v>
       </c>
       <c r="O105" s="5">
         <f t="shared" si="22"/>
-        <v>36571.870000000003</v>
+        <v>49449.87</v>
       </c>
       <c r="P105" s="102">
         <f t="shared" si="23"/>
@@ -11209,7 +11253,7 @@
       <c r="G106" s="103">
         <v>31788.880000000001</v>
       </c>
-      <c r="H106" s="372">
+      <c r="H106" s="182">
         <v>31788.28</v>
       </c>
       <c r="I106" s="42">
@@ -11222,22 +11266,22 @@
       </c>
       <c r="K106" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L106" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M106" s="158">
         <v>0</v>
       </c>
       <c r="N106" s="152">
         <f t="shared" si="21"/>
-        <v>34501.879999999997</v>
+        <v>46650.879999999997</v>
       </c>
       <c r="O106" s="5">
         <f t="shared" si="22"/>
-        <v>36572.879999999997</v>
+        <v>49450.879999999997</v>
       </c>
       <c r="P106" s="102">
         <f t="shared" si="23"/>
@@ -11260,7 +11304,7 @@
       <c r="G107" s="103">
         <v>47579.89</v>
       </c>
-      <c r="H107" s="372">
+      <c r="H107" s="182">
         <v>34500.89</v>
       </c>
       <c r="I107" s="42">
@@ -11273,22 +11317,22 @@
       </c>
       <c r="K107" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L107" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M107" s="158">
         <v>0</v>
       </c>
       <c r="N107" s="152">
         <f t="shared" si="21"/>
-        <v>47579.89</v>
+        <v>59728.89</v>
       </c>
       <c r="O107" s="5">
         <f t="shared" si="22"/>
-        <v>50435.89</v>
+        <v>63313.89</v>
       </c>
       <c r="P107" s="102">
         <f t="shared" si="23"/>
@@ -11311,7 +11355,7 @@
       <c r="G108" s="103">
         <v>34500.9</v>
       </c>
-      <c r="H108" s="275">
+      <c r="H108" s="33">
         <f>G108</f>
         <v>34500.9</v>
       </c>
@@ -11325,22 +11369,22 @@
       </c>
       <c r="K108" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L108" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M108" s="158">
         <v>0</v>
       </c>
       <c r="N108" s="152">
         <f t="shared" si="21"/>
-        <v>34500.9</v>
+        <v>46649.9</v>
       </c>
       <c r="O108" s="5">
         <f t="shared" si="22"/>
-        <v>36571.9</v>
+        <v>49449.9</v>
       </c>
       <c r="P108" s="102">
         <f t="shared" si="23"/>
@@ -11363,7 +11407,7 @@
       <c r="G109" s="103">
         <v>36571.910000000003</v>
       </c>
-      <c r="H109" s="275">
+      <c r="H109" s="33">
         <v>50435.91</v>
       </c>
       <c r="I109" s="42">
@@ -11376,22 +11420,22 @@
       </c>
       <c r="K109" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L109" s="18">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M109" s="158">
         <v>0</v>
       </c>
       <c r="N109" s="152">
         <f t="shared" si="21"/>
-        <v>20636.91</v>
+        <v>32785.910000000003</v>
       </c>
       <c r="O109" s="5">
         <f t="shared" si="22"/>
-        <v>21875.91</v>
+        <v>34753.910000000003</v>
       </c>
       <c r="P109" s="102">
         <f t="shared" si="23"/>
@@ -11427,22 +11471,22 @@
       </c>
       <c r="K110" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L110" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M110" s="158">
         <v>0</v>
       </c>
       <c r="N110" s="152">
         <f t="shared" si="21"/>
-        <v>179511.92</v>
+        <v>191660.92</v>
       </c>
       <c r="O110" s="114">
         <f t="shared" si="22"/>
-        <v>190283.92</v>
+        <v>203161.92</v>
       </c>
       <c r="P110" s="102">
         <f t="shared" si="23"/>
@@ -11465,8 +11509,8 @@
       <c r="G111" s="106">
         <v>34500.93</v>
       </c>
-      <c r="H111" s="275">
-        <f t="shared" ref="H109:H111" si="26">G111</f>
+      <c r="H111" s="33">
+        <f t="shared" ref="H111" si="26">G111</f>
         <v>34500.93</v>
       </c>
       <c r="I111" s="111">
@@ -11479,22 +11523,22 @@
       </c>
       <c r="K111" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L111" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M111" s="158">
         <v>0</v>
       </c>
       <c r="N111" s="152">
         <f t="shared" si="21"/>
-        <v>34500.93</v>
+        <v>46649.93</v>
       </c>
       <c r="O111" s="114">
         <f t="shared" si="22"/>
-        <v>36571.93</v>
+        <v>49449.93</v>
       </c>
       <c r="P111" s="102">
         <f t="shared" si="23"/>
@@ -11517,7 +11561,7 @@
       <c r="G112" s="106">
         <v>34500.94</v>
       </c>
-      <c r="H112" s="275">
+      <c r="H112" s="33">
         <f>G112</f>
         <v>34500.94</v>
       </c>
@@ -11531,22 +11575,22 @@
       </c>
       <c r="K112" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L112" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M112" s="158">
         <v>0</v>
       </c>
       <c r="N112" s="152">
         <f t="shared" si="21"/>
-        <v>34500.94</v>
+        <v>46649.94</v>
       </c>
       <c r="O112" s="114">
         <f t="shared" si="22"/>
-        <v>36571.94</v>
+        <v>49449.94</v>
       </c>
       <c r="P112" s="102">
         <f t="shared" si="23"/>
@@ -11569,7 +11613,7 @@
       <c r="G113" s="106">
         <v>34500.949999999997</v>
       </c>
-      <c r="H113" s="275">
+      <c r="H113" s="33">
         <f>G113</f>
         <v>34500.949999999997</v>
       </c>
@@ -11583,22 +11627,22 @@
       </c>
       <c r="K113" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L113" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M113" s="158">
         <v>0</v>
       </c>
       <c r="N113" s="152">
         <f t="shared" si="21"/>
-        <v>34500.949999999997</v>
+        <v>46649.95</v>
       </c>
       <c r="O113" s="114">
         <f t="shared" si="22"/>
-        <v>36571.949999999997</v>
+        <v>49449.95</v>
       </c>
       <c r="P113" s="102">
         <f t="shared" si="23"/>
@@ -11621,7 +11665,7 @@
       <c r="G114" s="106">
         <v>34500.959999999999</v>
       </c>
-      <c r="H114" s="275">
+      <c r="H114" s="33">
         <f>G114</f>
         <v>34500.959999999999</v>
       </c>
@@ -11635,22 +11679,22 @@
       </c>
       <c r="K114" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L114" s="112">
         <f t="shared" si="19"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M114" s="158">
         <v>0</v>
       </c>
       <c r="N114" s="152">
         <f t="shared" si="21"/>
-        <v>34500.959999999999</v>
+        <v>46649.96</v>
       </c>
       <c r="O114" s="114">
         <f t="shared" si="22"/>
-        <v>36571.96</v>
+        <v>49449.96</v>
       </c>
       <c r="P114" s="102">
         <f t="shared" si="23"/>
@@ -11673,7 +11717,7 @@
       <c r="G115" s="106">
         <v>34500.97</v>
       </c>
-      <c r="H115" s="275">
+      <c r="H115" s="33">
         <v>47579.97</v>
       </c>
       <c r="I115" s="111">
@@ -11686,22 +11730,22 @@
       </c>
       <c r="K115" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L115" s="112">
         <f t="shared" ref="L115:L131" si="28">N$2*F115</f>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M115" s="158">
         <v>0</v>
       </c>
       <c r="N115" s="152">
         <f t="shared" si="21"/>
-        <v>21421.97</v>
+        <v>33570.97</v>
       </c>
       <c r="O115" s="114">
         <f t="shared" si="22"/>
-        <v>22707.97</v>
+        <v>35585.97</v>
       </c>
       <c r="P115" s="102">
         <f t="shared" si="23"/>
@@ -11726,7 +11770,7 @@
       <c r="G116" s="106">
         <v>20464.98</v>
       </c>
-      <c r="H116" s="275">
+      <c r="H116" s="33">
         <f>G116</f>
         <v>20464.98</v>
       </c>
@@ -11740,22 +11784,22 @@
       </c>
       <c r="K116" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L116" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M116" s="158">
         <v>0</v>
       </c>
       <c r="N116" s="152">
         <f t="shared" si="21"/>
-        <v>34500.980000000003</v>
+        <v>46649.98</v>
       </c>
       <c r="O116" s="114">
         <f t="shared" si="22"/>
-        <v>36571.980000000003</v>
+        <v>49449.98</v>
       </c>
       <c r="P116" s="102">
         <f t="shared" si="23"/>
@@ -11791,22 +11835,22 @@
       </c>
       <c r="K117" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L117" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M117" s="158">
         <v>0</v>
       </c>
       <c r="N117" s="152">
         <f t="shared" si="21"/>
-        <v>33072.99</v>
+        <v>45221.99</v>
       </c>
       <c r="O117" s="114">
         <f t="shared" si="22"/>
-        <v>35057.99</v>
+        <v>47935.99</v>
       </c>
       <c r="P117" s="102">
         <f t="shared" si="23"/>
@@ -11831,8 +11875,8 @@
       <c r="G118" s="106">
         <v>34501</v>
       </c>
-      <c r="H118" s="275">
-        <f t="shared" ref="H118:H120" si="29">G118</f>
+      <c r="H118" s="33">
+        <f t="shared" ref="H118:H119" si="29">G118</f>
         <v>34501</v>
       </c>
       <c r="I118" s="111">
@@ -11845,22 +11889,22 @@
       </c>
       <c r="K118" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L118" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M118" s="158">
         <v>0</v>
       </c>
       <c r="N118" s="152">
         <f t="shared" si="21"/>
-        <v>34501</v>
+        <v>46650</v>
       </c>
       <c r="O118" s="114">
         <f t="shared" si="22"/>
-        <v>36572</v>
+        <v>49450</v>
       </c>
       <c r="P118" s="102">
         <f t="shared" si="23"/>
@@ -11886,7 +11930,7 @@
       <c r="G119" s="106">
         <v>34501.01</v>
       </c>
-      <c r="H119" s="275">
+      <c r="H119" s="33">
         <f t="shared" si="29"/>
         <v>34501.01</v>
       </c>
@@ -11900,22 +11944,22 @@
       </c>
       <c r="K119" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L119" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M119" s="158">
         <v>0</v>
       </c>
       <c r="N119" s="152">
         <f t="shared" si="21"/>
-        <v>34501.01</v>
+        <v>46650.01</v>
       </c>
       <c r="O119" s="114">
         <f t="shared" si="22"/>
-        <v>36572.01</v>
+        <v>49450.01</v>
       </c>
       <c r="P119" s="102">
         <f t="shared" si="23"/>
@@ -11938,7 +11982,7 @@
       <c r="G120" s="106">
         <v>34501.019999999997</v>
       </c>
-      <c r="H120" s="275">
+      <c r="H120" s="33">
         <f>G120</f>
         <v>34501.019999999997</v>
       </c>
@@ -11952,22 +11996,22 @@
       </c>
       <c r="K120" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L120" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M120" s="158">
         <v>0</v>
       </c>
       <c r="N120" s="152">
         <f t="shared" si="21"/>
-        <v>34501.019999999997</v>
+        <v>46650.02</v>
       </c>
       <c r="O120" s="114">
         <f t="shared" si="22"/>
-        <v>36572.019999999997</v>
+        <v>49450.02</v>
       </c>
       <c r="P120" s="102">
         <f t="shared" si="23"/>
@@ -11990,14 +12034,14 @@
         <v>2.3E-3</v>
       </c>
       <c r="G121" s="106">
-        <v>56674.03</v>
+        <v>60075.03</v>
       </c>
       <c r="H121" s="33">
-        <v>0</v>
+        <v>60075.03</v>
       </c>
       <c r="I121" s="111">
         <f t="shared" si="0"/>
-        <v>56674.03</v>
+        <v>0</v>
       </c>
       <c r="J121" s="112">
         <f t="shared" si="27"/>
@@ -12005,22 +12049,22 @@
       </c>
       <c r="K121" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L121" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M121" s="158">
         <v>0</v>
       </c>
       <c r="N121" s="152">
         <f t="shared" si="21"/>
-        <v>91175.03</v>
+        <v>46650.03</v>
       </c>
       <c r="O121" s="114">
         <f t="shared" si="22"/>
-        <v>96647.03</v>
+        <v>49450.03</v>
       </c>
       <c r="P121" s="102">
         <f t="shared" si="23"/>
@@ -12043,7 +12087,7 @@
       <c r="G122" s="106">
         <v>34501.040000000001</v>
       </c>
-      <c r="H122" s="275">
+      <c r="H122" s="33">
         <v>47580.04</v>
       </c>
       <c r="I122" s="111">
@@ -12056,22 +12100,22 @@
       </c>
       <c r="K122" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L122" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M122" s="158">
         <v>0</v>
       </c>
       <c r="N122" s="152">
         <f t="shared" si="21"/>
-        <v>21422.04</v>
+        <v>33571.040000000001</v>
       </c>
       <c r="O122" s="114">
         <f t="shared" si="22"/>
-        <v>22708.04</v>
+        <v>35586.04</v>
       </c>
       <c r="P122" s="102">
         <f t="shared" si="23"/>
@@ -12094,7 +12138,7 @@
       <c r="G123" s="106">
         <v>34013.050000000003</v>
       </c>
-      <c r="H123" s="275">
+      <c r="H123" s="33">
         <f>G123</f>
         <v>34013.050000000003</v>
       </c>
@@ -12108,22 +12152,22 @@
       </c>
       <c r="K123" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L123" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M123" s="158">
         <v>0</v>
       </c>
       <c r="N123" s="152">
         <f t="shared" si="21"/>
-        <v>34501.050000000003</v>
+        <v>46650.05</v>
       </c>
       <c r="O123" s="114">
         <f t="shared" si="22"/>
-        <v>36572.050000000003</v>
+        <v>49450.05</v>
       </c>
       <c r="P123" s="102">
         <f t="shared" si="23"/>
@@ -12146,7 +12190,7 @@
       <c r="G124" s="106">
         <v>55017.06</v>
       </c>
-      <c r="H124" s="275">
+      <c r="H124" s="33">
         <f>33595.06+34500.06</f>
         <v>68095.12</v>
       </c>
@@ -12160,22 +12204,22 @@
       </c>
       <c r="K124" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L124" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M124" s="158">
         <v>0</v>
       </c>
       <c r="N124" s="152">
         <f t="shared" si="21"/>
-        <v>21423.06</v>
+        <v>33572.06</v>
       </c>
       <c r="O124" s="114">
         <f t="shared" si="22"/>
-        <v>22709.06</v>
+        <v>35587.06</v>
       </c>
       <c r="P124" s="102">
         <f t="shared" si="23"/>
@@ -12203,7 +12247,7 @@
       <c r="G125" s="106">
         <v>57510.07</v>
       </c>
-      <c r="H125" s="275">
+      <c r="H125" s="33">
         <f>34500</f>
         <v>34500</v>
       </c>
@@ -12217,22 +12261,22 @@
       </c>
       <c r="K125" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L125" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M125" s="158">
         <v>0</v>
       </c>
       <c r="N125" s="152">
         <f t="shared" si="21"/>
-        <v>57511.07</v>
+        <v>69660.070000000007</v>
       </c>
       <c r="O125" s="114">
         <f t="shared" si="22"/>
-        <v>60963.07</v>
+        <v>73841.070000000007</v>
       </c>
       <c r="P125" s="102">
         <f t="shared" si="23"/>
@@ -12255,7 +12299,7 @@
       <c r="G126" s="106">
         <v>92604.08</v>
       </c>
-      <c r="H126" s="275">
+      <c r="H126" s="33">
         <f>58102+34500.08</f>
         <v>92602.08</v>
       </c>
@@ -12269,22 +12313,22 @@
       </c>
       <c r="K126" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L126" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M126" s="158">
         <v>0</v>
       </c>
       <c r="N126" s="152">
         <f t="shared" si="21"/>
-        <v>34503.08</v>
+        <v>46652.08</v>
       </c>
       <c r="O126" s="114">
         <f t="shared" si="22"/>
-        <v>36574.080000000002</v>
+        <v>49452.08</v>
       </c>
       <c r="P126" s="102">
         <f t="shared" si="23"/>
@@ -12307,7 +12351,7 @@
       <c r="G127" s="106">
         <v>34501.089999999997</v>
       </c>
-      <c r="H127" s="275">
+      <c r="H127" s="33">
         <f>G127</f>
         <v>34501.089999999997</v>
       </c>
@@ -12321,22 +12365,22 @@
       </c>
       <c r="K127" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L127" s="112">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M127" s="158">
         <v>0</v>
       </c>
       <c r="N127" s="152">
         <f t="shared" si="21"/>
-        <v>34501.089999999997</v>
+        <v>46650.09</v>
       </c>
       <c r="O127" s="114">
         <f t="shared" si="22"/>
-        <v>36572.089999999997</v>
+        <v>49450.09</v>
       </c>
       <c r="P127" s="102">
         <f t="shared" si="23"/>
@@ -12359,7 +12403,7 @@
       <c r="G128" s="103">
         <v>37357.1</v>
       </c>
-      <c r="H128" s="275">
+      <c r="H128" s="33">
         <f>G128</f>
         <v>37357.1</v>
       </c>
@@ -12373,22 +12417,22 @@
       </c>
       <c r="K128" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L128" s="18">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M128" s="158">
         <v>0</v>
       </c>
       <c r="N128" s="152">
         <f t="shared" si="21"/>
-        <v>34501.1</v>
+        <v>46650.1</v>
       </c>
       <c r="O128" s="5">
         <f t="shared" si="22"/>
-        <v>36572.1</v>
+        <v>49450.1</v>
       </c>
       <c r="P128" s="102">
         <f t="shared" si="23"/>
@@ -12411,7 +12455,7 @@
       <c r="G129" s="103">
         <v>34501.11</v>
       </c>
-      <c r="H129" s="275">
+      <c r="H129" s="33">
         <f>G129</f>
         <v>34501.11</v>
       </c>
@@ -12425,22 +12469,22 @@
       </c>
       <c r="K129" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L129" s="18">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M129" s="158">
         <v>0</v>
       </c>
       <c r="N129" s="152">
         <f t="shared" si="21"/>
-        <v>34501.11</v>
+        <v>46650.11</v>
       </c>
       <c r="O129" s="5">
         <f t="shared" si="22"/>
-        <v>36572.11</v>
+        <v>49450.11</v>
       </c>
       <c r="P129" s="102">
         <f t="shared" si="23"/>
@@ -12465,7 +12509,7 @@
       <c r="G130" s="103">
         <v>37357.120000000003</v>
       </c>
-      <c r="H130" s="275">
+      <c r="H130" s="33">
         <f>G130</f>
         <v>37357.120000000003</v>
       </c>
@@ -12479,22 +12523,22 @@
       </c>
       <c r="K130" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L130" s="18">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M130" s="158">
         <v>0</v>
       </c>
       <c r="N130" s="152">
         <f t="shared" si="21"/>
-        <v>34501.120000000003</v>
+        <v>46650.12</v>
       </c>
       <c r="O130" s="5">
         <f t="shared" si="22"/>
-        <v>36572.120000000003</v>
+        <v>49450.12</v>
       </c>
       <c r="P130" s="102">
         <f t="shared" si="23"/>
@@ -12519,7 +12563,7 @@
       <c r="G131" s="103">
         <v>34501.129999999997</v>
       </c>
-      <c r="H131" s="275">
+      <c r="H131" s="33">
         <v>47579.74</v>
       </c>
       <c r="I131" s="42">
@@ -12532,22 +12576,22 @@
       </c>
       <c r="K131" s="151">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>13814.4854</v>
       </c>
       <c r="L131" s="18">
         <f t="shared" si="28"/>
-        <v>34500</v>
+        <v>32834.697419999997</v>
       </c>
       <c r="M131" s="158">
         <v>0</v>
       </c>
       <c r="N131" s="152">
         <f t="shared" si="21"/>
-        <v>21422.13</v>
+        <v>33572.129999999997</v>
       </c>
       <c r="O131" s="5">
         <f t="shared" si="22"/>
-        <v>22708.13</v>
+        <v>35587.129999999997</v>
       </c>
       <c r="P131" s="102">
         <f t="shared" si="23"/>
@@ -12585,11 +12629,11 @@
       </c>
       <c r="G133" s="20">
         <f>SUM(G14:G132)</f>
-        <v>21967357.302086379</v>
+        <v>21970758.302086379</v>
       </c>
       <c r="H133" s="20">
-        <f>SUM(H14:H132)+89000</f>
-        <v>16178300.020825995</v>
+        <f>SUM(H14:H132)+29000</f>
+        <v>16415860.980825996</v>
       </c>
       <c r="I133" s="19"/>
       <c r="J133" s="41">
@@ -12599,57 +12643,57 @@
       <c r="K133" s="41"/>
       <c r="L133" s="20">
         <f>SUM(L14:L132)</f>
-        <v>15248611.856240001</v>
+        <v>14529737.466879962</v>
       </c>
       <c r="M133" s="139">
         <f>SUM(M14:M132)</f>
-        <v>450500</v>
+        <v>536244</v>
       </c>
       <c r="N133" s="21">
         <f>SUM(N14:N132)</f>
-        <v>21577233.287500381</v>
+        <v>26645423.969740376</v>
       </c>
       <c r="O133" s="20">
         <f>SUM(O14:O132)</f>
-        <v>22871932.580150399</v>
+        <v>28244215.103324801</v>
       </c>
       <c r="Q133" s="45"/>
     </row>
     <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
       <c r="L134" s="47">
         <f>L133-M1</f>
-        <v>810692.71623999998</v>
+        <v>253782.0668799635</v>
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="312"/>
-      <c r="D135" s="312"/>
-      <c r="E135" s="312"/>
-      <c r="F135" s="312"/>
-      <c r="G135" s="312"/>
-      <c r="H135" s="312"/>
-      <c r="I135" s="312"/>
-      <c r="J135" s="312"/>
-      <c r="K135" s="312"/>
-      <c r="L135" s="312"/>
-      <c r="M135" s="312"/>
-      <c r="N135" s="312"/>
-      <c r="O135" s="312"/>
+      <c r="C135" s="333"/>
+      <c r="D135" s="333"/>
+      <c r="E135" s="333"/>
+      <c r="F135" s="333"/>
+      <c r="G135" s="333"/>
+      <c r="H135" s="333"/>
+      <c r="I135" s="333"/>
+      <c r="J135" s="333"/>
+      <c r="K135" s="333"/>
+      <c r="L135" s="333"/>
+      <c r="M135" s="333"/>
+      <c r="N135" s="333"/>
+      <c r="O135" s="333"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="312"/>
-      <c r="D136" s="312"/>
-      <c r="E136" s="312"/>
-      <c r="F136" s="312"/>
-      <c r="G136" s="312"/>
-      <c r="H136" s="312"/>
-      <c r="I136" s="312"/>
-      <c r="J136" s="312"/>
-      <c r="K136" s="312"/>
-      <c r="L136" s="312"/>
-      <c r="M136" s="312"/>
-      <c r="N136" s="312"/>
-      <c r="O136" s="312"/>
+      <c r="C136" s="333"/>
+      <c r="D136" s="333"/>
+      <c r="E136" s="333"/>
+      <c r="F136" s="333"/>
+      <c r="G136" s="333"/>
+      <c r="H136" s="333"/>
+      <c r="I136" s="333"/>
+      <c r="J136" s="333"/>
+      <c r="K136" s="333"/>
+      <c r="L136" s="333"/>
+      <c r="M136" s="333"/>
+      <c r="N136" s="333"/>
+      <c r="O136" s="333"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
@@ -12667,126 +12711,126 @@
       <c r="O137" s="57"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="319" t="s">
+      <c r="C138" s="340" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="319"/>
-      <c r="E138" s="319"/>
-      <c r="F138" s="319"/>
-      <c r="G138" s="319"/>
-      <c r="H138" s="319"/>
-      <c r="I138" s="319"/>
-      <c r="J138" s="319"/>
-      <c r="K138" s="319"/>
-      <c r="L138" s="319"/>
-      <c r="M138" s="319"/>
-      <c r="N138" s="319"/>
-      <c r="O138" s="319"/>
+      <c r="D138" s="340"/>
+      <c r="E138" s="340"/>
+      <c r="F138" s="340"/>
+      <c r="G138" s="340"/>
+      <c r="H138" s="340"/>
+      <c r="I138" s="340"/>
+      <c r="J138" s="340"/>
+      <c r="K138" s="340"/>
+      <c r="L138" s="340"/>
+      <c r="M138" s="340"/>
+      <c r="N138" s="340"/>
+      <c r="O138" s="340"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="319"/>
-      <c r="D139" s="319"/>
-      <c r="E139" s="319"/>
-      <c r="F139" s="319"/>
-      <c r="G139" s="319"/>
-      <c r="H139" s="319"/>
-      <c r="I139" s="319"/>
-      <c r="J139" s="319"/>
-      <c r="K139" s="319"/>
-      <c r="L139" s="319"/>
-      <c r="M139" s="319"/>
-      <c r="N139" s="319"/>
-      <c r="O139" s="319"/>
+      <c r="C139" s="340"/>
+      <c r="D139" s="340"/>
+      <c r="E139" s="340"/>
+      <c r="F139" s="340"/>
+      <c r="G139" s="340"/>
+      <c r="H139" s="340"/>
+      <c r="I139" s="340"/>
+      <c r="J139" s="340"/>
+      <c r="K139" s="340"/>
+      <c r="L139" s="340"/>
+      <c r="M139" s="340"/>
+      <c r="N139" s="340"/>
+      <c r="O139" s="340"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="319"/>
-      <c r="D140" s="319"/>
-      <c r="E140" s="319"/>
-      <c r="F140" s="319"/>
-      <c r="G140" s="319"/>
-      <c r="H140" s="319"/>
-      <c r="I140" s="319"/>
-      <c r="J140" s="319"/>
-      <c r="K140" s="319"/>
-      <c r="L140" s="319"/>
-      <c r="M140" s="319"/>
-      <c r="N140" s="319"/>
-      <c r="O140" s="319"/>
+      <c r="C140" s="340"/>
+      <c r="D140" s="340"/>
+      <c r="E140" s="340"/>
+      <c r="F140" s="340"/>
+      <c r="G140" s="340"/>
+      <c r="H140" s="340"/>
+      <c r="I140" s="340"/>
+      <c r="J140" s="340"/>
+      <c r="K140" s="340"/>
+      <c r="L140" s="340"/>
+      <c r="M140" s="340"/>
+      <c r="N140" s="340"/>
+      <c r="O140" s="340"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="319"/>
-      <c r="D141" s="319"/>
-      <c r="E141" s="319"/>
-      <c r="F141" s="319"/>
-      <c r="G141" s="319"/>
-      <c r="H141" s="319"/>
-      <c r="I141" s="319"/>
-      <c r="J141" s="319"/>
-      <c r="K141" s="319"/>
-      <c r="L141" s="319"/>
-      <c r="M141" s="319"/>
-      <c r="N141" s="319"/>
-      <c r="O141" s="319"/>
+      <c r="C141" s="340"/>
+      <c r="D141" s="340"/>
+      <c r="E141" s="340"/>
+      <c r="F141" s="340"/>
+      <c r="G141" s="340"/>
+      <c r="H141" s="340"/>
+      <c r="I141" s="340"/>
+      <c r="J141" s="340"/>
+      <c r="K141" s="340"/>
+      <c r="L141" s="340"/>
+      <c r="M141" s="340"/>
+      <c r="N141" s="340"/>
+      <c r="O141" s="340"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="319"/>
-      <c r="D142" s="319"/>
-      <c r="E142" s="319"/>
-      <c r="F142" s="319"/>
-      <c r="G142" s="319"/>
-      <c r="H142" s="319"/>
-      <c r="I142" s="319"/>
-      <c r="J142" s="319"/>
-      <c r="K142" s="319"/>
-      <c r="L142" s="319"/>
-      <c r="M142" s="319"/>
-      <c r="N142" s="319"/>
-      <c r="O142" s="319"/>
+      <c r="C142" s="340"/>
+      <c r="D142" s="340"/>
+      <c r="E142" s="340"/>
+      <c r="F142" s="340"/>
+      <c r="G142" s="340"/>
+      <c r="H142" s="340"/>
+      <c r="I142" s="340"/>
+      <c r="J142" s="340"/>
+      <c r="K142" s="340"/>
+      <c r="L142" s="340"/>
+      <c r="M142" s="340"/>
+      <c r="N142" s="340"/>
+      <c r="O142" s="340"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="319"/>
-      <c r="D143" s="319"/>
-      <c r="E143" s="319"/>
-      <c r="F143" s="319"/>
-      <c r="G143" s="319"/>
-      <c r="H143" s="319"/>
-      <c r="I143" s="319"/>
-      <c r="J143" s="319"/>
-      <c r="K143" s="319"/>
-      <c r="L143" s="319"/>
-      <c r="M143" s="319"/>
-      <c r="N143" s="319"/>
-      <c r="O143" s="319"/>
+      <c r="C143" s="340"/>
+      <c r="D143" s="340"/>
+      <c r="E143" s="340"/>
+      <c r="F143" s="340"/>
+      <c r="G143" s="340"/>
+      <c r="H143" s="340"/>
+      <c r="I143" s="340"/>
+      <c r="J143" s="340"/>
+      <c r="K143" s="340"/>
+      <c r="L143" s="340"/>
+      <c r="M143" s="340"/>
+      <c r="N143" s="340"/>
+      <c r="O143" s="340"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="319"/>
-      <c r="D144" s="319"/>
-      <c r="E144" s="319"/>
-      <c r="F144" s="319"/>
-      <c r="G144" s="319"/>
-      <c r="H144" s="319"/>
-      <c r="I144" s="319"/>
-      <c r="J144" s="319"/>
-      <c r="K144" s="319"/>
-      <c r="L144" s="319"/>
-      <c r="M144" s="319"/>
-      <c r="N144" s="319"/>
-      <c r="O144" s="319"/>
+      <c r="C144" s="340"/>
+      <c r="D144" s="340"/>
+      <c r="E144" s="340"/>
+      <c r="F144" s="340"/>
+      <c r="G144" s="340"/>
+      <c r="H144" s="340"/>
+      <c r="I144" s="340"/>
+      <c r="J144" s="340"/>
+      <c r="K144" s="340"/>
+      <c r="L144" s="340"/>
+      <c r="M144" s="340"/>
+      <c r="N144" s="340"/>
+      <c r="O144" s="340"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="319"/>
-      <c r="D145" s="319"/>
-      <c r="E145" s="319"/>
-      <c r="F145" s="319"/>
-      <c r="G145" s="319"/>
-      <c r="H145" s="319"/>
-      <c r="I145" s="319"/>
-      <c r="J145" s="319"/>
-      <c r="K145" s="319"/>
-      <c r="L145" s="319"/>
-      <c r="M145" s="319"/>
-      <c r="N145" s="319"/>
-      <c r="O145" s="319"/>
+      <c r="C145" s="340"/>
+      <c r="D145" s="340"/>
+      <c r="E145" s="340"/>
+      <c r="F145" s="340"/>
+      <c r="G145" s="340"/>
+      <c r="H145" s="340"/>
+      <c r="I145" s="340"/>
+      <c r="J145" s="340"/>
+      <c r="K145" s="340"/>
+      <c r="L145" s="340"/>
+      <c r="M145" s="340"/>
+      <c r="N145" s="340"/>
+      <c r="O145" s="340"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
@@ -12819,115 +12863,115 @@
       <c r="O147" s="57"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="311" t="s">
+      <c r="C148" s="332" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="311"/>
-      <c r="E148" s="311"/>
-      <c r="F148" s="311"/>
-      <c r="G148" s="311"/>
-      <c r="H148" s="311"/>
-      <c r="I148" s="311"/>
-      <c r="J148" s="311"/>
-      <c r="K148" s="311"/>
-      <c r="L148" s="311"/>
-      <c r="M148" s="311"/>
-      <c r="N148" s="311"/>
-      <c r="O148" s="311"/>
+      <c r="D148" s="332"/>
+      <c r="E148" s="332"/>
+      <c r="F148" s="332"/>
+      <c r="G148" s="332"/>
+      <c r="H148" s="332"/>
+      <c r="I148" s="332"/>
+      <c r="J148" s="332"/>
+      <c r="K148" s="332"/>
+      <c r="L148" s="332"/>
+      <c r="M148" s="332"/>
+      <c r="N148" s="332"/>
+      <c r="O148" s="332"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="311"/>
-      <c r="D149" s="311"/>
-      <c r="E149" s="311"/>
-      <c r="F149" s="311"/>
-      <c r="G149" s="311"/>
-      <c r="H149" s="311"/>
-      <c r="I149" s="311"/>
-      <c r="J149" s="311"/>
-      <c r="K149" s="311"/>
-      <c r="L149" s="311"/>
-      <c r="M149" s="311"/>
-      <c r="N149" s="311"/>
-      <c r="O149" s="311"/>
+      <c r="C149" s="332"/>
+      <c r="D149" s="332"/>
+      <c r="E149" s="332"/>
+      <c r="F149" s="332"/>
+      <c r="G149" s="332"/>
+      <c r="H149" s="332"/>
+      <c r="I149" s="332"/>
+      <c r="J149" s="332"/>
+      <c r="K149" s="332"/>
+      <c r="L149" s="332"/>
+      <c r="M149" s="332"/>
+      <c r="N149" s="332"/>
+      <c r="O149" s="332"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="311"/>
-      <c r="D150" s="311"/>
-      <c r="E150" s="311"/>
-      <c r="F150" s="311"/>
-      <c r="G150" s="311"/>
-      <c r="H150" s="311"/>
-      <c r="I150" s="311"/>
-      <c r="J150" s="311"/>
-      <c r="K150" s="311"/>
-      <c r="L150" s="311"/>
-      <c r="M150" s="311"/>
-      <c r="N150" s="311"/>
-      <c r="O150" s="311"/>
+      <c r="C150" s="332"/>
+      <c r="D150" s="332"/>
+      <c r="E150" s="332"/>
+      <c r="F150" s="332"/>
+      <c r="G150" s="332"/>
+      <c r="H150" s="332"/>
+      <c r="I150" s="332"/>
+      <c r="J150" s="332"/>
+      <c r="K150" s="332"/>
+      <c r="L150" s="332"/>
+      <c r="M150" s="332"/>
+      <c r="N150" s="332"/>
+      <c r="O150" s="332"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
-        <v>-810692.71623999998</v>
+        <v>-253782.0668799635</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="311"/>
-      <c r="D151" s="311"/>
-      <c r="E151" s="311"/>
-      <c r="F151" s="311"/>
-      <c r="G151" s="311"/>
-      <c r="H151" s="311"/>
-      <c r="I151" s="311"/>
-      <c r="J151" s="311"/>
-      <c r="K151" s="311"/>
-      <c r="L151" s="311"/>
-      <c r="M151" s="311"/>
-      <c r="N151" s="311"/>
-      <c r="O151" s="311"/>
+      <c r="C151" s="332"/>
+      <c r="D151" s="332"/>
+      <c r="E151" s="332"/>
+      <c r="F151" s="332"/>
+      <c r="G151" s="332"/>
+      <c r="H151" s="332"/>
+      <c r="I151" s="332"/>
+      <c r="J151" s="332"/>
+      <c r="K151" s="332"/>
+      <c r="L151" s="332"/>
+      <c r="M151" s="332"/>
+      <c r="N151" s="332"/>
+      <c r="O151" s="332"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="311"/>
-      <c r="D152" s="311"/>
-      <c r="E152" s="311"/>
-      <c r="F152" s="311"/>
-      <c r="G152" s="311"/>
-      <c r="H152" s="311"/>
-      <c r="I152" s="311"/>
-      <c r="J152" s="311"/>
-      <c r="K152" s="311"/>
-      <c r="L152" s="311"/>
-      <c r="M152" s="311"/>
-      <c r="N152" s="311"/>
-      <c r="O152" s="311"/>
+      <c r="C152" s="332"/>
+      <c r="D152" s="332"/>
+      <c r="E152" s="332"/>
+      <c r="F152" s="332"/>
+      <c r="G152" s="332"/>
+      <c r="H152" s="332"/>
+      <c r="I152" s="332"/>
+      <c r="J152" s="332"/>
+      <c r="K152" s="332"/>
+      <c r="L152" s="332"/>
+      <c r="M152" s="332"/>
+      <c r="N152" s="332"/>
+      <c r="O152" s="332"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="311"/>
-      <c r="D153" s="311"/>
-      <c r="E153" s="311"/>
-      <c r="F153" s="311"/>
-      <c r="G153" s="311"/>
-      <c r="H153" s="311"/>
-      <c r="I153" s="311"/>
-      <c r="J153" s="311"/>
-      <c r="K153" s="311"/>
-      <c r="L153" s="311"/>
-      <c r="M153" s="311"/>
-      <c r="N153" s="311"/>
-      <c r="O153" s="311"/>
+      <c r="C153" s="332"/>
+      <c r="D153" s="332"/>
+      <c r="E153" s="332"/>
+      <c r="F153" s="332"/>
+      <c r="G153" s="332"/>
+      <c r="H153" s="332"/>
+      <c r="I153" s="332"/>
+      <c r="J153" s="332"/>
+      <c r="K153" s="332"/>
+      <c r="L153" s="332"/>
+      <c r="M153" s="332"/>
+      <c r="N153" s="332"/>
+      <c r="O153" s="332"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="311"/>
-      <c r="D154" s="311"/>
-      <c r="E154" s="311"/>
-      <c r="F154" s="311"/>
-      <c r="G154" s="311"/>
-      <c r="H154" s="311"/>
-      <c r="I154" s="311"/>
-      <c r="J154" s="311"/>
-      <c r="K154" s="311"/>
-      <c r="L154" s="311"/>
-      <c r="M154" s="311"/>
-      <c r="N154" s="311"/>
-      <c r="O154" s="311"/>
+      <c r="C154" s="332"/>
+      <c r="D154" s="332"/>
+      <c r="E154" s="332"/>
+      <c r="F154" s="332"/>
+      <c r="G154" s="332"/>
+      <c r="H154" s="332"/>
+      <c r="I154" s="332"/>
+      <c r="J154" s="332"/>
+      <c r="K154" s="332"/>
+      <c r="L154" s="332"/>
+      <c r="M154" s="332"/>
+      <c r="N154" s="332"/>
+      <c r="O154" s="332"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -12987,61 +13031,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="345" t="s">
+      <c r="A1" s="369" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
-      <c r="F1" s="345"/>
-      <c r="G1" s="345"/>
-      <c r="H1" s="345"/>
-      <c r="I1" s="345"/>
-      <c r="J1" s="345"/>
-      <c r="K1" s="345"/>
-      <c r="L1" s="345"/>
-      <c r="M1" s="345"/>
-      <c r="N1" s="345"/>
-      <c r="O1" s="346"/>
+      <c r="B1" s="369"/>
+      <c r="C1" s="369"/>
+      <c r="D1" s="369"/>
+      <c r="E1" s="369"/>
+      <c r="F1" s="369"/>
+      <c r="G1" s="369"/>
+      <c r="H1" s="369"/>
+      <c r="I1" s="369"/>
+      <c r="J1" s="369"/>
+      <c r="K1" s="369"/>
+      <c r="L1" s="369"/>
+      <c r="M1" s="369"/>
+      <c r="N1" s="369"/>
+      <c r="O1" s="370"/>
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="347"/>
-      <c r="B2" s="347"/>
-      <c r="C2" s="347"/>
-      <c r="D2" s="347"/>
-      <c r="E2" s="347"/>
-      <c r="F2" s="347"/>
-      <c r="G2" s="347"/>
-      <c r="H2" s="347"/>
-      <c r="I2" s="347"/>
-      <c r="J2" s="347"/>
-      <c r="K2" s="347"/>
-      <c r="L2" s="347"/>
-      <c r="M2" s="347"/>
-      <c r="N2" s="347"/>
-      <c r="O2" s="348"/>
+      <c r="A2" s="371"/>
+      <c r="B2" s="371"/>
+      <c r="C2" s="371"/>
+      <c r="D2" s="371"/>
+      <c r="E2" s="371"/>
+      <c r="F2" s="371"/>
+      <c r="G2" s="371"/>
+      <c r="H2" s="371"/>
+      <c r="I2" s="371"/>
+      <c r="J2" s="371"/>
+      <c r="K2" s="371"/>
+      <c r="L2" s="371"/>
+      <c r="M2" s="371"/>
+      <c r="N2" s="371"/>
+      <c r="O2" s="372"/>
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:27" s="190" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="342" t="s">
+      <c r="A3" s="366" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="343"/>
-      <c r="C3" s="343"/>
-      <c r="D3" s="343"/>
-      <c r="E3" s="343"/>
-      <c r="F3" s="343"/>
-      <c r="G3" s="343"/>
-      <c r="H3" s="343"/>
-      <c r="I3" s="343"/>
-      <c r="J3" s="343"/>
-      <c r="K3" s="343"/>
-      <c r="L3" s="343"/>
-      <c r="M3" s="343"/>
-      <c r="N3" s="343"/>
-      <c r="O3" s="344"/>
+      <c r="B3" s="367"/>
+      <c r="C3" s="367"/>
+      <c r="D3" s="367"/>
+      <c r="E3" s="367"/>
+      <c r="F3" s="367"/>
+      <c r="G3" s="367"/>
+      <c r="H3" s="367"/>
+      <c r="I3" s="367"/>
+      <c r="J3" s="367"/>
+      <c r="K3" s="367"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="367"/>
+      <c r="N3" s="367"/>
+      <c r="O3" s="368"/>
       <c r="P3" s="191"/>
       <c r="Q3" s="191"/>
       <c r="R3" s="191"/>
@@ -13056,85 +13100,85 @@
       <c r="AA3" s="191"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="304" t="s">
+      <c r="A4" s="325" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="304" t="s">
+      <c r="B4" s="325" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="304" t="s">
+      <c r="C4" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="304" t="s">
+      <c r="D4" s="325" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="301" t="s">
+      <c r="E4" s="322" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="301" t="s">
+      <c r="F4" s="322" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="301" t="s">
+      <c r="G4" s="322" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="301" t="s">
+      <c r="H4" s="322" t="s">
         <v>336</v>
       </c>
-      <c r="I4" s="301" t="s">
+      <c r="I4" s="322" t="s">
         <v>345</v>
       </c>
-      <c r="J4" s="349" t="s">
+      <c r="J4" s="373" t="s">
         <v>332</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="353" t="s">
+      <c r="L4" s="363" t="s">
         <v>342</v>
       </c>
-      <c r="M4" s="301" t="s">
+      <c r="M4" s="322" t="s">
         <v>343</v>
       </c>
-      <c r="N4" s="301" t="s">
+      <c r="N4" s="322" t="s">
         <v>333</v>
       </c>
-      <c r="O4" s="301" t="s">
+      <c r="O4" s="322" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="305"/>
-      <c r="B5" s="305"/>
-      <c r="C5" s="305"/>
-      <c r="D5" s="305"/>
-      <c r="E5" s="302"/>
-      <c r="F5" s="302"/>
-      <c r="G5" s="302"/>
-      <c r="H5" s="302"/>
-      <c r="I5" s="302"/>
-      <c r="J5" s="350"/>
+      <c r="A5" s="326"/>
+      <c r="B5" s="326"/>
+      <c r="C5" s="326"/>
+      <c r="D5" s="326"/>
+      <c r="E5" s="323"/>
+      <c r="F5" s="323"/>
+      <c r="G5" s="323"/>
+      <c r="H5" s="323"/>
+      <c r="I5" s="323"/>
+      <c r="J5" s="374"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="354"/>
-      <c r="M5" s="302"/>
-      <c r="N5" s="302"/>
-      <c r="O5" s="302"/>
+      <c r="L5" s="364"/>
+      <c r="M5" s="323"/>
+      <c r="N5" s="323"/>
+      <c r="O5" s="323"/>
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="352"/>
-      <c r="B6" s="352"/>
-      <c r="C6" s="352"/>
-      <c r="D6" s="352"/>
-      <c r="E6" s="341"/>
-      <c r="F6" s="341"/>
-      <c r="G6" s="341"/>
-      <c r="H6" s="341"/>
-      <c r="I6" s="341"/>
-      <c r="J6" s="351"/>
+      <c r="A6" s="376"/>
+      <c r="B6" s="376"/>
+      <c r="C6" s="376"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="362"/>
+      <c r="F6" s="362"/>
+      <c r="G6" s="362"/>
+      <c r="H6" s="362"/>
+      <c r="I6" s="362"/>
+      <c r="J6" s="375"/>
       <c r="K6" s="160"/>
-      <c r="L6" s="355"/>
-      <c r="M6" s="341"/>
-      <c r="N6" s="341"/>
-      <c r="O6" s="341"/>
+      <c r="L6" s="365"/>
+      <c r="M6" s="362"/>
+      <c r="N6" s="362"/>
+      <c r="O6" s="362"/>
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13189,8 +13233,8 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="310"/>
-      <c r="S7" s="310"/>
+      <c r="R7" s="331"/>
+      <c r="S7" s="331"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="161" t="s">
@@ -13244,8 +13288,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="310"/>
-      <c r="S8" s="310"/>
+      <c r="R8" s="331"/>
+      <c r="S8" s="331"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="161" t="s">
@@ -14031,7 +14075,7 @@
       <c r="K23" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L23" s="370">
+      <c r="L23" s="278">
         <f>J23</f>
         <v>189591.12</v>
       </c>
@@ -14352,7 +14396,7 @@
       <c r="K29" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L29" s="370">
+      <c r="L29" s="278">
         <f>J29</f>
         <v>189591.18</v>
       </c>
@@ -14975,7 +15019,7 @@
       <c r="K35" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L35" s="370">
+      <c r="L35" s="278">
         <f>J35</f>
         <v>189591.24</v>
       </c>
@@ -16373,7 +16417,7 @@
       <c r="K59" s="114">
         <v>-33257.557922213571</v>
       </c>
-      <c r="L59" s="370">
+      <c r="L59" s="278">
         <f>I59</f>
         <v>137927.48000000001</v>
       </c>
@@ -17577,10 +17621,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="L4:L6"/>
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17594,6 +17634,10 @@
     <mergeCell ref="D4:D6"/>
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
+    <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17619,8 +17663,8 @@
       <c r="H2" s="195"/>
       <c r="I2" s="195"/>
       <c r="J2" s="196"/>
-      <c r="K2" s="371"/>
-      <c r="L2" s="371"/>
+      <c r="K2" s="279"/>
+      <c r="L2" s="279"/>
       <c r="M2" s="53"/>
     </row>
     <row r="3" spans="3:13" x14ac:dyDescent="0.25">
@@ -17638,8 +17682,8 @@
       <c r="H3" s="197"/>
       <c r="I3" s="198"/>
       <c r="J3" s="199"/>
-      <c r="K3" s="373"/>
-      <c r="L3" s="373"/>
+      <c r="K3" s="280"/>
+      <c r="L3" s="280"/>
       <c r="M3" s="257"/>
     </row>
     <row r="4" spans="3:13" x14ac:dyDescent="0.25">
@@ -17661,8 +17705,8 @@
       </c>
       <c r="I4" s="198"/>
       <c r="J4" s="199"/>
-      <c r="K4" s="373"/>
-      <c r="L4" s="373"/>
+      <c r="K4" s="280"/>
+      <c r="L4" s="280"/>
       <c r="M4" s="257"/>
     </row>
     <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17676,49 +17720,49 @@
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
       <c r="J5" s="200"/>
-      <c r="K5" s="373"/>
-      <c r="L5" s="373"/>
+      <c r="K5" s="280"/>
+      <c r="L5" s="280"/>
       <c r="M5" s="257"/>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="356" t="s">
+      <c r="C6" s="377" t="s">
         <v>374</v>
       </c>
-      <c r="D6" s="357"/>
-      <c r="E6" s="357"/>
-      <c r="F6" s="357"/>
-      <c r="G6" s="357"/>
-      <c r="H6" s="357"/>
-      <c r="I6" s="357"/>
-      <c r="J6" s="358"/>
-      <c r="K6" s="371"/>
-      <c r="L6" s="371"/>
+      <c r="D6" s="378"/>
+      <c r="E6" s="378"/>
+      <c r="F6" s="378"/>
+      <c r="G6" s="378"/>
+      <c r="H6" s="378"/>
+      <c r="I6" s="378"/>
+      <c r="J6" s="379"/>
+      <c r="K6" s="279"/>
+      <c r="L6" s="279"/>
       <c r="M6" s="53"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="359"/>
-      <c r="D7" s="360"/>
-      <c r="E7" s="360"/>
-      <c r="F7" s="360"/>
-      <c r="G7" s="360"/>
-      <c r="H7" s="360"/>
-      <c r="I7" s="360"/>
-      <c r="J7" s="361"/>
-      <c r="K7" s="371"/>
-      <c r="L7" s="371"/>
+      <c r="C7" s="380"/>
+      <c r="D7" s="381"/>
+      <c r="E7" s="381"/>
+      <c r="F7" s="381"/>
+      <c r="G7" s="381"/>
+      <c r="H7" s="381"/>
+      <c r="I7" s="381"/>
+      <c r="J7" s="382"/>
+      <c r="K7" s="279"/>
+      <c r="L7" s="279"/>
       <c r="M7" s="53"/>
     </row>
     <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="362"/>
-      <c r="D8" s="363"/>
-      <c r="E8" s="363"/>
-      <c r="F8" s="363"/>
-      <c r="G8" s="363"/>
-      <c r="H8" s="363"/>
-      <c r="I8" s="363"/>
-      <c r="J8" s="364"/>
-      <c r="K8" s="371"/>
-      <c r="L8" s="371"/>
+      <c r="C8" s="383"/>
+      <c r="D8" s="384"/>
+      <c r="E8" s="384"/>
+      <c r="F8" s="384"/>
+      <c r="G8" s="384"/>
+      <c r="H8" s="384"/>
+      <c r="I8" s="384"/>
+      <c r="J8" s="385"/>
+      <c r="K8" s="279"/>
+      <c r="L8" s="279"/>
       <c r="M8" s="53"/>
     </row>
     <row r="9" spans="3:13" x14ac:dyDescent="0.25">
@@ -17757,8 +17801,8 @@
       <c r="H12" s="197"/>
       <c r="I12" s="198"/>
       <c r="J12" s="199"/>
-      <c r="K12" s="371"/>
-      <c r="L12" s="371"/>
+      <c r="K12" s="279"/>
+      <c r="L12" s="279"/>
     </row>
     <row r="13" spans="3:13" x14ac:dyDescent="0.25">
       <c r="C13" s="262" t="s">
@@ -17779,8 +17823,8 @@
       </c>
       <c r="I13" s="198"/>
       <c r="J13" s="199"/>
-      <c r="K13" s="371"/>
-      <c r="L13" s="371"/>
+      <c r="K13" s="279"/>
+      <c r="L13" s="279"/>
     </row>
     <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C14" s="192" t="s">
@@ -17793,42 +17837,42 @@
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="J14" s="200"/>
-      <c r="K14" s="371"/>
-      <c r="L14" s="371"/>
+      <c r="K14" s="279"/>
+      <c r="L14" s="279"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="356" t="s">
+      <c r="C15" s="377" t="s">
         <v>376</v>
       </c>
-      <c r="D15" s="357"/>
-      <c r="E15" s="357"/>
-      <c r="F15" s="357"/>
-      <c r="G15" s="357"/>
-      <c r="H15" s="357"/>
-      <c r="I15" s="357"/>
-      <c r="J15" s="358"/>
-      <c r="K15" s="371"/>
-      <c r="L15" s="371"/>
+      <c r="D15" s="378"/>
+      <c r="E15" s="378"/>
+      <c r="F15" s="378"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="379"/>
+      <c r="K15" s="279"/>
+      <c r="L15" s="279"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="359"/>
-      <c r="D16" s="360"/>
-      <c r="E16" s="360"/>
-      <c r="F16" s="360"/>
-      <c r="G16" s="360"/>
-      <c r="H16" s="360"/>
-      <c r="I16" s="360"/>
-      <c r="J16" s="361"/>
+      <c r="C16" s="380"/>
+      <c r="D16" s="381"/>
+      <c r="E16" s="381"/>
+      <c r="F16" s="381"/>
+      <c r="G16" s="381"/>
+      <c r="H16" s="381"/>
+      <c r="I16" s="381"/>
+      <c r="J16" s="382"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="362"/>
-      <c r="D17" s="363"/>
-      <c r="E17" s="363"/>
-      <c r="F17" s="363"/>
-      <c r="G17" s="363"/>
-      <c r="H17" s="363"/>
-      <c r="I17" s="363"/>
-      <c r="J17" s="364"/>
+      <c r="C17" s="383"/>
+      <c r="D17" s="384"/>
+      <c r="E17" s="384"/>
+      <c r="F17" s="384"/>
+      <c r="G17" s="384"/>
+      <c r="H17" s="384"/>
+      <c r="I17" s="384"/>
+      <c r="J17" s="385"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
@@ -17845,8 +17889,8 @@
       <c r="H20" s="195"/>
       <c r="I20" s="195"/>
       <c r="J20" s="196"/>
-      <c r="K20" s="371"/>
-      <c r="L20" s="371"/>
+      <c r="K20" s="279"/>
+      <c r="L20" s="279"/>
     </row>
     <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="268" t="s">
@@ -17863,8 +17907,8 @@
       <c r="H21" s="197"/>
       <c r="I21" s="198"/>
       <c r="J21" s="199"/>
-      <c r="K21" s="371"/>
-      <c r="L21" s="371"/>
+      <c r="K21" s="279"/>
+      <c r="L21" s="279"/>
     </row>
     <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="268" t="s">
@@ -17885,8 +17929,8 @@
       </c>
       <c r="I22" s="198"/>
       <c r="J22" s="199"/>
-      <c r="K22" s="371"/>
-      <c r="L22" s="371"/>
+      <c r="K22" s="279"/>
+      <c r="L22" s="279"/>
     </row>
     <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="192" t="s">
@@ -17899,44 +17943,44 @@
       <c r="H23" s="53"/>
       <c r="I23" s="53"/>
       <c r="J23" s="200"/>
-      <c r="K23" s="371"/>
-      <c r="L23" s="371"/>
+      <c r="K23" s="279"/>
+      <c r="L23" s="279"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="356" t="s">
+      <c r="C24" s="377" t="s">
         <v>378</v>
       </c>
-      <c r="D24" s="357"/>
-      <c r="E24" s="357"/>
-      <c r="F24" s="357"/>
-      <c r="G24" s="357"/>
-      <c r="H24" s="357"/>
-      <c r="I24" s="357"/>
-      <c r="J24" s="358"/>
-      <c r="K24" s="371"/>
-      <c r="L24" s="371"/>
+      <c r="D24" s="378"/>
+      <c r="E24" s="378"/>
+      <c r="F24" s="378"/>
+      <c r="G24" s="378"/>
+      <c r="H24" s="378"/>
+      <c r="I24" s="378"/>
+      <c r="J24" s="379"/>
+      <c r="K24" s="279"/>
+      <c r="L24" s="279"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="359"/>
-      <c r="D25" s="360"/>
-      <c r="E25" s="360"/>
-      <c r="F25" s="360"/>
-      <c r="G25" s="360"/>
-      <c r="H25" s="360"/>
-      <c r="I25" s="360"/>
-      <c r="J25" s="361"/>
-      <c r="K25" s="371"/>
-      <c r="L25" s="371"/>
+      <c r="C25" s="380"/>
+      <c r="D25" s="381"/>
+      <c r="E25" s="381"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="381"/>
+      <c r="J25" s="382"/>
+      <c r="K25" s="279"/>
+      <c r="L25" s="279"/>
     </row>
     <row r="26" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="362"/>
-      <c r="D26" s="363"/>
-      <c r="E26" s="363"/>
-      <c r="F26" s="363"/>
-      <c r="G26" s="363"/>
-      <c r="H26" s="363"/>
-      <c r="I26" s="363"/>
-      <c r="J26" s="364"/>
+      <c r="C26" s="383"/>
+      <c r="D26" s="384"/>
+      <c r="E26" s="384"/>
+      <c r="F26" s="384"/>
+      <c r="G26" s="384"/>
+      <c r="H26" s="384"/>
+      <c r="I26" s="384"/>
+      <c r="J26" s="385"/>
     </row>
     <row r="28" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
@@ -17971,7 +18015,7 @@
       </c>
       <c r="I30" s="198"/>
       <c r="J30" s="199"/>
-      <c r="K30" s="371"/>
+      <c r="K30" s="279"/>
     </row>
     <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" s="272" t="s">
@@ -17992,7 +18036,7 @@
       </c>
       <c r="I31" s="198"/>
       <c r="J31" s="199"/>
-      <c r="K31" s="371"/>
+      <c r="K31" s="279"/>
     </row>
     <row r="32" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C32" s="192" t="s">
@@ -18005,40 +18049,40 @@
       <c r="H32" s="53"/>
       <c r="I32" s="53"/>
       <c r="J32" s="200"/>
-      <c r="K32" s="371"/>
+      <c r="K32" s="279"/>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="356" t="s">
+      <c r="C33" s="377" t="s">
         <v>381</v>
       </c>
-      <c r="D33" s="357"/>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
-      <c r="G33" s="357"/>
-      <c r="H33" s="357"/>
-      <c r="I33" s="357"/>
-      <c r="J33" s="358"/>
-      <c r="K33" s="371"/>
+      <c r="D33" s="378"/>
+      <c r="E33" s="378"/>
+      <c r="F33" s="378"/>
+      <c r="G33" s="378"/>
+      <c r="H33" s="378"/>
+      <c r="I33" s="378"/>
+      <c r="J33" s="379"/>
+      <c r="K33" s="279"/>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="359"/>
-      <c r="D34" s="360"/>
-      <c r="E34" s="360"/>
-      <c r="F34" s="360"/>
-      <c r="G34" s="360"/>
-      <c r="H34" s="360"/>
-      <c r="I34" s="360"/>
-      <c r="J34" s="361"/>
+      <c r="C34" s="380"/>
+      <c r="D34" s="381"/>
+      <c r="E34" s="381"/>
+      <c r="F34" s="381"/>
+      <c r="G34" s="381"/>
+      <c r="H34" s="381"/>
+      <c r="I34" s="381"/>
+      <c r="J34" s="382"/>
     </row>
     <row r="35" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="362"/>
-      <c r="D35" s="363"/>
-      <c r="E35" s="363"/>
-      <c r="F35" s="363"/>
-      <c r="G35" s="363"/>
-      <c r="H35" s="363"/>
-      <c r="I35" s="363"/>
-      <c r="J35" s="364"/>
+      <c r="C35" s="383"/>
+      <c r="D35" s="384"/>
+      <c r="E35" s="384"/>
+      <c r="F35" s="384"/>
+      <c r="G35" s="384"/>
+      <c r="H35" s="384"/>
+      <c r="I35" s="384"/>
+      <c r="J35" s="385"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E73E562-1792-401D-A8F9-221228086463}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3989BDF4-75DB-4C7C-B26D-4343F0C7184E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="416">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1286,6 +1286,9 @@
   </si>
   <si>
     <t>Se adeudan a la desarrolladora las cuotas correspondientes a ARBA de los meses de mayo y junio. Debido a la falta de disponibilidad de fondos, la desarrolladora aceptó diferir el cobro de dichos importes para permitir que el consorcio pudiera afrontar gastos de carácter obligatorio e indispensables para su normal funcionamiento</t>
+  </si>
+  <si>
+    <t>Transferencia Rocha Sabrina</t>
   </si>
 </sst>
 </file>
@@ -2007,7 +2010,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="386">
+  <cellXfs count="384">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2379,11 +2382,24 @@
     <xf numFmtId="44" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="4" fillId="9" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2417,12 +2433,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2485,44 +2495,14 @@
     <xf numFmtId="164" fontId="28" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2541,6 +2521,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2614,8 +2603,32 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2645,18 +2658,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="20" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3210,108 +3211,108 @@
     <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="319" t="s">
+      <c r="A14" s="283" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="319"/>
-      <c r="C14" s="319"/>
-      <c r="D14" s="319"/>
-      <c r="E14" s="319"/>
-      <c r="F14" s="319"/>
-      <c r="G14" s="319"/>
-      <c r="H14" s="319"/>
-      <c r="I14" s="319"/>
-      <c r="J14" s="319"/>
+      <c r="B14" s="283"/>
+      <c r="C14" s="283"/>
+      <c r="D14" s="283"/>
+      <c r="E14" s="283"/>
+      <c r="F14" s="283"/>
+      <c r="G14" s="283"/>
+      <c r="H14" s="283"/>
+      <c r="I14" s="283"/>
+      <c r="J14" s="283"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="319"/>
-      <c r="B15" s="319"/>
-      <c r="C15" s="319"/>
-      <c r="D15" s="319"/>
-      <c r="E15" s="319"/>
-      <c r="F15" s="319"/>
-      <c r="G15" s="319"/>
-      <c r="H15" s="319"/>
-      <c r="I15" s="319"/>
-      <c r="J15" s="319"/>
+      <c r="A15" s="283"/>
+      <c r="B15" s="283"/>
+      <c r="C15" s="283"/>
+      <c r="D15" s="283"/>
+      <c r="E15" s="283"/>
+      <c r="F15" s="283"/>
+      <c r="G15" s="283"/>
+      <c r="H15" s="283"/>
+      <c r="I15" s="283"/>
+      <c r="J15" s="283"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="319"/>
-      <c r="B16" s="319"/>
-      <c r="C16" s="319"/>
-      <c r="D16" s="319"/>
-      <c r="E16" s="319"/>
-      <c r="F16" s="319"/>
-      <c r="G16" s="319"/>
-      <c r="H16" s="319"/>
-      <c r="I16" s="319"/>
-      <c r="J16" s="319"/>
+      <c r="A16" s="283"/>
+      <c r="B16" s="283"/>
+      <c r="C16" s="283"/>
+      <c r="D16" s="283"/>
+      <c r="E16" s="283"/>
+      <c r="F16" s="283"/>
+      <c r="G16" s="283"/>
+      <c r="H16" s="283"/>
+      <c r="I16" s="283"/>
+      <c r="J16" s="283"/>
     </row>
     <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="319"/>
-      <c r="B17" s="319"/>
-      <c r="C17" s="319"/>
-      <c r="D17" s="319"/>
-      <c r="E17" s="319"/>
-      <c r="F17" s="319"/>
-      <c r="G17" s="319"/>
-      <c r="H17" s="319"/>
-      <c r="I17" s="319"/>
-      <c r="J17" s="319"/>
+      <c r="A17" s="283"/>
+      <c r="B17" s="283"/>
+      <c r="C17" s="283"/>
+      <c r="D17" s="283"/>
+      <c r="E17" s="283"/>
+      <c r="F17" s="283"/>
+      <c r="G17" s="283"/>
+      <c r="H17" s="283"/>
+      <c r="I17" s="283"/>
+      <c r="J17" s="283"/>
     </row>
     <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="319"/>
-      <c r="B18" s="319"/>
-      <c r="C18" s="319"/>
-      <c r="D18" s="319"/>
-      <c r="E18" s="319"/>
-      <c r="F18" s="319"/>
-      <c r="G18" s="319"/>
-      <c r="H18" s="319"/>
-      <c r="I18" s="319"/>
-      <c r="J18" s="319"/>
+      <c r="A18" s="283"/>
+      <c r="B18" s="283"/>
+      <c r="C18" s="283"/>
+      <c r="D18" s="283"/>
+      <c r="E18" s="283"/>
+      <c r="F18" s="283"/>
+      <c r="G18" s="283"/>
+      <c r="H18" s="283"/>
+      <c r="I18" s="283"/>
+      <c r="J18" s="283"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="320" t="s">
+      <c r="A20" s="284" t="s">
         <v>382</v>
       </c>
-      <c r="B20" s="320"/>
-      <c r="C20" s="320"/>
-      <c r="D20" s="320"/>
-      <c r="E20" s="320"/>
-      <c r="F20" s="320"/>
-      <c r="G20" s="320"/>
-      <c r="H20" s="320"/>
-      <c r="I20" s="320"/>
-      <c r="J20" s="320"/>
+      <c r="B20" s="284"/>
+      <c r="C20" s="284"/>
+      <c r="D20" s="284"/>
+      <c r="E20" s="284"/>
+      <c r="F20" s="284"/>
+      <c r="G20" s="284"/>
+      <c r="H20" s="284"/>
+      <c r="I20" s="284"/>
+      <c r="J20" s="284"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="320"/>
-      <c r="B21" s="320"/>
-      <c r="C21" s="320"/>
-      <c r="D21" s="320"/>
-      <c r="E21" s="320"/>
-      <c r="F21" s="320"/>
-      <c r="G21" s="320"/>
-      <c r="H21" s="320"/>
-      <c r="I21" s="320"/>
-      <c r="J21" s="320"/>
+      <c r="A21" s="284"/>
+      <c r="B21" s="284"/>
+      <c r="C21" s="284"/>
+      <c r="D21" s="284"/>
+      <c r="E21" s="284"/>
+      <c r="F21" s="284"/>
+      <c r="G21" s="284"/>
+      <c r="H21" s="284"/>
+      <c r="I21" s="284"/>
+      <c r="J21" s="284"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="320"/>
-      <c r="B22" s="320"/>
-      <c r="C22" s="320"/>
-      <c r="D22" s="320"/>
-      <c r="E22" s="320"/>
-      <c r="F22" s="320"/>
-      <c r="G22" s="320"/>
-      <c r="H22" s="320"/>
-      <c r="I22" s="320"/>
-      <c r="J22" s="320"/>
+      <c r="A22" s="284"/>
+      <c r="B22" s="284"/>
+      <c r="C22" s="284"/>
+      <c r="D22" s="284"/>
+      <c r="E22" s="284"/>
+      <c r="F22" s="284"/>
+      <c r="G22" s="284"/>
+      <c r="H22" s="284"/>
+      <c r="I22" s="284"/>
+      <c r="J22" s="284"/>
     </row>
     <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H23" s="69"/>
@@ -3780,8 +3781,8 @@
       <c r="L44" s="50"/>
     </row>
     <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="297"/>
-      <c r="B45" s="298"/>
+      <c r="A45" s="285"/>
+      <c r="B45" s="286"/>
       <c r="C45" s="181"/>
       <c r="D45" s="33"/>
       <c r="E45" s="212"/>
@@ -4010,10 +4011,10 @@
       <c r="N51" s="64"/>
     </row>
     <row r="52" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="285" t="s">
+      <c r="A52" s="287" t="s">
         <v>386</v>
       </c>
-      <c r="B52" s="321"/>
+      <c r="B52" s="288"/>
       <c r="C52" s="141" t="s">
         <v>395</v>
       </c>
@@ -4288,10 +4289,10 @@
       </c>
     </row>
     <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="285" t="s">
+      <c r="A61" s="287" t="s">
         <v>396</v>
       </c>
-      <c r="B61" s="321"/>
+      <c r="B61" s="288"/>
       <c r="C61" s="33" t="s">
         <v>397</v>
       </c>
@@ -4311,10 +4312,10 @@
       <c r="L61" s="54"/>
     </row>
     <row r="62" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="297" t="s">
+      <c r="A62" s="285" t="s">
         <v>389</v>
       </c>
-      <c r="B62" s="298"/>
+      <c r="B62" s="286"/>
       <c r="C62" s="33" t="s">
         <v>390</v>
       </c>
@@ -4841,7 +4842,7 @@
         <v>403</v>
       </c>
       <c r="B79" s="65"/>
-      <c r="C79" s="282">
+      <c r="C79" s="281">
         <v>99500</v>
       </c>
       <c r="D79" s="65"/>
@@ -4856,7 +4857,7 @@
         <v>402</v>
       </c>
       <c r="B80" s="65"/>
-      <c r="C80" s="282">
+      <c r="C80" s="281">
         <v>99500</v>
       </c>
       <c r="D80" s="65"/>
@@ -4871,7 +4872,7 @@
         <v>401</v>
       </c>
       <c r="B81" s="65"/>
-      <c r="C81" s="282">
+      <c r="C81" s="281">
         <v>99500</v>
       </c>
       <c r="D81" s="65"/>
@@ -4886,7 +4887,7 @@
         <v>412</v>
       </c>
       <c r="B82" s="65"/>
-      <c r="C82" s="282">
+      <c r="C82" s="281">
         <v>85744</v>
       </c>
       <c r="D82" s="65"/>
@@ -4935,12 +4936,12 @@
       <c r="I85" s="46"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="306" t="s">
+      <c r="A86" s="307" t="s">
         <v>32</v>
       </c>
-      <c r="B86" s="307"/>
-      <c r="C86" s="307"/>
-      <c r="D86" s="307"/>
+      <c r="B86" s="308"/>
+      <c r="C86" s="308"/>
+      <c r="D86" s="308"/>
       <c r="E86" s="60" t="s">
         <v>10</v>
       </c>
@@ -4961,8 +4962,8 @@
       </c>
     </row>
     <row r="87" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="285"/>
-      <c r="B87" s="286"/>
+      <c r="A87" s="287"/>
+      <c r="B87" s="289"/>
       <c r="C87" s="250"/>
       <c r="D87" s="33"/>
       <c r="E87" s="226">
@@ -4976,8 +4977,8 @@
       <c r="J87" s="44"/>
     </row>
     <row r="88" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="308"/>
-      <c r="B88" s="309"/>
+      <c r="A88" s="309"/>
+      <c r="B88" s="310"/>
       <c r="C88" s="62"/>
       <c r="D88" s="33"/>
       <c r="E88" s="49"/>
@@ -4988,11 +4989,11 @@
       <c r="J88" s="44"/>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="303" t="s">
+      <c r="A89" s="304" t="s">
         <v>16</v>
       </c>
-      <c r="B89" s="304"/>
-      <c r="C89" s="305"/>
+      <c r="B89" s="305"/>
+      <c r="C89" s="306"/>
       <c r="D89" s="59">
         <f>SUM(D87:D88)</f>
         <v>0</v>
@@ -5042,30 +5043,30 @@
         <f>D76-D74</f>
         <v>15282253.399999999</v>
       </c>
-      <c r="D93" s="287" t="s">
+      <c r="D93" s="290" t="s">
         <v>284</v>
       </c>
-      <c r="E93" s="287"/>
-      <c r="F93" s="287"/>
-      <c r="G93" s="287"/>
-      <c r="H93" s="287"/>
-      <c r="I93" s="287"/>
+      <c r="E93" s="290"/>
+      <c r="F93" s="290"/>
+      <c r="G93" s="290"/>
+      <c r="H93" s="290"/>
+      <c r="I93" s="290"/>
     </row>
     <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D94" s="287"/>
-      <c r="E94" s="287"/>
-      <c r="F94" s="287"/>
-      <c r="G94" s="287"/>
-      <c r="H94" s="287"/>
-      <c r="I94" s="287"/>
+      <c r="D94" s="290"/>
+      <c r="E94" s="290"/>
+      <c r="F94" s="290"/>
+      <c r="G94" s="290"/>
+      <c r="H94" s="290"/>
+      <c r="I94" s="290"/>
     </row>
     <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="287"/>
-      <c r="E95" s="287"/>
-      <c r="F95" s="287"/>
-      <c r="G95" s="287"/>
-      <c r="H95" s="287"/>
-      <c r="I95" s="287"/>
+      <c r="D95" s="290"/>
+      <c r="E95" s="290"/>
+      <c r="F95" s="290"/>
+      <c r="G95" s="290"/>
+      <c r="H95" s="290"/>
+      <c r="I95" s="290"/>
     </row>
     <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
@@ -5073,12 +5074,12 @@
       </c>
       <c r="B96" s="9"/>
       <c r="C96" s="10"/>
-      <c r="D96" s="287"/>
-      <c r="E96" s="287"/>
-      <c r="F96" s="287"/>
-      <c r="G96" s="287"/>
-      <c r="H96" s="287"/>
-      <c r="I96" s="287"/>
+      <c r="D96" s="290"/>
+      <c r="E96" s="290"/>
+      <c r="F96" s="290"/>
+      <c r="G96" s="290"/>
+      <c r="H96" s="290"/>
+      <c r="I96" s="290"/>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="11" t="s">
@@ -5088,12 +5089,12 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C97" s="12"/>
-      <c r="D97" s="287"/>
-      <c r="E97" s="287"/>
-      <c r="F97" s="287"/>
-      <c r="G97" s="287"/>
-      <c r="H97" s="287"/>
-      <c r="I97" s="287"/>
+      <c r="D97" s="290"/>
+      <c r="E97" s="290"/>
+      <c r="F97" s="290"/>
+      <c r="G97" s="290"/>
+      <c r="H97" s="290"/>
+      <c r="I97" s="290"/>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
@@ -5101,17 +5102,17 @@
       </c>
       <c r="B98" s="22">
         <f>PRORRATEO!H133</f>
-        <v>16415860.980825996</v>
+        <v>16320875.050825996</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D98" s="287"/>
-      <c r="E98" s="287"/>
-      <c r="F98" s="287"/>
-      <c r="G98" s="287"/>
-      <c r="H98" s="287"/>
-      <c r="I98" s="287"/>
+      <c r="D98" s="290"/>
+      <c r="E98" s="290"/>
+      <c r="F98" s="290"/>
+      <c r="G98" s="290"/>
+      <c r="H98" s="290"/>
+      <c r="I98" s="290"/>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
@@ -5122,12 +5123,12 @@
         <v>912822.36</v>
       </c>
       <c r="C99" s="12"/>
-      <c r="D99" s="287"/>
-      <c r="E99" s="287"/>
-      <c r="F99" s="287"/>
-      <c r="G99" s="287"/>
-      <c r="H99" s="287"/>
-      <c r="I99" s="287"/>
+      <c r="D99" s="290"/>
+      <c r="E99" s="290"/>
+      <c r="F99" s="290"/>
+      <c r="G99" s="290"/>
+      <c r="H99" s="290"/>
+      <c r="I99" s="290"/>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
@@ -5138,12 +5139,12 @@
         <v>-15282253.399999999</v>
       </c>
       <c r="C100" s="10"/>
-      <c r="D100" s="287"/>
-      <c r="E100" s="287"/>
-      <c r="F100" s="287"/>
-      <c r="G100" s="287"/>
-      <c r="H100" s="287"/>
-      <c r="I100" s="287"/>
+      <c r="D100" s="290"/>
+      <c r="E100" s="290"/>
+      <c r="F100" s="290"/>
+      <c r="G100" s="290"/>
+      <c r="H100" s="290"/>
+      <c r="I100" s="290"/>
       <c r="K100" s="33"/>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -5155,12 +5156,12 @@
         <v>0</v>
       </c>
       <c r="C101" s="10"/>
-      <c r="D101" s="287"/>
-      <c r="E101" s="287"/>
-      <c r="F101" s="287"/>
-      <c r="G101" s="287"/>
-      <c r="H101" s="287"/>
-      <c r="I101" s="287"/>
+      <c r="D101" s="290"/>
+      <c r="E101" s="290"/>
+      <c r="F101" s="290"/>
+      <c r="G101" s="290"/>
+      <c r="H101" s="290"/>
+      <c r="I101" s="290"/>
       <c r="K101" s="39"/>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -5169,15 +5170,15 @@
       </c>
       <c r="B102" s="22">
         <f>B110</f>
-        <v>0</v>
+        <v>94985.93</v>
       </c>
       <c r="C102" s="10"/>
-      <c r="D102" s="287"/>
-      <c r="E102" s="287"/>
-      <c r="F102" s="287"/>
-      <c r="G102" s="287"/>
-      <c r="H102" s="287"/>
-      <c r="I102" s="287"/>
+      <c r="D102" s="290"/>
+      <c r="E102" s="290"/>
+      <c r="F102" s="290"/>
+      <c r="G102" s="290"/>
+      <c r="H102" s="290"/>
+      <c r="I102" s="290"/>
       <c r="K102" s="39"/>
     </row>
     <row r="103" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5188,12 +5189,12 @@
         <v>46200</v>
       </c>
       <c r="C103" s="10"/>
-      <c r="D103" s="287"/>
-      <c r="E103" s="287"/>
-      <c r="F103" s="287"/>
-      <c r="G103" s="287"/>
-      <c r="H103" s="287"/>
-      <c r="I103" s="287"/>
+      <c r="D103" s="290"/>
+      <c r="E103" s="290"/>
+      <c r="F103" s="290"/>
+      <c r="G103" s="290"/>
+      <c r="H103" s="290"/>
+      <c r="I103" s="290"/>
       <c r="K103" s="39"/>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -5205,12 +5206,12 @@
         <v>-100000</v>
       </c>
       <c r="C104" s="14"/>
-      <c r="D104" s="287"/>
-      <c r="E104" s="287"/>
-      <c r="F104" s="287"/>
-      <c r="G104" s="287"/>
-      <c r="H104" s="287"/>
-      <c r="I104" s="287"/>
+      <c r="D104" s="290"/>
+      <c r="E104" s="290"/>
+      <c r="F104" s="290"/>
+      <c r="G104" s="290"/>
+      <c r="H104" s="290"/>
+      <c r="I104" s="290"/>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="13" t="s">
@@ -5221,12 +5222,12 @@
         <v>-384244</v>
       </c>
       <c r="C105" s="14"/>
-      <c r="D105" s="287"/>
-      <c r="E105" s="287"/>
-      <c r="F105" s="287"/>
-      <c r="G105" s="287"/>
-      <c r="H105" s="287"/>
-      <c r="I105" s="287"/>
+      <c r="D105" s="290"/>
+      <c r="E105" s="290"/>
+      <c r="F105" s="290"/>
+      <c r="G105" s="290"/>
+      <c r="H105" s="290"/>
+      <c r="I105" s="290"/>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="11" t="s">
@@ -5234,25 +5235,25 @@
       </c>
       <c r="B106" s="15">
         <f>SUM(B97:B105)</f>
-        <v>2295399.0303661041</v>
+        <v>2295399.0303661046</v>
       </c>
       <c r="C106" s="51"/>
-      <c r="D106" s="287"/>
-      <c r="E106" s="287"/>
-      <c r="F106" s="287"/>
-      <c r="G106" s="287"/>
-      <c r="H106" s="287"/>
-      <c r="I106" s="287"/>
+      <c r="D106" s="290"/>
+      <c r="E106" s="290"/>
+      <c r="F106" s="290"/>
+      <c r="G106" s="290"/>
+      <c r="H106" s="290"/>
+      <c r="I106" s="290"/>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="14"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="287"/>
-      <c r="E107" s="287"/>
-      <c r="F107" s="287"/>
-      <c r="G107" s="287"/>
-      <c r="H107" s="287"/>
-      <c r="I107" s="287"/>
+      <c r="D107" s="290"/>
+      <c r="E107" s="290"/>
+      <c r="F107" s="290"/>
+      <c r="G107" s="290"/>
+      <c r="H107" s="290"/>
+      <c r="I107" s="290"/>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
@@ -5260,16 +5261,20 @@
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="287"/>
-      <c r="E108" s="287"/>
-      <c r="F108" s="287"/>
-      <c r="G108" s="287"/>
-      <c r="H108" s="287"/>
-      <c r="I108" s="287"/>
-    </row>
-    <row r="109" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="202"/>
-      <c r="B109" s="22"/>
+      <c r="D108" s="290"/>
+      <c r="E108" s="290"/>
+      <c r="F108" s="290"/>
+      <c r="G108" s="290"/>
+      <c r="H108" s="290"/>
+      <c r="I108" s="290"/>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="202" t="s">
+        <v>415</v>
+      </c>
+      <c r="B109" s="22">
+        <v>94985.93</v>
+      </c>
       <c r="C109" s="10"/>
       <c r="D109" s="17"/>
       <c r="E109" s="17"/>
@@ -5280,7 +5285,7 @@
       </c>
       <c r="B110" s="26">
         <f>SUM(B108:B109)</f>
-        <v>0</v>
+        <v>94985.93</v>
       </c>
       <c r="C110" s="10"/>
       <c r="E110" s="17"/>
@@ -5303,14 +5308,14 @@
         <v>106182.28</v>
       </c>
       <c r="C113" s="10"/>
-      <c r="D113" s="310" t="s">
+      <c r="D113" s="311" t="s">
         <v>410</v>
       </c>
-      <c r="E113" s="311"/>
-      <c r="F113" s="311"/>
-      <c r="G113" s="311"/>
-      <c r="H113" s="311"/>
-      <c r="I113" s="312"/>
+      <c r="E113" s="312"/>
+      <c r="F113" s="312"/>
+      <c r="G113" s="312"/>
+      <c r="H113" s="312"/>
+      <c r="I113" s="313"/>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
@@ -5320,12 +5325,12 @@
         <v>-60000</v>
       </c>
       <c r="C114" s="10"/>
-      <c r="D114" s="313"/>
-      <c r="E114" s="314"/>
-      <c r="F114" s="314"/>
-      <c r="G114" s="314"/>
-      <c r="H114" s="314"/>
-      <c r="I114" s="315"/>
+      <c r="D114" s="314"/>
+      <c r="E114" s="315"/>
+      <c r="F114" s="315"/>
+      <c r="G114" s="315"/>
+      <c r="H114" s="315"/>
+      <c r="I114" s="316"/>
     </row>
     <row r="115" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="205" t="s">
@@ -5336,12 +5341,12 @@
         <v>-72000</v>
       </c>
       <c r="C115" s="10"/>
-      <c r="D115" s="313"/>
-      <c r="E115" s="314"/>
-      <c r="F115" s="314"/>
-      <c r="G115" s="314"/>
-      <c r="H115" s="314"/>
-      <c r="I115" s="315"/>
+      <c r="D115" s="314"/>
+      <c r="E115" s="315"/>
+      <c r="F115" s="315"/>
+      <c r="G115" s="315"/>
+      <c r="H115" s="315"/>
+      <c r="I115" s="316"/>
     </row>
     <row r="116" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="25" t="s">
@@ -5352,39 +5357,27 @@
         <v>-25817.72</v>
       </c>
       <c r="C116" s="10"/>
-      <c r="D116" s="316"/>
-      <c r="E116" s="317"/>
-      <c r="F116" s="317"/>
-      <c r="G116" s="317"/>
-      <c r="H116" s="317"/>
-      <c r="I116" s="318"/>
+      <c r="D116" s="317"/>
+      <c r="E116" s="318"/>
+      <c r="F116" s="318"/>
+      <c r="G116" s="318"/>
+      <c r="H116" s="318"/>
+      <c r="I116" s="319"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="14"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="17"/>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="14"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="284" t="s">
-        <v>413</v>
-      </c>
-      <c r="E118" s="53"/>
       <c r="F118" s="53"/>
       <c r="G118" s="53"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="14"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="284"/>
-      <c r="E119" s="53"/>
       <c r="F119" s="53"/>
       <c r="G119" s="53"/>
     </row>
     <row r="120" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C120" s="10"/>
-      <c r="D120" s="32"/>
       <c r="H120" s="64"/>
       <c r="I120" s="64"/>
     </row>
@@ -5396,15 +5389,15 @@
         <v>498840</v>
       </c>
       <c r="C121" s="16"/>
-      <c r="D121" s="288" t="s">
+      <c r="D121" s="291" t="s">
         <v>414</v>
       </c>
-      <c r="E121" s="289"/>
-      <c r="F121" s="289"/>
-      <c r="G121" s="289"/>
-      <c r="H121" s="289"/>
-      <c r="I121" s="289"/>
-      <c r="J121" s="290"/>
+      <c r="E121" s="292"/>
+      <c r="F121" s="292"/>
+      <c r="G121" s="292"/>
+      <c r="H121" s="292"/>
+      <c r="I121" s="292"/>
+      <c r="J121" s="293"/>
     </row>
     <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
@@ -5414,13 +5407,13 @@
         <v>100000</v>
       </c>
       <c r="C122" s="16"/>
-      <c r="D122" s="291"/>
-      <c r="E122" s="292"/>
-      <c r="F122" s="292"/>
-      <c r="G122" s="292"/>
-      <c r="H122" s="292"/>
-      <c r="I122" s="292"/>
-      <c r="J122" s="293"/>
+      <c r="D122" s="294"/>
+      <c r="E122" s="295"/>
+      <c r="F122" s="295"/>
+      <c r="G122" s="295"/>
+      <c r="H122" s="295"/>
+      <c r="I122" s="295"/>
+      <c r="J122" s="296"/>
     </row>
     <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="11"/>
@@ -5428,13 +5421,13 @@
         <v>0</v>
       </c>
       <c r="C123" s="16"/>
-      <c r="D123" s="291"/>
-      <c r="E123" s="292"/>
-      <c r="F123" s="292"/>
-      <c r="G123" s="292"/>
-      <c r="H123" s="292"/>
-      <c r="I123" s="292"/>
-      <c r="J123" s="293"/>
+      <c r="D123" s="294"/>
+      <c r="E123" s="295"/>
+      <c r="F123" s="295"/>
+      <c r="G123" s="295"/>
+      <c r="H123" s="295"/>
+      <c r="I123" s="295"/>
+      <c r="J123" s="296"/>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="25" t="s">
@@ -5445,51 +5438,51 @@
         <v>598840</v>
       </c>
       <c r="C124" s="16"/>
-      <c r="D124" s="291"/>
-      <c r="E124" s="292"/>
-      <c r="F124" s="292"/>
-      <c r="G124" s="292"/>
-      <c r="H124" s="292"/>
-      <c r="I124" s="292"/>
-      <c r="J124" s="293"/>
+      <c r="D124" s="294"/>
+      <c r="E124" s="295"/>
+      <c r="F124" s="295"/>
+      <c r="G124" s="295"/>
+      <c r="H124" s="295"/>
+      <c r="I124" s="295"/>
+      <c r="J124" s="296"/>
     </row>
     <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C125" s="17"/>
-      <c r="D125" s="291"/>
-      <c r="E125" s="292"/>
-      <c r="F125" s="292"/>
-      <c r="G125" s="292"/>
-      <c r="H125" s="292"/>
-      <c r="I125" s="292"/>
-      <c r="J125" s="293"/>
+      <c r="D125" s="294"/>
+      <c r="E125" s="295"/>
+      <c r="F125" s="295"/>
+      <c r="G125" s="295"/>
+      <c r="H125" s="295"/>
+      <c r="I125" s="295"/>
+      <c r="J125" s="296"/>
     </row>
     <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="299" t="s">
+      <c r="A126" s="300" t="s">
         <v>362</v>
       </c>
-      <c r="B126" s="301">
+      <c r="B126" s="302">
         <f>B124+B106+B116</f>
-        <v>2868421.3103661039</v>
+        <v>2868421.3103661044</v>
       </c>
       <c r="C126" s="10"/>
-      <c r="D126" s="291"/>
-      <c r="E126" s="292"/>
-      <c r="F126" s="292"/>
-      <c r="G126" s="292"/>
-      <c r="H126" s="292"/>
-      <c r="I126" s="292"/>
-      <c r="J126" s="293"/>
+      <c r="D126" s="294"/>
+      <c r="E126" s="295"/>
+      <c r="F126" s="295"/>
+      <c r="G126" s="295"/>
+      <c r="H126" s="295"/>
+      <c r="I126" s="295"/>
+      <c r="J126" s="296"/>
     </row>
     <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="300"/>
-      <c r="B127" s="302"/>
-      <c r="D127" s="294"/>
-      <c r="E127" s="295"/>
-      <c r="F127" s="295"/>
-      <c r="G127" s="295"/>
-      <c r="H127" s="295"/>
-      <c r="I127" s="295"/>
-      <c r="J127" s="296"/>
+      <c r="A127" s="301"/>
+      <c r="B127" s="303"/>
+      <c r="D127" s="297"/>
+      <c r="E127" s="298"/>
+      <c r="F127" s="298"/>
+      <c r="G127" s="298"/>
+      <c r="H127" s="298"/>
+      <c r="I127" s="298"/>
+      <c r="J127" s="299"/>
     </row>
     <row r="133" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D133" s="53"/>
@@ -5499,14 +5492,16 @@
       <c r="H133" s="53"/>
     </row>
     <row r="134" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D134" s="283"/>
+      <c r="D134" s="282" t="s">
+        <v>413</v>
+      </c>
       <c r="E134" s="53"/>
       <c r="F134" s="53"/>
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
     </row>
     <row r="135" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D135" s="283"/>
+      <c r="D135" s="282"/>
       <c r="E135" s="53"/>
       <c r="F135" s="53"/>
       <c r="G135" s="53"/>
@@ -5514,11 +5509,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="D93:I108"/>
     <mergeCell ref="D121:J127"/>
@@ -5529,6 +5519,11 @@
     <mergeCell ref="A86:D86"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="D113:I116"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5563,13 +5558,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="356" t="s">
+      <c r="A1" s="350" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="357"/>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
+      <c r="B1" s="351"/>
+      <c r="C1" s="351"/>
+      <c r="D1" s="351"/>
+      <c r="E1" s="351"/>
       <c r="F1" s="125" t="s">
         <v>276</v>
       </c>
@@ -5581,20 +5576,20 @@
       <c r="L1" s="154" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="334">
+      <c r="M1" s="325">
         <f>RESUMEN!D76-N3</f>
         <v>14275955.399999999</v>
       </c>
-      <c r="N1" s="335"/>
+      <c r="N1" s="326"/>
       <c r="O1" s="126"/>
       <c r="P1" s="45"/>
     </row>
     <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="358"/>
-      <c r="B2" s="359"/>
-      <c r="C2" s="359"/>
-      <c r="D2" s="359"/>
-      <c r="E2" s="359"/>
+      <c r="A2" s="352"/>
+      <c r="B2" s="353"/>
+      <c r="C2" s="353"/>
+      <c r="D2" s="353"/>
+      <c r="E2" s="353"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5614,11 +5609,11 @@
       <c r="P2" s="45"/>
     </row>
     <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="358"/>
-      <c r="B3" s="359"/>
-      <c r="C3" s="359"/>
-      <c r="D3" s="359"/>
-      <c r="E3" s="359"/>
+      <c r="A3" s="352"/>
+      <c r="B3" s="353"/>
+      <c r="C3" s="353"/>
+      <c r="D3" s="353"/>
+      <c r="E3" s="353"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5638,11 +5633,11 @@
       <c r="P3" s="7"/>
     </row>
     <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="360"/>
-      <c r="B4" s="361"/>
-      <c r="C4" s="361"/>
-      <c r="D4" s="361"/>
-      <c r="E4" s="361"/>
+      <c r="A4" s="354"/>
+      <c r="B4" s="355"/>
+      <c r="C4" s="355"/>
+      <c r="D4" s="355"/>
+      <c r="E4" s="355"/>
       <c r="F4" s="130"/>
       <c r="G4" s="130"/>
       <c r="H4" s="130"/>
@@ -5658,95 +5653,95 @@
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="341" t="s">
+      <c r="C5" s="335" t="s">
         <v>407</v>
       </c>
-      <c r="D5" s="342"/>
-      <c r="E5" s="342"/>
-      <c r="F5" s="342"/>
-      <c r="G5" s="342"/>
-      <c r="H5" s="342"/>
-      <c r="I5" s="342"/>
-      <c r="J5" s="342"/>
-      <c r="K5" s="342"/>
-      <c r="L5" s="342"/>
-      <c r="M5" s="342"/>
-      <c r="N5" s="342"/>
-      <c r="O5" s="343"/>
+      <c r="D5" s="336"/>
+      <c r="E5" s="336"/>
+      <c r="F5" s="336"/>
+      <c r="G5" s="336"/>
+      <c r="H5" s="336"/>
+      <c r="I5" s="336"/>
+      <c r="J5" s="336"/>
+      <c r="K5" s="336"/>
+      <c r="L5" s="336"/>
+      <c r="M5" s="336"/>
+      <c r="N5" s="336"/>
+      <c r="O5" s="337"/>
       <c r="P5" s="7"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="344"/>
-      <c r="D6" s="345"/>
-      <c r="E6" s="345"/>
-      <c r="F6" s="345"/>
-      <c r="G6" s="345"/>
-      <c r="H6" s="345"/>
-      <c r="I6" s="345"/>
-      <c r="J6" s="345"/>
-      <c r="K6" s="345"/>
-      <c r="L6" s="345"/>
-      <c r="M6" s="345"/>
-      <c r="N6" s="345"/>
-      <c r="O6" s="346"/>
+      <c r="C6" s="338"/>
+      <c r="D6" s="339"/>
+      <c r="E6" s="339"/>
+      <c r="F6" s="339"/>
+      <c r="G6" s="339"/>
+      <c r="H6" s="339"/>
+      <c r="I6" s="339"/>
+      <c r="J6" s="339"/>
+      <c r="K6" s="339"/>
+      <c r="L6" s="339"/>
+      <c r="M6" s="339"/>
+      <c r="N6" s="339"/>
+      <c r="O6" s="340"/>
       <c r="P6" s="7"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="344"/>
-      <c r="D7" s="345"/>
-      <c r="E7" s="345"/>
-      <c r="F7" s="345"/>
-      <c r="G7" s="345"/>
-      <c r="H7" s="345"/>
-      <c r="I7" s="345"/>
-      <c r="J7" s="345"/>
-      <c r="K7" s="345"/>
-      <c r="L7" s="345"/>
-      <c r="M7" s="345"/>
-      <c r="N7" s="345"/>
-      <c r="O7" s="346"/>
+      <c r="C7" s="338"/>
+      <c r="D7" s="339"/>
+      <c r="E7" s="339"/>
+      <c r="F7" s="339"/>
+      <c r="G7" s="339"/>
+      <c r="H7" s="339"/>
+      <c r="I7" s="339"/>
+      <c r="J7" s="339"/>
+      <c r="K7" s="339"/>
+      <c r="L7" s="339"/>
+      <c r="M7" s="339"/>
+      <c r="N7" s="339"/>
+      <c r="O7" s="340"/>
       <c r="P7" s="7"/>
     </row>
     <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="347"/>
-      <c r="D8" s="348"/>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
-      <c r="G8" s="348"/>
-      <c r="H8" s="348"/>
-      <c r="I8" s="348"/>
-      <c r="J8" s="348"/>
-      <c r="K8" s="348"/>
-      <c r="L8" s="348"/>
-      <c r="M8" s="348"/>
-      <c r="N8" s="348"/>
-      <c r="O8" s="349"/>
+      <c r="C8" s="341"/>
+      <c r="D8" s="342"/>
+      <c r="E8" s="342"/>
+      <c r="F8" s="342"/>
+      <c r="G8" s="342"/>
+      <c r="H8" s="342"/>
+      <c r="I8" s="342"/>
+      <c r="J8" s="342"/>
+      <c r="K8" s="342"/>
+      <c r="L8" s="342"/>
+      <c r="M8" s="342"/>
+      <c r="N8" s="342"/>
+      <c r="O8" s="343"/>
       <c r="Q8" s="64"/>
     </row>
     <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="350" t="s">
+      <c r="C9" s="344" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="351"/>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
-      <c r="G9" s="351"/>
-      <c r="H9" s="351"/>
-      <c r="I9" s="351"/>
-      <c r="J9" s="351"/>
-      <c r="K9" s="351"/>
-      <c r="L9" s="351"/>
-      <c r="M9" s="351"/>
-      <c r="N9" s="351"/>
-      <c r="O9" s="352"/>
+      <c r="D9" s="345"/>
+      <c r="E9" s="345"/>
+      <c r="F9" s="345"/>
+      <c r="G9" s="345"/>
+      <c r="H9" s="345"/>
+      <c r="I9" s="345"/>
+      <c r="J9" s="345"/>
+      <c r="K9" s="345"/>
+      <c r="L9" s="345"/>
+      <c r="M9" s="345"/>
+      <c r="N9" s="345"/>
+      <c r="O9" s="346"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -5758,19 +5753,19 @@
     <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="353"/>
-      <c r="D10" s="354"/>
-      <c r="E10" s="354"/>
-      <c r="F10" s="354"/>
-      <c r="G10" s="354"/>
-      <c r="H10" s="354"/>
-      <c r="I10" s="354"/>
-      <c r="J10" s="354"/>
-      <c r="K10" s="354"/>
-      <c r="L10" s="354"/>
-      <c r="M10" s="354"/>
-      <c r="N10" s="354"/>
-      <c r="O10" s="355"/>
+      <c r="C10" s="347"/>
+      <c r="D10" s="348"/>
+      <c r="E10" s="348"/>
+      <c r="F10" s="348"/>
+      <c r="G10" s="348"/>
+      <c r="H10" s="348"/>
+      <c r="I10" s="348"/>
+      <c r="J10" s="348"/>
+      <c r="K10" s="348"/>
+      <c r="L10" s="348"/>
+      <c r="M10" s="348"/>
+      <c r="N10" s="348"/>
+      <c r="O10" s="349"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -5780,49 +5775,49 @@
       </c>
     </row>
     <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="325" t="s">
+      <c r="A11" s="321" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="327" t="s">
+      <c r="B11" s="356" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="325" t="s">
+      <c r="C11" s="321" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="329" t="s">
+      <c r="D11" s="358" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="329" t="s">
+      <c r="E11" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="325" t="s">
+      <c r="F11" s="321" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="325" t="s">
+      <c r="G11" s="321" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="325" t="s">
+      <c r="H11" s="321" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="336" t="s">
+      <c r="I11" s="327" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="322" t="s">
+      <c r="J11" s="329" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="322" t="s">
+      <c r="K11" s="329" t="s">
         <v>372</v>
       </c>
-      <c r="L11" s="322" t="s">
+      <c r="L11" s="329" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="338" t="s">
+      <c r="M11" s="332" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="322" t="s">
+      <c r="N11" s="329" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="322" t="s">
+      <c r="O11" s="329" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -5834,21 +5829,21 @@
       </c>
     </row>
     <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="326"/>
-      <c r="B12" s="328"/>
-      <c r="C12" s="326"/>
-      <c r="D12" s="330"/>
-      <c r="E12" s="330"/>
-      <c r="F12" s="326"/>
-      <c r="G12" s="326"/>
-      <c r="H12" s="326"/>
-      <c r="I12" s="337"/>
-      <c r="J12" s="323"/>
-      <c r="K12" s="323"/>
-      <c r="L12" s="323"/>
-      <c r="M12" s="339"/>
-      <c r="N12" s="323"/>
-      <c r="O12" s="323"/>
+      <c r="A12" s="322"/>
+      <c r="B12" s="357"/>
+      <c r="C12" s="322"/>
+      <c r="D12" s="359"/>
+      <c r="E12" s="359"/>
+      <c r="F12" s="322"/>
+      <c r="G12" s="322"/>
+      <c r="H12" s="322"/>
+      <c r="I12" s="328"/>
+      <c r="J12" s="330"/>
+      <c r="K12" s="330"/>
+      <c r="L12" s="330"/>
+      <c r="M12" s="333"/>
+      <c r="N12" s="330"/>
+      <c r="O12" s="330"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -5858,19 +5853,19 @@
       </c>
     </row>
     <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="326"/>
-      <c r="B13" s="328"/>
-      <c r="C13" s="326"/>
-      <c r="D13" s="330"/>
-      <c r="E13" s="330"/>
-      <c r="F13" s="326"/>
-      <c r="G13" s="326"/>
-      <c r="H13" s="326"/>
-      <c r="I13" s="337"/>
-      <c r="J13" s="323"/>
-      <c r="K13" s="324"/>
-      <c r="L13" s="324"/>
-      <c r="M13" s="339"/>
+      <c r="A13" s="322"/>
+      <c r="B13" s="357"/>
+      <c r="C13" s="322"/>
+      <c r="D13" s="359"/>
+      <c r="E13" s="359"/>
+      <c r="F13" s="322"/>
+      <c r="G13" s="322"/>
+      <c r="H13" s="322"/>
+      <c r="I13" s="328"/>
+      <c r="J13" s="330"/>
+      <c r="K13" s="331"/>
+      <c r="L13" s="331"/>
+      <c r="M13" s="333"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/07</v>
@@ -5939,8 +5934,8 @@
       <c r="P14" s="85" t="s">
         <v>348</v>
       </c>
-      <c r="R14" s="331"/>
-      <c r="S14" s="331"/>
+      <c r="R14" s="320"/>
+      <c r="S14" s="320"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
@@ -5958,12 +5953,12 @@
       <c r="G15" s="106">
         <v>209690.989172</v>
       </c>
-      <c r="H15" s="281">
-        <v>94985.93</v>
+      <c r="H15" s="33">
+        <v>0</v>
       </c>
       <c r="I15" s="111">
         <f t="shared" ref="I15:I131" si="0">G15-H15</f>
-        <v>114705.05917200001</v>
+        <v>209690.989172</v>
       </c>
       <c r="J15" s="112">
         <v>0</v>
@@ -5980,17 +5975,17 @@
       </c>
       <c r="N15" s="113">
         <f t="shared" ref="N15:N18" si="2">L15+J15+I15+M15+K15</f>
-        <v>428664.38162000006</v>
+        <v>523650.31162000005</v>
       </c>
       <c r="O15" s="114">
         <f t="shared" ref="O15:O18" si="3">N15*6% + N15</f>
-        <v>454384.24451720004</v>
+        <v>555069.33031720005</v>
       </c>
       <c r="P15" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="R15" s="331"/>
-      <c r="S15" s="331"/>
+      <c r="R15" s="320"/>
+      <c r="S15" s="320"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
@@ -12633,7 +12628,7 @@
       </c>
       <c r="H133" s="20">
         <f>SUM(H14:H132)+29000</f>
-        <v>16415860.980825996</v>
+        <v>16320875.050825996</v>
       </c>
       <c r="I133" s="19"/>
       <c r="J133" s="41">
@@ -12651,11 +12646,11 @@
       </c>
       <c r="N133" s="21">
         <f>SUM(N14:N132)</f>
-        <v>26645423.969740376</v>
+        <v>26740409.899740376</v>
       </c>
       <c r="O133" s="20">
         <f>SUM(O14:O132)</f>
-        <v>28244215.103324801</v>
+        <v>28344900.1891248</v>
       </c>
       <c r="Q133" s="45"/>
     </row>
@@ -12666,34 +12661,34 @@
       </c>
     </row>
     <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="333"/>
-      <c r="D135" s="333"/>
-      <c r="E135" s="333"/>
-      <c r="F135" s="333"/>
-      <c r="G135" s="333"/>
-      <c r="H135" s="333"/>
-      <c r="I135" s="333"/>
-      <c r="J135" s="333"/>
-      <c r="K135" s="333"/>
-      <c r="L135" s="333"/>
-      <c r="M135" s="333"/>
-      <c r="N135" s="333"/>
-      <c r="O135" s="333"/>
+      <c r="C135" s="324"/>
+      <c r="D135" s="324"/>
+      <c r="E135" s="324"/>
+      <c r="F135" s="324"/>
+      <c r="G135" s="324"/>
+      <c r="H135" s="324"/>
+      <c r="I135" s="324"/>
+      <c r="J135" s="324"/>
+      <c r="K135" s="324"/>
+      <c r="L135" s="324"/>
+      <c r="M135" s="324"/>
+      <c r="N135" s="324"/>
+      <c r="O135" s="324"/>
     </row>
     <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="333"/>
-      <c r="D136" s="333"/>
-      <c r="E136" s="333"/>
-      <c r="F136" s="333"/>
-      <c r="G136" s="333"/>
-      <c r="H136" s="333"/>
-      <c r="I136" s="333"/>
-      <c r="J136" s="333"/>
-      <c r="K136" s="333"/>
-      <c r="L136" s="333"/>
-      <c r="M136" s="333"/>
-      <c r="N136" s="333"/>
-      <c r="O136" s="333"/>
+      <c r="C136" s="324"/>
+      <c r="D136" s="324"/>
+      <c r="E136" s="324"/>
+      <c r="F136" s="324"/>
+      <c r="G136" s="324"/>
+      <c r="H136" s="324"/>
+      <c r="I136" s="324"/>
+      <c r="J136" s="324"/>
+      <c r="K136" s="324"/>
+      <c r="L136" s="324"/>
+      <c r="M136" s="324"/>
+      <c r="N136" s="324"/>
+      <c r="O136" s="324"/>
     </row>
     <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C137" s="57"/>
@@ -12711,126 +12706,126 @@
       <c r="O137" s="57"/>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="340" t="s">
+      <c r="C138" s="334" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="340"/>
-      <c r="E138" s="340"/>
-      <c r="F138" s="340"/>
-      <c r="G138" s="340"/>
-      <c r="H138" s="340"/>
-      <c r="I138" s="340"/>
-      <c r="J138" s="340"/>
-      <c r="K138" s="340"/>
-      <c r="L138" s="340"/>
-      <c r="M138" s="340"/>
-      <c r="N138" s="340"/>
-      <c r="O138" s="340"/>
+      <c r="D138" s="334"/>
+      <c r="E138" s="334"/>
+      <c r="F138" s="334"/>
+      <c r="G138" s="334"/>
+      <c r="H138" s="334"/>
+      <c r="I138" s="334"/>
+      <c r="J138" s="334"/>
+      <c r="K138" s="334"/>
+      <c r="L138" s="334"/>
+      <c r="M138" s="334"/>
+      <c r="N138" s="334"/>
+      <c r="O138" s="334"/>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="340"/>
-      <c r="D139" s="340"/>
-      <c r="E139" s="340"/>
-      <c r="F139" s="340"/>
-      <c r="G139" s="340"/>
-      <c r="H139" s="340"/>
-      <c r="I139" s="340"/>
-      <c r="J139" s="340"/>
-      <c r="K139" s="340"/>
-      <c r="L139" s="340"/>
-      <c r="M139" s="340"/>
-      <c r="N139" s="340"/>
-      <c r="O139" s="340"/>
+      <c r="C139" s="334"/>
+      <c r="D139" s="334"/>
+      <c r="E139" s="334"/>
+      <c r="F139" s="334"/>
+      <c r="G139" s="334"/>
+      <c r="H139" s="334"/>
+      <c r="I139" s="334"/>
+      <c r="J139" s="334"/>
+      <c r="K139" s="334"/>
+      <c r="L139" s="334"/>
+      <c r="M139" s="334"/>
+      <c r="N139" s="334"/>
+      <c r="O139" s="334"/>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="340"/>
-      <c r="D140" s="340"/>
-      <c r="E140" s="340"/>
-      <c r="F140" s="340"/>
-      <c r="G140" s="340"/>
-      <c r="H140" s="340"/>
-      <c r="I140" s="340"/>
-      <c r="J140" s="340"/>
-      <c r="K140" s="340"/>
-      <c r="L140" s="340"/>
-      <c r="M140" s="340"/>
-      <c r="N140" s="340"/>
-      <c r="O140" s="340"/>
+      <c r="C140" s="334"/>
+      <c r="D140" s="334"/>
+      <c r="E140" s="334"/>
+      <c r="F140" s="334"/>
+      <c r="G140" s="334"/>
+      <c r="H140" s="334"/>
+      <c r="I140" s="334"/>
+      <c r="J140" s="334"/>
+      <c r="K140" s="334"/>
+      <c r="L140" s="334"/>
+      <c r="M140" s="334"/>
+      <c r="N140" s="334"/>
+      <c r="O140" s="334"/>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="340"/>
-      <c r="D141" s="340"/>
-      <c r="E141" s="340"/>
-      <c r="F141" s="340"/>
-      <c r="G141" s="340"/>
-      <c r="H141" s="340"/>
-      <c r="I141" s="340"/>
-      <c r="J141" s="340"/>
-      <c r="K141" s="340"/>
-      <c r="L141" s="340"/>
-      <c r="M141" s="340"/>
-      <c r="N141" s="340"/>
-      <c r="O141" s="340"/>
+      <c r="C141" s="334"/>
+      <c r="D141" s="334"/>
+      <c r="E141" s="334"/>
+      <c r="F141" s="334"/>
+      <c r="G141" s="334"/>
+      <c r="H141" s="334"/>
+      <c r="I141" s="334"/>
+      <c r="J141" s="334"/>
+      <c r="K141" s="334"/>
+      <c r="L141" s="334"/>
+      <c r="M141" s="334"/>
+      <c r="N141" s="334"/>
+      <c r="O141" s="334"/>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="340"/>
-      <c r="D142" s="340"/>
-      <c r="E142" s="340"/>
-      <c r="F142" s="340"/>
-      <c r="G142" s="340"/>
-      <c r="H142" s="340"/>
-      <c r="I142" s="340"/>
-      <c r="J142" s="340"/>
-      <c r="K142" s="340"/>
-      <c r="L142" s="340"/>
-      <c r="M142" s="340"/>
-      <c r="N142" s="340"/>
-      <c r="O142" s="340"/>
+      <c r="C142" s="334"/>
+      <c r="D142" s="334"/>
+      <c r="E142" s="334"/>
+      <c r="F142" s="334"/>
+      <c r="G142" s="334"/>
+      <c r="H142" s="334"/>
+      <c r="I142" s="334"/>
+      <c r="J142" s="334"/>
+      <c r="K142" s="334"/>
+      <c r="L142" s="334"/>
+      <c r="M142" s="334"/>
+      <c r="N142" s="334"/>
+      <c r="O142" s="334"/>
     </row>
     <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="340"/>
-      <c r="D143" s="340"/>
-      <c r="E143" s="340"/>
-      <c r="F143" s="340"/>
-      <c r="G143" s="340"/>
-      <c r="H143" s="340"/>
-      <c r="I143" s="340"/>
-      <c r="J143" s="340"/>
-      <c r="K143" s="340"/>
-      <c r="L143" s="340"/>
-      <c r="M143" s="340"/>
-      <c r="N143" s="340"/>
-      <c r="O143" s="340"/>
+      <c r="C143" s="334"/>
+      <c r="D143" s="334"/>
+      <c r="E143" s="334"/>
+      <c r="F143" s="334"/>
+      <c r="G143" s="334"/>
+      <c r="H143" s="334"/>
+      <c r="I143" s="334"/>
+      <c r="J143" s="334"/>
+      <c r="K143" s="334"/>
+      <c r="L143" s="334"/>
+      <c r="M143" s="334"/>
+      <c r="N143" s="334"/>
+      <c r="O143" s="334"/>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="340"/>
-      <c r="D144" s="340"/>
-      <c r="E144" s="340"/>
-      <c r="F144" s="340"/>
-      <c r="G144" s="340"/>
-      <c r="H144" s="340"/>
-      <c r="I144" s="340"/>
-      <c r="J144" s="340"/>
-      <c r="K144" s="340"/>
-      <c r="L144" s="340"/>
-      <c r="M144" s="340"/>
-      <c r="N144" s="340"/>
-      <c r="O144" s="340"/>
+      <c r="C144" s="334"/>
+      <c r="D144" s="334"/>
+      <c r="E144" s="334"/>
+      <c r="F144" s="334"/>
+      <c r="G144" s="334"/>
+      <c r="H144" s="334"/>
+      <c r="I144" s="334"/>
+      <c r="J144" s="334"/>
+      <c r="K144" s="334"/>
+      <c r="L144" s="334"/>
+      <c r="M144" s="334"/>
+      <c r="N144" s="334"/>
+      <c r="O144" s="334"/>
     </row>
     <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="340"/>
-      <c r="D145" s="340"/>
-      <c r="E145" s="340"/>
-      <c r="F145" s="340"/>
-      <c r="G145" s="340"/>
-      <c r="H145" s="340"/>
-      <c r="I145" s="340"/>
-      <c r="J145" s="340"/>
-      <c r="K145" s="340"/>
-      <c r="L145" s="340"/>
-      <c r="M145" s="340"/>
-      <c r="N145" s="340"/>
-      <c r="O145" s="340"/>
+      <c r="C145" s="334"/>
+      <c r="D145" s="334"/>
+      <c r="E145" s="334"/>
+      <c r="F145" s="334"/>
+      <c r="G145" s="334"/>
+      <c r="H145" s="334"/>
+      <c r="I145" s="334"/>
+      <c r="J145" s="334"/>
+      <c r="K145" s="334"/>
+      <c r="L145" s="334"/>
+      <c r="M145" s="334"/>
+      <c r="N145" s="334"/>
+      <c r="O145" s="334"/>
     </row>
     <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="57"/>
@@ -12863,118 +12858,125 @@
       <c r="O147" s="57"/>
     </row>
     <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="332" t="s">
+      <c r="C148" s="323" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="332"/>
-      <c r="E148" s="332"/>
-      <c r="F148" s="332"/>
-      <c r="G148" s="332"/>
-      <c r="H148" s="332"/>
-      <c r="I148" s="332"/>
-      <c r="J148" s="332"/>
-      <c r="K148" s="332"/>
-      <c r="L148" s="332"/>
-      <c r="M148" s="332"/>
-      <c r="N148" s="332"/>
-      <c r="O148" s="332"/>
+      <c r="D148" s="323"/>
+      <c r="E148" s="323"/>
+      <c r="F148" s="323"/>
+      <c r="G148" s="323"/>
+      <c r="H148" s="323"/>
+      <c r="I148" s="323"/>
+      <c r="J148" s="323"/>
+      <c r="K148" s="323"/>
+      <c r="L148" s="323"/>
+      <c r="M148" s="323"/>
+      <c r="N148" s="323"/>
+      <c r="O148" s="323"/>
     </row>
     <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="332"/>
-      <c r="D149" s="332"/>
-      <c r="E149" s="332"/>
-      <c r="F149" s="332"/>
-      <c r="G149" s="332"/>
-      <c r="H149" s="332"/>
-      <c r="I149" s="332"/>
-      <c r="J149" s="332"/>
-      <c r="K149" s="332"/>
-      <c r="L149" s="332"/>
-      <c r="M149" s="332"/>
-      <c r="N149" s="332"/>
-      <c r="O149" s="332"/>
+      <c r="C149" s="323"/>
+      <c r="D149" s="323"/>
+      <c r="E149" s="323"/>
+      <c r="F149" s="323"/>
+      <c r="G149" s="323"/>
+      <c r="H149" s="323"/>
+      <c r="I149" s="323"/>
+      <c r="J149" s="323"/>
+      <c r="K149" s="323"/>
+      <c r="L149" s="323"/>
+      <c r="M149" s="323"/>
+      <c r="N149" s="323"/>
+      <c r="O149" s="323"/>
     </row>
     <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="332"/>
-      <c r="D150" s="332"/>
-      <c r="E150" s="332"/>
-      <c r="F150" s="332"/>
-      <c r="G150" s="332"/>
-      <c r="H150" s="332"/>
-      <c r="I150" s="332"/>
-      <c r="J150" s="332"/>
-      <c r="K150" s="332"/>
-      <c r="L150" s="332"/>
-      <c r="M150" s="332"/>
-      <c r="N150" s="332"/>
-      <c r="O150" s="332"/>
+      <c r="C150" s="323"/>
+      <c r="D150" s="323"/>
+      <c r="E150" s="323"/>
+      <c r="F150" s="323"/>
+      <c r="G150" s="323"/>
+      <c r="H150" s="323"/>
+      <c r="I150" s="323"/>
+      <c r="J150" s="323"/>
+      <c r="K150" s="323"/>
+      <c r="L150" s="323"/>
+      <c r="M150" s="323"/>
+      <c r="N150" s="323"/>
+      <c r="O150" s="323"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>-253782.0668799635</v>
       </c>
     </row>
     <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="332"/>
-      <c r="D151" s="332"/>
-      <c r="E151" s="332"/>
-      <c r="F151" s="332"/>
-      <c r="G151" s="332"/>
-      <c r="H151" s="332"/>
-      <c r="I151" s="332"/>
-      <c r="J151" s="332"/>
-      <c r="K151" s="332"/>
-      <c r="L151" s="332"/>
-      <c r="M151" s="332"/>
-      <c r="N151" s="332"/>
-      <c r="O151" s="332"/>
+      <c r="C151" s="323"/>
+      <c r="D151" s="323"/>
+      <c r="E151" s="323"/>
+      <c r="F151" s="323"/>
+      <c r="G151" s="323"/>
+      <c r="H151" s="323"/>
+      <c r="I151" s="323"/>
+      <c r="J151" s="323"/>
+      <c r="K151" s="323"/>
+      <c r="L151" s="323"/>
+      <c r="M151" s="323"/>
+      <c r="N151" s="323"/>
+      <c r="O151" s="323"/>
     </row>
     <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="332"/>
-      <c r="D152" s="332"/>
-      <c r="E152" s="332"/>
-      <c r="F152" s="332"/>
-      <c r="G152" s="332"/>
-      <c r="H152" s="332"/>
-      <c r="I152" s="332"/>
-      <c r="J152" s="332"/>
-      <c r="K152" s="332"/>
-      <c r="L152" s="332"/>
-      <c r="M152" s="332"/>
-      <c r="N152" s="332"/>
-      <c r="O152" s="332"/>
+      <c r="C152" s="323"/>
+      <c r="D152" s="323"/>
+      <c r="E152" s="323"/>
+      <c r="F152" s="323"/>
+      <c r="G152" s="323"/>
+      <c r="H152" s="323"/>
+      <c r="I152" s="323"/>
+      <c r="J152" s="323"/>
+      <c r="K152" s="323"/>
+      <c r="L152" s="323"/>
+      <c r="M152" s="323"/>
+      <c r="N152" s="323"/>
+      <c r="O152" s="323"/>
     </row>
     <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="332"/>
-      <c r="D153" s="332"/>
-      <c r="E153" s="332"/>
-      <c r="F153" s="332"/>
-      <c r="G153" s="332"/>
-      <c r="H153" s="332"/>
-      <c r="I153" s="332"/>
-      <c r="J153" s="332"/>
-      <c r="K153" s="332"/>
-      <c r="L153" s="332"/>
-      <c r="M153" s="332"/>
-      <c r="N153" s="332"/>
-      <c r="O153" s="332"/>
+      <c r="C153" s="323"/>
+      <c r="D153" s="323"/>
+      <c r="E153" s="323"/>
+      <c r="F153" s="323"/>
+      <c r="G153" s="323"/>
+      <c r="H153" s="323"/>
+      <c r="I153" s="323"/>
+      <c r="J153" s="323"/>
+      <c r="K153" s="323"/>
+      <c r="L153" s="323"/>
+      <c r="M153" s="323"/>
+      <c r="N153" s="323"/>
+      <c r="O153" s="323"/>
     </row>
     <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="332"/>
-      <c r="D154" s="332"/>
-      <c r="E154" s="332"/>
-      <c r="F154" s="332"/>
-      <c r="G154" s="332"/>
-      <c r="H154" s="332"/>
-      <c r="I154" s="332"/>
-      <c r="J154" s="332"/>
-      <c r="K154" s="332"/>
-      <c r="L154" s="332"/>
-      <c r="M154" s="332"/>
-      <c r="N154" s="332"/>
-      <c r="O154" s="332"/>
+      <c r="C154" s="323"/>
+      <c r="D154" s="323"/>
+      <c r="E154" s="323"/>
+      <c r="F154" s="323"/>
+      <c r="G154" s="323"/>
+      <c r="H154" s="323"/>
+      <c r="I154" s="323"/>
+      <c r="J154" s="323"/>
+      <c r="K154" s="323"/>
+      <c r="L154" s="323"/>
+      <c r="M154" s="323"/>
+      <c r="N154" s="323"/>
+      <c r="O154" s="323"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -12991,13 +12993,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13031,61 +13026,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="369" t="s">
+      <c r="A1" s="371" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="369"/>
-      <c r="C1" s="369"/>
-      <c r="D1" s="369"/>
-      <c r="E1" s="369"/>
-      <c r="F1" s="369"/>
-      <c r="G1" s="369"/>
-      <c r="H1" s="369"/>
-      <c r="I1" s="369"/>
-      <c r="J1" s="369"/>
-      <c r="K1" s="369"/>
-      <c r="L1" s="369"/>
-      <c r="M1" s="369"/>
-      <c r="N1" s="369"/>
-      <c r="O1" s="370"/>
+      <c r="B1" s="371"/>
+      <c r="C1" s="371"/>
+      <c r="D1" s="371"/>
+      <c r="E1" s="371"/>
+      <c r="F1" s="371"/>
+      <c r="G1" s="371"/>
+      <c r="H1" s="371"/>
+      <c r="I1" s="371"/>
+      <c r="J1" s="371"/>
+      <c r="K1" s="371"/>
+      <c r="L1" s="371"/>
+      <c r="M1" s="371"/>
+      <c r="N1" s="371"/>
+      <c r="O1" s="372"/>
       <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="371"/>
-      <c r="B2" s="371"/>
-      <c r="C2" s="371"/>
-      <c r="D2" s="371"/>
-      <c r="E2" s="371"/>
-      <c r="F2" s="371"/>
-      <c r="G2" s="371"/>
-      <c r="H2" s="371"/>
-      <c r="I2" s="371"/>
-      <c r="J2" s="371"/>
-      <c r="K2" s="371"/>
-      <c r="L2" s="371"/>
-      <c r="M2" s="371"/>
-      <c r="N2" s="371"/>
-      <c r="O2" s="372"/>
+      <c r="A2" s="373"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
+      <c r="D2" s="373"/>
+      <c r="E2" s="373"/>
+      <c r="F2" s="373"/>
+      <c r="G2" s="373"/>
+      <c r="H2" s="373"/>
+      <c r="I2" s="373"/>
+      <c r="J2" s="373"/>
+      <c r="K2" s="373"/>
+      <c r="L2" s="373"/>
+      <c r="M2" s="373"/>
+      <c r="N2" s="373"/>
+      <c r="O2" s="374"/>
       <c r="R2" s="32"/>
     </row>
     <row r="3" spans="1:27" s="190" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="366" t="s">
+      <c r="A3" s="368" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="367"/>
-      <c r="C3" s="367"/>
-      <c r="D3" s="367"/>
-      <c r="E3" s="367"/>
-      <c r="F3" s="367"/>
-      <c r="G3" s="367"/>
-      <c r="H3" s="367"/>
-      <c r="I3" s="367"/>
-      <c r="J3" s="367"/>
-      <c r="K3" s="367"/>
-      <c r="L3" s="367"/>
-      <c r="M3" s="367"/>
-      <c r="N3" s="367"/>
-      <c r="O3" s="368"/>
+      <c r="B3" s="369"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369"/>
+      <c r="E3" s="369"/>
+      <c r="F3" s="369"/>
+      <c r="G3" s="369"/>
+      <c r="H3" s="369"/>
+      <c r="I3" s="369"/>
+      <c r="J3" s="369"/>
+      <c r="K3" s="369"/>
+      <c r="L3" s="369"/>
+      <c r="M3" s="369"/>
+      <c r="N3" s="369"/>
+      <c r="O3" s="370"/>
       <c r="P3" s="191"/>
       <c r="Q3" s="191"/>
       <c r="R3" s="191"/>
@@ -13100,85 +13095,85 @@
       <c r="AA3" s="191"/>
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="325" t="s">
+      <c r="A4" s="321" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="325" t="s">
+      <c r="B4" s="321" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="325" t="s">
+      <c r="C4" s="321" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="325" t="s">
+      <c r="D4" s="321" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="322" t="s">
+      <c r="E4" s="329" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="322" t="s">
+      <c r="F4" s="329" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="322" t="s">
+      <c r="G4" s="329" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="322" t="s">
+      <c r="H4" s="329" t="s">
         <v>336</v>
       </c>
-      <c r="I4" s="322" t="s">
+      <c r="I4" s="329" t="s">
         <v>345</v>
       </c>
-      <c r="J4" s="373" t="s">
+      <c r="J4" s="360" t="s">
         <v>332</v>
       </c>
       <c r="K4" s="100"/>
-      <c r="L4" s="363" t="s">
+      <c r="L4" s="365" t="s">
         <v>342</v>
       </c>
-      <c r="M4" s="322" t="s">
+      <c r="M4" s="329" t="s">
         <v>343</v>
       </c>
-      <c r="N4" s="322" t="s">
+      <c r="N4" s="329" t="s">
         <v>333</v>
       </c>
-      <c r="O4" s="322" t="s">
+      <c r="O4" s="329" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="326"/>
-      <c r="B5" s="326"/>
-      <c r="C5" s="326"/>
-      <c r="D5" s="326"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="323"/>
-      <c r="J5" s="374"/>
+      <c r="A5" s="322"/>
+      <c r="B5" s="322"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322"/>
+      <c r="E5" s="330"/>
+      <c r="F5" s="330"/>
+      <c r="G5" s="330"/>
+      <c r="H5" s="330"/>
+      <c r="I5" s="330"/>
+      <c r="J5" s="361"/>
       <c r="K5" s="100"/>
-      <c r="L5" s="364"/>
-      <c r="M5" s="323"/>
-      <c r="N5" s="323"/>
-      <c r="O5" s="323"/>
+      <c r="L5" s="366"/>
+      <c r="M5" s="330"/>
+      <c r="N5" s="330"/>
+      <c r="O5" s="330"/>
       <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="376"/>
-      <c r="B6" s="376"/>
-      <c r="C6" s="376"/>
-      <c r="D6" s="376"/>
-      <c r="E6" s="362"/>
-      <c r="F6" s="362"/>
-      <c r="G6" s="362"/>
-      <c r="H6" s="362"/>
-      <c r="I6" s="362"/>
-      <c r="J6" s="375"/>
+      <c r="A6" s="364"/>
+      <c r="B6" s="364"/>
+      <c r="C6" s="364"/>
+      <c r="D6" s="364"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="363"/>
+      <c r="H6" s="363"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="362"/>
       <c r="K6" s="160"/>
-      <c r="L6" s="365"/>
-      <c r="M6" s="362"/>
-      <c r="N6" s="362"/>
-      <c r="O6" s="362"/>
+      <c r="L6" s="367"/>
+      <c r="M6" s="363"/>
+      <c r="N6" s="363"/>
+      <c r="O6" s="363"/>
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -13233,8 +13228,8 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="331"/>
-      <c r="S7" s="331"/>
+      <c r="R7" s="320"/>
+      <c r="S7" s="320"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" s="161" t="s">
@@ -13288,8 +13283,8 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="331"/>
-      <c r="S8" s="331"/>
+      <c r="R8" s="320"/>
+      <c r="S8" s="320"/>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" s="161" t="s">
@@ -17621,6 +17616,8 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17636,8 +17633,6 @@
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
     <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17725,42 +17720,42 @@
       <c r="M5" s="257"/>
     </row>
     <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="377" t="s">
+      <c r="C6" s="375" t="s">
         <v>374</v>
       </c>
-      <c r="D6" s="378"/>
-      <c r="E6" s="378"/>
-      <c r="F6" s="378"/>
-      <c r="G6" s="378"/>
-      <c r="H6" s="378"/>
-      <c r="I6" s="378"/>
-      <c r="J6" s="379"/>
+      <c r="D6" s="376"/>
+      <c r="E6" s="376"/>
+      <c r="F6" s="376"/>
+      <c r="G6" s="376"/>
+      <c r="H6" s="376"/>
+      <c r="I6" s="376"/>
+      <c r="J6" s="377"/>
       <c r="K6" s="279"/>
       <c r="L6" s="279"/>
       <c r="M6" s="53"/>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="380"/>
-      <c r="D7" s="381"/>
-      <c r="E7" s="381"/>
-      <c r="F7" s="381"/>
-      <c r="G7" s="381"/>
-      <c r="H7" s="381"/>
-      <c r="I7" s="381"/>
-      <c r="J7" s="382"/>
+      <c r="C7" s="378"/>
+      <c r="D7" s="379"/>
+      <c r="E7" s="379"/>
+      <c r="F7" s="379"/>
+      <c r="G7" s="379"/>
+      <c r="H7" s="379"/>
+      <c r="I7" s="379"/>
+      <c r="J7" s="380"/>
       <c r="K7" s="279"/>
       <c r="L7" s="279"/>
       <c r="M7" s="53"/>
     </row>
     <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="383"/>
-      <c r="D8" s="384"/>
-      <c r="E8" s="384"/>
-      <c r="F8" s="384"/>
-      <c r="G8" s="384"/>
-      <c r="H8" s="384"/>
-      <c r="I8" s="384"/>
-      <c r="J8" s="385"/>
+      <c r="C8" s="381"/>
+      <c r="D8" s="382"/>
+      <c r="E8" s="382"/>
+      <c r="F8" s="382"/>
+      <c r="G8" s="382"/>
+      <c r="H8" s="382"/>
+      <c r="I8" s="382"/>
+      <c r="J8" s="383"/>
       <c r="K8" s="279"/>
       <c r="L8" s="279"/>
       <c r="M8" s="53"/>
@@ -17841,38 +17836,38 @@
       <c r="L14" s="279"/>
     </row>
     <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="377" t="s">
+      <c r="C15" s="375" t="s">
         <v>376</v>
       </c>
-      <c r="D15" s="378"/>
-      <c r="E15" s="378"/>
-      <c r="F15" s="378"/>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="379"/>
+      <c r="D15" s="376"/>
+      <c r="E15" s="376"/>
+      <c r="F15" s="376"/>
+      <c r="G15" s="376"/>
+      <c r="H15" s="376"/>
+      <c r="I15" s="376"/>
+      <c r="J15" s="377"/>
       <c r="K15" s="279"/>
       <c r="L15" s="279"/>
     </row>
     <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="380"/>
-      <c r="D16" s="381"/>
-      <c r="E16" s="381"/>
-      <c r="F16" s="381"/>
-      <c r="G16" s="381"/>
-      <c r="H16" s="381"/>
-      <c r="I16" s="381"/>
-      <c r="J16" s="382"/>
+      <c r="C16" s="378"/>
+      <c r="D16" s="379"/>
+      <c r="E16" s="379"/>
+      <c r="F16" s="379"/>
+      <c r="G16" s="379"/>
+      <c r="H16" s="379"/>
+      <c r="I16" s="379"/>
+      <c r="J16" s="380"/>
     </row>
     <row r="17" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="383"/>
-      <c r="D17" s="384"/>
-      <c r="E17" s="384"/>
-      <c r="F17" s="384"/>
-      <c r="G17" s="384"/>
-      <c r="H17" s="384"/>
-      <c r="I17" s="384"/>
-      <c r="J17" s="385"/>
+      <c r="C17" s="381"/>
+      <c r="D17" s="382"/>
+      <c r="E17" s="382"/>
+      <c r="F17" s="382"/>
+      <c r="G17" s="382"/>
+      <c r="H17" s="382"/>
+      <c r="I17" s="382"/>
+      <c r="J17" s="383"/>
     </row>
     <row r="19" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="20" spans="3:12" x14ac:dyDescent="0.25">
@@ -17947,40 +17942,40 @@
       <c r="L23" s="279"/>
     </row>
     <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="377" t="s">
+      <c r="C24" s="375" t="s">
         <v>378</v>
       </c>
-      <c r="D24" s="378"/>
-      <c r="E24" s="378"/>
-      <c r="F24" s="378"/>
-      <c r="G24" s="378"/>
-      <c r="H24" s="378"/>
-      <c r="I24" s="378"/>
-      <c r="J24" s="379"/>
+      <c r="D24" s="376"/>
+      <c r="E24" s="376"/>
+      <c r="F24" s="376"/>
+      <c r="G24" s="376"/>
+      <c r="H24" s="376"/>
+      <c r="I24" s="376"/>
+      <c r="J24" s="377"/>
       <c r="K24" s="279"/>
       <c r="L24" s="279"/>
     </row>
     <row r="25" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="380"/>
-      <c r="D25" s="381"/>
-      <c r="E25" s="381"/>
-      <c r="F25" s="381"/>
-      <c r="G25" s="381"/>
-      <c r="H25" s="381"/>
-      <c r="I25" s="381"/>
-      <c r="J25" s="382"/>
+      <c r="C25" s="378"/>
+      <c r="D25" s="379"/>
+      <c r="E25" s="379"/>
+      <c r="F25" s="379"/>
+      <c r="G25" s="379"/>
+      <c r="H25" s="379"/>
+      <c r="I25" s="379"/>
+      <c r="J25" s="380"/>
       <c r="K25" s="279"/>
       <c r="L25" s="279"/>
     </row>
     <row r="26" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="383"/>
-      <c r="D26" s="384"/>
-      <c r="E26" s="384"/>
-      <c r="F26" s="384"/>
-      <c r="G26" s="384"/>
-      <c r="H26" s="384"/>
-      <c r="I26" s="384"/>
-      <c r="J26" s="385"/>
+      <c r="C26" s="381"/>
+      <c r="D26" s="382"/>
+      <c r="E26" s="382"/>
+      <c r="F26" s="382"/>
+      <c r="G26" s="382"/>
+      <c r="H26" s="382"/>
+      <c r="I26" s="382"/>
+      <c r="J26" s="383"/>
     </row>
     <row r="28" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="29" spans="3:12" x14ac:dyDescent="0.25">
@@ -18052,37 +18047,37 @@
       <c r="K32" s="279"/>
     </row>
     <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="377" t="s">
+      <c r="C33" s="375" t="s">
         <v>381</v>
       </c>
-      <c r="D33" s="378"/>
-      <c r="E33" s="378"/>
-      <c r="F33" s="378"/>
-      <c r="G33" s="378"/>
-      <c r="H33" s="378"/>
-      <c r="I33" s="378"/>
-      <c r="J33" s="379"/>
+      <c r="D33" s="376"/>
+      <c r="E33" s="376"/>
+      <c r="F33" s="376"/>
+      <c r="G33" s="376"/>
+      <c r="H33" s="376"/>
+      <c r="I33" s="376"/>
+      <c r="J33" s="377"/>
       <c r="K33" s="279"/>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="380"/>
-      <c r="D34" s="381"/>
-      <c r="E34" s="381"/>
-      <c r="F34" s="381"/>
-      <c r="G34" s="381"/>
-      <c r="H34" s="381"/>
-      <c r="I34" s="381"/>
-      <c r="J34" s="382"/>
+      <c r="C34" s="378"/>
+      <c r="D34" s="379"/>
+      <c r="E34" s="379"/>
+      <c r="F34" s="379"/>
+      <c r="G34" s="379"/>
+      <c r="H34" s="379"/>
+      <c r="I34" s="379"/>
+      <c r="J34" s="380"/>
     </row>
     <row r="35" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="383"/>
-      <c r="D35" s="384"/>
-      <c r="E35" s="384"/>
-      <c r="F35" s="384"/>
-      <c r="G35" s="384"/>
-      <c r="H35" s="384"/>
-      <c r="I35" s="384"/>
-      <c r="J35" s="385"/>
+      <c r="C35" s="381"/>
+      <c r="D35" s="382"/>
+      <c r="E35" s="382"/>
+      <c r="F35" s="382"/>
+      <c r="G35" s="382"/>
+      <c r="H35" s="382"/>
+      <c r="I35" s="382"/>
+      <c r="J35" s="383"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
+++ b/2026/EL MIRADOR/Junio/JUNIO - EL MIRADOR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\EL MIRADOR\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\EL MIRADOR\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D9706E-05E8-475B-B399-A275A815CCBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0E06BDA-CE06-4D77-8B08-D2FD3BFD492A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -24,16 +24,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$J$127</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="724" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="703" uniqueCount="411">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -1162,33 +1157,6 @@
     <t>Cuota ARBA</t>
   </si>
   <si>
-    <t>8D</t>
-  </si>
-  <si>
-    <t>Habia abonado bien el mes pasado, $206.121,4 y lo pusimos impago</t>
-  </si>
-  <si>
-    <t>UF 51</t>
-  </si>
-  <si>
-    <t>Abono de mas este mes, abono $377.877,51 - Le debe quedar dinero a favor</t>
-  </si>
-  <si>
-    <t>COCHERA 37</t>
-  </si>
-  <si>
-    <t>La cochera 37 habia pagado $33.586,06 el 10/05 y se lo pusimos al 2F</t>
-  </si>
-  <si>
-    <t>COCHERA 39</t>
-  </si>
-  <si>
-    <t>Jose ferraro</t>
-  </si>
-  <si>
-    <t>Anbono $58.102,08 el 07/05 de la cochera 39 por ende dice que no debe tener deuda alguna - Esa plata se la imputamos a la COCH 30</t>
-  </si>
-  <si>
     <t>VTO 17/07</t>
   </si>
   <si>
@@ -1289,6 +1257,18 @@
   </si>
   <si>
     <t>Transferencia Rocha Sabrina</t>
+  </si>
+  <si>
+    <t>El mes pasado se le puso el uso del sum al 10 E y era el 10 C</t>
+  </si>
+  <si>
+    <t>El 31/05 abono $437.743,36 y $37.368,03 - Creo que no se lo pusimos nunca porque en ese mes el banco cerro antes.</t>
+  </si>
+  <si>
+    <t>7F</t>
+  </si>
+  <si>
+    <t>10C</t>
   </si>
 </sst>
 </file>
@@ -1522,7 +1502,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1622,18 +1602,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2010,7 +1978,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="402">
+  <cellXfs count="395">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -2347,21 +2315,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="16" fontId="0" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2372,11 +2325,52 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="12" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="4" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="16" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="10" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2412,12 +2406,6 @@
     <xf numFmtId="0" fontId="29" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2451,71 +2439,41 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="20" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="28" fillId="18" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -2534,6 +2492,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2607,6 +2574,30 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="1" fontId="24" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2638,19 +2629,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2679,32 +2658,14 @@
     <xf numFmtId="6" fontId="0" fillId="2" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="28" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="16" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="16" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="16" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="16" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="16" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hipervínculo" xfId="5" builtinId="8"/>
@@ -2786,9 +2747,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2826,9 +2787,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2861,26 +2822,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2913,26 +2857,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3107,24 +3034,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N135"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
-    <col min="3" max="3" width="20.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="1" max="1" width="33.44140625" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" customWidth="1"/>
-    <col min="11" max="11" width="18.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.140625" customWidth="1"/>
+    <col min="6" max="9" width="15.6640625" customWidth="1"/>
+    <col min="10" max="10" width="14.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" customWidth="1"/>
     <col min="13" max="13" width="13" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="18" customWidth="1"/>
-    <col min="17" max="17" width="18.28515625" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="82"/>
       <c r="B1" s="91"/>
       <c r="C1" s="98" t="s">
@@ -3138,7 +3065,7 @@
       <c r="I1" s="80"/>
       <c r="J1" s="81"/>
     </row>
-    <row r="2" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A2" s="83"/>
       <c r="B2" s="92"/>
       <c r="C2" s="92" t="s">
@@ -3152,7 +3079,7 @@
       <c r="I2" s="93"/>
       <c r="J2" s="79"/>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="83"/>
       <c r="B3" s="92"/>
       <c r="C3" s="92" t="s">
@@ -3168,7 +3095,7 @@
       <c r="I3" s="93"/>
       <c r="J3" s="79"/>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="83"/>
       <c r="B4" s="92"/>
       <c r="C4" s="92" t="s">
@@ -3182,11 +3109,11 @@
       <c r="I4" s="93"/>
       <c r="J4" s="79"/>
     </row>
-    <row r="5" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A5" s="87"/>
       <c r="B5" s="92"/>
       <c r="C5" s="92" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="D5" s="92"/>
       <c r="E5" s="92" t="s">
@@ -3198,7 +3125,7 @@
       <c r="I5" s="92"/>
       <c r="J5" s="88"/>
     </row>
-    <row r="6" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A6" s="87"/>
       <c r="B6" s="92"/>
       <c r="C6" s="92" t="s">
@@ -3212,7 +3139,7 @@
       <c r="I6" s="92"/>
       <c r="J6" s="88"/>
     </row>
-    <row r="7" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="89"/>
       <c r="B7" s="90"/>
       <c r="C7" s="90"/>
@@ -3224,118 +3151,118 @@
       <c r="I7" s="90"/>
       <c r="J7" s="94"/>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="309" t="s">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="286" t="s">
         <v>245</v>
       </c>
-      <c r="B14" s="309"/>
-      <c r="C14" s="309"/>
-      <c r="D14" s="309"/>
-      <c r="E14" s="309"/>
-      <c r="F14" s="309"/>
-      <c r="G14" s="309"/>
-      <c r="H14" s="309"/>
-      <c r="I14" s="309"/>
-      <c r="J14" s="309"/>
-    </row>
-    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="309"/>
-      <c r="B15" s="309"/>
-      <c r="C15" s="309"/>
-      <c r="D15" s="309"/>
-      <c r="E15" s="309"/>
-      <c r="F15" s="309"/>
-      <c r="G15" s="309"/>
-      <c r="H15" s="309"/>
-      <c r="I15" s="309"/>
-      <c r="J15" s="309"/>
-    </row>
-    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="309"/>
-      <c r="B16" s="309"/>
-      <c r="C16" s="309"/>
-      <c r="D16" s="309"/>
-      <c r="E16" s="309"/>
-      <c r="F16" s="309"/>
-      <c r="G16" s="309"/>
-      <c r="H16" s="309"/>
-      <c r="I16" s="309"/>
-      <c r="J16" s="309"/>
-    </row>
-    <row r="17" spans="1:12" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="309"/>
-      <c r="B17" s="309"/>
-      <c r="C17" s="309"/>
-      <c r="D17" s="309"/>
-      <c r="E17" s="309"/>
-      <c r="F17" s="309"/>
-      <c r="G17" s="309"/>
-      <c r="H17" s="309"/>
-      <c r="I17" s="309"/>
-      <c r="J17" s="309"/>
-    </row>
-    <row r="18" spans="1:12" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="309"/>
-      <c r="B18" s="309"/>
-      <c r="C18" s="309"/>
-      <c r="D18" s="309"/>
-      <c r="E18" s="309"/>
-      <c r="F18" s="309"/>
-      <c r="G18" s="309"/>
-      <c r="H18" s="309"/>
-      <c r="I18" s="309"/>
-      <c r="J18" s="309"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B14" s="286"/>
+      <c r="C14" s="286"/>
+      <c r="D14" s="286"/>
+      <c r="E14" s="286"/>
+      <c r="F14" s="286"/>
+      <c r="G14" s="286"/>
+      <c r="H14" s="286"/>
+      <c r="I14" s="286"/>
+      <c r="J14" s="286"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="286"/>
+      <c r="B15" s="286"/>
+      <c r="C15" s="286"/>
+      <c r="D15" s="286"/>
+      <c r="E15" s="286"/>
+      <c r="F15" s="286"/>
+      <c r="G15" s="286"/>
+      <c r="H15" s="286"/>
+      <c r="I15" s="286"/>
+      <c r="J15" s="286"/>
+    </row>
+    <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="286"/>
+      <c r="B16" s="286"/>
+      <c r="C16" s="286"/>
+      <c r="D16" s="286"/>
+      <c r="E16" s="286"/>
+      <c r="F16" s="286"/>
+      <c r="G16" s="286"/>
+      <c r="H16" s="286"/>
+      <c r="I16" s="286"/>
+      <c r="J16" s="286"/>
+    </row>
+    <row r="17" spans="1:12" ht="25.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="286"/>
+      <c r="B17" s="286"/>
+      <c r="C17" s="286"/>
+      <c r="D17" s="286"/>
+      <c r="E17" s="286"/>
+      <c r="F17" s="286"/>
+      <c r="G17" s="286"/>
+      <c r="H17" s="286"/>
+      <c r="I17" s="286"/>
+      <c r="J17" s="286"/>
+    </row>
+    <row r="18" spans="1:12" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="286"/>
+      <c r="B18" s="286"/>
+      <c r="C18" s="286"/>
+      <c r="D18" s="286"/>
+      <c r="E18" s="286"/>
+      <c r="F18" s="286"/>
+      <c r="G18" s="286"/>
+      <c r="H18" s="286"/>
+      <c r="I18" s="286"/>
+      <c r="J18" s="286"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="H19" s="69"/>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="310" t="s">
-        <v>382</v>
-      </c>
-      <c r="B20" s="310"/>
-      <c r="C20" s="310"/>
-      <c r="D20" s="310"/>
-      <c r="E20" s="310"/>
-      <c r="F20" s="310"/>
-      <c r="G20" s="310"/>
-      <c r="H20" s="310"/>
-      <c r="I20" s="310"/>
-      <c r="J20" s="310"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="310"/>
-      <c r="B21" s="310"/>
-      <c r="C21" s="310"/>
-      <c r="D21" s="310"/>
-      <c r="E21" s="310"/>
-      <c r="F21" s="310"/>
-      <c r="G21" s="310"/>
-      <c r="H21" s="310"/>
-      <c r="I21" s="310"/>
-      <c r="J21" s="310"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="310"/>
-      <c r="B22" s="310"/>
-      <c r="C22" s="310"/>
-      <c r="D22" s="310"/>
-      <c r="E22" s="310"/>
-      <c r="F22" s="310"/>
-      <c r="G22" s="310"/>
-      <c r="H22" s="310"/>
-      <c r="I22" s="310"/>
-      <c r="J22" s="310"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="287" t="s">
+        <v>373</v>
+      </c>
+      <c r="B20" s="287"/>
+      <c r="C20" s="287"/>
+      <c r="D20" s="287"/>
+      <c r="E20" s="287"/>
+      <c r="F20" s="287"/>
+      <c r="G20" s="287"/>
+      <c r="H20" s="287"/>
+      <c r="I20" s="287"/>
+      <c r="J20" s="287"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="287"/>
+      <c r="B21" s="287"/>
+      <c r="C21" s="287"/>
+      <c r="D21" s="287"/>
+      <c r="E21" s="287"/>
+      <c r="F21" s="287"/>
+      <c r="G21" s="287"/>
+      <c r="H21" s="287"/>
+      <c r="I21" s="287"/>
+      <c r="J21" s="287"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="287"/>
+      <c r="B22" s="287"/>
+      <c r="C22" s="287"/>
+      <c r="D22" s="287"/>
+      <c r="E22" s="287"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="287"/>
+      <c r="H22" s="287"/>
+      <c r="I22" s="287"/>
+      <c r="J22" s="287"/>
+    </row>
+    <row r="23" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H23" s="69"/>
     </row>
-    <row r="24" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="200" t="s">
         <v>18</v>
       </c>
@@ -3361,7 +3288,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="205" t="s">
         <v>339</v>
       </c>
@@ -3376,13 +3303,13 @@
       <c r="J25" s="44"/>
       <c r="L25" s="50"/>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" s="207" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B26" s="175"/>
       <c r="C26" s="175" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D26" s="173">
         <v>250000</v>
@@ -3395,15 +3322,15 @@
       <c r="J26" s="44"/>
       <c r="L26" s="50"/>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" s="207" t="s">
         <v>365</v>
       </c>
       <c r="B27" s="175" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="C27" s="175" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="D27" s="173">
         <v>3000000</v>
@@ -3416,7 +3343,7 @@
       <c r="J27" s="3"/>
       <c r="L27" s="50"/>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="208" t="s">
         <v>35</v>
       </c>
@@ -3459,7 +3386,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="207" t="s">
         <v>234</v>
       </c>
@@ -3474,7 +3401,7 @@
       <c r="J29" s="44"/>
       <c r="L29" s="50"/>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" s="207"/>
       <c r="B30" s="175"/>
       <c r="C30" s="175"/>
@@ -3487,7 +3414,7 @@
       <c r="J30" s="44"/>
       <c r="L30" s="50"/>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" s="208" t="s">
         <v>16</v>
       </c>
@@ -3515,7 +3442,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" s="207" t="s">
         <v>230</v>
       </c>
@@ -3530,7 +3457,7 @@
       <c r="J32" s="38"/>
       <c r="L32" s="50"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="136" t="s">
         <v>340</v>
       </c>
@@ -3547,15 +3474,15 @@
       <c r="J33" s="38"/>
       <c r="L33" s="50"/>
     </row>
-    <row r="34" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="136" t="s">
         <v>357</v>
       </c>
       <c r="B34" s="136" t="s">
-        <v>384</v>
-      </c>
-      <c r="C34" s="269" t="s">
-        <v>404</v>
+        <v>375</v>
+      </c>
+      <c r="C34" s="254" t="s">
+        <v>395</v>
       </c>
       <c r="D34" s="173">
         <v>0</v>
@@ -3568,15 +3495,15 @@
       <c r="J34" s="38"/>
       <c r="L34" s="50"/>
     </row>
-    <row r="35" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="136" t="s">
         <v>233</v>
       </c>
       <c r="B35" s="136" t="s">
-        <v>384</v>
-      </c>
-      <c r="C35" s="269" t="s">
-        <v>404</v>
+        <v>375</v>
+      </c>
+      <c r="C35" s="254" t="s">
+        <v>395</v>
       </c>
       <c r="D35" s="173">
         <v>0</v>
@@ -3589,7 +3516,7 @@
       <c r="J35" s="38"/>
       <c r="L35" s="50"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="136"/>
       <c r="B36" s="136"/>
       <c r="C36" s="136"/>
@@ -3602,7 +3529,7 @@
       <c r="J36" s="38"/>
       <c r="L36" s="50"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="208" t="s">
         <v>232</v>
       </c>
@@ -3645,7 +3572,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="207" t="s">
         <v>1</v>
       </c>
@@ -3660,7 +3587,7 @@
       <c r="J38" s="3"/>
       <c r="L38" s="50"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="175"/>
       <c r="B39" s="175"/>
       <c r="C39" s="175"/>
@@ -3673,7 +3600,7 @@
       <c r="J39" s="3"/>
       <c r="L39" s="50"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="175"/>
       <c r="B40" s="175"/>
       <c r="C40" s="175"/>
@@ -3686,7 +3613,7 @@
       <c r="J40" s="3"/>
       <c r="L40" s="50"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="175"/>
       <c r="B41" s="175"/>
       <c r="C41" s="214"/>
@@ -3699,7 +3626,7 @@
       <c r="J41" s="3"/>
       <c r="L41" s="50"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="208" t="s">
         <v>231</v>
       </c>
@@ -3742,7 +3669,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="207" t="s">
         <v>222</v>
       </c>
@@ -3757,7 +3684,7 @@
       <c r="J43" s="25"/>
       <c r="L43" s="50"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="175" t="s">
         <v>226</v>
       </c>
@@ -3798,9 +3725,9 @@
       </c>
       <c r="L44" s="50"/>
     </row>
-    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="287"/>
-      <c r="B45" s="288"/>
+    <row r="45" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="288"/>
+      <c r="B45" s="289"/>
       <c r="C45" s="175"/>
       <c r="D45" s="33"/>
       <c r="E45" s="206"/>
@@ -3812,7 +3739,7 @@
       <c r="K45" s="32"/>
       <c r="L45" s="50"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="208" t="s">
         <v>2</v>
       </c>
@@ -3855,7 +3782,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="207" t="s">
         <v>3</v>
       </c>
@@ -3870,13 +3797,13 @@
       <c r="J47" s="3"/>
       <c r="L47" s="50"/>
     </row>
-    <row r="48" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="218" t="s">
         <v>227</v>
       </c>
       <c r="B48" s="175"/>
       <c r="C48" s="214" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D48" s="219">
         <v>35948.89</v>
@@ -3916,7 +3843,7 @@
       <c r="M48" s="64"/>
       <c r="N48" s="64"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="175" t="s">
         <v>228</v>
       </c>
@@ -3960,13 +3887,13 @@
       <c r="M49" s="64"/>
       <c r="N49" s="64"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="175" t="s">
         <v>229</v>
       </c>
       <c r="B50" s="175"/>
       <c r="C50" s="175" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D50" s="33">
         <v>158988.79999999999</v>
@@ -3997,13 +3924,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="218" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="B51" s="175"/>
-      <c r="C51" s="269" t="s">
-        <v>399</v>
+      <c r="C51" s="254" t="s">
+        <v>390</v>
       </c>
       <c r="D51" s="33">
         <v>427892</v>
@@ -4028,13 +3955,13 @@
       <c r="M51" s="64"/>
       <c r="N51" s="64"/>
     </row>
-    <row r="52" spans="1:14" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="275" t="s">
+    <row r="52" spans="1:14" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="290" t="s">
+        <v>377</v>
+      </c>
+      <c r="B52" s="291"/>
+      <c r="C52" s="136" t="s">
         <v>386</v>
-      </c>
-      <c r="B52" s="311"/>
-      <c r="C52" s="136" t="s">
-        <v>395</v>
       </c>
       <c r="D52" s="33">
         <v>50000</v>
@@ -4065,13 +3992,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="136" t="s">
         <v>259</v>
       </c>
       <c r="B53" s="136"/>
       <c r="C53" s="214" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D53" s="33">
         <v>6491.94</v>
@@ -4102,13 +4029,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="136" t="s">
         <v>260</v>
       </c>
       <c r="B54" s="136"/>
       <c r="C54" s="214" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D54" s="33">
         <v>1145602.71</v>
@@ -4154,7 +4081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="221" t="s">
         <v>258</v>
       </c>
@@ -4189,7 +4116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="208" t="s">
         <v>4</v>
       </c>
@@ -4236,7 +4163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="175"/>
       <c r="B57" s="175"/>
       <c r="C57" s="175"/>
@@ -4249,7 +4176,7 @@
       <c r="J57" s="3"/>
       <c r="L57" s="50"/>
     </row>
-    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="175"/>
       <c r="B58" s="175"/>
       <c r="C58" s="175"/>
@@ -4262,7 +4189,7 @@
       <c r="J58" s="3"/>
       <c r="L58" s="50"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="207" t="s">
         <v>223</v>
       </c>
@@ -4277,13 +4204,13 @@
       <c r="J59" s="3"/>
       <c r="L59" s="50"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="212" t="s">
         <v>338</v>
       </c>
       <c r="B60" s="223"/>
       <c r="C60" s="136" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D60" s="33">
         <v>200000</v>
@@ -4306,13 +4233,13 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="275" t="s">
-        <v>396</v>
-      </c>
-      <c r="B61" s="311"/>
+    <row r="61" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="290" t="s">
+        <v>387</v>
+      </c>
+      <c r="B61" s="291"/>
       <c r="C61" s="33" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="D61" s="33">
         <v>1010955</v>
@@ -4329,13 +4256,13 @@
       <c r="K61" s="32"/>
       <c r="L61" s="54"/>
     </row>
-    <row r="62" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="287" t="s">
-        <v>389</v>
-      </c>
-      <c r="B62" s="288"/>
+    <row r="62" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="288" t="s">
+        <v>380</v>
+      </c>
+      <c r="B62" s="289"/>
       <c r="C62" s="33" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D62" s="33">
         <v>1145449.82</v>
@@ -4373,13 +4300,13 @@
         <v>1145449.8199999998</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="267" t="s">
-        <v>411</v>
-      </c>
-      <c r="B63" s="268"/>
+    <row r="63" spans="1:14" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="252" t="s">
+        <v>402</v>
+      </c>
+      <c r="B63" s="253"/>
       <c r="C63" s="33" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D63" s="33">
         <v>464585.55</v>
@@ -4411,7 +4338,7 @@
       <c r="K63" s="32"/>
       <c r="L63" s="54"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="208" t="s">
         <v>224</v>
       </c>
@@ -4455,7 +4382,7 @@
       </c>
       <c r="N64" s="32"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A65" s="207" t="s">
         <v>5</v>
       </c>
@@ -4470,15 +4397,15 @@
       <c r="J65" s="3"/>
       <c r="L65" s="50"/>
     </row>
-    <row r="66" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="224" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="175" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C66" s="175" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D66" s="33">
         <v>860560</v>
@@ -4511,7 +4438,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="207"/>
       <c r="B67" s="175"/>
       <c r="C67" s="175"/>
@@ -4543,7 +4470,7 @@
       <c r="L67" s="50"/>
       <c r="N67" s="33"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="175"/>
       <c r="B68" s="175"/>
       <c r="C68" s="175"/>
@@ -4557,7 +4484,7 @@
       <c r="L68" s="50"/>
       <c r="N68" s="32"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="208" t="s">
         <v>7</v>
       </c>
@@ -4601,7 +4528,7 @@
       </c>
       <c r="N69" s="32"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="175" t="s">
         <v>26</v>
       </c>
@@ -4637,7 +4564,7 @@
       </c>
       <c r="L70" s="50"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="175" t="s">
         <v>27</v>
       </c>
@@ -4672,7 +4599,7 @@
       </c>
       <c r="L71" s="50"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="208" t="s">
         <v>225</v>
       </c>
@@ -4715,7 +4642,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="73"/>
       <c r="B73" s="73"/>
       <c r="C73" s="73"/>
@@ -4728,7 +4655,7 @@
       <c r="J73" s="72"/>
       <c r="L73" s="50"/>
     </row>
-    <row r="74" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="228" t="s">
         <v>292</v>
       </c>
@@ -4770,7 +4697,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="231"/>
       <c r="B75" s="232"/>
       <c r="C75" s="232"/>
@@ -4784,7 +4711,7 @@
       <c r="K75" s="32"/>
       <c r="L75" s="50"/>
     </row>
-    <row r="76" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="233" t="s">
         <v>28</v>
       </c>
@@ -4831,7 +4758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="65"/>
       <c r="B77" s="65"/>
       <c r="C77" s="65"/>
@@ -4842,7 +4769,7 @@
       <c r="H77" s="32"/>
       <c r="I77" s="32"/>
     </row>
-    <row r="78" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="237" t="s">
         <v>36</v>
       </c>
@@ -4855,12 +4782,12 @@
       <c r="H78" s="32"/>
       <c r="I78" s="32"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="239" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B79" s="65"/>
-      <c r="C79" s="273">
+      <c r="C79" s="256">
         <v>99500</v>
       </c>
       <c r="D79" s="65"/>
@@ -4870,12 +4797,12 @@
       <c r="H79" s="32"/>
       <c r="I79" s="32"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="239" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="B80" s="65"/>
-      <c r="C80" s="273">
+      <c r="C80" s="256">
         <v>99500</v>
       </c>
       <c r="D80" s="65"/>
@@ -4885,12 +4812,12 @@
       <c r="H80" s="32"/>
       <c r="I80" s="32"/>
     </row>
-    <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="239" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B81" s="65"/>
-      <c r="C81" s="273">
+      <c r="C81" s="256">
         <v>99500</v>
       </c>
       <c r="D81" s="65"/>
@@ -4900,12 +4827,12 @@
       <c r="H81" s="32"/>
       <c r="I81" s="32"/>
     </row>
-    <row r="82" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="239" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B82" s="65"/>
-      <c r="C82" s="273">
+      <c r="C82" s="256">
         <v>85744</v>
       </c>
       <c r="D82" s="65"/>
@@ -4915,7 +4842,7 @@
       <c r="H82" s="32"/>
       <c r="I82" s="32"/>
     </row>
-    <row r="83" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="240" t="s">
         <v>16</v>
       </c>
@@ -4931,7 +4858,7 @@
       <c r="H83" s="32"/>
       <c r="I83" s="32"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A84" s="65"/>
       <c r="B84" s="65"/>
       <c r="C84" s="65"/>
@@ -4942,7 +4869,7 @@
       <c r="H84" s="32"/>
       <c r="I84" s="32"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A85" s="65"/>
       <c r="B85" s="65"/>
       <c r="C85" s="65"/>
@@ -4953,13 +4880,13 @@
       <c r="H85" s="46"/>
       <c r="I85" s="46"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A86" s="296" t="s">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A86" s="310" t="s">
         <v>32</v>
       </c>
-      <c r="B86" s="297"/>
-      <c r="C86" s="297"/>
-      <c r="D86" s="297"/>
+      <c r="B86" s="311"/>
+      <c r="C86" s="311"/>
+      <c r="D86" s="311"/>
       <c r="E86" s="60" t="s">
         <v>10</v>
       </c>
@@ -4979,9 +4906,9 @@
         <v>169</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="275"/>
-      <c r="B87" s="276"/>
+    <row r="87" spans="1:13" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="290"/>
+      <c r="B87" s="292"/>
       <c r="C87" s="244"/>
       <c r="D87" s="33"/>
       <c r="E87" s="220">
@@ -4994,9 +4921,9 @@
       <c r="I87" s="49"/>
       <c r="J87" s="44"/>
     </row>
-    <row r="88" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="298"/>
-      <c r="B88" s="299"/>
+    <row r="88" spans="1:13" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="312"/>
+      <c r="B88" s="313"/>
       <c r="C88" s="62"/>
       <c r="D88" s="33"/>
       <c r="E88" s="49"/>
@@ -5006,12 +4933,12 @@
       <c r="I88" s="49"/>
       <c r="J88" s="44"/>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A89" s="293" t="s">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A89" s="307" t="s">
         <v>16</v>
       </c>
-      <c r="B89" s="294"/>
-      <c r="C89" s="295"/>
+      <c r="B89" s="308"/>
+      <c r="C89" s="309"/>
       <c r="D89" s="59">
         <f>SUM(D87:D88)</f>
         <v>0</v>
@@ -5037,14 +4964,14 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="E91" s="32"/>
       <c r="F91" s="32"/>
       <c r="G91" s="32"/>
       <c r="H91" s="32"/>
       <c r="I91" s="32"/>
     </row>
-    <row r="92" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="27" t="s">
         <v>29</v>
       </c>
@@ -5053,7 +4980,7 @@
         <v>20282253.399999999</v>
       </c>
     </row>
-    <row r="93" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" ht="18.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="29" t="s">
         <v>31</v>
       </c>
@@ -5061,45 +4988,45 @@
         <f>D76-D74</f>
         <v>15282253.399999999</v>
       </c>
-      <c r="D93" s="277" t="s">
+      <c r="D93" s="293" t="s">
         <v>284</v>
       </c>
-      <c r="E93" s="277"/>
-      <c r="F93" s="277"/>
-      <c r="G93" s="277"/>
-      <c r="H93" s="277"/>
-      <c r="I93" s="277"/>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D94" s="277"/>
-      <c r="E94" s="277"/>
-      <c r="F94" s="277"/>
-      <c r="G94" s="277"/>
-      <c r="H94" s="277"/>
-      <c r="I94" s="277"/>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="D95" s="277"/>
-      <c r="E95" s="277"/>
-      <c r="F95" s="277"/>
-      <c r="G95" s="277"/>
-      <c r="H95" s="277"/>
-      <c r="I95" s="277"/>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E93" s="293"/>
+      <c r="F93" s="293"/>
+      <c r="G93" s="293"/>
+      <c r="H93" s="293"/>
+      <c r="I93" s="293"/>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D94" s="293"/>
+      <c r="E94" s="293"/>
+      <c r="F94" s="293"/>
+      <c r="G94" s="293"/>
+      <c r="H94" s="293"/>
+      <c r="I94" s="293"/>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="D95" s="293"/>
+      <c r="E95" s="293"/>
+      <c r="F95" s="293"/>
+      <c r="G95" s="293"/>
+      <c r="H95" s="293"/>
+      <c r="I95" s="293"/>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
         <v>19</v>
       </c>
       <c r="B96" s="9"/>
       <c r="C96" s="10"/>
-      <c r="D96" s="277"/>
-      <c r="E96" s="277"/>
-      <c r="F96" s="277"/>
-      <c r="G96" s="277"/>
-      <c r="H96" s="277"/>
-      <c r="I96" s="277"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D96" s="293"/>
+      <c r="E96" s="293"/>
+      <c r="F96" s="293"/>
+      <c r="G96" s="293"/>
+      <c r="H96" s="293"/>
+      <c r="I96" s="293"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="11" t="s">
         <v>20</v>
       </c>
@@ -5107,14 +5034,14 @@
         <v>687013.08954010718</v>
       </c>
       <c r="C97" s="12"/>
-      <c r="D97" s="277"/>
-      <c r="E97" s="277"/>
-      <c r="F97" s="277"/>
-      <c r="G97" s="277"/>
-      <c r="H97" s="277"/>
-      <c r="I97" s="277"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D97" s="293"/>
+      <c r="E97" s="293"/>
+      <c r="F97" s="293"/>
+      <c r="G97" s="293"/>
+      <c r="H97" s="293"/>
+      <c r="I97" s="293"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>21</v>
       </c>
@@ -5125,14 +5052,14 @@
       <c r="C98" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="D98" s="277"/>
-      <c r="E98" s="277"/>
-      <c r="F98" s="277"/>
-      <c r="G98" s="277"/>
-      <c r="H98" s="277"/>
-      <c r="I98" s="277"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D98" s="293"/>
+      <c r="E98" s="293"/>
+      <c r="F98" s="293"/>
+      <c r="G98" s="293"/>
+      <c r="H98" s="293"/>
+      <c r="I98" s="293"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>344</v>
       </c>
@@ -5141,14 +5068,14 @@
         <v>912822.36</v>
       </c>
       <c r="C99" s="12"/>
-      <c r="D99" s="277"/>
-      <c r="E99" s="277"/>
-      <c r="F99" s="277"/>
-      <c r="G99" s="277"/>
-      <c r="H99" s="277"/>
-      <c r="I99" s="277"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D99" s="293"/>
+      <c r="E99" s="293"/>
+      <c r="F99" s="293"/>
+      <c r="G99" s="293"/>
+      <c r="H99" s="293"/>
+      <c r="I99" s="293"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>34</v>
       </c>
@@ -5157,15 +5084,15 @@
         <v>-15282253.399999999</v>
       </c>
       <c r="C100" s="10"/>
-      <c r="D100" s="277"/>
-      <c r="E100" s="277"/>
-      <c r="F100" s="277"/>
-      <c r="G100" s="277"/>
-      <c r="H100" s="277"/>
-      <c r="I100" s="277"/>
+      <c r="D100" s="293"/>
+      <c r="E100" s="293"/>
+      <c r="F100" s="293"/>
+      <c r="G100" s="293"/>
+      <c r="H100" s="293"/>
+      <c r="I100" s="293"/>
       <c r="K100" s="33"/>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>33</v>
       </c>
@@ -5174,15 +5101,15 @@
         <v>0</v>
       </c>
       <c r="C101" s="10"/>
-      <c r="D101" s="277"/>
-      <c r="E101" s="277"/>
-      <c r="F101" s="277"/>
-      <c r="G101" s="277"/>
-      <c r="H101" s="277"/>
-      <c r="I101" s="277"/>
+      <c r="D101" s="293"/>
+      <c r="E101" s="293"/>
+      <c r="F101" s="293"/>
+      <c r="G101" s="293"/>
+      <c r="H101" s="293"/>
+      <c r="I101" s="293"/>
       <c r="K101" s="39"/>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>274</v>
       </c>
@@ -5191,31 +5118,31 @@
         <v>94985.93</v>
       </c>
       <c r="C102" s="10"/>
-      <c r="D102" s="277"/>
-      <c r="E102" s="277"/>
-      <c r="F102" s="277"/>
-      <c r="G102" s="277"/>
-      <c r="H102" s="277"/>
-      <c r="I102" s="277"/>
+      <c r="D102" s="293"/>
+      <c r="E102" s="293"/>
+      <c r="F102" s="293"/>
+      <c r="G102" s="293"/>
+      <c r="H102" s="293"/>
+      <c r="I102" s="293"/>
       <c r="K102" s="39"/>
     </row>
-    <row r="103" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="188" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="B103" s="22">
         <v>46200</v>
       </c>
       <c r="C103" s="10"/>
-      <c r="D103" s="277"/>
-      <c r="E103" s="277"/>
-      <c r="F103" s="277"/>
-      <c r="G103" s="277"/>
-      <c r="H103" s="277"/>
-      <c r="I103" s="277"/>
+      <c r="D103" s="293"/>
+      <c r="E103" s="293"/>
+      <c r="F103" s="293"/>
+      <c r="G103" s="293"/>
+      <c r="H103" s="293"/>
+      <c r="I103" s="293"/>
       <c r="K103" s="39"/>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="13" t="s">
         <v>30</v>
       </c>
@@ -5224,14 +5151,14 @@
         <v>-100000</v>
       </c>
       <c r="C104" s="14"/>
-      <c r="D104" s="277"/>
-      <c r="E104" s="277"/>
-      <c r="F104" s="277"/>
-      <c r="G104" s="277"/>
-      <c r="H104" s="277"/>
-      <c r="I104" s="277"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D104" s="293"/>
+      <c r="E104" s="293"/>
+      <c r="F104" s="293"/>
+      <c r="G104" s="293"/>
+      <c r="H104" s="293"/>
+      <c r="I104" s="293"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="13" t="s">
         <v>36</v>
       </c>
@@ -5240,14 +5167,14 @@
         <v>-384244</v>
       </c>
       <c r="C105" s="14"/>
-      <c r="D105" s="277"/>
-      <c r="E105" s="277"/>
-      <c r="F105" s="277"/>
-      <c r="G105" s="277"/>
-      <c r="H105" s="277"/>
-      <c r="I105" s="277"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D105" s="293"/>
+      <c r="E105" s="293"/>
+      <c r="F105" s="293"/>
+      <c r="G105" s="293"/>
+      <c r="H105" s="293"/>
+      <c r="I105" s="293"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="11" t="s">
         <v>23</v>
       </c>
@@ -5256,39 +5183,39 @@
         <v>2295399.0303661046</v>
       </c>
       <c r="C106" s="51"/>
-      <c r="D106" s="277"/>
-      <c r="E106" s="277"/>
-      <c r="F106" s="277"/>
-      <c r="G106" s="277"/>
-      <c r="H106" s="277"/>
-      <c r="I106" s="277"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D106" s="293"/>
+      <c r="E106" s="293"/>
+      <c r="F106" s="293"/>
+      <c r="G106" s="293"/>
+      <c r="H106" s="293"/>
+      <c r="I106" s="293"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="14"/>
       <c r="C107" s="10"/>
-      <c r="D107" s="277"/>
-      <c r="E107" s="277"/>
-      <c r="F107" s="277"/>
-      <c r="G107" s="277"/>
-      <c r="H107" s="277"/>
-      <c r="I107" s="277"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D107" s="293"/>
+      <c r="E107" s="293"/>
+      <c r="F107" s="293"/>
+      <c r="G107" s="293"/>
+      <c r="H107" s="293"/>
+      <c r="I107" s="293"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>273</v>
       </c>
       <c r="B108" s="5"/>
       <c r="C108" s="10"/>
-      <c r="D108" s="277"/>
-      <c r="E108" s="277"/>
-      <c r="F108" s="277"/>
-      <c r="G108" s="277"/>
-      <c r="H108" s="277"/>
-      <c r="I108" s="277"/>
-    </row>
-    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D108" s="293"/>
+      <c r="E108" s="293"/>
+      <c r="F108" s="293"/>
+      <c r="G108" s="293"/>
+      <c r="H108" s="293"/>
+      <c r="I108" s="293"/>
+    </row>
+    <row r="109" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="196" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="B109" s="22">
         <v>94985.93</v>
@@ -5297,7 +5224,7 @@
       <c r="D109" s="17"/>
       <c r="E109" s="17"/>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="25" t="s">
         <v>16</v>
       </c>
@@ -5308,17 +5235,17 @@
       <c r="C110" s="10"/>
       <c r="E110" s="17"/>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" s="14"/>
       <c r="C111" s="10"/>
       <c r="D111" s="17"/>
     </row>
-    <row r="112" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A112" s="14"/>
       <c r="C112" s="10"/>
       <c r="D112" s="17"/>
     </row>
-    <row r="113" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="8" t="s">
         <v>19</v>
       </c>
@@ -5326,47 +5253,47 @@
         <v>106182.28</v>
       </c>
       <c r="C113" s="10"/>
-      <c r="D113" s="300" t="s">
-        <v>410</v>
-      </c>
-      <c r="E113" s="301"/>
-      <c r="F113" s="301"/>
-      <c r="G113" s="301"/>
-      <c r="H113" s="301"/>
-      <c r="I113" s="302"/>
-    </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D113" s="314" t="s">
+        <v>401</v>
+      </c>
+      <c r="E113" s="315"/>
+      <c r="F113" s="315"/>
+      <c r="G113" s="315"/>
+      <c r="H113" s="315"/>
+      <c r="I113" s="316"/>
+    </row>
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="11" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="B114" s="23">
         <v>-60000</v>
       </c>
       <c r="C114" s="10"/>
-      <c r="D114" s="303"/>
-      <c r="E114" s="304"/>
-      <c r="F114" s="304"/>
-      <c r="G114" s="304"/>
-      <c r="H114" s="304"/>
-      <c r="I114" s="305"/>
-    </row>
-    <row r="115" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D114" s="317"/>
+      <c r="E114" s="318"/>
+      <c r="F114" s="318"/>
+      <c r="G114" s="318"/>
+      <c r="H114" s="318"/>
+      <c r="I114" s="319"/>
+    </row>
+    <row r="115" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="199" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="B115" s="23">
         <f>-24000*3</f>
         <v>-72000</v>
       </c>
       <c r="C115" s="10"/>
-      <c r="D115" s="303"/>
-      <c r="E115" s="304"/>
-      <c r="F115" s="304"/>
-      <c r="G115" s="304"/>
-      <c r="H115" s="304"/>
-      <c r="I115" s="305"/>
-    </row>
-    <row r="116" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D115" s="317"/>
+      <c r="E115" s="318"/>
+      <c r="F115" s="318"/>
+      <c r="G115" s="318"/>
+      <c r="H115" s="318"/>
+      <c r="I115" s="319"/>
+    </row>
+    <row r="116" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="25" t="s">
         <v>16</v>
       </c>
@@ -5375,31 +5302,31 @@
         <v>-25817.72</v>
       </c>
       <c r="C116" s="10"/>
-      <c r="D116" s="306"/>
-      <c r="E116" s="307"/>
-      <c r="F116" s="307"/>
-      <c r="G116" s="307"/>
-      <c r="H116" s="307"/>
-      <c r="I116" s="308"/>
-    </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D116" s="320"/>
+      <c r="E116" s="321"/>
+      <c r="F116" s="321"/>
+      <c r="G116" s="321"/>
+      <c r="H116" s="321"/>
+      <c r="I116" s="322"/>
+    </row>
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="14"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="14"/>
       <c r="F118" s="53"/>
       <c r="G118" s="53"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="14"/>
       <c r="F119" s="53"/>
       <c r="G119" s="53"/>
     </row>
-    <row r="120" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="H120" s="64"/>
       <c r="I120" s="64"/>
     </row>
-    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>361</v>
       </c>
@@ -5407,17 +5334,17 @@
         <v>498840</v>
       </c>
       <c r="C121" s="16"/>
-      <c r="D121" s="278" t="s">
-        <v>414</v>
-      </c>
-      <c r="E121" s="279"/>
-      <c r="F121" s="279"/>
-      <c r="G121" s="279"/>
-      <c r="H121" s="279"/>
-      <c r="I121" s="279"/>
-      <c r="J121" s="280"/>
-    </row>
-    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D121" s="294" t="s">
+        <v>405</v>
+      </c>
+      <c r="E121" s="295"/>
+      <c r="F121" s="295"/>
+      <c r="G121" s="295"/>
+      <c r="H121" s="295"/>
+      <c r="I121" s="295"/>
+      <c r="J121" s="296"/>
+    </row>
+    <row r="122" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="11" t="s">
         <v>240</v>
       </c>
@@ -5425,29 +5352,29 @@
         <v>100000</v>
       </c>
       <c r="C122" s="16"/>
-      <c r="D122" s="281"/>
-      <c r="E122" s="282"/>
-      <c r="F122" s="282"/>
-      <c r="G122" s="282"/>
-      <c r="H122" s="282"/>
-      <c r="I122" s="282"/>
-      <c r="J122" s="283"/>
-    </row>
-    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D122" s="297"/>
+      <c r="E122" s="298"/>
+      <c r="F122" s="298"/>
+      <c r="G122" s="298"/>
+      <c r="H122" s="298"/>
+      <c r="I122" s="298"/>
+      <c r="J122" s="299"/>
+    </row>
+    <row r="123" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="11"/>
       <c r="B123" s="63">
         <v>0</v>
       </c>
       <c r="C123" s="16"/>
-      <c r="D123" s="281"/>
-      <c r="E123" s="282"/>
-      <c r="F123" s="282"/>
-      <c r="G123" s="282"/>
-      <c r="H123" s="282"/>
-      <c r="I123" s="282"/>
-      <c r="J123" s="283"/>
-    </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D123" s="297"/>
+      <c r="E123" s="298"/>
+      <c r="F123" s="298"/>
+      <c r="G123" s="298"/>
+      <c r="H123" s="298"/>
+      <c r="I123" s="298"/>
+      <c r="J123" s="299"/>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="25" t="s">
         <v>16</v>
       </c>
@@ -5456,70 +5383,70 @@
         <v>598840</v>
       </c>
       <c r="C124" s="16"/>
-      <c r="D124" s="281"/>
-      <c r="E124" s="282"/>
-      <c r="F124" s="282"/>
-      <c r="G124" s="282"/>
-      <c r="H124" s="282"/>
-      <c r="I124" s="282"/>
-      <c r="J124" s="283"/>
-    </row>
-    <row r="125" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D124" s="297"/>
+      <c r="E124" s="298"/>
+      <c r="F124" s="298"/>
+      <c r="G124" s="298"/>
+      <c r="H124" s="298"/>
+      <c r="I124" s="298"/>
+      <c r="J124" s="299"/>
+    </row>
+    <row r="125" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C125" s="17"/>
-      <c r="D125" s="281"/>
-      <c r="E125" s="282"/>
-      <c r="F125" s="282"/>
-      <c r="G125" s="282"/>
-      <c r="H125" s="282"/>
-      <c r="I125" s="282"/>
-      <c r="J125" s="283"/>
-    </row>
-    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="289" t="s">
+      <c r="D125" s="297"/>
+      <c r="E125" s="298"/>
+      <c r="F125" s="298"/>
+      <c r="G125" s="298"/>
+      <c r="H125" s="298"/>
+      <c r="I125" s="298"/>
+      <c r="J125" s="299"/>
+    </row>
+    <row r="126" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="303" t="s">
         <v>362</v>
       </c>
-      <c r="B126" s="291">
+      <c r="B126" s="305">
         <f>B124+B106+B116</f>
         <v>2868421.3103661044</v>
       </c>
       <c r="C126" s="10"/>
-      <c r="D126" s="281"/>
-      <c r="E126" s="282"/>
-      <c r="F126" s="282"/>
-      <c r="G126" s="282"/>
-      <c r="H126" s="282"/>
-      <c r="I126" s="282"/>
-      <c r="J126" s="283"/>
-    </row>
-    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="290"/>
-      <c r="B127" s="292"/>
-      <c r="D127" s="284"/>
-      <c r="E127" s="285"/>
-      <c r="F127" s="285"/>
-      <c r="G127" s="285"/>
-      <c r="H127" s="285"/>
-      <c r="I127" s="285"/>
-      <c r="J127" s="286"/>
-    </row>
-    <row r="133" spans="4:8" x14ac:dyDescent="0.25">
+      <c r="D126" s="297"/>
+      <c r="E126" s="298"/>
+      <c r="F126" s="298"/>
+      <c r="G126" s="298"/>
+      <c r="H126" s="298"/>
+      <c r="I126" s="298"/>
+      <c r="J126" s="299"/>
+    </row>
+    <row r="127" spans="1:10" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="304"/>
+      <c r="B127" s="306"/>
+      <c r="D127" s="300"/>
+      <c r="E127" s="301"/>
+      <c r="F127" s="301"/>
+      <c r="G127" s="301"/>
+      <c r="H127" s="301"/>
+      <c r="I127" s="301"/>
+      <c r="J127" s="302"/>
+    </row>
+    <row r="133" spans="4:8" x14ac:dyDescent="0.3">
       <c r="D133" s="53"/>
       <c r="E133" s="53"/>
       <c r="F133" s="53"/>
       <c r="G133" s="53"/>
       <c r="H133" s="53"/>
     </row>
-    <row r="134" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D134" s="274" t="s">
-        <v>413</v>
+    <row r="134" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D134" s="257" t="s">
+        <v>404</v>
       </c>
       <c r="E134" s="53"/>
       <c r="F134" s="53"/>
       <c r="G134" s="53"/>
       <c r="H134" s="53"/>
     </row>
-    <row r="135" spans="4:8" x14ac:dyDescent="0.25">
-      <c r="D135" s="274"/>
+    <row r="135" spans="4:8" x14ac:dyDescent="0.3">
+      <c r="D135" s="257"/>
       <c r="E135" s="53"/>
       <c r="F135" s="53"/>
       <c r="G135" s="53"/>
@@ -5527,11 +5454,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A14:J18"/>
-    <mergeCell ref="A20:J22"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A61:B61"/>
     <mergeCell ref="A87:B87"/>
     <mergeCell ref="D93:I108"/>
     <mergeCell ref="D121:J127"/>
@@ -5542,6 +5464,11 @@
     <mergeCell ref="A86:D86"/>
     <mergeCell ref="A88:B88"/>
     <mergeCell ref="D113:I116"/>
+    <mergeCell ref="A14:J18"/>
+    <mergeCell ref="A20:J22"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="90" orientation="landscape" r:id="rId1"/>
@@ -5552,37 +5479,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:DJ154"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="8.140625" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" customWidth="1"/>
-    <col min="5" max="5" width="25.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" customWidth="1"/>
-    <col min="7" max="7" width="15.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="12" width="13.28515625" customWidth="1"/>
-    <col min="13" max="13" width="11.140625" customWidth="1"/>
-    <col min="14" max="14" width="15.42578125" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="8.109375" customWidth="1"/>
+    <col min="4" max="4" width="42.6640625" customWidth="1"/>
+    <col min="5" max="5" width="25.5546875" customWidth="1"/>
+    <col min="6" max="6" width="9.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" customWidth="1"/>
+    <col min="11" max="11" width="12.5546875" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" customWidth="1"/>
+    <col min="13" max="13" width="11.109375" customWidth="1"/>
+    <col min="14" max="14" width="15.44140625" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A1" s="346" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A1" s="353" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="347"/>
-      <c r="C1" s="347"/>
-      <c r="D1" s="347"/>
-      <c r="E1" s="347"/>
+      <c r="B1" s="354"/>
+      <c r="C1" s="354"/>
+      <c r="D1" s="354"/>
+      <c r="E1" s="354"/>
       <c r="F1" s="120" t="s">
         <v>276</v>
       </c>
@@ -5594,20 +5521,20 @@
       <c r="L1" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="M1" s="324">
+      <c r="M1" s="328">
         <f>RESUMEN!D76-N3</f>
         <v>14275955.399999999</v>
       </c>
-      <c r="N1" s="325"/>
+      <c r="N1" s="329"/>
       <c r="O1" s="121"/>
       <c r="P1" s="45"/>
     </row>
-    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="348"/>
-      <c r="B2" s="349"/>
-      <c r="C2" s="349"/>
-      <c r="D2" s="349"/>
-      <c r="E2" s="349"/>
+    <row r="2" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="355"/>
+      <c r="B2" s="356"/>
+      <c r="C2" s="356"/>
+      <c r="D2" s="356"/>
+      <c r="E2" s="356"/>
       <c r="F2" s="4" t="s">
         <v>275</v>
       </c>
@@ -5626,12 +5553,12 @@
       <c r="O2" s="122"/>
       <c r="P2" s="45"/>
     </row>
-    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="348"/>
-      <c r="B3" s="349"/>
-      <c r="C3" s="349"/>
-      <c r="D3" s="349"/>
-      <c r="E3" s="349"/>
+    <row r="3" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="355"/>
+      <c r="B3" s="356"/>
+      <c r="C3" s="356"/>
+      <c r="D3" s="356"/>
+      <c r="E3" s="356"/>
       <c r="F3" s="4" t="s">
         <v>277</v>
       </c>
@@ -5650,12 +5577,12 @@
       <c r="O3" s="124"/>
       <c r="P3" s="7"/>
     </row>
-    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="350"/>
-      <c r="B4" s="351"/>
-      <c r="C4" s="351"/>
-      <c r="D4" s="351"/>
-      <c r="E4" s="351"/>
+    <row r="4" spans="1:19" ht="2.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="357"/>
+      <c r="B4" s="358"/>
+      <c r="C4" s="358"/>
+      <c r="D4" s="358"/>
+      <c r="E4" s="358"/>
       <c r="F4" s="125"/>
       <c r="G4" s="125"/>
       <c r="H4" s="125"/>
@@ -5668,98 +5595,98 @@
       <c r="O4" s="128"/>
       <c r="P4" s="7"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
-      <c r="C5" s="331" t="s">
-        <v>407</v>
-      </c>
-      <c r="D5" s="332"/>
-      <c r="E5" s="332"/>
-      <c r="F5" s="332"/>
-      <c r="G5" s="332"/>
-      <c r="H5" s="332"/>
-      <c r="I5" s="332"/>
-      <c r="J5" s="332"/>
-      <c r="K5" s="332"/>
-      <c r="L5" s="332"/>
-      <c r="M5" s="332"/>
-      <c r="N5" s="332"/>
-      <c r="O5" s="333"/>
+      <c r="C5" s="338" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="339"/>
+      <c r="E5" s="339"/>
+      <c r="F5" s="339"/>
+      <c r="G5" s="339"/>
+      <c r="H5" s="339"/>
+      <c r="I5" s="339"/>
+      <c r="J5" s="339"/>
+      <c r="K5" s="339"/>
+      <c r="L5" s="339"/>
+      <c r="M5" s="339"/>
+      <c r="N5" s="339"/>
+      <c r="O5" s="340"/>
       <c r="P5" s="7"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4"/>
-      <c r="C6" s="334"/>
-      <c r="D6" s="335"/>
-      <c r="E6" s="335"/>
-      <c r="F6" s="335"/>
-      <c r="G6" s="335"/>
-      <c r="H6" s="335"/>
-      <c r="I6" s="335"/>
-      <c r="J6" s="335"/>
-      <c r="K6" s="335"/>
-      <c r="L6" s="335"/>
-      <c r="M6" s="335"/>
-      <c r="N6" s="335"/>
-      <c r="O6" s="336"/>
+      <c r="C6" s="341"/>
+      <c r="D6" s="342"/>
+      <c r="E6" s="342"/>
+      <c r="F6" s="342"/>
+      <c r="G6" s="342"/>
+      <c r="H6" s="342"/>
+      <c r="I6" s="342"/>
+      <c r="J6" s="342"/>
+      <c r="K6" s="342"/>
+      <c r="L6" s="342"/>
+      <c r="M6" s="342"/>
+      <c r="N6" s="342"/>
+      <c r="O6" s="343"/>
       <c r="P6" s="7"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="334"/>
-      <c r="D7" s="335"/>
-      <c r="E7" s="335"/>
-      <c r="F7" s="335"/>
-      <c r="G7" s="335"/>
-      <c r="H7" s="335"/>
-      <c r="I7" s="335"/>
-      <c r="J7" s="335"/>
-      <c r="K7" s="335"/>
-      <c r="L7" s="335"/>
-      <c r="M7" s="335"/>
-      <c r="N7" s="335"/>
-      <c r="O7" s="336"/>
+      <c r="C7" s="341"/>
+      <c r="D7" s="342"/>
+      <c r="E7" s="342"/>
+      <c r="F7" s="342"/>
+      <c r="G7" s="342"/>
+      <c r="H7" s="342"/>
+      <c r="I7" s="342"/>
+      <c r="J7" s="342"/>
+      <c r="K7" s="342"/>
+      <c r="L7" s="342"/>
+      <c r="M7" s="342"/>
+      <c r="N7" s="342"/>
+      <c r="O7" s="343"/>
       <c r="P7" s="7"/>
     </row>
-    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4"/>
       <c r="B8" s="4"/>
-      <c r="C8" s="337"/>
-      <c r="D8" s="338"/>
-      <c r="E8" s="338"/>
-      <c r="F8" s="338"/>
-      <c r="G8" s="338"/>
-      <c r="H8" s="338"/>
-      <c r="I8" s="338"/>
-      <c r="J8" s="338"/>
-      <c r="K8" s="338"/>
-      <c r="L8" s="338"/>
-      <c r="M8" s="338"/>
-      <c r="N8" s="338"/>
-      <c r="O8" s="339"/>
+      <c r="C8" s="344"/>
+      <c r="D8" s="345"/>
+      <c r="E8" s="345"/>
+      <c r="F8" s="345"/>
+      <c r="G8" s="345"/>
+      <c r="H8" s="345"/>
+      <c r="I8" s="345"/>
+      <c r="J8" s="345"/>
+      <c r="K8" s="345"/>
+      <c r="L8" s="345"/>
+      <c r="M8" s="345"/>
+      <c r="N8" s="345"/>
+      <c r="O8" s="346"/>
       <c r="Q8" s="64"/>
     </row>
-    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
-      <c r="C9" s="340" t="s">
+      <c r="C9" s="347" t="s">
         <v>289</v>
       </c>
-      <c r="D9" s="341"/>
-      <c r="E9" s="341"/>
-      <c r="F9" s="341"/>
-      <c r="G9" s="341"/>
-      <c r="H9" s="341"/>
-      <c r="I9" s="341"/>
-      <c r="J9" s="341"/>
-      <c r="K9" s="341"/>
-      <c r="L9" s="341"/>
-      <c r="M9" s="341"/>
-      <c r="N9" s="341"/>
-      <c r="O9" s="342"/>
+      <c r="D9" s="348"/>
+      <c r="E9" s="348"/>
+      <c r="F9" s="348"/>
+      <c r="G9" s="348"/>
+      <c r="H9" s="348"/>
+      <c r="I9" s="348"/>
+      <c r="J9" s="348"/>
+      <c r="K9" s="348"/>
+      <c r="L9" s="348"/>
+      <c r="M9" s="348"/>
+      <c r="N9" s="348"/>
+      <c r="O9" s="349"/>
       <c r="Q9" t="s">
         <v>235</v>
       </c>
@@ -5768,22 +5695,22 @@
         <v>199021.59712799999</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
-      <c r="C10" s="343"/>
-      <c r="D10" s="344"/>
-      <c r="E10" s="344"/>
-      <c r="F10" s="344"/>
-      <c r="G10" s="344"/>
-      <c r="H10" s="344"/>
-      <c r="I10" s="344"/>
-      <c r="J10" s="344"/>
-      <c r="K10" s="344"/>
-      <c r="L10" s="344"/>
-      <c r="M10" s="344"/>
-      <c r="N10" s="344"/>
-      <c r="O10" s="345"/>
+      <c r="C10" s="350"/>
+      <c r="D10" s="351"/>
+      <c r="E10" s="351"/>
+      <c r="F10" s="351"/>
+      <c r="G10" s="351"/>
+      <c r="H10" s="351"/>
+      <c r="I10" s="351"/>
+      <c r="J10" s="351"/>
+      <c r="K10" s="351"/>
+      <c r="L10" s="351"/>
+      <c r="M10" s="351"/>
+      <c r="N10" s="351"/>
+      <c r="O10" s="352"/>
       <c r="Q10" t="s">
         <v>236</v>
       </c>
@@ -5792,50 +5719,50 @@
         <v>235877.44844800004</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="315" t="s">
+    <row r="11" spans="1:19" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="324" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="317" t="s">
+      <c r="B11" s="359" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="315" t="s">
+      <c r="C11" s="324" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="319" t="s">
+      <c r="D11" s="361" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="319" t="s">
+      <c r="E11" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="F11" s="315" t="s">
+      <c r="F11" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="G11" s="315" t="s">
+      <c r="G11" s="324" t="s">
         <v>12</v>
       </c>
-      <c r="H11" s="315" t="s">
+      <c r="H11" s="324" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="326" t="s">
+      <c r="I11" s="330" t="s">
         <v>14</v>
       </c>
-      <c r="J11" s="312" t="s">
+      <c r="J11" s="332" t="s">
         <v>15</v>
       </c>
-      <c r="K11" s="312" t="s">
+      <c r="K11" s="332" t="s">
         <v>372</v>
       </c>
-      <c r="L11" s="312" t="s">
+      <c r="L11" s="332" t="s">
         <v>17</v>
       </c>
-      <c r="M11" s="328" t="s">
+      <c r="M11" s="335" t="s">
         <v>37</v>
       </c>
-      <c r="N11" s="312" t="s">
+      <c r="N11" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="O11" s="312" t="s">
+      <c r="O11" s="332" t="s">
         <v>261</v>
       </c>
       <c r="Q11" t="s">
@@ -5846,22 +5773,22 @@
         <v>222977.900486</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="316"/>
-      <c r="B12" s="318"/>
-      <c r="C12" s="316"/>
-      <c r="D12" s="320"/>
-      <c r="E12" s="320"/>
-      <c r="F12" s="316"/>
-      <c r="G12" s="316"/>
-      <c r="H12" s="316"/>
-      <c r="I12" s="327"/>
-      <c r="J12" s="313"/>
-      <c r="K12" s="313"/>
-      <c r="L12" s="313"/>
-      <c r="M12" s="329"/>
-      <c r="N12" s="313"/>
-      <c r="O12" s="313"/>
+    <row r="12" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="325"/>
+      <c r="B12" s="360"/>
+      <c r="C12" s="325"/>
+      <c r="D12" s="362"/>
+      <c r="E12" s="362"/>
+      <c r="F12" s="325"/>
+      <c r="G12" s="325"/>
+      <c r="H12" s="325"/>
+      <c r="I12" s="331"/>
+      <c r="J12" s="333"/>
+      <c r="K12" s="333"/>
+      <c r="L12" s="333"/>
+      <c r="M12" s="336"/>
+      <c r="N12" s="333"/>
+      <c r="O12" s="333"/>
       <c r="Q12" t="s">
         <v>238</v>
       </c>
@@ -5870,20 +5797,20 @@
         <v>274576.09233400004</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="316"/>
-      <c r="B13" s="318"/>
-      <c r="C13" s="316"/>
-      <c r="D13" s="320"/>
-      <c r="E13" s="320"/>
-      <c r="F13" s="316"/>
-      <c r="G13" s="316"/>
-      <c r="H13" s="316"/>
-      <c r="I13" s="327"/>
-      <c r="J13" s="313"/>
-      <c r="K13" s="314"/>
-      <c r="L13" s="314"/>
-      <c r="M13" s="329"/>
+    <row r="13" spans="1:19" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="325"/>
+      <c r="B13" s="360"/>
+      <c r="C13" s="325"/>
+      <c r="D13" s="362"/>
+      <c r="E13" s="362"/>
+      <c r="F13" s="325"/>
+      <c r="G13" s="325"/>
+      <c r="H13" s="325"/>
+      <c r="I13" s="331"/>
+      <c r="J13" s="333"/>
+      <c r="K13" s="334"/>
+      <c r="L13" s="334"/>
+      <c r="M13" s="336"/>
       <c r="N13" s="101" t="str">
         <f>RESUMEN!A20</f>
         <v>VTO 17/07</v>
@@ -5900,7 +5827,7 @@
         <v>320645.90648399998</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="195" t="s">
         <v>114</v>
       </c>
@@ -5952,10 +5879,10 @@
       <c r="P14" s="85" t="s">
         <v>348</v>
       </c>
-      <c r="R14" s="321"/>
-      <c r="S14" s="321"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R14" s="323"/>
+      <c r="S14" s="323"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="24" t="s">
@@ -6002,10 +5929,10 @@
       <c r="P15" s="85" t="s">
         <v>347</v>
       </c>
-      <c r="R15" s="321"/>
-      <c r="S15" s="321"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="R15" s="323"/>
+      <c r="S15" s="323"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -6057,7 +5984,7 @@
       <c r="P16" s="85"/>
       <c r="S16" s="32"/>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>114</v>
       </c>
@@ -6072,7 +5999,7 @@
       <c r="F17" s="110">
         <v>1.49E-2</v>
       </c>
-      <c r="G17" s="401">
+      <c r="G17" s="106">
         <v>284549.06967438007</v>
       </c>
       <c r="H17" s="33"/>
@@ -6104,54 +6031,54 @@
       <c r="P17" s="85"/>
       <c r="S17" s="32"/>
     </row>
-    <row r="18" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>114</v>
       </c>
       <c r="B18" s="3"/>
-      <c r="C18" s="376" t="s">
+      <c r="C18" s="258" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="377" t="s">
+      <c r="D18" s="259" t="s">
         <v>251</v>
       </c>
-      <c r="E18" s="377"/>
-      <c r="F18" s="378">
+      <c r="E18" s="259"/>
+      <c r="F18" s="260">
         <v>1.7399999999999999E-2</v>
       </c>
-      <c r="G18" s="379">
+      <c r="G18" s="261">
         <v>624853.36696599983</v>
       </c>
-      <c r="H18" s="380"/>
-      <c r="I18" s="381">
+      <c r="H18" s="262"/>
+      <c r="I18" s="263">
         <f t="shared" si="0"/>
         <v>624853.36696599983</v>
       </c>
-      <c r="J18" s="382">
-        <v>0</v>
-      </c>
-      <c r="K18" s="382">
+      <c r="J18" s="264">
+        <v>0</v>
+      </c>
+      <c r="K18" s="264">
         <f t="shared" si="1"/>
         <v>104509.58519999999</v>
       </c>
-      <c r="L18" s="382">
+      <c r="L18" s="264">
         <v>320645.90648399998</v>
       </c>
-      <c r="M18" s="383">
-        <v>0</v>
-      </c>
-      <c r="N18" s="384">
+      <c r="M18" s="265">
+        <v>0</v>
+      </c>
+      <c r="N18" s="266">
         <f t="shared" si="2"/>
         <v>1050008.8586499998</v>
       </c>
-      <c r="O18" s="385">
+      <c r="O18" s="267">
         <f t="shared" si="3"/>
         <v>1113009.3901689998</v>
       </c>
       <c r="P18" s="85"/>
       <c r="S18" s="32"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="43" t="s">
         <v>116</v>
       </c>
@@ -6205,7 +6132,7 @@
       </c>
       <c r="S19" s="32"/>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="43" t="s">
         <v>117</v>
       </c>
@@ -6260,7 +6187,7 @@
       </c>
       <c r="S20" s="32"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="43" t="s">
         <v>116</v>
       </c>
@@ -6313,7 +6240,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
         <v>118</v>
       </c>
@@ -6371,7 +6298,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
         <v>118</v>
       </c>
@@ -6427,7 +6354,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="43" t="s">
         <v>118</v>
       </c>
@@ -6483,7 +6410,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="43" t="s">
         <v>116</v>
       </c>
@@ -6539,7 +6466,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="43" t="s">
         <v>117</v>
       </c>
@@ -6593,7 +6520,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="78" t="s">
         <v>116</v>
       </c>
@@ -6648,7 +6575,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="78" t="s">
         <v>118</v>
       </c>
@@ -6702,7 +6629,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="78" t="s">
         <v>118</v>
       </c>
@@ -6756,50 +6683,50 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="78" t="s">
         <v>118</v>
       </c>
       <c r="B30" s="24"/>
-      <c r="C30" s="386" t="s">
+      <c r="C30" s="268" t="s">
         <v>51</v>
       </c>
-      <c r="D30" s="387" t="s">
+      <c r="D30" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="E30" s="388"/>
-      <c r="F30" s="389">
+      <c r="E30" s="270"/>
+      <c r="F30" s="271">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G30" s="390">
+      <c r="G30" s="272">
         <v>1414368.12</v>
       </c>
-      <c r="H30" s="391"/>
-      <c r="I30" s="392">
+      <c r="H30" s="273"/>
+      <c r="I30" s="274">
         <f t="shared" si="0"/>
         <v>1414368.12</v>
       </c>
-      <c r="J30" s="393">
+      <c r="J30" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K30" s="394">
+      <c r="K30" s="276">
         <f t="shared" si="5"/>
         <v>57059.830999999998</v>
       </c>
-      <c r="L30" s="393">
+      <c r="L30" s="275">
         <f t="shared" si="6"/>
         <v>135621.57629999999</v>
       </c>
-      <c r="M30" s="395">
+      <c r="M30" s="277">
         <f>99500+24000</f>
         <v>123500</v>
       </c>
-      <c r="N30" s="396">
+      <c r="N30" s="278">
         <f t="shared" si="7"/>
         <v>1730550.12</v>
       </c>
-      <c r="O30" s="397">
+      <c r="O30" s="279">
         <f t="shared" si="8"/>
         <v>1834383.12</v>
       </c>
@@ -6808,7 +6735,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="78" t="s">
         <v>116</v>
       </c>
@@ -6862,7 +6789,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="43" t="s">
         <v>117</v>
       </c>
@@ -6918,7 +6845,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A33" s="43" t="s">
         <v>116</v>
       </c>
@@ -6972,7 +6899,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="34" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A34" s="108" t="s">
         <v>118</v>
       </c>
@@ -7028,7 +6955,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="35" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A35" s="43" t="s">
         <v>118</v>
       </c>
@@ -7084,50 +7011,50 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="43" t="s">
         <v>118</v>
       </c>
       <c r="B36" s="3"/>
-      <c r="C36" s="386" t="s">
+      <c r="C36" s="268" t="s">
         <v>57</v>
       </c>
-      <c r="D36" s="387" t="s">
+      <c r="D36" s="269" t="s">
         <v>178</v>
       </c>
-      <c r="E36" s="388"/>
-      <c r="F36" s="389">
+      <c r="E36" s="270"/>
+      <c r="F36" s="271">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G36" s="390">
+      <c r="G36" s="272">
         <v>896617.18</v>
       </c>
-      <c r="H36" s="391"/>
-      <c r="I36" s="398">
+      <c r="H36" s="273"/>
+      <c r="I36" s="280">
         <f t="shared" si="0"/>
         <v>896617.18</v>
       </c>
-      <c r="J36" s="393">
+      <c r="J36" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K36" s="394">
+      <c r="K36" s="276">
         <f t="shared" si="5"/>
         <v>57059.830999999998</v>
       </c>
-      <c r="L36" s="393">
+      <c r="L36" s="275">
         <f t="shared" si="6"/>
         <v>135621.57629999999</v>
       </c>
-      <c r="M36" s="395">
+      <c r="M36" s="277">
         <f>99500+24000</f>
         <v>123500</v>
       </c>
-      <c r="N36" s="396">
+      <c r="N36" s="278">
         <f t="shared" si="7"/>
         <v>1212799.18</v>
       </c>
-      <c r="O36" s="397">
+      <c r="O36" s="279">
         <f t="shared" si="8"/>
         <v>1285567.18</v>
       </c>
@@ -7136,7 +7063,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="43" t="s">
         <v>116</v>
       </c>
@@ -7195,7 +7122,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="43" t="s">
         <v>117</v>
       </c>
@@ -7249,7 +7176,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A39" s="78" t="s">
         <v>116</v>
       </c>
@@ -7401,7 +7328,7 @@
       <c r="DI39" s="53"/>
       <c r="DJ39" s="53"/>
     </row>
-    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A40" s="78" t="s">
         <v>118</v>
       </c>
@@ -7555,7 +7482,7 @@
       <c r="DI40" s="53"/>
       <c r="DJ40" s="53"/>
     </row>
-    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A41" s="78" t="s">
         <v>118</v>
       </c>
@@ -7709,52 +7636,52 @@
       <c r="DI41" s="53"/>
       <c r="DJ41" s="53"/>
     </row>
-    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="78" t="s">
         <v>118</v>
       </c>
       <c r="B42" s="24"/>
-      <c r="C42" s="386" t="s">
+      <c r="C42" s="268" t="s">
         <v>63</v>
       </c>
-      <c r="D42" s="387" t="s">
+      <c r="D42" s="269" t="s">
         <v>263</v>
       </c>
-      <c r="E42" s="388"/>
-      <c r="F42" s="389">
+      <c r="E42" s="270"/>
+      <c r="F42" s="271">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G42" s="399">
+      <c r="G42" s="281">
         <v>641837.24</v>
       </c>
-      <c r="H42" s="391">
-        <v>0</v>
-      </c>
-      <c r="I42" s="392">
+      <c r="H42" s="273">
+        <v>0</v>
+      </c>
+      <c r="I42" s="274">
         <f t="shared" si="0"/>
         <v>641837.24</v>
       </c>
-      <c r="J42" s="393">
+      <c r="J42" s="275">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K42" s="394">
+      <c r="K42" s="276">
         <f t="shared" si="5"/>
         <v>57059.830999999998</v>
       </c>
-      <c r="L42" s="393">
+      <c r="L42" s="275">
         <f t="shared" si="6"/>
         <v>135621.57629999999</v>
       </c>
-      <c r="M42" s="395">
+      <c r="M42" s="277">
         <f>99500+24000</f>
         <v>123500</v>
       </c>
-      <c r="N42" s="396">
+      <c r="N42" s="278">
         <f t="shared" si="7"/>
         <v>958019.24</v>
       </c>
-      <c r="O42" s="397">
+      <c r="O42" s="279">
         <f t="shared" si="8"/>
         <v>1015500.24</v>
       </c>
@@ -7861,7 +7788,7 @@
       <c r="DI42" s="53"/>
       <c r="DJ42" s="53"/>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="43" t="s">
         <v>116</v>
       </c>
@@ -7914,7 +7841,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="43" t="s">
         <v>117</v>
       </c>
@@ -7970,7 +7897,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="43" t="s">
         <v>116</v>
       </c>
@@ -8030,7 +7957,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="132" t="s">
         <v>118</v>
       </c>
@@ -8084,7 +8011,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="43" t="s">
         <v>118</v>
       </c>
@@ -8140,7 +8067,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="43" t="s">
         <v>118</v>
       </c>
@@ -8194,7 +8121,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" s="43" t="s">
         <v>116</v>
       </c>
@@ -8248,7 +8175,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" s="43" t="s">
         <v>117</v>
       </c>
@@ -8303,7 +8230,7 @@
       </c>
       <c r="Q50" s="32"/>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" s="43" t="s">
         <v>116</v>
       </c>
@@ -8358,7 +8285,7 @@
       </c>
       <c r="Q51" s="32"/>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" s="43" t="s">
         <v>118</v>
       </c>
@@ -8417,7 +8344,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" s="43" t="s">
         <v>118</v>
       </c>
@@ -8471,18 +8398,18 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" s="43" t="s">
         <v>118</v>
       </c>
       <c r="B54" s="3"/>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="387" t="s">
         <v>75</v>
       </c>
-      <c r="D54" s="78" t="s">
+      <c r="D54" s="388" t="s">
         <v>190</v>
       </c>
-      <c r="E54" s="104"/>
+      <c r="E54" s="389"/>
       <c r="F54" s="105">
         <v>9.4999999999999998E-3</v>
       </c>
@@ -8524,7 +8451,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" s="43" t="s">
         <v>116</v>
       </c>
@@ -8579,7 +8506,7 @@
       </c>
       <c r="R55" s="45"/>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" s="43" t="s">
         <v>117</v>
       </c>
@@ -8635,7 +8562,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" s="43" t="s">
         <v>116</v>
       </c>
@@ -8689,7 +8616,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" s="43" t="s">
         <v>118</v>
       </c>
@@ -8745,7 +8672,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" s="78" t="s">
         <v>118</v>
       </c>
@@ -8802,7 +8729,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" s="78" t="s">
         <v>118</v>
       </c>
@@ -8859,7 +8786,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" s="78" t="s">
         <v>116</v>
       </c>
@@ -8913,7 +8840,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" s="78" t="s">
         <v>117</v>
       </c>
@@ -8967,7 +8894,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" s="43" t="s">
         <v>116</v>
       </c>
@@ -9021,7 +8948,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" s="43" t="s">
         <v>118</v>
       </c>
@@ -9076,7 +9003,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="43" t="s">
         <v>118</v>
       </c>
@@ -9129,7 +9056,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="43" t="s">
         <v>118</v>
       </c>
@@ -9184,7 +9111,7 @@
       </c>
       <c r="S66" s="142"/>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="43" t="s">
         <v>116</v>
       </c>
@@ -9239,7 +9166,7 @@
       </c>
       <c r="S67" s="32"/>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="108" t="s">
         <v>117</v>
       </c>
@@ -9293,18 +9220,18 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="43" t="s">
         <v>116</v>
       </c>
       <c r="B69" s="3"/>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="283" t="s">
         <v>90</v>
       </c>
-      <c r="D69" s="78" t="s">
+      <c r="D69" s="284" t="s">
         <v>201</v>
       </c>
-      <c r="E69" s="104"/>
+      <c r="E69" s="285"/>
       <c r="F69" s="105">
         <v>1.7299999999999999E-2</v>
       </c>
@@ -9331,22 +9258,22 @@
         <v>246974.02841999996</v>
       </c>
       <c r="M69" s="153">
-        <v>45375</v>
+        <v>0</v>
       </c>
       <c r="N69" s="147">
         <f t="shared" si="7"/>
-        <v>297881.51</v>
+        <v>252506.51</v>
       </c>
       <c r="O69" s="114">
         <f t="shared" si="8"/>
-        <v>315754.51</v>
+        <v>267657.51</v>
       </c>
       <c r="P69" s="102">
         <f t="shared" si="9"/>
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="43" t="s">
         <v>118</v>
       </c>
@@ -9400,7 +9327,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="43" t="s">
         <v>118</v>
       </c>
@@ -9454,52 +9381,52 @@
         <v>0.53000000000000025</v>
       </c>
       <c r="R71" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.25">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="43" t="s">
         <v>118</v>
       </c>
       <c r="B72" s="3"/>
-      <c r="C72" s="386" t="s">
+      <c r="C72" s="268" t="s">
         <v>93</v>
       </c>
-      <c r="D72" s="387" t="s">
+      <c r="D72" s="269" t="s">
         <v>203</v>
       </c>
-      <c r="E72" s="388"/>
-      <c r="F72" s="389">
+      <c r="E72" s="270"/>
+      <c r="F72" s="271">
         <v>9.4999999999999998E-3</v>
       </c>
-      <c r="G72" s="390">
+      <c r="G72" s="272">
         <v>444267.54</v>
       </c>
-      <c r="H72" s="391"/>
-      <c r="I72" s="392">
+      <c r="H72" s="273"/>
+      <c r="I72" s="274">
         <f t="shared" si="0"/>
         <v>444267.54</v>
       </c>
-      <c r="J72" s="393">
+      <c r="J72" s="275">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="K72" s="394">
+      <c r="K72" s="276">
         <f t="shared" si="5"/>
         <v>57059.830999999998</v>
       </c>
-      <c r="L72" s="393">
+      <c r="L72" s="275">
         <f t="shared" si="13"/>
         <v>135621.57629999999</v>
       </c>
-      <c r="M72" s="395">
-        <v>0</v>
-      </c>
-      <c r="N72" s="396">
+      <c r="M72" s="277">
+        <v>0</v>
+      </c>
+      <c r="N72" s="278">
         <f t="shared" si="7"/>
         <v>636949.54</v>
       </c>
-      <c r="O72" s="397">
+      <c r="O72" s="279">
         <f t="shared" si="8"/>
         <v>675167.54</v>
       </c>
@@ -9508,7 +9435,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="43" t="s">
         <v>119</v>
       </c>
@@ -9563,7 +9490,7 @@
       </c>
       <c r="Q73" s="53"/>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="43" t="s">
         <v>116</v>
       </c>
@@ -9617,7 +9544,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="43" t="s">
         <v>118</v>
       </c>
@@ -9671,7 +9598,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="43" t="s">
         <v>118</v>
       </c>
@@ -9727,7 +9654,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="78" t="s">
         <v>118</v>
       </c>
@@ -9781,7 +9708,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="78" t="s">
         <v>119</v>
       </c>
@@ -9835,7 +9762,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="43" t="s">
         <v>116</v>
       </c>
@@ -9889,7 +9816,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="43" t="s">
         <v>118</v>
       </c>
@@ -9942,7 +9869,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="43" t="s">
         <v>118</v>
       </c>
@@ -9998,7 +9925,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="43" t="s">
         <v>118</v>
       </c>
@@ -10052,7 +9979,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="43" t="s">
         <v>119</v>
       </c>
@@ -10106,7 +10033,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="43" t="s">
         <v>116</v>
       </c>
@@ -10159,7 +10086,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="43" t="s">
         <v>118</v>
       </c>
@@ -10213,7 +10140,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="43" t="s">
         <v>118</v>
       </c>
@@ -10267,7 +10194,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="78" t="s">
         <v>118</v>
       </c>
@@ -10321,7 +10248,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="78"/>
       <c r="B88" s="24"/>
       <c r="C88" s="24" t="s">
@@ -10373,7 +10300,7 @@
         <v>0.7000000000000004</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="78"/>
       <c r="B89" s="24"/>
       <c r="C89" s="24" t="s">
@@ -10425,7 +10352,7 @@
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="78"/>
       <c r="B90" s="24"/>
       <c r="C90" s="24" t="s">
@@ -10477,7 +10404,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" s="78"/>
       <c r="B91" s="24"/>
       <c r="C91" s="24" t="s">
@@ -10529,7 +10456,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" s="78"/>
       <c r="B92" s="24"/>
       <c r="C92" s="136" t="s">
@@ -10584,7 +10511,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" s="78"/>
       <c r="B93" s="24"/>
       <c r="C93" s="24" t="s">
@@ -10636,7 +10563,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" s="78"/>
       <c r="B94" s="24"/>
       <c r="C94" s="24" t="s">
@@ -10688,7 +10615,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="78"/>
       <c r="B95" s="24"/>
       <c r="C95" s="24" t="s">
@@ -10740,7 +10667,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="78"/>
       <c r="B96" s="24"/>
       <c r="C96" s="24" t="s">
@@ -10792,47 +10719,47 @@
         <v>0.78000000000000047</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="78"/>
       <c r="B97" s="24"/>
-      <c r="C97" s="386" t="s">
+      <c r="C97" s="268" t="s">
         <v>129</v>
       </c>
-      <c r="D97" s="387" t="s">
+      <c r="D97" s="269" t="s">
         <v>197</v>
       </c>
-      <c r="E97" s="387"/>
-      <c r="F97" s="400">
+      <c r="E97" s="269"/>
+      <c r="F97" s="282">
         <v>2.3E-3</v>
       </c>
-      <c r="G97" s="390">
+      <c r="G97" s="272">
         <v>358863.79</v>
       </c>
-      <c r="H97" s="391"/>
-      <c r="I97" s="392">
+      <c r="H97" s="273"/>
+      <c r="I97" s="274">
         <f>G97-H97</f>
         <v>358863.79</v>
       </c>
-      <c r="J97" s="393">
+      <c r="J97" s="275">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K97" s="394">
+      <c r="K97" s="276">
         <f t="shared" si="20"/>
         <v>13814.4854</v>
       </c>
-      <c r="L97" s="393">
+      <c r="L97" s="275">
         <f t="shared" si="19"/>
         <v>32834.697419999997</v>
       </c>
-      <c r="M97" s="395">
-        <v>0</v>
-      </c>
-      <c r="N97" s="396">
+      <c r="M97" s="277">
+        <v>0</v>
+      </c>
+      <c r="N97" s="278">
         <f t="shared" si="21"/>
         <v>405513.79</v>
       </c>
-      <c r="O97" s="397">
+      <c r="O97" s="279">
         <f t="shared" si="22"/>
         <v>429845.79</v>
       </c>
@@ -10841,7 +10768,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="78"/>
       <c r="B98" s="24"/>
       <c r="C98" s="24" t="s">
@@ -10893,7 +10820,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="78"/>
       <c r="B99" s="24"/>
       <c r="C99" s="24" t="s">
@@ -10944,7 +10871,7 @@
         <v>0.8100000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="78"/>
       <c r="B100" s="24"/>
       <c r="C100" s="24" t="s">
@@ -10996,47 +10923,47 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="78"/>
       <c r="B101" s="24"/>
-      <c r="C101" s="386" t="s">
+      <c r="C101" s="268" t="s">
         <v>133</v>
       </c>
-      <c r="D101" s="387" t="s">
+      <c r="D101" s="269" t="s">
         <v>220</v>
       </c>
-      <c r="E101" s="387"/>
-      <c r="F101" s="400">
+      <c r="E101" s="269"/>
+      <c r="F101" s="282">
         <v>2.3E-3</v>
       </c>
-      <c r="G101" s="390">
+      <c r="G101" s="272">
         <v>109681.83</v>
       </c>
-      <c r="H101" s="391"/>
-      <c r="I101" s="392">
+      <c r="H101" s="273"/>
+      <c r="I101" s="274">
         <f t="shared" si="0"/>
         <v>109681.83</v>
       </c>
-      <c r="J101" s="393">
+      <c r="J101" s="275">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K101" s="394">
+      <c r="K101" s="276">
         <f t="shared" si="20"/>
         <v>13814.4854</v>
       </c>
-      <c r="L101" s="393">
+      <c r="L101" s="275">
         <f t="shared" si="19"/>
         <v>32834.697419999997</v>
       </c>
-      <c r="M101" s="395">
-        <v>0</v>
-      </c>
-      <c r="N101" s="396">
+      <c r="M101" s="277">
+        <v>0</v>
+      </c>
+      <c r="N101" s="278">
         <f t="shared" si="21"/>
         <v>156331.82999999999</v>
       </c>
-      <c r="O101" s="397">
+      <c r="O101" s="279">
         <f t="shared" si="22"/>
         <v>165712.82999999999</v>
       </c>
@@ -11045,7 +10972,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="78"/>
       <c r="B102" s="24"/>
       <c r="C102" s="24" t="s">
@@ -11097,7 +11024,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="78"/>
       <c r="B103" s="24"/>
       <c r="C103" s="24" t="s">
@@ -11149,7 +11076,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="78"/>
       <c r="B104" s="24"/>
       <c r="C104" s="24" t="s">
@@ -11198,7 +11125,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="78"/>
       <c r="B105" s="24"/>
       <c r="C105" s="24" t="s">
@@ -11250,7 +11177,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="78"/>
       <c r="B106" s="24"/>
       <c r="C106" s="24" t="s">
@@ -11301,7 +11228,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="78"/>
       <c r="B107" s="24"/>
       <c r="C107" s="24" t="s">
@@ -11352,7 +11279,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="78"/>
       <c r="B108" s="24"/>
       <c r="C108" s="24" t="s">
@@ -11404,7 +11331,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="78"/>
       <c r="B109" s="24"/>
       <c r="C109" s="24" t="s">
@@ -11455,49 +11382,49 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="78"/>
       <c r="B110" s="24"/>
-      <c r="C110" s="386" t="s">
+      <c r="C110" s="268" t="s">
         <v>142</v>
       </c>
-      <c r="D110" s="387" t="s">
+      <c r="D110" s="269" t="s">
         <v>203</v>
       </c>
-      <c r="E110" s="387"/>
-      <c r="F110" s="400">
+      <c r="E110" s="269"/>
+      <c r="F110" s="282">
         <v>2.3E-3</v>
       </c>
-      <c r="G110" s="390">
+      <c r="G110" s="272">
         <v>145010.92000000001</v>
       </c>
-      <c r="H110" s="391">
-        <v>0</v>
-      </c>
-      <c r="I110" s="392">
+      <c r="H110" s="273">
+        <v>0</v>
+      </c>
+      <c r="I110" s="274">
         <f t="shared" si="0"/>
         <v>145010.92000000001</v>
       </c>
-      <c r="J110" s="393">
+      <c r="J110" s="275">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K110" s="394">
+      <c r="K110" s="276">
         <f t="shared" si="20"/>
         <v>13814.4854</v>
       </c>
-      <c r="L110" s="393">
+      <c r="L110" s="275">
         <f t="shared" si="19"/>
         <v>32834.697419999997</v>
       </c>
-      <c r="M110" s="395">
-        <v>0</v>
-      </c>
-      <c r="N110" s="396">
+      <c r="M110" s="277">
+        <v>0</v>
+      </c>
+      <c r="N110" s="278">
         <f t="shared" si="21"/>
         <v>191660.92</v>
       </c>
-      <c r="O110" s="397">
+      <c r="O110" s="279">
         <f t="shared" si="22"/>
         <v>203161.92</v>
       </c>
@@ -11506,7 +11433,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="78"/>
       <c r="B111" s="24"/>
       <c r="C111" s="24" t="s">
@@ -11558,7 +11485,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="78"/>
       <c r="B112" s="24"/>
       <c r="C112" s="24" t="s">
@@ -11610,7 +11537,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="78"/>
       <c r="B113" s="24"/>
       <c r="C113" s="24" t="s">
@@ -11662,7 +11589,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" s="78"/>
       <c r="B114" s="24"/>
       <c r="C114" s="24" t="s">
@@ -11714,7 +11641,7 @@
         <v>0.96000000000000063</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" s="78"/>
       <c r="B115" s="24"/>
       <c r="C115" s="24" t="s">
@@ -11765,7 +11692,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" s="78"/>
       <c r="B116" s="24"/>
       <c r="C116" s="24" t="s">
@@ -11819,7 +11746,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" s="78"/>
       <c r="B117" s="24"/>
       <c r="C117" s="24" t="s">
@@ -11870,7 +11797,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="78"/>
       <c r="B118" s="24"/>
       <c r="C118" s="24" t="s">
@@ -11927,7 +11854,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" s="97"/>
       <c r="B119" s="24"/>
       <c r="C119" s="24" t="s">
@@ -11979,7 +11906,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" s="97"/>
       <c r="B120" s="24"/>
       <c r="C120" s="24" t="s">
@@ -12031,7 +11958,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="97"/>
       <c r="B121" s="24"/>
       <c r="C121" s="24" t="s">
@@ -12084,7 +12011,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="97"/>
       <c r="B122" s="24"/>
       <c r="C122" s="24" t="s">
@@ -12135,7 +12062,7 @@
         <v>1.0400000000000007</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="97"/>
       <c r="B123" s="24"/>
       <c r="C123" s="24" t="s">
@@ -12187,7 +12114,7 @@
         <v>1.0500000000000007</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="97"/>
       <c r="B124" s="24"/>
       <c r="C124" s="24" t="s">
@@ -12242,7 +12169,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="135"/>
       <c r="B125" s="130"/>
       <c r="C125" s="24" t="s">
@@ -12296,7 +12223,7 @@
         <v>1.0700000000000007</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="135"/>
       <c r="B126" s="130"/>
       <c r="C126" s="24" t="s">
@@ -12348,7 +12275,7 @@
         <v>1.0800000000000007</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="97"/>
       <c r="B127" s="24"/>
       <c r="C127" s="24" t="s">
@@ -12400,7 +12327,7 @@
         <v>1.0900000000000007</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="97"/>
       <c r="B128" s="24"/>
       <c r="C128" s="24" t="s">
@@ -12452,7 +12379,7 @@
         <v>1.1000000000000008</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" s="97"/>
       <c r="B129" s="24"/>
       <c r="C129" s="24" t="s">
@@ -12504,7 +12431,7 @@
         <v>1.1100000000000008</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" s="97" t="s">
         <v>24</v>
       </c>
@@ -12558,7 +12485,7 @@
         <v>1.1200000000000008</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" s="97" t="s">
         <v>24</v>
       </c>
@@ -12611,7 +12538,7 @@
         <v>1.1300000000000008</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" s="40" t="s">
         <v>24</v>
       </c>
@@ -12630,7 +12557,7 @@
       <c r="N132" s="2"/>
       <c r="O132" s="5"/>
     </row>
-    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19"/>
       <c r="B133" s="19"/>
       <c r="C133" s="19"/>
@@ -12660,55 +12587,55 @@
       </c>
       <c r="M133" s="134">
         <f>SUM(M14:M132)</f>
-        <v>581619</v>
+        <v>536244</v>
       </c>
       <c r="N133" s="21">
         <f>SUM(N14:N132)</f>
-        <v>26785784.899740376</v>
+        <v>26740409.899740376</v>
       </c>
       <c r="O133" s="20">
         <f>SUM(O14:O132)</f>
-        <v>28392997.1891248</v>
+        <v>28344900.1891248</v>
       </c>
       <c r="Q133" s="45"/>
     </row>
-    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="L134" s="47">
         <f>L133-M1</f>
         <v>253782.0668799635</v>
       </c>
     </row>
-    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C135" s="323"/>
-      <c r="D135" s="323"/>
-      <c r="E135" s="323"/>
-      <c r="F135" s="323"/>
-      <c r="G135" s="323"/>
-      <c r="H135" s="323"/>
-      <c r="I135" s="323"/>
-      <c r="J135" s="323"/>
-      <c r="K135" s="323"/>
-      <c r="L135" s="323"/>
-      <c r="M135" s="323"/>
-      <c r="N135" s="323"/>
-      <c r="O135" s="323"/>
-    </row>
-    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="C136" s="323"/>
-      <c r="D136" s="323"/>
-      <c r="E136" s="323"/>
-      <c r="F136" s="323"/>
-      <c r="G136" s="323"/>
-      <c r="H136" s="323"/>
-      <c r="I136" s="323"/>
-      <c r="J136" s="323"/>
-      <c r="K136" s="323"/>
-      <c r="L136" s="323"/>
-      <c r="M136" s="323"/>
-      <c r="N136" s="323"/>
-      <c r="O136" s="323"/>
-    </row>
-    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C135" s="327"/>
+      <c r="D135" s="327"/>
+      <c r="E135" s="327"/>
+      <c r="F135" s="327"/>
+      <c r="G135" s="327"/>
+      <c r="H135" s="327"/>
+      <c r="I135" s="327"/>
+      <c r="J135" s="327"/>
+      <c r="K135" s="327"/>
+      <c r="L135" s="327"/>
+      <c r="M135" s="327"/>
+      <c r="N135" s="327"/>
+      <c r="O135" s="327"/>
+    </row>
+    <row r="136" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
+      <c r="C136" s="327"/>
+      <c r="D136" s="327"/>
+      <c r="E136" s="327"/>
+      <c r="F136" s="327"/>
+      <c r="G136" s="327"/>
+      <c r="H136" s="327"/>
+      <c r="I136" s="327"/>
+      <c r="J136" s="327"/>
+      <c r="K136" s="327"/>
+      <c r="L136" s="327"/>
+      <c r="M136" s="327"/>
+      <c r="N136" s="327"/>
+      <c r="O136" s="327"/>
+    </row>
+    <row r="137" spans="1:17" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C137" s="57"/>
       <c r="D137" s="57"/>
       <c r="E137" s="57"/>
@@ -12723,129 +12650,129 @@
       <c r="N137" s="57"/>
       <c r="O137" s="57"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C138" s="330" t="s">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C138" s="337" t="s">
         <v>245</v>
       </c>
-      <c r="D138" s="330"/>
-      <c r="E138" s="330"/>
-      <c r="F138" s="330"/>
-      <c r="G138" s="330"/>
-      <c r="H138" s="330"/>
-      <c r="I138" s="330"/>
-      <c r="J138" s="330"/>
-      <c r="K138" s="330"/>
-      <c r="L138" s="330"/>
-      <c r="M138" s="330"/>
-      <c r="N138" s="330"/>
-      <c r="O138" s="330"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C139" s="330"/>
-      <c r="D139" s="330"/>
-      <c r="E139" s="330"/>
-      <c r="F139" s="330"/>
-      <c r="G139" s="330"/>
-      <c r="H139" s="330"/>
-      <c r="I139" s="330"/>
-      <c r="J139" s="330"/>
-      <c r="K139" s="330"/>
-      <c r="L139" s="330"/>
-      <c r="M139" s="330"/>
-      <c r="N139" s="330"/>
-      <c r="O139" s="330"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C140" s="330"/>
-      <c r="D140" s="330"/>
-      <c r="E140" s="330"/>
-      <c r="F140" s="330"/>
-      <c r="G140" s="330"/>
-      <c r="H140" s="330"/>
-      <c r="I140" s="330"/>
-      <c r="J140" s="330"/>
-      <c r="K140" s="330"/>
-      <c r="L140" s="330"/>
-      <c r="M140" s="330"/>
-      <c r="N140" s="330"/>
-      <c r="O140" s="330"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C141" s="330"/>
-      <c r="D141" s="330"/>
-      <c r="E141" s="330"/>
-      <c r="F141" s="330"/>
-      <c r="G141" s="330"/>
-      <c r="H141" s="330"/>
-      <c r="I141" s="330"/>
-      <c r="J141" s="330"/>
-      <c r="K141" s="330"/>
-      <c r="L141" s="330"/>
-      <c r="M141" s="330"/>
-      <c r="N141" s="330"/>
-      <c r="O141" s="330"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C142" s="330"/>
-      <c r="D142" s="330"/>
-      <c r="E142" s="330"/>
-      <c r="F142" s="330"/>
-      <c r="G142" s="330"/>
-      <c r="H142" s="330"/>
-      <c r="I142" s="330"/>
-      <c r="J142" s="330"/>
-      <c r="K142" s="330"/>
-      <c r="L142" s="330"/>
-      <c r="M142" s="330"/>
-      <c r="N142" s="330"/>
-      <c r="O142" s="330"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C143" s="330"/>
-      <c r="D143" s="330"/>
-      <c r="E143" s="330"/>
-      <c r="F143" s="330"/>
-      <c r="G143" s="330"/>
-      <c r="H143" s="330"/>
-      <c r="I143" s="330"/>
-      <c r="J143" s="330"/>
-      <c r="K143" s="330"/>
-      <c r="L143" s="330"/>
-      <c r="M143" s="330"/>
-      <c r="N143" s="330"/>
-      <c r="O143" s="330"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="C144" s="330"/>
-      <c r="D144" s="330"/>
-      <c r="E144" s="330"/>
-      <c r="F144" s="330"/>
-      <c r="G144" s="330"/>
-      <c r="H144" s="330"/>
-      <c r="I144" s="330"/>
-      <c r="J144" s="330"/>
-      <c r="K144" s="330"/>
-      <c r="L144" s="330"/>
-      <c r="M144" s="330"/>
-      <c r="N144" s="330"/>
-      <c r="O144" s="330"/>
-    </row>
-    <row r="145" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C145" s="330"/>
-      <c r="D145" s="330"/>
-      <c r="E145" s="330"/>
-      <c r="F145" s="330"/>
-      <c r="G145" s="330"/>
-      <c r="H145" s="330"/>
-      <c r="I145" s="330"/>
-      <c r="J145" s="330"/>
-      <c r="K145" s="330"/>
-      <c r="L145" s="330"/>
-      <c r="M145" s="330"/>
-      <c r="N145" s="330"/>
-      <c r="O145" s="330"/>
-    </row>
-    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D138" s="337"/>
+      <c r="E138" s="337"/>
+      <c r="F138" s="337"/>
+      <c r="G138" s="337"/>
+      <c r="H138" s="337"/>
+      <c r="I138" s="337"/>
+      <c r="J138" s="337"/>
+      <c r="K138" s="337"/>
+      <c r="L138" s="337"/>
+      <c r="M138" s="337"/>
+      <c r="N138" s="337"/>
+      <c r="O138" s="337"/>
+    </row>
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C139" s="337"/>
+      <c r="D139" s="337"/>
+      <c r="E139" s="337"/>
+      <c r="F139" s="337"/>
+      <c r="G139" s="337"/>
+      <c r="H139" s="337"/>
+      <c r="I139" s="337"/>
+      <c r="J139" s="337"/>
+      <c r="K139" s="337"/>
+      <c r="L139" s="337"/>
+      <c r="M139" s="337"/>
+      <c r="N139" s="337"/>
+      <c r="O139" s="337"/>
+    </row>
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C140" s="337"/>
+      <c r="D140" s="337"/>
+      <c r="E140" s="337"/>
+      <c r="F140" s="337"/>
+      <c r="G140" s="337"/>
+      <c r="H140" s="337"/>
+      <c r="I140" s="337"/>
+      <c r="J140" s="337"/>
+      <c r="K140" s="337"/>
+      <c r="L140" s="337"/>
+      <c r="M140" s="337"/>
+      <c r="N140" s="337"/>
+      <c r="O140" s="337"/>
+    </row>
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C141" s="337"/>
+      <c r="D141" s="337"/>
+      <c r="E141" s="337"/>
+      <c r="F141" s="337"/>
+      <c r="G141" s="337"/>
+      <c r="H141" s="337"/>
+      <c r="I141" s="337"/>
+      <c r="J141" s="337"/>
+      <c r="K141" s="337"/>
+      <c r="L141" s="337"/>
+      <c r="M141" s="337"/>
+      <c r="N141" s="337"/>
+      <c r="O141" s="337"/>
+    </row>
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C142" s="337"/>
+      <c r="D142" s="337"/>
+      <c r="E142" s="337"/>
+      <c r="F142" s="337"/>
+      <c r="G142" s="337"/>
+      <c r="H142" s="337"/>
+      <c r="I142" s="337"/>
+      <c r="J142" s="337"/>
+      <c r="K142" s="337"/>
+      <c r="L142" s="337"/>
+      <c r="M142" s="337"/>
+      <c r="N142" s="337"/>
+      <c r="O142" s="337"/>
+    </row>
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C143" s="337"/>
+      <c r="D143" s="337"/>
+      <c r="E143" s="337"/>
+      <c r="F143" s="337"/>
+      <c r="G143" s="337"/>
+      <c r="H143" s="337"/>
+      <c r="I143" s="337"/>
+      <c r="J143" s="337"/>
+      <c r="K143" s="337"/>
+      <c r="L143" s="337"/>
+      <c r="M143" s="337"/>
+      <c r="N143" s="337"/>
+      <c r="O143" s="337"/>
+    </row>
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="C144" s="337"/>
+      <c r="D144" s="337"/>
+      <c r="E144" s="337"/>
+      <c r="F144" s="337"/>
+      <c r="G144" s="337"/>
+      <c r="H144" s="337"/>
+      <c r="I144" s="337"/>
+      <c r="J144" s="337"/>
+      <c r="K144" s="337"/>
+      <c r="L144" s="337"/>
+      <c r="M144" s="337"/>
+      <c r="N144" s="337"/>
+      <c r="O144" s="337"/>
+    </row>
+    <row r="145" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C145" s="337"/>
+      <c r="D145" s="337"/>
+      <c r="E145" s="337"/>
+      <c r="F145" s="337"/>
+      <c r="G145" s="337"/>
+      <c r="H145" s="337"/>
+      <c r="I145" s="337"/>
+      <c r="J145" s="337"/>
+      <c r="K145" s="337"/>
+      <c r="L145" s="337"/>
+      <c r="M145" s="337"/>
+      <c r="N145" s="337"/>
+      <c r="O145" s="337"/>
+    </row>
+    <row r="146" spans="3:17" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C146" s="57"/>
       <c r="D146" s="57"/>
       <c r="E146" s="57"/>
@@ -12860,7 +12787,7 @@
       <c r="N146" s="57"/>
       <c r="O146" s="57"/>
     </row>
-    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="3:17" ht="45" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C147" s="57"/>
       <c r="D147" s="57"/>
       <c r="E147" s="57"/>
@@ -12875,119 +12802,126 @@
       <c r="N147" s="57"/>
       <c r="O147" s="57"/>
     </row>
-    <row r="148" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C148" s="322" t="s">
+    <row r="148" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C148" s="326" t="s">
         <v>244</v>
       </c>
-      <c r="D148" s="322"/>
-      <c r="E148" s="322"/>
-      <c r="F148" s="322"/>
-      <c r="G148" s="322"/>
-      <c r="H148" s="322"/>
-      <c r="I148" s="322"/>
-      <c r="J148" s="322"/>
-      <c r="K148" s="322"/>
-      <c r="L148" s="322"/>
-      <c r="M148" s="322"/>
-      <c r="N148" s="322"/>
-      <c r="O148" s="322"/>
-    </row>
-    <row r="149" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C149" s="322"/>
-      <c r="D149" s="322"/>
-      <c r="E149" s="322"/>
-      <c r="F149" s="322"/>
-      <c r="G149" s="322"/>
-      <c r="H149" s="322"/>
-      <c r="I149" s="322"/>
-      <c r="J149" s="322"/>
-      <c r="K149" s="322"/>
-      <c r="L149" s="322"/>
-      <c r="M149" s="322"/>
-      <c r="N149" s="322"/>
-      <c r="O149" s="322"/>
-    </row>
-    <row r="150" spans="3:17" x14ac:dyDescent="0.25">
-      <c r="C150" s="322"/>
-      <c r="D150" s="322"/>
-      <c r="E150" s="322"/>
-      <c r="F150" s="322"/>
-      <c r="G150" s="322"/>
-      <c r="H150" s="322"/>
-      <c r="I150" s="322"/>
-      <c r="J150" s="322"/>
-      <c r="K150" s="322"/>
-      <c r="L150" s="322"/>
-      <c r="M150" s="322"/>
-      <c r="N150" s="322"/>
-      <c r="O150" s="322"/>
+      <c r="D148" s="326"/>
+      <c r="E148" s="326"/>
+      <c r="F148" s="326"/>
+      <c r="G148" s="326"/>
+      <c r="H148" s="326"/>
+      <c r="I148" s="326"/>
+      <c r="J148" s="326"/>
+      <c r="K148" s="326"/>
+      <c r="L148" s="326"/>
+      <c r="M148" s="326"/>
+      <c r="N148" s="326"/>
+      <c r="O148" s="326"/>
+    </row>
+    <row r="149" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C149" s="326"/>
+      <c r="D149" s="326"/>
+      <c r="E149" s="326"/>
+      <c r="F149" s="326"/>
+      <c r="G149" s="326"/>
+      <c r="H149" s="326"/>
+      <c r="I149" s="326"/>
+      <c r="J149" s="326"/>
+      <c r="K149" s="326"/>
+      <c r="L149" s="326"/>
+      <c r="M149" s="326"/>
+      <c r="N149" s="326"/>
+      <c r="O149" s="326"/>
+    </row>
+    <row r="150" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C150" s="326"/>
+      <c r="D150" s="326"/>
+      <c r="E150" s="326"/>
+      <c r="F150" s="326"/>
+      <c r="G150" s="326"/>
+      <c r="H150" s="326"/>
+      <c r="I150" s="326"/>
+      <c r="J150" s="326"/>
+      <c r="K150" s="326"/>
+      <c r="L150" s="326"/>
+      <c r="M150" s="326"/>
+      <c r="N150" s="326"/>
+      <c r="O150" s="326"/>
       <c r="Q150" s="64">
         <f>M1-L133</f>
         <v>-253782.0668799635</v>
       </c>
     </row>
-    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C151" s="322"/>
-      <c r="D151" s="322"/>
-      <c r="E151" s="322"/>
-      <c r="F151" s="322"/>
-      <c r="G151" s="322"/>
-      <c r="H151" s="322"/>
-      <c r="I151" s="322"/>
-      <c r="J151" s="322"/>
-      <c r="K151" s="322"/>
-      <c r="L151" s="322"/>
-      <c r="M151" s="322"/>
-      <c r="N151" s="322"/>
-      <c r="O151" s="322"/>
-    </row>
-    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C152" s="322"/>
-      <c r="D152" s="322"/>
-      <c r="E152" s="322"/>
-      <c r="F152" s="322"/>
-      <c r="G152" s="322"/>
-      <c r="H152" s="322"/>
-      <c r="I152" s="322"/>
-      <c r="J152" s="322"/>
-      <c r="K152" s="322"/>
-      <c r="L152" s="322"/>
-      <c r="M152" s="322"/>
-      <c r="N152" s="322"/>
-      <c r="O152" s="322"/>
-    </row>
-    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C153" s="322"/>
-      <c r="D153" s="322"/>
-      <c r="E153" s="322"/>
-      <c r="F153" s="322"/>
-      <c r="G153" s="322"/>
-      <c r="H153" s="322"/>
-      <c r="I153" s="322"/>
-      <c r="J153" s="322"/>
-      <c r="K153" s="322"/>
-      <c r="L153" s="322"/>
-      <c r="M153" s="322"/>
-      <c r="N153" s="322"/>
-      <c r="O153" s="322"/>
-    </row>
-    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C154" s="322"/>
-      <c r="D154" s="322"/>
-      <c r="E154" s="322"/>
-      <c r="F154" s="322"/>
-      <c r="G154" s="322"/>
-      <c r="H154" s="322"/>
-      <c r="I154" s="322"/>
-      <c r="J154" s="322"/>
-      <c r="K154" s="322"/>
-      <c r="L154" s="322"/>
-      <c r="M154" s="322"/>
-      <c r="N154" s="322"/>
-      <c r="O154" s="322"/>
+    <row r="151" spans="3:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C151" s="326"/>
+      <c r="D151" s="326"/>
+      <c r="E151" s="326"/>
+      <c r="F151" s="326"/>
+      <c r="G151" s="326"/>
+      <c r="H151" s="326"/>
+      <c r="I151" s="326"/>
+      <c r="J151" s="326"/>
+      <c r="K151" s="326"/>
+      <c r="L151" s="326"/>
+      <c r="M151" s="326"/>
+      <c r="N151" s="326"/>
+      <c r="O151" s="326"/>
+    </row>
+    <row r="152" spans="3:17" ht="5.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C152" s="326"/>
+      <c r="D152" s="326"/>
+      <c r="E152" s="326"/>
+      <c r="F152" s="326"/>
+      <c r="G152" s="326"/>
+      <c r="H152" s="326"/>
+      <c r="I152" s="326"/>
+      <c r="J152" s="326"/>
+      <c r="K152" s="326"/>
+      <c r="L152" s="326"/>
+      <c r="M152" s="326"/>
+      <c r="N152" s="326"/>
+      <c r="O152" s="326"/>
+    </row>
+    <row r="153" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C153" s="326"/>
+      <c r="D153" s="326"/>
+      <c r="E153" s="326"/>
+      <c r="F153" s="326"/>
+      <c r="G153" s="326"/>
+      <c r="H153" s="326"/>
+      <c r="I153" s="326"/>
+      <c r="J153" s="326"/>
+      <c r="K153" s="326"/>
+      <c r="L153" s="326"/>
+      <c r="M153" s="326"/>
+      <c r="N153" s="326"/>
+      <c r="O153" s="326"/>
+    </row>
+    <row r="154" spans="3:17" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C154" s="326"/>
+      <c r="D154" s="326"/>
+      <c r="E154" s="326"/>
+      <c r="F154" s="326"/>
+      <c r="G154" s="326"/>
+      <c r="H154" s="326"/>
+      <c r="I154" s="326"/>
+      <c r="J154" s="326"/>
+      <c r="K154" s="326"/>
+      <c r="L154" s="326"/>
+      <c r="M154" s="326"/>
+      <c r="N154" s="326"/>
+      <c r="O154" s="326"/>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="K11:K13"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="F11:F13"/>
+    <mergeCell ref="E11:E13"/>
     <mergeCell ref="R14:S15"/>
     <mergeCell ref="G11:G13"/>
     <mergeCell ref="C148:O154"/>
@@ -13004,13 +12938,6 @@
     <mergeCell ref="C5:O8"/>
     <mergeCell ref="C9:O10"/>
     <mergeCell ref="A1:E4"/>
-    <mergeCell ref="K11:K13"/>
-    <mergeCell ref="A11:A13"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="C11:C13"/>
-    <mergeCell ref="D11:D13"/>
-    <mergeCell ref="F11:F13"/>
-    <mergeCell ref="E11:E13"/>
   </mergeCells>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13021,84 +12948,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7AB47CA-548A-40FB-AC1D-01E96423736C}">
   <dimension ref="A1:DJ82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.140625" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="21.44140625" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="17.33203125" customWidth="1"/>
     <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="0.140625" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="16.5703125" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" customWidth="1"/>
-    <col min="15" max="15" width="19.5703125" customWidth="1"/>
-    <col min="16" max="16" width="7.7109375" customWidth="1"/>
-    <col min="17" max="17" width="43.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="0.109375" customWidth="1"/>
+    <col min="12" max="12" width="16.33203125" customWidth="1"/>
+    <col min="13" max="13" width="16.5546875" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" customWidth="1"/>
+    <col min="15" max="15" width="19.5546875" customWidth="1"/>
+    <col min="16" max="16" width="7.6640625" customWidth="1"/>
+    <col min="17" max="17" width="43.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="355" t="s">
+    <row r="1" spans="1:27" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="370" t="s">
         <v>304</v>
       </c>
-      <c r="B1" s="355"/>
-      <c r="C1" s="355"/>
-      <c r="D1" s="355"/>
-      <c r="E1" s="355"/>
-      <c r="F1" s="355"/>
-      <c r="G1" s="355"/>
-      <c r="H1" s="355"/>
-      <c r="I1" s="355"/>
-      <c r="J1" s="355"/>
-      <c r="K1" s="355"/>
-      <c r="L1" s="355"/>
-      <c r="M1" s="355"/>
-      <c r="N1" s="355"/>
-      <c r="O1" s="356"/>
+      <c r="B1" s="370"/>
+      <c r="C1" s="370"/>
+      <c r="D1" s="370"/>
+      <c r="E1" s="370"/>
+      <c r="F1" s="370"/>
+      <c r="G1" s="370"/>
+      <c r="H1" s="370"/>
+      <c r="I1" s="370"/>
+      <c r="J1" s="370"/>
+      <c r="K1" s="370"/>
+      <c r="L1" s="370"/>
+      <c r="M1" s="370"/>
+      <c r="N1" s="370"/>
+      <c r="O1" s="371"/>
       <c r="R1" s="32"/>
     </row>
-    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="357"/>
-      <c r="B2" s="357"/>
-      <c r="C2" s="357"/>
-      <c r="D2" s="357"/>
-      <c r="E2" s="357"/>
-      <c r="F2" s="357"/>
-      <c r="G2" s="357"/>
-      <c r="H2" s="357"/>
-      <c r="I2" s="357"/>
-      <c r="J2" s="357"/>
-      <c r="K2" s="357"/>
-      <c r="L2" s="357"/>
-      <c r="M2" s="357"/>
-      <c r="N2" s="357"/>
-      <c r="O2" s="358"/>
+    <row r="2" spans="1:27" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="372"/>
+      <c r="B2" s="372"/>
+      <c r="C2" s="372"/>
+      <c r="D2" s="372"/>
+      <c r="E2" s="372"/>
+      <c r="F2" s="372"/>
+      <c r="G2" s="372"/>
+      <c r="H2" s="372"/>
+      <c r="I2" s="372"/>
+      <c r="J2" s="372"/>
+      <c r="K2" s="372"/>
+      <c r="L2" s="372"/>
+      <c r="M2" s="372"/>
+      <c r="N2" s="372"/>
+      <c r="O2" s="373"/>
       <c r="R2" s="32"/>
     </row>
-    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="352" t="s">
+    <row r="3" spans="1:27" s="184" customFormat="1" ht="79.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="367" t="s">
         <v>364</v>
       </c>
-      <c r="B3" s="353"/>
-      <c r="C3" s="353"/>
-      <c r="D3" s="353"/>
-      <c r="E3" s="353"/>
-      <c r="F3" s="353"/>
-      <c r="G3" s="353"/>
-      <c r="H3" s="353"/>
-      <c r="I3" s="353"/>
-      <c r="J3" s="353"/>
-      <c r="K3" s="353"/>
-      <c r="L3" s="353"/>
-      <c r="M3" s="353"/>
-      <c r="N3" s="353"/>
-      <c r="O3" s="354"/>
+      <c r="B3" s="368"/>
+      <c r="C3" s="368"/>
+      <c r="D3" s="368"/>
+      <c r="E3" s="368"/>
+      <c r="F3" s="368"/>
+      <c r="G3" s="368"/>
+      <c r="H3" s="368"/>
+      <c r="I3" s="368"/>
+      <c r="J3" s="368"/>
+      <c r="K3" s="368"/>
+      <c r="L3" s="368"/>
+      <c r="M3" s="368"/>
+      <c r="N3" s="368"/>
+      <c r="O3" s="369"/>
       <c r="P3" s="185"/>
       <c r="Q3" s="185"/>
       <c r="R3" s="185"/>
@@ -13112,89 +13039,89 @@
       <c r="Z3" s="185"/>
       <c r="AA3" s="185"/>
     </row>
-    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="315" t="s">
+    <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="324" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="315" t="s">
+      <c r="B4" s="324" t="s">
         <v>306</v>
       </c>
-      <c r="C4" s="315" t="s">
+      <c r="C4" s="324" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="315" t="s">
+      <c r="D4" s="324" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="312" t="s">
+      <c r="E4" s="332" t="s">
         <v>330</v>
       </c>
-      <c r="F4" s="312" t="s">
+      <c r="F4" s="332" t="s">
         <v>331</v>
       </c>
-      <c r="G4" s="312" t="s">
+      <c r="G4" s="332" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="312" t="s">
+      <c r="H4" s="332" t="s">
         <v>336</v>
       </c>
-      <c r="I4" s="312" t="s">
+      <c r="I4" s="332" t="s">
         <v>345</v>
       </c>
-      <c r="J4" s="359" t="s">
+      <c r="J4" s="374" t="s">
         <v>332</v>
       </c>
       <c r="K4" s="100"/>
       <c r="L4" s="364" t="s">
         <v>342</v>
       </c>
-      <c r="M4" s="312" t="s">
+      <c r="M4" s="332" t="s">
         <v>343</v>
       </c>
-      <c r="N4" s="312" t="s">
+      <c r="N4" s="332" t="s">
         <v>333</v>
       </c>
-      <c r="O4" s="312" t="s">
+      <c r="O4" s="332" t="s">
         <v>16</v>
       </c>
       <c r="R4" s="32"/>
     </row>
-    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="316"/>
-      <c r="B5" s="316"/>
-      <c r="C5" s="316"/>
-      <c r="D5" s="316"/>
-      <c r="E5" s="313"/>
-      <c r="F5" s="313"/>
-      <c r="G5" s="313"/>
-      <c r="H5" s="313"/>
-      <c r="I5" s="313"/>
-      <c r="J5" s="360"/>
+    <row r="5" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="325"/>
+      <c r="B5" s="325"/>
+      <c r="C5" s="325"/>
+      <c r="D5" s="325"/>
+      <c r="E5" s="333"/>
+      <c r="F5" s="333"/>
+      <c r="G5" s="333"/>
+      <c r="H5" s="333"/>
+      <c r="I5" s="333"/>
+      <c r="J5" s="375"/>
       <c r="K5" s="100"/>
       <c r="L5" s="365"/>
-      <c r="M5" s="313"/>
-      <c r="N5" s="313"/>
-      <c r="O5" s="313"/>
+      <c r="M5" s="333"/>
+      <c r="N5" s="333"/>
+      <c r="O5" s="333"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="363"/>
-      <c r="B6" s="363"/>
-      <c r="C6" s="363"/>
-      <c r="D6" s="363"/>
-      <c r="E6" s="362"/>
-      <c r="F6" s="362"/>
-      <c r="G6" s="362"/>
-      <c r="H6" s="362"/>
-      <c r="I6" s="362"/>
-      <c r="J6" s="361"/>
+    <row r="6" spans="1:27" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="377"/>
+      <c r="B6" s="377"/>
+      <c r="C6" s="377"/>
+      <c r="D6" s="377"/>
+      <c r="E6" s="363"/>
+      <c r="F6" s="363"/>
+      <c r="G6" s="363"/>
+      <c r="H6" s="363"/>
+      <c r="I6" s="363"/>
+      <c r="J6" s="376"/>
       <c r="K6" s="154"/>
       <c r="L6" s="366"/>
-      <c r="M6" s="362"/>
-      <c r="N6" s="362"/>
-      <c r="O6" s="362"/>
+      <c r="M6" s="363"/>
+      <c r="N6" s="363"/>
+      <c r="O6" s="363"/>
       <c r="R6" s="32"/>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="155" t="s">
         <v>109</v>
       </c>
@@ -13246,10 +13173,10 @@
       <c r="P7" s="85">
         <v>0.7</v>
       </c>
-      <c r="R7" s="321"/>
-      <c r="S7" s="321"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R7" s="323"/>
+      <c r="S7" s="323"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="155" t="s">
         <v>312</v>
       </c>
@@ -13301,10 +13228,10 @@
         <f>P7+0.01</f>
         <v>0.71</v>
       </c>
-      <c r="R8" s="321"/>
-      <c r="S8" s="321"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="R8" s="323"/>
+      <c r="S8" s="323"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="155" t="s">
         <v>110</v>
       </c>
@@ -13358,7 +13285,7 @@
       </c>
       <c r="S9" s="32"/>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="155" t="s">
         <v>111</v>
       </c>
@@ -13413,7 +13340,7 @@
       </c>
       <c r="S10" s="32"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="159" t="s">
         <v>112</v>
       </c>
@@ -13468,7 +13395,7 @@
       </c>
       <c r="S11" s="32"/>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="162" t="s">
         <v>40</v>
       </c>
@@ -13524,7 +13451,7 @@
       </c>
       <c r="S12" s="32"/>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="155" t="s">
         <v>41</v>
       </c>
@@ -13577,7 +13504,7 @@
       </c>
       <c r="S13" s="32"/>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="155" t="s">
         <v>42</v>
       </c>
@@ -13631,7 +13558,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="155" t="s">
         <v>43</v>
       </c>
@@ -13685,7 +13612,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="155" t="s">
         <v>44</v>
       </c>
@@ -13737,7 +13664,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="17" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A17" s="155" t="s">
         <v>45</v>
       </c>
@@ -13791,7 +13718,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A18" s="155" t="s">
         <v>46</v>
       </c>
@@ -13845,7 +13772,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A19" s="155" t="s">
         <v>47</v>
       </c>
@@ -13897,7 +13824,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="20" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A20" s="155" t="s">
         <v>48</v>
       </c>
@@ -13949,7 +13876,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="21" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A21" s="155" t="s">
         <v>49</v>
       </c>
@@ -14001,7 +13928,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A22" s="155" t="s">
         <v>50</v>
       </c>
@@ -14053,7 +13980,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A23" s="155" t="s">
         <v>51</v>
       </c>
@@ -14088,7 +14015,7 @@
       <c r="K23" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L23" s="270">
+      <c r="L23" s="255">
         <f>J23</f>
         <v>189591.12</v>
       </c>
@@ -14108,7 +14035,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A24" s="155" t="s">
         <v>52</v>
       </c>
@@ -14160,7 +14087,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A25" s="155" t="s">
         <v>53</v>
       </c>
@@ -14212,7 +14139,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="26" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A26" s="155" t="s">
         <v>54</v>
       </c>
@@ -14266,7 +14193,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="27" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A27" s="155" t="s">
         <v>55</v>
       </c>
@@ -14322,7 +14249,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="28" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A28" s="155" t="s">
         <v>56</v>
       </c>
@@ -14374,7 +14301,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="29" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A29" s="155" t="s">
         <v>57</v>
       </c>
@@ -14409,7 +14336,7 @@
       <c r="K29" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L29" s="270">
+      <c r="L29" s="255">
         <f>J29</f>
         <v>189591.18</v>
       </c>
@@ -14427,7 +14354,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="30" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A30" s="155" t="s">
         <v>58</v>
       </c>
@@ -14482,7 +14409,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="31" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A31" s="155" t="s">
         <v>59</v>
       </c>
@@ -14536,7 +14463,7 @@
         <v>0.20000000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="155" t="s">
         <v>60</v>
       </c>
@@ -14689,7 +14616,7 @@
       <c r="DI32" s="53"/>
       <c r="DJ32" s="53"/>
     </row>
-    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="155" t="s">
         <v>61</v>
       </c>
@@ -14843,7 +14770,7 @@
       <c r="DI33" s="53"/>
       <c r="DJ33" s="53"/>
     </row>
-    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A34" s="155" t="s">
         <v>62</v>
       </c>
@@ -14997,7 +14924,7 @@
       <c r="DI34" s="53"/>
       <c r="DJ34" s="53"/>
     </row>
-    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:114" s="109" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A35" s="155" t="s">
         <v>63</v>
       </c>
@@ -15032,7 +14959,7 @@
       <c r="K35" s="114">
         <v>-59269.126292764471</v>
       </c>
-      <c r="L35" s="270">
+      <c r="L35" s="255">
         <f>J35</f>
         <v>189591.24</v>
       </c>
@@ -15148,7 +15075,7 @@
       <c r="DI35" s="53"/>
       <c r="DJ35" s="53"/>
     </row>
-    <row r="36" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A36" s="155" t="s">
         <v>64</v>
       </c>
@@ -15202,7 +15129,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="37" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A37" s="155" t="s">
         <v>65</v>
       </c>
@@ -15256,7 +15183,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A38" s="155" t="s">
         <v>66</v>
       </c>
@@ -15316,7 +15243,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="39" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A39" s="155" t="s">
         <v>67</v>
       </c>
@@ -15370,7 +15297,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="40" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A40" s="155" t="s">
         <v>68</v>
       </c>
@@ -15422,7 +15349,7 @@
         <v>0.29000000000000009</v>
       </c>
     </row>
-    <row r="41" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A41" s="155" t="s">
         <v>69</v>
       </c>
@@ -15474,7 +15401,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="42" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A42" s="155" t="s">
         <v>70</v>
       </c>
@@ -15528,7 +15455,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="43" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A43" s="155" t="s">
         <v>71</v>
       </c>
@@ -15583,7 +15510,7 @@
       </c>
       <c r="Q43" s="32"/>
     </row>
-    <row r="44" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A44" s="155" t="s">
         <v>72</v>
       </c>
@@ -15638,7 +15565,7 @@
       </c>
       <c r="Q44" s="32"/>
     </row>
-    <row r="45" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A45" s="155" t="s">
         <v>73</v>
       </c>
@@ -15695,7 +15622,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="46" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A46" s="155" t="s">
         <v>74</v>
       </c>
@@ -15747,7 +15674,7 @@
         <v>0.35000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A47" s="155" t="s">
         <v>75</v>
       </c>
@@ -15799,7 +15726,7 @@
         <v>0.36000000000000015</v>
       </c>
     </row>
-    <row r="48" spans="1:114" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:114" x14ac:dyDescent="0.3">
       <c r="A48" s="155" t="s">
         <v>76</v>
       </c>
@@ -15854,7 +15781,7 @@
       </c>
       <c r="R48" s="45"/>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="155" t="s">
         <v>77</v>
       </c>
@@ -15906,7 +15833,7 @@
         <v>0.38000000000000017</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="155" t="s">
         <v>78</v>
       </c>
@@ -15961,7 +15888,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="155" t="s">
         <v>79</v>
       </c>
@@ -16013,7 +15940,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="155" t="s">
         <v>80</v>
       </c>
@@ -16068,7 +15995,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="155" t="s">
         <v>81</v>
       </c>
@@ -16125,7 +16052,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="155" t="s">
         <v>82</v>
       </c>
@@ -16179,7 +16106,7 @@
         <v>0.43000000000000022</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="155" t="s">
         <v>83</v>
       </c>
@@ -16231,7 +16158,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="155" t="s">
         <v>84</v>
       </c>
@@ -16285,7 +16212,7 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="155" t="s">
         <v>85</v>
       </c>
@@ -16339,7 +16266,7 @@
         <v>0.46000000000000024</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="155" t="s">
         <v>86</v>
       </c>
@@ -16393,7 +16320,7 @@
         <v>0.47000000000000025</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="155" t="s">
         <v>87</v>
       </c>
@@ -16430,7 +16357,7 @@
       <c r="K59" s="114">
         <v>-33257.557922213571</v>
       </c>
-      <c r="L59" s="270">
+      <c r="L59" s="255">
         <f>I59</f>
         <v>137927.48000000001</v>
       </c>
@@ -16452,7 +16379,7 @@
       </c>
       <c r="S59" s="142"/>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="155" t="s">
         <v>88</v>
       </c>
@@ -16507,7 +16434,7 @@
       </c>
       <c r="S60" s="32"/>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="155" t="s">
         <v>89</v>
       </c>
@@ -16560,7 +16487,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="155" t="s">
         <v>90</v>
       </c>
@@ -16614,7 +16541,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="155" t="s">
         <v>91</v>
       </c>
@@ -16666,7 +16593,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="155" t="s">
         <v>92</v>
       </c>
@@ -16721,7 +16648,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" s="155" t="s">
         <v>93</v>
       </c>
@@ -16776,7 +16703,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" s="155" t="s">
         <v>94</v>
       </c>
@@ -16831,7 +16758,7 @@
       </c>
       <c r="Q66" s="53"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" s="155" t="s">
         <v>95</v>
       </c>
@@ -16885,7 +16812,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" s="155" t="s">
         <v>96</v>
       </c>
@@ -16929,7 +16856,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" s="155" t="s">
         <v>97</v>
       </c>
@@ -16982,7 +16909,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" s="155" t="s">
         <v>98</v>
       </c>
@@ -17036,7 +16963,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" s="155" t="s">
         <v>99</v>
       </c>
@@ -17090,7 +17017,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" s="155" t="s">
         <v>100</v>
       </c>
@@ -17144,7 +17071,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" s="155" t="s">
         <v>101</v>
       </c>
@@ -17197,7 +17124,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" s="155" t="s">
         <v>102</v>
       </c>
@@ -17251,7 +17178,7 @@
         <v>0.63000000000000034</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" s="155" t="s">
         <v>103</v>
       </c>
@@ -17303,7 +17230,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" s="155" t="s">
         <v>104</v>
       </c>
@@ -17357,7 +17284,7 @@
         <v>0.65000000000000036</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" s="155" t="s">
         <v>105</v>
       </c>
@@ -17412,7 +17339,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" s="155" t="s">
         <v>106</v>
       </c>
@@ -17466,7 +17393,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" s="155" t="s">
         <v>107</v>
       </c>
@@ -17520,7 +17447,7 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="155" t="s">
         <v>108</v>
       </c>
@@ -17576,7 +17503,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="24"/>
       <c r="B81" s="24"/>
       <c r="C81" s="78"/>
@@ -17593,7 +17520,7 @@
       <c r="N81" s="113"/>
       <c r="O81" s="114"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="19"/>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -17634,9 +17561,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="M4:M6"/>
-    <mergeCell ref="A3:O3"/>
-    <mergeCell ref="A1:O2"/>
     <mergeCell ref="R7:S8"/>
     <mergeCell ref="J4:J6"/>
     <mergeCell ref="N4:N6"/>
@@ -17651,6 +17575,9 @@
     <mergeCell ref="H4:H6"/>
     <mergeCell ref="I4:I6"/>
     <mergeCell ref="L4:L6"/>
+    <mergeCell ref="M4:M6"/>
+    <mergeCell ref="A3:O3"/>
+    <mergeCell ref="A1:O2"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" scale="110" orientation="landscape" r:id="rId1"/>
@@ -17659,11 +17586,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7365EFC1-5C09-4380-B9A2-A73102AE2F7A}">
-  <dimension ref="C1:M35"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="C1:M17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+    </row>
+    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C2" s="246" t="s">
         <v>349</v>
       </c>
@@ -17676,11 +17607,11 @@
       <c r="H2" s="189"/>
       <c r="I2" s="189"/>
       <c r="J2" s="190"/>
-      <c r="K2" s="271"/>
-      <c r="L2" s="271"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
       <c r="M2" s="53"/>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C3" s="248" t="s">
         <v>350</v>
       </c>
@@ -17695,11 +17626,11 @@
       <c r="H3" s="191"/>
       <c r="I3" s="192"/>
       <c r="J3" s="193"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="272"/>
+      <c r="K3" s="251"/>
+      <c r="L3" s="251"/>
       <c r="M3" s="251"/>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
       <c r="C4" s="248" t="s">
         <v>352</v>
       </c>
@@ -17713,16 +17644,16 @@
       <c r="G4" s="53" t="s">
         <v>355</v>
       </c>
-      <c r="H4" s="249" t="s">
-        <v>373</v>
+      <c r="H4" s="53" t="s">
+        <v>410</v>
       </c>
       <c r="I4" s="192"/>
       <c r="J4" s="193"/>
-      <c r="K4" s="272"/>
-      <c r="L4" s="272"/>
+      <c r="K4" s="251"/>
+      <c r="L4" s="251"/>
       <c r="M4" s="251"/>
     </row>
-    <row r="5" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C5" s="186" t="s">
         <v>356</v>
       </c>
@@ -17733,78 +17664,82 @@
       <c r="H5" s="53"/>
       <c r="I5" s="53"/>
       <c r="J5" s="194"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
+      <c r="K5" s="251"/>
+      <c r="L5" s="251"/>
       <c r="M5" s="251"/>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C6" s="367" t="s">
-        <v>374</v>
-      </c>
-      <c r="D6" s="368"/>
-      <c r="E6" s="368"/>
-      <c r="F6" s="368"/>
-      <c r="G6" s="368"/>
-      <c r="H6" s="368"/>
-      <c r="I6" s="368"/>
-      <c r="J6" s="369"/>
-      <c r="K6" s="271"/>
-      <c r="L6" s="271"/>
+    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C6" s="378" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="379"/>
+      <c r="E6" s="379"/>
+      <c r="F6" s="379"/>
+      <c r="G6" s="379"/>
+      <c r="H6" s="379"/>
+      <c r="I6" s="379"/>
+      <c r="J6" s="380"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
       <c r="M6" s="53"/>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C7" s="370"/>
-      <c r="D7" s="371"/>
-      <c r="E7" s="371"/>
-      <c r="F7" s="371"/>
-      <c r="G7" s="371"/>
-      <c r="H7" s="371"/>
-      <c r="I7" s="371"/>
-      <c r="J7" s="372"/>
-      <c r="K7" s="271"/>
-      <c r="L7" s="271"/>
+    <row r="7" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C7" s="381"/>
+      <c r="D7" s="382"/>
+      <c r="E7" s="382"/>
+      <c r="F7" s="382"/>
+      <c r="G7" s="382"/>
+      <c r="H7" s="382"/>
+      <c r="I7" s="382"/>
+      <c r="J7" s="383"/>
+      <c r="K7" s="53"/>
+      <c r="L7" s="53"/>
       <c r="M7" s="53"/>
     </row>
-    <row r="8" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="373"/>
-      <c r="D8" s="374"/>
-      <c r="E8" s="374"/>
-      <c r="F8" s="374"/>
-      <c r="G8" s="374"/>
-      <c r="H8" s="374"/>
-      <c r="I8" s="374"/>
-      <c r="J8" s="375"/>
-      <c r="K8" s="271"/>
-      <c r="L8" s="271"/>
+    <row r="8" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="384"/>
+      <c r="D8" s="385"/>
+      <c r="E8" s="385"/>
+      <c r="F8" s="385"/>
+      <c r="G8" s="385"/>
+      <c r="H8" s="385"/>
+      <c r="I8" s="385"/>
+      <c r="J8" s="386"/>
+      <c r="K8" s="53"/>
+      <c r="L8" s="53"/>
       <c r="M8" s="53"/>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.3">
       <c r="K9" s="53"/>
       <c r="L9" s="53"/>
       <c r="M9" s="53"/>
     </row>
-    <row r="10" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C11" s="252" t="s">
+    <row r="10" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="K10" s="53"/>
+      <c r="L10" s="53"/>
+      <c r="M10" s="53"/>
+    </row>
+    <row r="11" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C11" s="390" t="s">
         <v>349</v>
       </c>
-      <c r="D11" s="253">
+      <c r="D11" s="391">
         <f>D2+1</f>
         <v>2</v>
       </c>
-      <c r="E11" s="253"/>
+      <c r="E11" s="391"/>
       <c r="F11" s="189"/>
       <c r="G11" s="189"/>
       <c r="H11" s="189"/>
       <c r="I11" s="189"/>
       <c r="J11" s="190"/>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C12" s="254" t="s">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C12" s="392" t="s">
         <v>350</v>
       </c>
-      <c r="D12" s="255"/>
-      <c r="E12" s="256">
+      <c r="D12" s="393"/>
+      <c r="E12" s="394">
         <v>0</v>
       </c>
       <c r="F12" s="53"/>
@@ -17814,32 +17749,28 @@
       <c r="H12" s="191"/>
       <c r="I12" s="192"/>
       <c r="J12" s="193"/>
-      <c r="K12" s="271"/>
-      <c r="L12" s="271"/>
-    </row>
-    <row r="13" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C13" s="254" t="s">
+    </row>
+    <row r="13" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C13" s="392" t="s">
         <v>352</v>
       </c>
-      <c r="D13" s="255" t="s">
+      <c r="D13" s="393" t="s">
         <v>353</v>
       </c>
-      <c r="E13" s="255" t="s">
+      <c r="E13" s="393" t="s">
         <v>354</v>
       </c>
       <c r="F13" s="53"/>
       <c r="G13" s="53" t="s">
         <v>355</v>
       </c>
-      <c r="H13" s="255" t="s">
-        <v>375</v>
+      <c r="H13" s="53" t="s">
+        <v>409</v>
       </c>
       <c r="I13" s="192"/>
       <c r="J13" s="193"/>
-      <c r="K13" s="271"/>
-      <c r="L13" s="271"/>
-    </row>
-    <row r="14" spans="3:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="3:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C14" s="186" t="s">
         <v>356</v>
       </c>
@@ -17850,259 +17781,43 @@
       <c r="H14" s="53"/>
       <c r="I14" s="53"/>
       <c r="J14" s="194"/>
-      <c r="K14" s="271"/>
-      <c r="L14" s="271"/>
-    </row>
-    <row r="15" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C15" s="367" t="s">
-        <v>376</v>
-      </c>
-      <c r="D15" s="368"/>
-      <c r="E15" s="368"/>
-      <c r="F15" s="368"/>
-      <c r="G15" s="368"/>
-      <c r="H15" s="368"/>
-      <c r="I15" s="368"/>
-      <c r="J15" s="369"/>
-      <c r="K15" s="271"/>
-      <c r="L15" s="271"/>
-    </row>
-    <row r="16" spans="3:13" x14ac:dyDescent="0.25">
-      <c r="C16" s="370"/>
-      <c r="D16" s="371"/>
-      <c r="E16" s="371"/>
-      <c r="F16" s="371"/>
-      <c r="G16" s="371"/>
-      <c r="H16" s="371"/>
-      <c r="I16" s="371"/>
-      <c r="J16" s="372"/>
-    </row>
-    <row r="17" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="373"/>
-      <c r="D17" s="374"/>
-      <c r="E17" s="374"/>
-      <c r="F17" s="374"/>
-      <c r="G17" s="374"/>
-      <c r="H17" s="374"/>
-      <c r="I17" s="374"/>
-      <c r="J17" s="375"/>
-    </row>
-    <row r="19" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C20" s="258" t="s">
-        <v>349</v>
-      </c>
-      <c r="D20" s="259">
-        <f>D11+1</f>
-        <v>3</v>
-      </c>
-      <c r="E20" s="259"/>
-      <c r="F20" s="189"/>
-      <c r="G20" s="189"/>
-      <c r="H20" s="189"/>
-      <c r="I20" s="189"/>
-      <c r="J20" s="190"/>
-      <c r="K20" s="271"/>
-      <c r="L20" s="271"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C21" s="260" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="257"/>
-      <c r="E21" s="261">
-        <v>0</v>
-      </c>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="H21" s="191"/>
-      <c r="I21" s="192"/>
-      <c r="J21" s="193"/>
-      <c r="K21" s="271"/>
-      <c r="L21" s="271"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C22" s="260" t="s">
-        <v>352</v>
-      </c>
-      <c r="D22" s="257" t="s">
-        <v>353</v>
-      </c>
-      <c r="E22" s="257" t="s">
-        <v>354</v>
-      </c>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="H22" s="257" t="s">
-        <v>377</v>
-      </c>
-      <c r="I22" s="192"/>
-      <c r="J22" s="193"/>
-      <c r="K22" s="271"/>
-      <c r="L22" s="271"/>
-    </row>
-    <row r="23" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="186" t="s">
-        <v>356</v>
-      </c>
-      <c r="D23" s="53"/>
-      <c r="E23" s="53"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="53"/>
-      <c r="H23" s="53"/>
-      <c r="I23" s="53"/>
-      <c r="J23" s="194"/>
-      <c r="K23" s="271"/>
-      <c r="L23" s="271"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C24" s="367" t="s">
-        <v>378</v>
-      </c>
-      <c r="D24" s="368"/>
-      <c r="E24" s="368"/>
-      <c r="F24" s="368"/>
-      <c r="G24" s="368"/>
-      <c r="H24" s="368"/>
-      <c r="I24" s="368"/>
-      <c r="J24" s="369"/>
-      <c r="K24" s="271"/>
-      <c r="L24" s="271"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C25" s="370"/>
-      <c r="D25" s="371"/>
-      <c r="E25" s="371"/>
-      <c r="F25" s="371"/>
-      <c r="G25" s="371"/>
-      <c r="H25" s="371"/>
-      <c r="I25" s="371"/>
-      <c r="J25" s="372"/>
-      <c r="K25" s="271"/>
-      <c r="L25" s="271"/>
-    </row>
-    <row r="26" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="373"/>
-      <c r="D26" s="374"/>
-      <c r="E26" s="374"/>
-      <c r="F26" s="374"/>
-      <c r="G26" s="374"/>
-      <c r="H26" s="374"/>
-      <c r="I26" s="374"/>
-      <c r="J26" s="375"/>
-    </row>
-    <row r="28" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C29" s="262" t="s">
-        <v>349</v>
-      </c>
-      <c r="D29" s="263">
-        <f>D20+1</f>
-        <v>4</v>
-      </c>
-      <c r="E29" s="263"/>
-      <c r="F29" s="189"/>
-      <c r="G29" s="189"/>
-      <c r="H29" s="189"/>
-      <c r="I29" s="189"/>
-      <c r="J29" s="190"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C30" s="264" t="s">
-        <v>350</v>
-      </c>
-      <c r="D30" s="265"/>
-      <c r="E30" s="266">
-        <v>0</v>
-      </c>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53" t="s">
-        <v>351</v>
-      </c>
-      <c r="H30" s="191" t="s">
-        <v>380</v>
-      </c>
-      <c r="I30" s="192"/>
-      <c r="J30" s="193"/>
-      <c r="K30" s="271"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
-      <c r="C31" s="264" t="s">
-        <v>352</v>
-      </c>
-      <c r="D31" s="265" t="s">
-        <v>353</v>
-      </c>
-      <c r="E31" s="265" t="s">
-        <v>354</v>
-      </c>
-      <c r="F31" s="53"/>
-      <c r="G31" s="53" t="s">
-        <v>355</v>
-      </c>
-      <c r="H31" s="265" t="s">
-        <v>379</v>
-      </c>
-      <c r="I31" s="192"/>
-      <c r="J31" s="193"/>
-      <c r="K31" s="271"/>
-    </row>
-    <row r="32" spans="3:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="186" t="s">
-        <v>356</v>
-      </c>
-      <c r="D32" s="53"/>
-      <c r="E32" s="53"/>
-      <c r="F32" s="53"/>
-      <c r="G32" s="53"/>
-      <c r="H32" s="53"/>
-      <c r="I32" s="53"/>
-      <c r="J32" s="194"/>
-      <c r="K32" s="271"/>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C33" s="367" t="s">
-        <v>381</v>
-      </c>
-      <c r="D33" s="368"/>
-      <c r="E33" s="368"/>
-      <c r="F33" s="368"/>
-      <c r="G33" s="368"/>
-      <c r="H33" s="368"/>
-      <c r="I33" s="368"/>
-      <c r="J33" s="369"/>
-      <c r="K33" s="271"/>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C34" s="370"/>
-      <c r="D34" s="371"/>
-      <c r="E34" s="371"/>
-      <c r="F34" s="371"/>
-      <c r="G34" s="371"/>
-      <c r="H34" s="371"/>
-      <c r="I34" s="371"/>
-      <c r="J34" s="372"/>
-    </row>
-    <row r="35" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="373"/>
-      <c r="D35" s="374"/>
-      <c r="E35" s="374"/>
-      <c r="F35" s="374"/>
-      <c r="G35" s="374"/>
-      <c r="H35" s="374"/>
-      <c r="I35" s="374"/>
-      <c r="J35" s="375"/>
+    </row>
+    <row r="15" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C15" s="378" t="s">
+        <v>408</v>
+      </c>
+      <c r="D15" s="379"/>
+      <c r="E15" s="379"/>
+      <c r="F15" s="379"/>
+      <c r="G15" s="379"/>
+      <c r="H15" s="379"/>
+      <c r="I15" s="379"/>
+      <c r="J15" s="380"/>
+    </row>
+    <row r="16" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C16" s="381"/>
+      <c r="D16" s="382"/>
+      <c r="E16" s="382"/>
+      <c r="F16" s="382"/>
+      <c r="G16" s="382"/>
+      <c r="H16" s="382"/>
+      <c r="I16" s="382"/>
+      <c r="J16" s="383"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="384"/>
+      <c r="D17" s="385"/>
+      <c r="E17" s="385"/>
+      <c r="F17" s="385"/>
+      <c r="G17" s="385"/>
+      <c r="H17" s="385"/>
+      <c r="I17" s="385"/>
+      <c r="J17" s="386"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="C6:J8"/>
     <mergeCell ref="C15:J17"/>
-    <mergeCell ref="C24:J26"/>
-    <mergeCell ref="C33:J35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
